--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,77 +8,77 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97274DCA-2B12-4A25-8316-AE071A0DAC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0D1460-B6C1-4443-AB1F-925851CC483F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="Substrate Costing Master" sheetId="8" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId2"/>
     <sheet name="Roll" sheetId="4" r:id="rId3"/>
     <sheet name="Data" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
-    <sheet name="Sleeve" sheetId="3" r:id="rId6"/>
-    <sheet name="Pouch" sheetId="5" r:id="rId7"/>
-    <sheet name="Overall" sheetId="6" r:id="rId8"/>
+    <sheet name="Sleeve" sheetId="3" r:id="rId5"/>
+    <sheet name="Pouch" sheetId="5" r:id="rId6"/>
+    <sheet name="Overall" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Substrate Costing Master'!$A$1:$F$46</definedName>
-    <definedName name="Adhesive" localSheetId="6">A[Adhesive]</definedName>
+    <definedName name="Adhesive" localSheetId="5">A[Adhesive]</definedName>
     <definedName name="Adhesive" localSheetId="2">A[Adhesive]</definedName>
-    <definedName name="Adhesive" localSheetId="5">A[Adhesive]</definedName>
+    <definedName name="Adhesive" localSheetId="4">A[Adhesive]</definedName>
     <definedName name="Adhesive">A[Adhesive]</definedName>
-    <definedName name="CO_Pouch" localSheetId="6">Pouch!$K$14</definedName>
+    <definedName name="CO_Pouch" localSheetId="5">Pouch!$K$14</definedName>
     <definedName name="CO_Pouch" localSheetId="2">Roll!$K$14</definedName>
     <definedName name="CO_Pouch">Sleeve!$K$14</definedName>
-    <definedName name="CO_Roll" localSheetId="6">Pouch!$C$14</definedName>
+    <definedName name="CO_Roll" localSheetId="5">Pouch!$C$14</definedName>
     <definedName name="CO_Roll" localSheetId="2">Roll!$C$14</definedName>
     <definedName name="CO_Roll">Sleeve!$C$14</definedName>
-    <definedName name="CO_Sleeve" localSheetId="6">Pouch!$G$15</definedName>
+    <definedName name="CO_Sleeve" localSheetId="5">Pouch!$G$15</definedName>
     <definedName name="CO_Sleeve" localSheetId="2">Roll!$G$15</definedName>
     <definedName name="CO_Sleeve">Sleeve!$G$15</definedName>
-    <definedName name="FLW" localSheetId="6">Pouch!$I$35</definedName>
+    <definedName name="FLW" localSheetId="5">Pouch!$I$35</definedName>
     <definedName name="FLW" localSheetId="2">Roll!$I$35</definedName>
     <definedName name="FLW">Sleeve!$I$35</definedName>
     <definedName name="Forms">Overall!$G$2:$M$2</definedName>
-    <definedName name="Ink" localSheetId="6">Table4[Ink]</definedName>
+    <definedName name="Ink" localSheetId="5">Table4[Ink]</definedName>
     <definedName name="Ink" localSheetId="2">Table4[Ink]</definedName>
-    <definedName name="Ink" localSheetId="5">Table4[Ink]</definedName>
+    <definedName name="Ink" localSheetId="4">Table4[Ink]</definedName>
     <definedName name="Ink">Table4[Ink]</definedName>
-    <definedName name="Nb_Ups_Sleeve" localSheetId="6">Pouch!$G$17</definedName>
+    <definedName name="Nb_Ups_Sleeve" localSheetId="5">Pouch!$G$17</definedName>
     <definedName name="Nb_Ups_Sleeve" localSheetId="2">Roll!$G$17</definedName>
     <definedName name="Nb_Ups_Sleeve">Sleeve!$G$17</definedName>
-    <definedName name="OQKG" localSheetId="6">Pouch!$I$36</definedName>
+    <definedName name="OQKG" localSheetId="5">Pouch!$I$36</definedName>
     <definedName name="OQKG" localSheetId="2">Roll!$I$36</definedName>
     <definedName name="OQKG">Sleeve!$I$36</definedName>
-    <definedName name="OQM" localSheetId="6">Pouch!$I$38</definedName>
+    <definedName name="OQM" localSheetId="5">Pouch!$I$38</definedName>
     <definedName name="OQM" localSheetId="2">Roll!$I$38</definedName>
     <definedName name="OQM">Sleeve!$I$38</definedName>
     <definedName name="Packaging">A[Packaging]</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Pouch!$A$1:$O$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">Pouch!$A$1:$O$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Roll!$A$1:$L$79</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">Sleeve!$A$1:$L$78</definedName>
-    <definedName name="Ptypes" localSheetId="6">PTypeT[Product Type]</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">Sleeve!$A$1:$L$78</definedName>
+    <definedName name="Ptypes" localSheetId="5">PTypeT[Product Type]</definedName>
     <definedName name="Ptypes" localSheetId="2">PTypeT[Product Type]</definedName>
-    <definedName name="Ptypes" localSheetId="5">PTypeT[Product Type]</definedName>
+    <definedName name="Ptypes" localSheetId="4">PTypeT[Product Type]</definedName>
     <definedName name="Ptypes">PTypeT[Product Type]</definedName>
-    <definedName name="Substrate" localSheetId="6">Table3[Substrate]</definedName>
+    <definedName name="Substrate" localSheetId="5">Table3[Substrate]</definedName>
     <definedName name="Substrate" localSheetId="2">Table3[Substrate]</definedName>
-    <definedName name="Substrate" localSheetId="5">Table3[Substrate]</definedName>
+    <definedName name="Substrate" localSheetId="4">Table3[Substrate]</definedName>
     <definedName name="Substrate">Table3[Substrate]</definedName>
-    <definedName name="Substrates" localSheetId="6">Table3[Substrate]</definedName>
+    <definedName name="Substrates" localSheetId="5">Table3[Substrate]</definedName>
     <definedName name="Substrates" localSheetId="2">Table3[Substrate]</definedName>
-    <definedName name="Substrates" localSheetId="5">Table3[Substrate]</definedName>
+    <definedName name="Substrates" localSheetId="4">Table3[Substrate]</definedName>
     <definedName name="Substrates">Table3[Substrate]</definedName>
-    <definedName name="Type" localSheetId="6">T[Material Type]</definedName>
+    <definedName name="Type" localSheetId="5">T[Material Type]</definedName>
     <definedName name="Type" localSheetId="2">T[Material Type]</definedName>
-    <definedName name="Type" localSheetId="5">T[Material Type]</definedName>
+    <definedName name="Type" localSheetId="4">T[Material Type]</definedName>
     <definedName name="Type">T[Material Type]</definedName>
-    <definedName name="Unit" localSheetId="6">UT[Units]</definedName>
+    <definedName name="Unit" localSheetId="5">UT[Units]</definedName>
     <definedName name="Unit" localSheetId="2">UT[Units]</definedName>
-    <definedName name="Unit" localSheetId="5">UT[Units]</definedName>
+    <definedName name="Unit" localSheetId="4">UT[Units]</definedName>
     <definedName name="Unit">UT[Units]</definedName>
-    <definedName name="UnitsDD" localSheetId="6">Pouch!$K$5</definedName>
+    <definedName name="UnitsDD" localSheetId="5">Pouch!$K$5</definedName>
     <definedName name="UnitsDD" localSheetId="2">Roll!$K$5</definedName>
     <definedName name="UnitsDD">Sleeve!$K$5</definedName>
   </definedNames>
@@ -3225,158 +3225,191 @@
     <xf numFmtId="185" fontId="39" fillId="0" borderId="81" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="39" fillId="0" borderId="73" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="39" fillId="0" borderId="80" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3402,35 +3435,23 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3441,32 +3462,11 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4269,6 +4269,603 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -4662,603 +5259,6 @@
         </vertical>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF003366"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -13021,15 +13021,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:F46" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="50" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="49" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="48" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="47" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="46" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="45" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="52" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="51" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="50" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="49" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="48" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="47" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13104,32 +13104,32 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="38" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="66" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="64">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="35">
+    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="63">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="34">
+    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="62">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="33" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="32">
+    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="61" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="60">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table17[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="31">
+    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="59">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="30">
+    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="58">
       <calculatedColumnFormula>table17[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13142,16 +13142,16 @@
   <autoFilter ref="D1:G33" xr:uid="{837835BF-F846-4004-BCD7-070D9DCCAD90}"/>
   <tableColumns count="4">
     <tableColumn id="2" xr3:uid="{9E3142C9-50FA-4916-9CEF-822169826878}" name="Material"/>
-    <tableColumn id="3" xr3:uid="{32A96633-FC6A-40F7-974B-25881602DB09}" name="Density" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{32A96633-FC6A-40F7-974B-25881602DB09}" name="Density" dataDxfId="46"/>
     <tableColumn id="4" xr3:uid="{705696B6-E241-4CE0-AFE1-37043FC331F9}" name="Solid" dataCellStyle="Percent"/>
-    <tableColumn id="1" xr3:uid="{69EE0737-5119-452D-80EC-62F1CE8D7933}" name="Cost Per Kg" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{69EE0737-5119-452D-80EC-62F1CE8D7933}" name="Cost Per Kg" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}" name="T" displayName="T" ref="P1:P5" totalsRowShown="0" headerRowDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}" name="T" displayName="T" ref="P1:P5" totalsRowShown="0" headerRowDxfId="44">
   <autoFilter ref="P1:P5" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{128D7DDA-5198-45F5-9AC3-6316B0FAB04C}" name="Material Type"/>
@@ -13161,38 +13161,38 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}" name="Table3" displayName="Table3" ref="Q1:Q18" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}" name="Table3" displayName="Table3" ref="Q1:Q18" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="Q1:Q18" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9E980FBC-6C44-4579-9F83-F013225FDE31}" name="Substrate" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{9E980FBC-6C44-4579-9F83-F013225FDE31}" name="Substrate" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}" name="Table4" displayName="Table4" ref="R1:R9" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}" name="Table4" displayName="Table4" ref="R1:R9" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="R1:R9" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6C1C3C3D-7FBA-4671-9A3E-6181E3719E8D}" name="Ink" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{6C1C3C3D-7FBA-4671-9A3E-6181E3719E8D}" name="Ink" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}" name="A" displayName="A" ref="S1:T4" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}" name="A" displayName="A" ref="S1:T4" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="S1:T4" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{012E7603-7A8C-46AD-914C-FAE7D12FAF3F}" name="Adhesive" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{4325B70E-CBBC-4618-9B76-FCD61F8B754A}" name="Packaging" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{012E7603-7A8C-46AD-914C-FAE7D12FAF3F}" name="Adhesive" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{4325B70E-CBBC-4618-9B76-FCD61F8B754A}" name="Packaging" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}" name="PTypeT" displayName="PTypeT" ref="K1:K4" totalsRowShown="0" headerRowDxfId="59" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}" name="PTypeT" displayName="PTypeT" ref="K1:K4" totalsRowShown="0" headerRowDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="K1:K4" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{15A59F61-F80E-4915-8496-D6FC380FA80A}" name="Product Type"/>
@@ -13202,10 +13202,10 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}" name="UT" displayName="UT" ref="M1:M6" totalsRowShown="0" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}" name="UT" displayName="UT" ref="M1:M6" totalsRowShown="0" dataDxfId="31">
   <autoFilter ref="M1:M6" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{031412D9-180B-4257-B711-44F88C9C965F}" name="Units" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{031412D9-180B-4257-B711-44F88C9C965F}" name="Units" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13549,18 +13549,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20A07BB-02D0-4AF9-8BEB-9FE7CE591B3C}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="243" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="243" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="243" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" style="243" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="243" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="243" customWidth="1"/>
     <col min="4" max="4" width="30" style="243" customWidth="1"/>
     <col min="5" max="5" width="12" style="243" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="243" customWidth="1"/>
-    <col min="7" max="16384" width="8.7109375" style="243"/>
+    <col min="6" max="6" width="16.44140625" style="243" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="243"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="258" t="s">
         <v>250</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="256" t="s">
         <v>253</v>
       </c>
@@ -13597,7 +13597,7 @@
       <c r="E2" s="255"/>
       <c r="F2" s="257"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="256" t="s">
         <v>253</v>
       </c>
@@ -13613,7 +13613,7 @@
       <c r="E3" s="255"/>
       <c r="F3" s="257"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="256" t="s">
         <v>253</v>
       </c>
@@ -13629,7 +13629,7 @@
       <c r="E4" s="255"/>
       <c r="F4" s="257"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="256" t="s">
         <v>253</v>
       </c>
@@ -13645,7 +13645,7 @@
       <c r="E5" s="255"/>
       <c r="F5" s="257"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="256" t="s">
         <v>253</v>
       </c>
@@ -13661,7 +13661,7 @@
       <c r="E6" s="255"/>
       <c r="F6" s="257"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="256" t="s">
         <v>253</v>
       </c>
@@ -13677,7 +13677,7 @@
       <c r="E7" s="255"/>
       <c r="F7" s="257"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="256" t="s">
         <v>253</v>
       </c>
@@ -13693,7 +13693,7 @@
       <c r="E8" s="255"/>
       <c r="F8" s="257"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="256" t="s">
         <v>253</v>
       </c>
@@ -13709,7 +13709,7 @@
       <c r="E9" s="255"/>
       <c r="F9" s="257"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="256" t="s">
         <v>253</v>
       </c>
@@ -13725,7 +13725,7 @@
       <c r="E10" s="255"/>
       <c r="F10" s="257"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="256" t="s">
         <v>258</v>
       </c>
@@ -13741,7 +13741,7 @@
       <c r="E11" s="255"/>
       <c r="F11" s="257"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="256" t="s">
         <v>258</v>
       </c>
@@ -13757,7 +13757,7 @@
       <c r="E12" s="255"/>
       <c r="F12" s="257"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="256" t="s">
         <v>258</v>
       </c>
@@ -13773,7 +13773,7 @@
       <c r="E13" s="255"/>
       <c r="F13" s="257"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="256" t="s">
         <v>258</v>
       </c>
@@ -13789,7 +13789,7 @@
       <c r="E14" s="255"/>
       <c r="F14" s="257"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="256" t="s">
         <v>258</v>
       </c>
@@ -13805,7 +13805,7 @@
       <c r="E15" s="255"/>
       <c r="F15" s="257"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="256" t="s">
         <v>258</v>
       </c>
@@ -13821,7 +13821,7 @@
       <c r="E16" s="255"/>
       <c r="F16" s="257"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="256" t="s">
         <v>258</v>
       </c>
@@ -13837,7 +13837,7 @@
       <c r="E17" s="255"/>
       <c r="F17" s="257"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="256" t="s">
         <v>258</v>
       </c>
@@ -13853,7 +13853,7 @@
       <c r="E18" s="255"/>
       <c r="F18" s="257"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="256" t="s">
         <v>261</v>
       </c>
@@ -13869,7 +13869,7 @@
       <c r="E19" s="255"/>
       <c r="F19" s="257"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="256" t="s">
         <v>261</v>
       </c>
@@ -13885,7 +13885,7 @@
       <c r="E20" s="255"/>
       <c r="F20" s="257"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="256" t="s">
         <v>261</v>
       </c>
@@ -13901,7 +13901,7 @@
       <c r="E21" s="255"/>
       <c r="F21" s="257"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="256" t="s">
         <v>261</v>
       </c>
@@ -13917,7 +13917,7 @@
       <c r="E22" s="255"/>
       <c r="F22" s="257"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="256" t="s">
         <v>261</v>
       </c>
@@ -13933,7 +13933,7 @@
       <c r="E23" s="255"/>
       <c r="F23" s="257"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="256" t="s">
         <v>264</v>
       </c>
@@ -13949,7 +13949,7 @@
       <c r="E24" s="255"/>
       <c r="F24" s="257"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="256" t="s">
         <v>264</v>
       </c>
@@ -13965,7 +13965,7 @@
       <c r="E25" s="255"/>
       <c r="F25" s="257"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="256" t="s">
         <v>264</v>
       </c>
@@ -13981,7 +13981,7 @@
       <c r="E26" s="255"/>
       <c r="F26" s="257"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="256" t="s">
         <v>264</v>
       </c>
@@ -13997,7 +13997,7 @@
       <c r="E27" s="255"/>
       <c r="F27" s="257"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="256" t="s">
         <v>264</v>
       </c>
@@ -14013,7 +14013,7 @@
       <c r="E28" s="255"/>
       <c r="F28" s="257"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="256" t="s">
         <v>268</v>
       </c>
@@ -14029,7 +14029,7 @@
       <c r="E29" s="255"/>
       <c r="F29" s="257"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="256" t="s">
         <v>268</v>
       </c>
@@ -14045,7 +14045,7 @@
       <c r="E30" s="255"/>
       <c r="F30" s="257"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="256" t="s">
         <v>268</v>
       </c>
@@ -14061,7 +14061,7 @@
       <c r="E31" s="255"/>
       <c r="F31" s="257"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="256" t="s">
         <v>269</v>
       </c>
@@ -14077,7 +14077,7 @@
       <c r="E32" s="255"/>
       <c r="F32" s="257"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="256" t="s">
         <v>270</v>
       </c>
@@ -14093,7 +14093,7 @@
       <c r="E33" s="255"/>
       <c r="F33" s="257"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="256" t="s">
         <v>270</v>
       </c>
@@ -14109,7 +14109,7 @@
       <c r="E34" s="255"/>
       <c r="F34" s="257"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="256" t="s">
         <v>270</v>
       </c>
@@ -14125,7 +14125,7 @@
       <c r="E35" s="255"/>
       <c r="F35" s="257"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="256" t="s">
         <v>270</v>
       </c>
@@ -14141,7 +14141,7 @@
       <c r="E36" s="255"/>
       <c r="F36" s="257"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="256" t="s">
         <v>270</v>
       </c>
@@ -14157,7 +14157,7 @@
       <c r="E37" s="255"/>
       <c r="F37" s="257"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="256" t="s">
         <v>270</v>
       </c>
@@ -14173,7 +14173,7 @@
       <c r="E38" s="255"/>
       <c r="F38" s="257"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="256" t="s">
         <v>270</v>
       </c>
@@ -14189,7 +14189,7 @@
       <c r="E39" s="255"/>
       <c r="F39" s="257"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="256" t="s">
         <v>279</v>
       </c>
@@ -14205,7 +14205,7 @@
       <c r="E40" s="255"/>
       <c r="F40" s="257"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="256" t="s">
         <v>279</v>
       </c>
@@ -14221,7 +14221,7 @@
       <c r="E41" s="255"/>
       <c r="F41" s="257"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="256" t="s">
         <v>279</v>
       </c>
@@ -14237,7 +14237,7 @@
       <c r="E42" s="255"/>
       <c r="F42" s="257"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="256" t="s">
         <v>279</v>
       </c>
@@ -14253,7 +14253,7 @@
       <c r="E43" s="255"/>
       <c r="F43" s="257"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="256" t="s">
         <v>278</v>
       </c>
@@ -14269,7 +14269,7 @@
       <c r="E44" s="255"/>
       <c r="F44" s="257"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="256" t="s">
         <v>278</v>
       </c>
@@ -14285,7 +14285,7 @@
       <c r="E45" s="255"/>
       <c r="F45" s="257"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="261" t="s">
         <v>278</v>
       </c>
@@ -14313,12 +14313,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5C0031-DFF6-400F-8663-F3120A3CF8C5}">
   <dimension ref="D4:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D4" s="244" t="s">
         <v>319</v>
       </c>
@@ -14326,7 +14326,7 @@
       <c r="F4" s="245"/>
       <c r="G4" s="245"/>
     </row>
-    <row r="5" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D5" s="246" t="s">
         <v>312</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="6" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D6" s="248" t="s">
         <v>316</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>0.21202602647520757</v>
       </c>
     </row>
-    <row r="7" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D7" s="248" t="s">
         <v>261</v>
       </c>
@@ -14384,7 +14384,7 @@
         <v>0.22705855956921697</v>
       </c>
     </row>
-    <row r="8" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D8" s="248" t="s">
         <v>275</v>
       </c>
@@ -14406,7 +14406,7 @@
         <v>0.56091541395557554</v>
       </c>
     </row>
-    <row r="9" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:11" ht="15" x14ac:dyDescent="0.3">
       <c r="D9" s="250" t="s">
         <v>317</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="10" spans="4:11" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="D10" s="252" t="s">
         <v>318</v>
       </c>
@@ -14450,45 +14450,45 @@
     <tabColor rgb="FFFFFF99"/>
   </sheetPr>
   <dimension ref="A1:Y123"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" customWidth="1"/>
+    <col min="13" max="13" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" customWidth="1"/>
-    <col min="19" max="19" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" customWidth="1"/>
+    <col min="19" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="284" t="s">
+    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="303" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="J1" s="303"/>
+      <c r="K1" s="303"/>
+      <c r="L1" s="303"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -14496,7 +14496,7 @@
       <c r="Q1" s="9"/>
       <c r="R1" s="9"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -14515,32 +14515,32 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="274" t="s">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="304" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="285" t="s">
+      <c r="B3" s="304"/>
+      <c r="C3" s="305" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="304" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="285" t="s">
+      <c r="H3" s="304"/>
+      <c r="I3" s="305" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
+      <c r="J3" s="305"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="305"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -14559,33 +14559,33 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="274" t="s">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="304" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="304"/>
+      <c r="C5" s="312" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="312"/>
+      <c r="E5" s="312"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="304" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="304"/>
+      <c r="I5" s="313">
         <v>10000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="313"/>
+      <c r="K5" s="312" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="312"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -14603,171 +14603,171 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="M8" s="6"/>
       <c r="O8" s="19"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="277" t="s">
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="314" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="314"/>
+      <c r="C9" s="314"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="277" t="s">
+    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="314" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
+      <c r="B10" s="314"/>
+      <c r="C10" s="314"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="286"/>
+      <c r="O10" s="298"/>
+      <c r="P10" s="298"/>
       <c r="Q10" s="44"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="287" t="s">
+    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="299" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="288"/>
-      <c r="C12" s="289"/>
+      <c r="B12" s="300"/>
+      <c r="C12" s="301"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="290"/>
-      <c r="J12" s="290"/>
-      <c r="K12" s="290"/>
-      <c r="M12" s="290"/>
-      <c r="N12" s="290"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="282" t="s">
+      <c r="I12" s="302"/>
+      <c r="J12" s="302"/>
+      <c r="K12" s="302"/>
+      <c r="M12" s="302"/>
+      <c r="N12" s="302"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="315" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="283"/>
+      <c r="B13" s="316"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
+      <c r="I13" s="295"/>
+      <c r="J13" s="295"/>
       <c r="K13" s="21"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="291" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="293" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="292"/>
+      <c r="B14" s="294"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
+      <c r="I14" s="295"/>
+      <c r="J14" s="295"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="278"/>
+      <c r="M14" s="295"/>
+      <c r="N14" s="295"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="291" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="293" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="292"/>
+      <c r="B15" s="294"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
+      <c r="M15" s="295"/>
+      <c r="N15" s="295"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="291" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="293" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="292"/>
+      <c r="B16" s="294"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
+      <c r="I16" s="295"/>
+      <c r="J16" s="295"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="293" t="s">
+      <c r="M16" s="295"/>
+      <c r="N16" s="295"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="294"/>
+      <c r="B17" s="297"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="278"/>
-      <c r="N17" s="278"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M19" s="347"/>
-      <c r="N19" s="347"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M20" s="347"/>
-      <c r="N20" s="347"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="280"/>
+      <c r="M17" s="295"/>
+      <c r="N17" s="295"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M18" s="295"/>
+      <c r="N18" s="295"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M19" s="267"/>
+      <c r="N19" s="267"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M20" s="267"/>
+      <c r="N20" s="267"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C21" s="289"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="280"/>
-      <c r="F21" s="280"/>
-      <c r="G21" s="280"/>
-      <c r="H21" s="280"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="280"/>
+      <c r="E21" s="289"/>
+      <c r="F21" s="289"/>
+      <c r="G21" s="289"/>
+      <c r="H21" s="289"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C22" s="289"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="280"/>
-      <c r="F22" s="280"/>
-      <c r="G22" s="280"/>
-      <c r="H22" s="280"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="281"/>
+      <c r="E22" s="289"/>
+      <c r="F22" s="289"/>
+      <c r="G22" s="289"/>
+      <c r="H22" s="289"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="290"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="281"/>
-      <c r="F23" s="281"/>
-      <c r="G23" s="281"/>
-      <c r="H23" s="281"/>
-    </row>
-    <row r="24" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="E23" s="290"/>
+      <c r="F23" s="290"/>
+      <c r="G23" s="290"/>
+      <c r="H23" s="290"/>
+    </row>
+    <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
         <v>11</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="172" t="s">
         <v>34</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>0.14634146341463414</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="172" t="s">
         <v>27</v>
       </c>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="M26" s="101"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="172" t="s">
         <v>35</v>
       </c>
@@ -14932,7 +14932,7 @@
         <v>2.6132404181184669E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="172" t="s">
         <v>34</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>0.81010452961672474</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="165" t="s">
         <v>188</v>
       </c>
@@ -14992,7 +14992,7 @@
       <c r="J29" s="52"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="59"/>
       <c r="B30" s="46"/>
       <c r="C30" s="48"/>
@@ -15005,13 +15005,13 @@
       <c r="J30" s="52"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="295" t="s">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="291" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="296"/>
-      <c r="C31" s="296"/>
-      <c r="D31" s="296"/>
+      <c r="B31" s="292"/>
+      <c r="C31" s="292"/>
+      <c r="D31" s="292"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="K31" s="64"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -15049,7 +15049,7 @@
       <c r="K32" s="18"/>
       <c r="N32" s="38"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -15062,11 +15062,11 @@
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="C34" s="11"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -15074,25 +15074,25 @@
         <f>B37/B36</f>
         <v>0.98119658119658115</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="271" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="271"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>348.43205574912889</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="271" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="271"/>
+      <c r="H35" s="271"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
@@ -15100,19 +15100,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="271" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="271"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.87</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="271"/>
+      <c r="H36" s="271"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -15129,7 +15129,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -15137,25 +15137,25 @@
         <f>SUM(F25:F30)</f>
         <v>114.8</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="271" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="271"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.7108013937282234</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="271"/>
+      <c r="H37" s="271"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3484.320557491289</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>83</v>
       </c>
@@ -15163,38 +15163,38 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22230500000000003</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="271"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.5400013664002188</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="271" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="271"/>
+      <c r="H38" s="271"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>85400.013664002181</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="297" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C39" s="271" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="271"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.843205574912893</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
       <c r="B41" s="82"/>
       <c r="C41" s="82"/>
@@ -15209,7 +15209,7 @@
       <c r="L41" s="82"/>
       <c r="M41" s="82"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="94" t="s">
         <v>84</v>
       </c>
@@ -15226,7 +15226,7 @@
       <c r="L42" s="82"/>
       <c r="M42" s="82"/>
     </row>
-    <row r="43" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="94"/>
       <c r="B43" s="82"/>
       <c r="C43" s="82"/>
@@ -15241,12 +15241,12 @@
       <c r="L43" s="82"/>
       <c r="M43" s="82"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="314" t="s">
+    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="272" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="315"/>
-      <c r="C44" s="316"/>
+      <c r="B44" s="273"/>
+      <c r="C44" s="274"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -15260,7 +15260,7 @@
       <c r="L44" s="82"/>
       <c r="M44" s="82"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="76"/>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -15275,12 +15275,12 @@
       <c r="L45" s="82"/>
       <c r="M45" s="82"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="317" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="317"/>
-      <c r="C46" s="317"/>
+      <c r="B46" s="275"/>
+      <c r="C46" s="275"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -15294,12 +15294,12 @@
       <c r="L46" s="82"/>
       <c r="M46" s="82"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="317" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="275" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="317"/>
-      <c r="C47" s="317"/>
+      <c r="B47" s="275"/>
+      <c r="C47" s="275"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.388940688057041</v>
@@ -15314,12 +15314,12 @@
       <c r="L47" s="82"/>
       <c r="M47" s="82"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="317" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="275" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="317"/>
-      <c r="C48" s="317"/>
+      <c r="B48" s="275"/>
+      <c r="C48" s="275"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2208.673891569932</v>
@@ -15334,12 +15334,12 @@
       <c r="L48" s="82"/>
       <c r="M48" s="82"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="317" t="s">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="275" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="317"/>
-      <c r="C49" s="317"/>
+      <c r="B49" s="275"/>
+      <c r="C49" s="275"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -15354,12 +15354,12 @@
       <c r="L49" s="82"/>
       <c r="M49" s="82"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="317" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="275" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="317"/>
-      <c r="C50" s="317"/>
+      <c r="B50" s="275"/>
+      <c r="C50" s="275"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>22086.738915699316</v>
@@ -15374,7 +15374,7 @@
       <c r="L50" s="82"/>
       <c r="M50" s="82"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="76"/>
       <c r="B51" s="76"/>
       <c r="C51" s="76"/>
@@ -15389,12 +15389,12 @@
       <c r="L51" s="82"/>
       <c r="M51" s="82"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="317" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="275" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="317"/>
-      <c r="C52" s="317"/>
+      <c r="B52" s="275"/>
+      <c r="C52" s="275"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -15408,12 +15408,12 @@
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="317" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="275" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="317"/>
-      <c r="C53" s="317"/>
+      <c r="B53" s="275"/>
+      <c r="C53" s="275"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.26494805034054</v>
@@ -15428,7 +15428,7 @@
       <c r="L53" s="82"/>
       <c r="M53" s="82"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="82"/>
       <c r="B54" s="82"/>
       <c r="C54" s="82"/>
@@ -15443,7 +15443,7 @@
       <c r="L54" s="82"/>
       <c r="M54" s="82"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -15458,7 +15458,7 @@
       <c r="L55" s="82"/>
       <c r="M55" s="82"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="82"/>
       <c r="B56" s="82"/>
       <c r="C56" s="82"/>
@@ -15473,7 +15473,7 @@
       <c r="L56" s="82"/>
       <c r="M56" s="82"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="81" t="s">
         <v>108</v>
       </c>
@@ -15490,7 +15490,7 @@
       <c r="L57" s="82"/>
       <c r="M57" s="82"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="81"/>
       <c r="B58" s="82"/>
       <c r="C58" s="82"/>
@@ -15505,7 +15505,7 @@
       <c r="L58" s="82"/>
       <c r="M58" s="82"/>
     </row>
-    <row r="59" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="82"/>
       <c r="B59" s="82"/>
       <c r="C59" s="107" t="s">
@@ -15533,7 +15533,7 @@
       <c r="M59" s="82"/>
       <c r="N59" s="19"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="84" t="b">
         <v>1</v>
       </c>
@@ -15559,7 +15559,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4119.064211050274</v>
       </c>
-      <c r="H60" s="311">
+      <c r="H60" s="268">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9496.7315381437129</v>
       </c>
@@ -15569,7 +15569,7 @@
       <c r="L60" s="82"/>
       <c r="M60" s="82"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="84" t="b">
         <v>1</v>
       </c>
@@ -15593,14 +15593,14 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2608.0002732800435</v>
       </c>
-      <c r="H61" s="312"/>
+      <c r="H61" s="269"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
       <c r="L61" s="82"/>
       <c r="M61" s="82"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="84" t="b">
         <v>1</v>
       </c>
@@ -15624,14 +15624,14 @@
         <f t="shared" si="2"/>
         <v>167.33335610667029</v>
       </c>
-      <c r="H62" s="312"/>
+      <c r="H62" s="269"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
       <c r="L62" s="82"/>
       <c r="M62" s="82"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="84" t="b">
         <v>1</v>
       </c>
@@ -15655,14 +15655,14 @@
         <f t="shared" si="2"/>
         <v>811.66678053335147</v>
       </c>
-      <c r="H63" s="312"/>
+      <c r="H63" s="269"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
       <c r="L63" s="82"/>
       <c r="M63" s="82"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="84" t="b">
         <v>1</v>
       </c>
@@ -15686,14 +15686,14 @@
         <f t="shared" si="2"/>
         <v>811.66678053335147</v>
       </c>
-      <c r="H64" s="312"/>
+      <c r="H64" s="269"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
       <c r="L64" s="82"/>
       <c r="M64" s="82"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="84" t="b">
         <v>1</v>
       </c>
@@ -15717,14 +15717,14 @@
         <f t="shared" si="2"/>
         <v>811.66678053335147</v>
       </c>
-      <c r="H65" s="312"/>
+      <c r="H65" s="269"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
       <c r="L65" s="82"/>
       <c r="M65" s="82"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="84" t="b">
         <v>1</v>
       </c>
@@ -15748,14 +15748,14 @@
         <f t="shared" si="2"/>
         <v>167.33335610667029</v>
       </c>
-      <c r="H66" s="312"/>
+      <c r="H66" s="269"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
       <c r="L66" s="82"/>
       <c r="M66" s="82"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="84" t="b">
         <v>0</v>
       </c>
@@ -15778,14 +15778,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="312"/>
+      <c r="H67" s="269"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
       <c r="L67" s="82"/>
       <c r="M67" s="82"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="84" t="b">
         <v>0</v>
       </c>
@@ -15808,14 +15808,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="312"/>
+      <c r="H68" s="269"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
       <c r="L68" s="82"/>
       <c r="M68" s="82"/>
     </row>
-    <row r="69" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="84" t="b">
         <v>0</v>
       </c>
@@ -15838,14 +15838,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="313"/>
+      <c r="H69" s="270"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
       <c r="L69" s="82"/>
       <c r="M69" s="82"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="82"/>
       <c r="B70" s="82"/>
       <c r="C70" s="82"/>
@@ -15865,7 +15865,7 @@
       <c r="L70" s="82"/>
       <c r="M70" s="82"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="82"/>
       <c r="B71" s="82"/>
       <c r="C71" s="82"/>
@@ -15880,7 +15880,7 @@
       <c r="L71" s="82"/>
       <c r="M71" s="82"/>
     </row>
-    <row r="72" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="82"/>
       <c r="B72" s="86" t="s">
         <v>128</v>
@@ -15897,24 +15897,24 @@
       <c r="L72" s="82"/>
       <c r="M72" s="82"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B73" s="301"/>
-      <c r="C73" s="302" t="s">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B73" s="279"/>
+      <c r="C73" s="280" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="304" t="s">
+      <c r="E73" s="282" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="306" t="s">
+      <c r="F73" s="284" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="306" t="s">
+      <c r="G73" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="308" t="s">
+      <c r="H73" s="286" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -15925,17 +15925,17 @@
       <c r="N73" s="39"/>
       <c r="O73" s="39"/>
     </row>
-    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="301"/>
-      <c r="C74" s="303"/>
+      <c r="B74" s="279"/>
+      <c r="C74" s="281"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="305"/>
-      <c r="F74" s="307"/>
-      <c r="G74" s="307"/>
-      <c r="H74" s="309"/>
+      <c r="E74" s="283"/>
+      <c r="F74" s="285"/>
+      <c r="G74" s="285"/>
+      <c r="H74" s="287"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -15944,7 +15944,7 @@
       <c r="N74" s="40"/>
       <c r="O74" s="40"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="82"/>
       <c r="B75" s="182" t="s">
         <v>45</v>
@@ -15979,7 +15979,7 @@
       <c r="N75" s="15"/>
       <c r="O75" s="15"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="82"/>
       <c r="B76" s="187" t="s">
         <v>46</v>
@@ -16016,7 +16016,7 @@
       <c r="N76" s="15"/>
       <c r="O76" s="15"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="82"/>
       <c r="B77" s="187" t="s">
         <v>90</v>
@@ -16053,7 +16053,7 @@
       <c r="N77" s="41"/>
       <c r="O77" s="41"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="82"/>
       <c r="B78" s="187" t="s">
         <v>47</v>
@@ -16090,7 +16090,7 @@
       <c r="N78" s="41"/>
       <c r="O78" s="41"/>
     </row>
-    <row r="79" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="190" t="s">
         <v>154</v>
       </c>
@@ -16126,7 +16126,7 @@
       <c r="N79" s="41"/>
       <c r="O79" s="41"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="54"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -16142,7 +16142,7 @@
       <c r="M80" s="41"/>
       <c r="N80" s="41"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="54"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -16158,7 +16158,7 @@
       <c r="M81" s="41"/>
       <c r="N81" s="41"/>
     </row>
-    <row r="82" spans="1:25" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A82" s="54"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -16166,33 +16166,33 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="300"/>
-      <c r="I82" s="300"/>
-      <c r="J82" s="300"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
       <c r="N82" s="41"/>
     </row>
-    <row r="83" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="299" t="s">
+      <c r="B83" s="277" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="299"/>
-      <c r="D83" s="299"/>
-      <c r="E83" s="299"/>
-      <c r="F83" s="299"/>
-      <c r="G83" s="299"/>
-      <c r="H83" s="299"/>
-      <c r="I83" s="299"/>
-      <c r="J83" s="299"/>
-      <c r="K83" s="299"/>
-      <c r="L83" s="299"/>
+      <c r="C83" s="277"/>
+      <c r="D83" s="277"/>
+      <c r="E83" s="277"/>
+      <c r="F83" s="277"/>
+      <c r="G83" s="277"/>
+      <c r="H83" s="277"/>
+      <c r="I83" s="277"/>
+      <c r="J83" s="277"/>
+      <c r="K83" s="277"/>
+      <c r="L83" s="277"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="54"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -16208,7 +16208,7 @@
       <c r="M84" s="41"/>
       <c r="N84" s="41"/>
     </row>
-    <row r="85" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="54"/>
       <c r="B85" s="150" t="s">
         <v>137</v>
@@ -16230,7 +16230,7 @@
       <c r="M85" s="41"/>
       <c r="N85" s="41"/>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="54"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -16248,7 +16248,7 @@
       <c r="R86" s="20"/>
       <c r="S86" s="20"/>
     </row>
-    <row r="87" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="54"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -16265,7 +16265,7 @@
       <c r="N87" s="41"/>
       <c r="S87" s="130"/>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="54"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -16273,16 +16273,16 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="310"/>
-      <c r="I88" s="310"/>
+      <c r="H88" s="288"/>
+      <c r="I88" s="288"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="310"/>
-      <c r="L88" s="310"/>
+      <c r="K88" s="288"/>
+      <c r="L88" s="288"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
     </row>
-    <row r="89" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="54"/>
       <c r="B89" s="41"/>
       <c r="C89" s="41"/>
@@ -16293,7 +16293,7 @@
       <c r="M89" s="41"/>
       <c r="N89" s="41"/>
     </row>
-    <row r="90" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="54"/>
       <c r="B90" s="155" t="s">
         <v>12</v>
@@ -16314,7 +16314,7 @@
       <c r="M90" s="41"/>
       <c r="N90" s="41"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="54"/>
       <c r="B91" s="143" t="str">
         <f t="shared" ref="B91:B103" si="5">IF(ISTEXT(B25), B25, "")</f>
@@ -16342,7 +16342,7 @@
       <c r="X91" s="101"/>
       <c r="Y91" s="101"/>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="54"/>
       <c r="B92" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16367,10 +16367,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="306" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="306"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7670642687969504</v>
@@ -16379,7 +16379,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B93" s="146" t="str">
         <f t="shared" si="5"/>
         <v>Solvent Base</v>
@@ -16402,7 +16402,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="53"/>
       <c r="B94" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16430,12 +16430,12 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="310" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U94" s="311"/>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
       <c r="B95" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16466,16 +16466,16 @@
         <f>R95/S92</f>
         <v>0.76614776168096488</v>
       </c>
-      <c r="T95" s="269">
+      <c r="T95" s="307">
         <f>R96-R95</f>
         <v>-7.405642907569554E-2</v>
       </c>
-      <c r="U95" s="271">
+      <c r="U95" s="309">
         <f>(R96-R95)/R95</f>
         <v>-2.565944155227725E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="53"/>
       <c r="B96" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16506,10 +16506,10 @@
         <f>R96/S92</f>
         <v>0.74648883796970411</v>
       </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="308"/>
+      <c r="U96" s="309"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
       <c r="B97" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16540,7 +16540,7 @@
         <v>0.23385223831903515</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" s="53"/>
       <c r="B98" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16571,7 +16571,7 @@
         <v>0.25351116203029589</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" s="53"/>
       <c r="B99" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16591,7 +16591,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" s="53"/>
       <c r="B100" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16611,7 +16611,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="53"/>
       <c r="B101" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16631,7 +16631,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="53"/>
       <c r="B102" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16651,7 +16651,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="53"/>
       <c r="B103" s="146" t="str">
         <f t="shared" si="5"/>
@@ -16671,7 +16671,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="148" t="s">
         <v>139</v>
       </c>
@@ -16691,14 +16691,14 @@
         <v>0.15093010678305055</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
         <v>19876.75</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B106" s="41"/>
       <c r="D106" s="87" t="s">
         <v>141</v>
@@ -16708,7 +16708,7 @@
         <v>1.8930238095238094</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B107" s="41"/>
       <c r="D107" s="87" t="s">
         <v>142</v>
@@ -16718,14 +16718,14 @@
         <v>-2.2428045553031666E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B108" s="41"/>
     </row>
-    <row r="109" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41"/>
       <c r="E109" s="4"/>
     </row>
-    <row r="110" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="155" t="s">
         <v>143</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B111" s="143" t="str">
         <f t="shared" ref="B111:B120" si="9">IF(A60=TRUE, B60, "")</f>
         <v>Extrusion</v>
@@ -16763,7 +16763,7 @@
         <v>0.40414507772020725</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B112" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Printing</v>
@@ -16784,7 +16784,7 @@
         <v>0.21761658031088082</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B113" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Rewinding</v>
@@ -16805,7 +16805,7 @@
         <v>2.072538860103627E-2</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B114" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Lamination 1</v>
@@ -16826,7 +16826,7 @@
         <v>0.10362694300518134</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Lamination 2</v>
@@ -16847,7 +16847,7 @@
         <v>0.10362694300518134</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B116" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Lamination 3</v>
@@ -16868,7 +16868,7 @@
         <v>0.10362694300518134</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Slitting</v>
@@ -16889,7 +16889,7 @@
         <v>4.6632124352331605E-2</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B118" s="146" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -16910,7 +16910,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B119" s="146" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -16931,7 +16931,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B120" s="148" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -16952,30 +16952,30 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B121" s="41"/>
       <c r="E121" s="141">
         <f>SUM(E111:E120)</f>
         <v>9650</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="298" t="s">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B122" s="276" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="298"/>
-      <c r="D122" s="298"/>
+      <c r="C122" s="276"/>
+      <c r="D122" s="276"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B123" s="298" t="s">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B123" s="276" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="298"/>
-      <c r="D123" s="298"/>
+      <c r="C123" s="276"/>
+      <c r="D123" s="276"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-3.2248500069465565E-2</v>
@@ -16983,64 +16983,6 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -17056,6 +16998,64 @@
     <mergeCell ref="G21:G23"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -17101,31 +17101,31 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="D1:AD33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" customWidth="1"/>
+    <col min="16" max="16" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="22" max="22" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" customWidth="1"/>
+    <col min="28" max="28" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D1" t="s">
         <v>12</v>
       </c>
@@ -17162,18 +17162,18 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="267" t="s">
+      <c r="W1" s="317" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="267"/>
-      <c r="Y1" s="267"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="267"/>
-      <c r="AB1" s="267"/>
-      <c r="AC1" s="267"/>
-      <c r="AD1" s="267"/>
-    </row>
-    <row r="2" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="X1" s="317"/>
+      <c r="Y1" s="317"/>
+      <c r="Z1" s="317"/>
+      <c r="AA1" s="317"/>
+      <c r="AB1" s="317"/>
+      <c r="AC1" s="317"/>
+      <c r="AD1" s="317"/>
+    </row>
+    <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
         <v>124</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D3" s="102" t="s">
         <v>114</v>
       </c>
@@ -17303,7 +17303,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D4" s="102" t="s">
         <v>115</v>
       </c>
@@ -17352,7 +17352,7 @@
       <c r="AC4" s="172"/>
       <c r="AD4" s="172"/>
     </row>
-    <row r="5" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D5" s="102" t="s">
         <v>116</v>
       </c>
@@ -17392,7 +17392,7 @@
       <c r="AC5" s="172"/>
       <c r="AD5" s="172"/>
     </row>
-    <row r="6" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D6" s="102" t="s">
         <v>118</v>
       </c>
@@ -17429,7 +17429,7 @@
       <c r="AC6" s="172"/>
       <c r="AD6" s="172"/>
     </row>
-    <row r="7" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D7" s="102" t="s">
         <v>117</v>
       </c>
@@ -17463,7 +17463,7 @@
       <c r="AC7" s="172"/>
       <c r="AD7" s="172"/>
     </row>
-    <row r="8" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D8" s="102" t="s">
         <v>123</v>
       </c>
@@ -17497,7 +17497,7 @@
       <c r="AC8" s="172"/>
       <c r="AD8" s="172"/>
     </row>
-    <row r="9" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>20</v>
       </c>
@@ -17531,7 +17531,7 @@
       <c r="AC9" s="172"/>
       <c r="AD9" s="172"/>
     </row>
-    <row r="10" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D10" s="102" t="s">
         <v>119</v>
       </c>
@@ -17562,7 +17562,7 @@
       <c r="AC10" s="172"/>
       <c r="AD10" s="172"/>
     </row>
-    <row r="11" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D11" s="102" t="s">
         <v>120</v>
       </c>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="V11" s="2"/>
     </row>
-    <row r="12" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>21</v>
       </c>
@@ -17597,7 +17597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D13" s="102" t="s">
         <v>121</v>
       </c>
@@ -17614,7 +17614,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D14" s="102" t="s">
         <v>122</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>22</v>
       </c>
@@ -17648,7 +17648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="4:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>23</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D17" s="102" t="s">
         <v>111</v>
       </c>
@@ -17683,7 +17683,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D18" s="102" t="s">
         <v>110</v>
       </c>
@@ -17701,7 +17701,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>28</v>
       </c>
@@ -17715,7 +17715,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="20" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>29</v>
       </c>
@@ -17729,7 +17729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>30</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="22" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D22" s="102" t="s">
         <v>112</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="23" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D23" s="102" t="s">
         <v>113</v>
       </c>
@@ -17771,7 +17771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>31</v>
       </c>
@@ -17785,7 +17785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>32</v>
       </c>
@@ -17799,7 +17799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
         <v>33</v>
       </c>
@@ -17813,7 +17813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
         <v>24</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="28" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
         <v>25</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>26</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
         <v>58</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
         <v>189</v>
       </c>
@@ -17877,7 +17877,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="103"/>
     </row>
-    <row r="32" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
         <v>191</v>
       </c>
@@ -17885,7 +17885,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="103"/>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
         <v>190</v>
       </c>
@@ -17911,520 +17911,49 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941D5018-3274-429A-BC96-6832248D126F}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I1" s="233" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="233" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="233" t="s">
-        <v>220</v>
-      </c>
-      <c r="L1" s="233" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="233" t="s">
-        <v>221</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>222</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I2" s="234" t="s">
-        <v>124</v>
-      </c>
-      <c r="J2" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="236">
-        <v>100</v>
-      </c>
-      <c r="L2" s="236">
-        <v>2.7</v>
-      </c>
-      <c r="M2" s="236">
-        <v>5</v>
-      </c>
-      <c r="N2" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O2" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I3" s="234" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K3" s="236">
-        <v>100</v>
-      </c>
-      <c r="L3" s="236">
-        <v>0.91</v>
-      </c>
-      <c r="M3" s="236">
-        <v>5</v>
-      </c>
-      <c r="N3" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O3" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="I4" s="234" t="s">
-        <v>115</v>
-      </c>
-      <c r="J4" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K4" s="236">
-        <v>100</v>
-      </c>
-      <c r="L4" s="236">
-        <v>0.91</v>
-      </c>
-      <c r="M4" s="236">
-        <v>5</v>
-      </c>
-      <c r="N4" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O4" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="239">
-        <v>0.91</v>
-      </c>
-      <c r="I5" s="234" t="s">
-        <v>227</v>
-      </c>
-      <c r="J5" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K5" s="236">
-        <v>100</v>
-      </c>
-      <c r="L5" s="236">
-        <v>0.95</v>
-      </c>
-      <c r="M5" s="236">
-        <v>5</v>
-      </c>
-      <c r="N5" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="240">
-        <v>1.4</v>
-      </c>
-      <c r="G6" s="231" t="s">
-        <v>124</v>
-      </c>
-      <c r="I6" s="234" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="235"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="237"/>
-      <c r="O6" s="238"/>
-    </row>
-    <row r="7" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="239">
-        <v>0.91</v>
-      </c>
-      <c r="G7" s="231" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="234" t="s">
-        <v>228</v>
-      </c>
-      <c r="J7" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K7" s="236">
-        <v>100</v>
-      </c>
-      <c r="L7" s="236">
-        <v>0.92</v>
-      </c>
-      <c r="M7" s="236">
-        <v>5</v>
-      </c>
-      <c r="N7" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="240">
-        <v>2.7</v>
-      </c>
-      <c r="G8" s="231" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="236">
-        <v>100</v>
-      </c>
-      <c r="L8" s="236">
-        <v>0.92</v>
-      </c>
-      <c r="M8" s="236">
-        <v>5</v>
-      </c>
-      <c r="N8" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="239">
-        <v>0.92</v>
-      </c>
-      <c r="G9" s="231" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="234" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K9" s="236">
-        <v>100</v>
-      </c>
-      <c r="L9" s="236">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="M9" s="236">
-        <v>5</v>
-      </c>
-      <c r="N9" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="240">
-        <v>0.93</v>
-      </c>
-      <c r="G10" s="231" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="234" t="s">
-        <v>241</v>
-      </c>
-      <c r="J10" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K10" s="236">
-        <v>100</v>
-      </c>
-      <c r="L10" s="236">
-        <v>1</v>
-      </c>
-      <c r="M10" s="236">
-        <v>8</v>
-      </c>
-      <c r="N10" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="239">
-        <v>1.24</v>
-      </c>
-      <c r="G11" s="231" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="234" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K11" s="236">
-        <v>100</v>
-      </c>
-      <c r="L11" s="236">
-        <v>1.38</v>
-      </c>
-      <c r="M11" s="236">
-        <v>5</v>
-      </c>
-      <c r="N11" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O11" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="240">
-        <v>0.92</v>
-      </c>
-      <c r="G12" s="231" t="s">
-        <v>123</v>
-      </c>
-      <c r="I12" s="234" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="236">
-        <v>100</v>
-      </c>
-      <c r="L12" s="236">
-        <v>1.38</v>
-      </c>
-      <c r="M12" s="236">
-        <v>5</v>
-      </c>
-      <c r="N12" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B13" s="239">
-        <v>1</v>
-      </c>
-      <c r="G13" s="229" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="234" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="240">
-        <v>1</v>
-      </c>
-      <c r="G14" s="231" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="234" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" s="239">
-        <v>1</v>
-      </c>
-      <c r="G15" s="231" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" s="231" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="241" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="242">
-        <v>1</v>
-      </c>
-      <c r="G16" s="230" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="231" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G17" s="231" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="234" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G18" s="231" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="234" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G19" s="229" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="229" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G20" s="230" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="230" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G21" s="231" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G22" s="232" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="I23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="I24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I2:O12">
-    <sortCondition ref="I2:I12"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D83BBB9-D6D7-4548-8051-07540CE54455}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:U130"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" customWidth="1"/>
+    <col min="13" max="13" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" customWidth="1"/>
-    <col min="20" max="23" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" customWidth="1"/>
+    <col min="20" max="23" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="284" t="s">
+    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="303" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="J1" s="303"/>
+      <c r="K1" s="303"/>
+      <c r="L1" s="303"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -18433,7 +17962,7 @@
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -18453,33 +17982,33 @@
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="274" t="s">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="304" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="285" t="s">
+      <c r="B3" s="304"/>
+      <c r="C3" s="305" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="304" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="285" t="s">
+      <c r="H3" s="304"/>
+      <c r="I3" s="305" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
+      <c r="J3" s="305"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="305"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -18499,34 +18028,34 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="274" t="s">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="304" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="304"/>
+      <c r="C5" s="312" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="312"/>
+      <c r="E5" s="312"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="304" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="304"/>
+      <c r="I5" s="313">
         <v>20000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="313"/>
+      <c r="K5" s="312" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="312"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -18545,114 +18074,114 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="M8" s="6"/>
       <c r="P8" s="19"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="277" t="s">
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="314" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="314"/>
+      <c r="C9" s="314"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="277" t="s">
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="314" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="286"/>
-      <c r="Q10" s="286"/>
+      <c r="B10" s="314"/>
+      <c r="C10" s="314"/>
+      <c r="N10" s="298"/>
+      <c r="O10" s="298"/>
+      <c r="P10" s="298"/>
+      <c r="Q10" s="298"/>
       <c r="R10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="290"/>
-      <c r="B12" s="290"/>
-      <c r="C12" s="290"/>
-      <c r="E12" s="331" t="s">
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="302"/>
+      <c r="B12" s="302"/>
+      <c r="C12" s="302"/>
+      <c r="E12" s="321" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="332"/>
-      <c r="G12" s="333"/>
-      <c r="I12" s="290"/>
-      <c r="J12" s="290"/>
-      <c r="K12" s="290"/>
-      <c r="M12" s="290"/>
-      <c r="N12" s="290"/>
-      <c r="O12" s="290"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="278"/>
-      <c r="B13" s="278"/>
+      <c r="F12" s="322"/>
+      <c r="G12" s="323"/>
+      <c r="I12" s="302"/>
+      <c r="J12" s="302"/>
+      <c r="K12" s="302"/>
+      <c r="M12" s="302"/>
+      <c r="N12" s="302"/>
+      <c r="O12" s="302"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="295"/>
+      <c r="B13" s="295"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="334" t="s">
+      <c r="E13" s="324" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="335"/>
+      <c r="F13" s="325"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
+      <c r="I13" s="295"/>
+      <c r="J13" s="295"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="278"/>
-      <c r="N13" s="278"/>
+      <c r="M13" s="295"/>
+      <c r="N13" s="295"/>
       <c r="O13" s="129"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="278"/>
-      <c r="B14" s="278"/>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="295"/>
+      <c r="B14" s="295"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="291" t="s">
+      <c r="E14" s="293" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="292"/>
+      <c r="F14" s="294"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
+      <c r="I14" s="295"/>
+      <c r="J14" s="295"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="278"/>
+      <c r="M14" s="295"/>
+      <c r="N14" s="295"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="278"/>
-      <c r="B15" s="278"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="295"/>
+      <c r="B15" s="295"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="329" t="s">
+      <c r="E15" s="319" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="330"/>
+      <c r="F15" s="320"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
+      <c r="M15" s="295"/>
+      <c r="N15" s="295"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="278"/>
-      <c r="B16" s="278"/>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="295"/>
+      <c r="B16" s="295"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -18661,76 +18190,76 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
+      <c r="I16" s="295"/>
+      <c r="J16" s="295"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
+      <c r="M16" s="295"/>
+      <c r="N16" s="295"/>
       <c r="O16" s="129"/>
     </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="278"/>
-      <c r="B17" s="278"/>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="295"/>
+      <c r="B17" s="295"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="293" t="s">
+      <c r="E17" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="294"/>
+      <c r="F17" s="297"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="278"/>
-      <c r="N17" s="278"/>
+      <c r="M17" s="295"/>
+      <c r="N17" s="295"/>
       <c r="O17" s="130"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M18" s="295"/>
+      <c r="N18" s="295"/>
       <c r="O18" s="101"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M19" s="279"/>
-      <c r="N19" s="279"/>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M19" s="318"/>
+      <c r="N19" s="318"/>
       <c r="O19" s="132"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M20" s="279"/>
-      <c r="N20" s="279"/>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M20" s="318"/>
+      <c r="N20" s="318"/>
       <c r="O20" s="133"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="280" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C21" s="289" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="280" t="s">
+      <c r="E21" s="289" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="280"/>
-      <c r="G21" s="280" t="s">
+      <c r="F21" s="289"/>
+      <c r="G21" s="289" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="280" t="s">
+      <c r="H21" s="289" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="280"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C22" s="289"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="280"/>
-      <c r="F22" s="280"/>
-      <c r="G22" s="280"/>
-      <c r="H22" s="280"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="281"/>
+      <c r="E22" s="289"/>
+      <c r="F22" s="289"/>
+      <c r="G22" s="289"/>
+      <c r="H22" s="289"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="290"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="281"/>
-      <c r="F23" s="281"/>
-      <c r="G23" s="281"/>
-      <c r="H23" s="281"/>
-    </row>
-    <row r="24" spans="1:15" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="290"/>
+      <c r="F23" s="290"/>
+      <c r="G23" s="290"/>
+      <c r="H23" s="290"/>
+    </row>
+    <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
         <v>11</v>
       </c>
@@ -18765,7 +18294,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="66" t="s">
         <v>34</v>
       </c>
@@ -18808,7 +18337,7 @@
         <v>0.94091580502215655</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>27</v>
       </c>
@@ -18852,7 +18381,7 @@
       </c>
       <c r="M26" s="14"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="59"/>
       <c r="B27" s="46"/>
       <c r="C27" s="48"/>
@@ -18865,7 +18394,7 @@
       <c r="J27" s="52"/>
       <c r="K27" s="58"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="59"/>
       <c r="B28" s="46"/>
       <c r="C28" s="48"/>
@@ -18878,7 +18407,7 @@
       <c r="J28" s="52"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="59"/>
       <c r="B29" s="46"/>
       <c r="C29" s="48"/>
@@ -18891,7 +18420,7 @@
       <c r="J29" s="52"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="59"/>
       <c r="B30" s="46"/>
       <c r="C30" s="48"/>
@@ -18904,13 +18433,13 @@
       <c r="J30" s="52"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="295" t="s">
+    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="291" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="296"/>
-      <c r="C31" s="296"/>
-      <c r="D31" s="296"/>
+      <c r="B31" s="292"/>
+      <c r="C31" s="292"/>
+      <c r="D31" s="292"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -18934,7 +18463,7 @@
       </c>
       <c r="K31" s="64"/>
     </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -18948,7 +18477,7 @@
       <c r="K32" s="18"/>
       <c r="N32" s="38"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -18961,11 +18490,11 @@
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="C34" s="11"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -18973,25 +18502,25 @@
         <f>B37/B36</f>
         <v>0.91486486486486496</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="271" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="271"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5560.3420833656528</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="271" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="271"/>
+      <c r="H35" s="271"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
@@ -18999,19 +18528,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="271" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="271"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.17984505000000001</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="271"/>
+      <c r="H36" s="271"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -19022,7 +18551,7 @@
       </c>
       <c r="K36" s="13"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -19030,25 +18559,25 @@
         <f>SUM(F25:F30)</f>
         <v>33.85</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="271" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="271"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>29.542097488921712</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="271"/>
+      <c r="H37" s="271"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>111206.84166731306</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>83</v>
       </c>
@@ -19056,39 +18585,39 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10466300000000001</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="271"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>29.249601474179915</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="271" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="271"/>
+      <c r="H38" s="271"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>584992.02948359831</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C39" s="297" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C39" s="271" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="271"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>895.2150754218701</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C40" s="297"/>
-      <c r="D40" s="297"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C40" s="271"/>
+      <c r="D40" s="271"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
       <c r="B41" s="82"/>
       <c r="C41" s="82"/>
@@ -19103,7 +18632,7 @@
       <c r="L41" s="82"/>
       <c r="M41" s="82"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="94" t="s">
         <v>84</v>
       </c>
@@ -19120,7 +18649,7 @@
       <c r="L42" s="82"/>
       <c r="M42" s="82"/>
     </row>
-    <row r="43" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="94"/>
       <c r="B43" s="82"/>
       <c r="C43" s="82"/>
@@ -19135,12 +18664,12 @@
       <c r="L43" s="82"/>
       <c r="M43" s="82"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="314" t="s">
+    <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="272" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="315"/>
-      <c r="C44" s="316"/>
+      <c r="B44" s="273"/>
+      <c r="C44" s="274"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -19154,7 +18683,7 @@
       <c r="L44" s="82"/>
       <c r="M44" s="82"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="76"/>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -19169,12 +18698,12 @@
       <c r="L45" s="82"/>
       <c r="M45" s="82"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="317" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="317"/>
-      <c r="C46" s="317"/>
+      <c r="B46" s="275"/>
+      <c r="C46" s="275"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -19188,12 +18717,12 @@
       <c r="L46" s="82"/>
       <c r="M46" s="82"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="317" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="275" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="317"/>
-      <c r="C47" s="317"/>
+      <c r="B47" s="275"/>
+      <c r="C47" s="275"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.801683863720231</v>
@@ -19208,12 +18737,12 @@
       <c r="L47" s="82"/>
       <c r="M47" s="82"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="317" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="275" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="317"/>
-      <c r="C48" s="317"/>
+      <c r="B48" s="275"/>
+      <c r="C48" s="275"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6984.1850084778926</v>
@@ -19228,12 +18757,12 @@
       <c r="L48" s="82"/>
       <c r="M48" s="82"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="317" t="s">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="275" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="317"/>
-      <c r="C49" s="317"/>
+      <c r="B49" s="275"/>
+      <c r="C49" s="275"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -19248,12 +18777,12 @@
       <c r="L49" s="82"/>
       <c r="M49" s="82"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="317" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="275" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="317"/>
-      <c r="C50" s="317"/>
+      <c r="B50" s="275"/>
+      <c r="C50" s="275"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>43380.031108558345</v>
@@ -19268,7 +18797,7 @@
       <c r="L50" s="82"/>
       <c r="M50" s="82"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="76"/>
       <c r="B51" s="76"/>
       <c r="C51" s="76"/>
@@ -19283,12 +18812,12 @@
       <c r="L51" s="82"/>
       <c r="M51" s="82"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="317" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="275" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="317"/>
-      <c r="C52" s="317"/>
+      <c r="B52" s="275"/>
+      <c r="C52" s="275"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -19302,12 +18831,12 @@
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="317" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="275" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="317"/>
-      <c r="C53" s="317"/>
+      <c r="B53" s="275"/>
+      <c r="C53" s="275"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1739.3365512543585</v>
@@ -19322,7 +18851,7 @@
       <c r="L53" s="82"/>
       <c r="M53" s="82"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="82"/>
       <c r="B54" s="82"/>
       <c r="C54" s="82"/>
@@ -19337,7 +18866,7 @@
       <c r="L54" s="82"/>
       <c r="M54" s="82"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -19352,7 +18881,7 @@
       <c r="L55" s="82"/>
       <c r="M55" s="82"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="82"/>
       <c r="B56" s="82"/>
       <c r="C56" s="82"/>
@@ -19367,7 +18896,7 @@
       <c r="L56" s="82"/>
       <c r="M56" s="82"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="81" t="s">
         <v>108</v>
       </c>
@@ -19384,7 +18913,7 @@
       <c r="L57" s="82"/>
       <c r="M57" s="82"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="81"/>
       <c r="B58" s="82"/>
       <c r="C58" s="82"/>
@@ -19399,7 +18928,7 @@
       <c r="L58" s="82"/>
       <c r="M58" s="82"/>
     </row>
-    <row r="59" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="82"/>
       <c r="B59" s="82"/>
       <c r="C59" s="107" t="s">
@@ -19427,7 +18956,7 @@
       <c r="M59" s="82"/>
       <c r="N59" s="19"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="84" t="b">
         <v>0</v>
       </c>
@@ -19460,7 +18989,7 @@
       <c r="L60" s="82"/>
       <c r="M60" s="82"/>
     </row>
-    <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="84" t="b">
         <v>1</v>
       </c>
@@ -19491,7 +19020,7 @@
       <c r="L61" s="82"/>
       <c r="M61" s="82"/>
     </row>
-    <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="84" t="b">
         <v>0</v>
       </c>
@@ -19521,7 +19050,7 @@
       <c r="L62" s="82"/>
       <c r="M62" s="82"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="84" t="b">
         <v>0</v>
       </c>
@@ -19551,7 +19080,7 @@
       <c r="L63" s="82"/>
       <c r="M63" s="82"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="84" t="b">
         <v>0</v>
       </c>
@@ -19581,7 +19110,7 @@
       <c r="L64" s="82"/>
       <c r="M64" s="82"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="84" t="b">
         <v>0</v>
       </c>
@@ -19611,7 +19140,7 @@
       <c r="L65" s="82"/>
       <c r="M65" s="82"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="84" t="b">
         <v>1</v>
       </c>
@@ -19642,7 +19171,7 @@
       <c r="L66" s="82"/>
       <c r="M66" s="82"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="84" t="b">
         <v>1</v>
       </c>
@@ -19674,7 +19203,7 @@
       <c r="M67" s="82"/>
       <c r="O67" s="13"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="84" t="b">
         <v>1</v>
       </c>
@@ -19705,7 +19234,7 @@
       <c r="L68" s="82"/>
       <c r="M68" s="82"/>
     </row>
-    <row r="69" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="84" t="b">
         <v>0</v>
       </c>
@@ -19735,7 +19264,7 @@
       <c r="L69" s="82"/>
       <c r="M69" s="82"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="82"/>
       <c r="B70" s="82"/>
       <c r="C70" s="82"/>
@@ -19755,7 +19284,7 @@
       <c r="L70" s="82"/>
       <c r="M70" s="82"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="82"/>
       <c r="B71" s="82"/>
       <c r="C71" s="82"/>
@@ -19770,7 +19299,7 @@
       <c r="L71" s="82"/>
       <c r="M71" s="82"/>
     </row>
-    <row r="72" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="82"/>
       <c r="B72" s="86" t="s">
         <v>128</v>
@@ -19787,24 +19316,24 @@
       <c r="L72" s="82"/>
       <c r="M72" s="82"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B73" s="301"/>
-      <c r="C73" s="302" t="s">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B73" s="279"/>
+      <c r="C73" s="280" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="304" t="s">
+      <c r="E73" s="282" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="306" t="s">
+      <c r="F73" s="284" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="306" t="s">
+      <c r="G73" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="308" t="s">
+      <c r="H73" s="286" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -19816,17 +19345,17 @@
       <c r="O73" s="39"/>
       <c r="P73" s="39"/>
     </row>
-    <row r="74" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="301"/>
-      <c r="C74" s="303"/>
+      <c r="B74" s="279"/>
+      <c r="C74" s="281"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="305"/>
-      <c r="F74" s="307"/>
-      <c r="G74" s="307"/>
-      <c r="H74" s="309"/>
+      <c r="E74" s="283"/>
+      <c r="F74" s="285"/>
+      <c r="G74" s="285"/>
+      <c r="H74" s="287"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -19836,7 +19365,7 @@
       <c r="O74" s="40"/>
       <c r="P74" s="40"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="82"/>
       <c r="B75" s="182" t="s">
         <v>45</v>
@@ -19872,7 +19401,7 @@
       <c r="O75" s="15"/>
       <c r="P75" s="15"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="82"/>
       <c r="B76" s="187" t="s">
         <v>46</v>
@@ -19910,7 +19439,7 @@
       <c r="O76" s="15"/>
       <c r="P76" s="15"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="82"/>
       <c r="B77" s="187" t="s">
         <v>90</v>
@@ -19948,7 +19477,7 @@
       <c r="O77" s="41"/>
       <c r="P77" s="41"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="82"/>
       <c r="B78" s="187" t="s">
         <v>47</v>
@@ -19986,7 +19515,7 @@
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
     </row>
-    <row r="79" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="190" t="s">
         <v>154</v>
       </c>
@@ -20023,7 +19552,7 @@
       <c r="O79" s="41"/>
       <c r="P79" s="41"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="54"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -20040,7 +19569,7 @@
       <c r="N80" s="41"/>
       <c r="O80" s="41"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="54"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -20057,7 +19586,7 @@
       <c r="N81" s="41"/>
       <c r="O81" s="41"/>
     </row>
-    <row r="82" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A82" s="54"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -20065,33 +19594,33 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="300"/>
-      <c r="I82" s="300"/>
-      <c r="J82" s="300"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
       <c r="N82" s="41"/>
     </row>
-    <row r="83" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="299" t="s">
+      <c r="B83" s="277" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="299"/>
-      <c r="D83" s="299"/>
-      <c r="E83" s="299"/>
-      <c r="F83" s="299"/>
-      <c r="G83" s="299"/>
-      <c r="H83" s="299"/>
-      <c r="I83" s="299"/>
-      <c r="J83" s="299"/>
-      <c r="K83" s="299"/>
-      <c r="L83" s="299"/>
+      <c r="C83" s="277"/>
+      <c r="D83" s="277"/>
+      <c r="E83" s="277"/>
+      <c r="F83" s="277"/>
+      <c r="G83" s="277"/>
+      <c r="H83" s="277"/>
+      <c r="I83" s="277"/>
+      <c r="J83" s="277"/>
+      <c r="K83" s="277"/>
+      <c r="L83" s="277"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="54"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -20107,7 +19636,7 @@
       <c r="M84" s="41"/>
       <c r="N84" s="41"/>
     </row>
-    <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="54"/>
       <c r="B85" s="150" t="s">
         <v>137</v>
@@ -20129,7 +19658,7 @@
       <c r="M85" s="41"/>
       <c r="N85" s="41"/>
     </row>
-    <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="54"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -20145,7 +19674,7 @@
       <c r="M86" s="41"/>
       <c r="N86" s="41"/>
     </row>
-    <row r="87" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="54"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -20153,21 +19682,21 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="318" t="s">
+      <c r="H87" s="329" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="319"/>
+      <c r="I87" s="330"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="320" t="s">
+      <c r="K87" s="331" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="321"/>
+      <c r="L87" s="332"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
-    <row r="88" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="54"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -20175,29 +19704,29 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="322">
+      <c r="H88" s="333">
         <f>C75+H70</f>
         <v>10.356866246447392</v>
       </c>
-      <c r="I88" s="323"/>
+      <c r="I88" s="334"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.95343569181762111</v>
       </c>
-      <c r="K88" s="324">
+      <c r="K88" s="335">
         <f>E106+E122</f>
         <v>20.231472181191531</v>
       </c>
-      <c r="L88" s="325"/>
+      <c r="L88" s="336"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
-    <row r="89" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D89" s="42"/>
       <c r="E89" s="42"/>
       <c r="F89" s="42"/>
     </row>
-    <row r="90" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="53"/>
       <c r="B90" s="155" t="s">
         <v>12</v>
@@ -20216,7 +19745,7 @@
       </c>
       <c r="P90" s="222"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B91" s="143" t="str">
         <f t="shared" ref="B91:B103" si="7">IF(ISTEXT(B25), B25, "")</f>
         <v>BOPP Transparent</v>
@@ -20238,7 +19767,7 @@
       </c>
       <c r="P91" s="222"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B92" s="146" t="str">
         <f t="shared" si="7"/>
         <v>All Colors</v>
@@ -20260,10 +19789,10 @@
         <v>0.88063321721809495</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="306" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="306"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.584455611292297</v>
@@ -20272,7 +19801,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B93" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20292,7 +19821,7 @@
       </c>
       <c r="P93" s="222"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B94" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20317,12 +19846,12 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="310" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U94" s="311"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20352,16 +19881,16 @@
         <f>R95/S92</f>
         <v>0.89403132904680693</v>
       </c>
-      <c r="T95" s="269">
+      <c r="T95" s="307">
         <f>R96-R95</f>
         <v>9.8746059347441388</v>
       </c>
-      <c r="U95" s="271">
+      <c r="U95" s="309">
         <f>(R96-R95)/R95</f>
         <v>0.95343569181762111</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B96" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20393,10 +19922,10 @@
         <f>R96/S92</f>
         <v>1.7464327077631765</v>
       </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
-    </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="308"/>
+      <c r="U96" s="309"/>
+    </row>
+    <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20428,7 +19957,7 @@
         <v>0.10596867095319308</v>
       </c>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B98" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20460,7 +19989,7 @@
         <v>-0.74643270776317661</v>
       </c>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B99" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20481,7 +20010,7 @@
       <c r="I99" s="3"/>
       <c r="P99" s="222"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B100" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20501,7 +20030,7 @@
       </c>
       <c r="P100" s="222"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B101" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20521,7 +20050,7 @@
       </c>
       <c r="P101" s="222"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B102" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20541,7 +20070,7 @@
       </c>
       <c r="P102" s="222"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B103" s="146" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -20561,7 +20090,7 @@
       </c>
       <c r="P103" s="222"/>
     </row>
-    <row r="104" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="148" t="s">
         <v>139</v>
       </c>
@@ -20582,7 +20111,7 @@
       </c>
       <c r="P104" s="222"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
@@ -20590,7 +20119,7 @@
       </c>
       <c r="P105" s="222"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B106" s="41"/>
       <c r="D106" s="87" t="s">
         <v>141</v>
@@ -20601,7 +20130,7 @@
       </c>
       <c r="P106" s="222"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B107" s="41"/>
       <c r="D107" s="87" t="s">
         <v>142</v>
@@ -20612,16 +20141,16 @@
       </c>
       <c r="P107" s="222"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B108" s="41"/>
       <c r="P108" s="222"/>
     </row>
-    <row r="109" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41"/>
       <c r="E109" s="4"/>
       <c r="P109" s="222"/>
     </row>
-    <row r="110" spans="2:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="155" t="s">
         <v>143</v>
       </c>
@@ -20639,7 +20168,7 @@
       </c>
       <c r="P110" s="222"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B111" s="143" t="str">
         <f t="shared" ref="B111:B120" si="12">IF(A60=TRUE, B60, "")</f>
         <v/>
@@ -20659,7 +20188,7 @@
       </c>
       <c r="P111" s="222"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B112" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Printing</v>
@@ -20681,7 +20210,7 @@
       </c>
       <c r="P112" s="222"/>
     </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="146" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -20701,7 +20230,7 @@
       </c>
       <c r="P113" s="222"/>
     </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B114" s="146" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -20721,7 +20250,7 @@
       </c>
       <c r="P114" s="222"/>
     </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="146" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -20741,7 +20270,7 @@
       </c>
       <c r="P115" s="222"/>
     </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="146" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -20761,7 +20290,7 @@
       </c>
       <c r="P116" s="222"/>
     </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Slitting</v>
@@ -20783,7 +20312,7 @@
       </c>
       <c r="P117" s="222"/>
     </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Sleeving</v>
@@ -20805,7 +20334,7 @@
       </c>
       <c r="P118" s="222"/>
     </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B119" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Doctoring</v>
@@ -20827,7 +20356,7 @@
       </c>
       <c r="P119" s="222"/>
     </row>
-    <row r="120" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B120" s="148" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -20847,7 +20376,7 @@
       </c>
       <c r="P120" s="222"/>
     </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B121" s="41"/>
       <c r="E121" s="141">
         <f>SUM(E111:E120)</f>
@@ -20855,76 +20384,94 @@
       </c>
       <c r="P121" s="222"/>
     </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B122" s="298" t="s">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B122" s="276" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="298"/>
-      <c r="D122" s="298"/>
+      <c r="C122" s="276"/>
+      <c r="D122" s="276"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
       </c>
       <c r="P122" s="222"/>
     </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B123" s="298" t="s">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B123" s="276" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="298"/>
-      <c r="D123" s="298"/>
+      <c r="C123" s="276"/>
+      <c r="D123" s="276"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.77517475095143862</v>
       </c>
       <c r="P123" s="222"/>
     </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P124" s="222"/>
     </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P125" s="222"/>
     </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P126" s="222"/>
     </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P127" s="222"/>
     </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P128" s="222"/>
     </row>
-    <row r="129" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="16:16" x14ac:dyDescent="0.3">
       <c r="P129" s="222"/>
     </row>
-    <row r="130" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="16:16" x14ac:dyDescent="0.3">
       <c r="P130" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="A1:L1"/>
@@ -20941,47 +20488,29 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -21022,51 +20551,51 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42444A01-6BD4-415F-ACC7-DA57DCC971A9}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:U130"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" customWidth="1"/>
+    <col min="13" max="13" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" customWidth="1"/>
-    <col min="20" max="23" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" customWidth="1"/>
+    <col min="20" max="23" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="284" t="s">
+    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="303" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="J1" s="303"/>
+      <c r="K1" s="303"/>
+      <c r="L1" s="303"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21075,7 +20604,7 @@
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -21095,33 +20624,33 @@
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="274" t="s">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="304" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="285" t="s">
+      <c r="B3" s="304"/>
+      <c r="C3" s="305" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="304" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="285" t="s">
+      <c r="H3" s="304"/>
+      <c r="I3" s="305" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
+      <c r="J3" s="305"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="305"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -21141,34 +20670,34 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="274" t="s">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="304" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="304"/>
+      <c r="C5" s="312" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="312"/>
+      <c r="E5" s="312"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="304" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="304"/>
+      <c r="I5" s="313">
         <v>500</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="313"/>
+      <c r="K5" s="312" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="312"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -21187,107 +20716,107 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="M8" s="6"/>
       <c r="P8" s="19"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="277" t="s">
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="314" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="314"/>
+      <c r="C9" s="314"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="277" t="s">
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="314" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="286"/>
-      <c r="Q10" s="286"/>
+      <c r="B10" s="314"/>
+      <c r="C10" s="314"/>
+      <c r="N10" s="298"/>
+      <c r="O10" s="298"/>
+      <c r="P10" s="298"/>
+      <c r="Q10" s="298"/>
       <c r="R10" s="44"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="290"/>
-      <c r="B12" s="290"/>
-      <c r="C12" s="290"/>
-      <c r="E12" s="290"/>
-      <c r="F12" s="290"/>
-      <c r="G12" s="290"/>
-      <c r="I12" s="336" t="s">
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="302"/>
+      <c r="B12" s="302"/>
+      <c r="C12" s="302"/>
+      <c r="E12" s="302"/>
+      <c r="F12" s="302"/>
+      <c r="G12" s="302"/>
+      <c r="I12" s="343" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="337"/>
-      <c r="K12" s="338"/>
-      <c r="M12" s="336" t="s">
+      <c r="J12" s="344"/>
+      <c r="K12" s="345"/>
+      <c r="M12" s="343" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="337"/>
-      <c r="O12" s="338"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="278"/>
-      <c r="B13" s="278"/>
+      <c r="N12" s="344"/>
+      <c r="O12" s="345"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="295"/>
+      <c r="B13" s="295"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="334" t="s">
+      <c r="I13" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="335"/>
+      <c r="J13" s="325"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="334" t="s">
+      <c r="M13" s="324" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="335"/>
+      <c r="N13" s="325"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="278"/>
-      <c r="B14" s="278"/>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="295"/>
+      <c r="B14" s="295"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="291" t="s">
+      <c r="I14" s="293" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="292"/>
+      <c r="J14" s="294"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="291" t="s">
+      <c r="M14" s="293" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="292"/>
+      <c r="N14" s="294"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="278"/>
-      <c r="B15" s="278"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="295"/>
+      <c r="B15" s="295"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -21296,10 +20825,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="291" t="s">
+      <c r="M15" s="293" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="292"/>
+      <c r="N15" s="294"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -21307,106 +20836,106 @@
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="278"/>
-      <c r="B16" s="278"/>
+    <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="295"/>
+      <c r="B16" s="295"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="293" t="s">
+      <c r="I16" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="294"/>
+      <c r="J16" s="297"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="291" t="s">
+      <c r="M16" s="293" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="292"/>
+      <c r="N16" s="294"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="278"/>
-      <c r="B17" s="278"/>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="295"/>
+      <c r="B17" s="295"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="291" t="s">
+      <c r="M17" s="293" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="292"/>
+      <c r="N17" s="294"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M18" s="291" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M18" s="293" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="292"/>
+      <c r="N18" s="294"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0095041508317739</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M19" s="341" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M19" s="337" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="342"/>
+      <c r="N19" s="338"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M20" s="343"/>
-      <c r="N20" s="344"/>
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M20" s="339"/>
+      <c r="N20" s="340"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="280" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C21" s="289" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="280" t="s">
+      <c r="E21" s="289" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="280"/>
-      <c r="G21" s="280" t="s">
+      <c r="F21" s="289"/>
+      <c r="G21" s="289" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="280" t="s">
+      <c r="H21" s="289" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="280"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C22" s="289"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="280"/>
-      <c r="F22" s="280"/>
-      <c r="G22" s="280"/>
-      <c r="H22" s="280"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="281"/>
+      <c r="E22" s="289"/>
+      <c r="F22" s="289"/>
+      <c r="G22" s="289"/>
+      <c r="H22" s="289"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="290"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="281"/>
-      <c r="F23" s="281"/>
-      <c r="G23" s="281"/>
-      <c r="H23" s="281"/>
-    </row>
-    <row r="24" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="E23" s="290"/>
+      <c r="F23" s="290"/>
+      <c r="G23" s="290"/>
+      <c r="H23" s="290"/>
+    </row>
+    <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
         <v>11</v>
       </c>
@@ -21441,7 +20970,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="172" t="s">
         <v>34</v>
       </c>
@@ -21484,7 +21013,7 @@
         <v>9.7227848833844541E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="172" t="s">
         <v>27</v>
       </c>
@@ -21528,7 +21057,7 @@
       </c>
       <c r="M26" s="14"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="172" t="s">
         <v>35</v>
       </c>
@@ -21571,7 +21100,7 @@
         <v>1.7362115863186527E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="172" t="s">
         <v>34</v>
       </c>
@@ -21614,7 +21143,7 @@
         <v>0.14115400196770647</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="172" t="s">
         <v>35</v>
       </c>
@@ -21657,7 +21186,7 @@
         <v>1.7362115863186527E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="172" t="s">
         <v>34</v>
       </c>
@@ -21700,7 +21229,7 @@
         <v>0.53243821980438688</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="172" t="s">
         <v>35</v>
       </c>
@@ -21743,7 +21272,7 @@
         <v>2.3149487817582037E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="172" t="s">
         <v>34</v>
       </c>
@@ -21786,13 +21315,13 @@
         <v>0.15973146594131607</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="339" t="s">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="341" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="340"/>
-      <c r="C33" s="340"/>
-      <c r="D33" s="340"/>
+      <c r="B33" s="342"/>
+      <c r="C33" s="342"/>
+      <c r="D33" s="342"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21816,7 +21345,7 @@
       </c>
       <c r="K33" s="200"/>
     </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -21830,7 +21359,7 @@
       <c r="K34" s="18"/>
       <c r="N34" s="38"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -21838,25 +21367,25 @@
         <f>B37/B36</f>
         <v>1.0600613496932514</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="271" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="271"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.929085817184177</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="271" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="271"/>
+      <c r="H35" s="271"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
@@ -21864,19 +21393,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="271" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="271"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.566728000000005</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="271"/>
+      <c r="H36" s="271"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21887,7 +21416,7 @@
       </c>
       <c r="K36" s="13"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -21895,25 +21424,25 @@
         <f>SUM(F25:F32)</f>
         <v>172.79</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="271" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="271"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7873719543955096</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="271"/>
+      <c r="H37" s="271"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>499.99999999999994</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>83</v>
       </c>
@@ -21921,35 +21450,35 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.37950350000000005</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="271"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.0919704783110626</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="271" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="271"/>
+      <c r="H38" s="271"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C39" s="297" t="s">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C39" s="271" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="271"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0380166033270974</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
       <c r="B41" s="82"/>
       <c r="C41" s="82"/>
@@ -21964,7 +21493,7 @@
       <c r="L41" s="82"/>
       <c r="M41" s="82"/>
     </row>
-    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="94" t="s">
         <v>84</v>
       </c>
@@ -21981,7 +21510,7 @@
       <c r="L42" s="82"/>
       <c r="M42" s="82"/>
     </row>
-    <row r="43" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="94"/>
       <c r="B43" s="82"/>
       <c r="C43" s="82"/>
@@ -21996,12 +21525,12 @@
       <c r="L43" s="82"/>
       <c r="M43" s="82"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="314" t="s">
+    <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="272" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="315"/>
-      <c r="C44" s="316"/>
+      <c r="B44" s="273"/>
+      <c r="C44" s="274"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -22015,7 +21544,7 @@
       <c r="L44" s="82"/>
       <c r="M44" s="82"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="76"/>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -22030,12 +21559,12 @@
       <c r="L45" s="82"/>
       <c r="M45" s="82"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="317" t="s">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="317"/>
-      <c r="C46" s="317"/>
+      <c r="B46" s="275"/>
+      <c r="C46" s="275"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -22049,12 +21578,12 @@
       <c r="L46" s="82"/>
       <c r="M46" s="82"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="317" t="s">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="275" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="317"/>
-      <c r="C47" s="317"/>
+      <c r="B47" s="275"/>
+      <c r="C47" s="275"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.381970487307228</v>
@@ -22069,12 +21598,12 @@
       <c r="L47" s="82"/>
       <c r="M47" s="82"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="317" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="275" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="317"/>
-      <c r="C48" s="317"/>
+      <c r="B48" s="275"/>
+      <c r="C48" s="275"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>284.40086623540481</v>
@@ -22089,12 +21618,12 @@
       <c r="L48" s="82"/>
       <c r="M48" s="82"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="317" t="s">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="275" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="317"/>
-      <c r="C49" s="317"/>
+      <c r="B49" s="275"/>
+      <c r="C49" s="275"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -22109,12 +21638,12 @@
       <c r="L49" s="82"/>
       <c r="M49" s="82"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="317" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="275" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="317"/>
-      <c r="C50" s="317"/>
+      <c r="B50" s="275"/>
+      <c r="C50" s="275"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>917.42214914646695</v>
@@ -22129,7 +21658,7 @@
       <c r="L50" s="82"/>
       <c r="M50" s="82"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="76"/>
       <c r="B51" s="76"/>
       <c r="C51" s="76"/>
@@ -22144,12 +21673,12 @@
       <c r="L51" s="82"/>
       <c r="M51" s="82"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="317" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="275" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="317"/>
-      <c r="C52" s="317"/>
+      <c r="B52" s="275"/>
+      <c r="C52" s="275"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -22163,12 +21692,12 @@
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="317" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="275" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="317"/>
-      <c r="C53" s="317"/>
+      <c r="B53" s="275"/>
+      <c r="C53" s="275"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.17634485576332</v>
@@ -22183,7 +21712,7 @@
       <c r="L53" s="82"/>
       <c r="M53" s="82"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="82"/>
       <c r="B54" s="82"/>
       <c r="C54" s="82"/>
@@ -22198,7 +21727,7 @@
       <c r="L54" s="82"/>
       <c r="M54" s="82"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -22213,7 +21742,7 @@
       <c r="L55" s="82"/>
       <c r="M55" s="82"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="82"/>
       <c r="B56" s="82"/>
       <c r="C56" s="82"/>
@@ -22228,7 +21757,7 @@
       <c r="L56" s="82"/>
       <c r="M56" s="82"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="81" t="s">
         <v>108</v>
       </c>
@@ -22245,7 +21774,7 @@
       <c r="L57" s="82"/>
       <c r="M57" s="82"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="81"/>
       <c r="B58" s="82"/>
       <c r="C58" s="82"/>
@@ -22260,7 +21789,7 @@
       <c r="L58" s="82"/>
       <c r="M58" s="82"/>
     </row>
-    <row r="59" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="82"/>
       <c r="B59" s="82"/>
       <c r="C59" s="107" t="s">
@@ -22288,7 +21817,7 @@
       <c r="M59" s="82"/>
       <c r="N59" s="19"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="84" t="b">
         <v>1</v>
       </c>
@@ -22324,7 +21853,7 @@
       <c r="L60" s="82"/>
       <c r="M60" s="82"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="84" t="b">
         <v>1</v>
       </c>
@@ -22355,7 +21884,7 @@
       <c r="L61" s="82"/>
       <c r="M61" s="82"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="84" t="b">
         <v>1</v>
       </c>
@@ -22386,7 +21915,7 @@
       <c r="L62" s="82"/>
       <c r="M62" s="82"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="84" t="b">
         <v>1</v>
       </c>
@@ -22417,7 +21946,7 @@
       <c r="L63" s="82"/>
       <c r="M63" s="82"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="84" t="b">
         <v>1</v>
       </c>
@@ -22448,7 +21977,7 @@
       <c r="L64" s="82"/>
       <c r="M64" s="82"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="84" t="b">
         <v>1</v>
       </c>
@@ -22479,7 +22008,7 @@
       <c r="L65" s="82"/>
       <c r="M65" s="82"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="84" t="b">
         <v>1</v>
       </c>
@@ -22510,7 +22039,7 @@
       <c r="L66" s="82"/>
       <c r="M66" s="82"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="84" t="b">
         <v>0</v>
       </c>
@@ -22541,7 +22070,7 @@
       <c r="M67" s="82"/>
       <c r="O67" s="13"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="84" t="b">
         <v>0</v>
       </c>
@@ -22571,7 +22100,7 @@
       <c r="L68" s="82"/>
       <c r="M68" s="82"/>
     </row>
-    <row r="69" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="84" t="b">
         <v>1</v>
       </c>
@@ -22602,7 +22131,7 @@
       <c r="L69" s="82"/>
       <c r="M69" s="82"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="82"/>
       <c r="B70" s="82"/>
       <c r="C70" s="82"/>
@@ -22622,7 +22151,7 @@
       <c r="L70" s="82"/>
       <c r="M70" s="82"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="82"/>
       <c r="B71" s="82"/>
       <c r="C71" s="82"/>
@@ -22637,7 +22166,7 @@
       <c r="L71" s="82"/>
       <c r="M71" s="82"/>
     </row>
-    <row r="72" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="82"/>
       <c r="B72" s="86" t="s">
         <v>128</v>
@@ -22654,24 +22183,24 @@
       <c r="L72" s="82"/>
       <c r="M72" s="82"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B73" s="301"/>
-      <c r="C73" s="302" t="s">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B73" s="279"/>
+      <c r="C73" s="280" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="304" t="s">
+      <c r="E73" s="282" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="306" t="s">
+      <c r="F73" s="284" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="306" t="s">
+      <c r="G73" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="308" t="s">
+      <c r="H73" s="286" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22683,17 +22212,17 @@
       <c r="O73" s="39"/>
       <c r="P73" s="39"/>
     </row>
-    <row r="74" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="301"/>
-      <c r="C74" s="303"/>
+      <c r="B74" s="279"/>
+      <c r="C74" s="281"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="305"/>
-      <c r="F74" s="307"/>
-      <c r="G74" s="307"/>
-      <c r="H74" s="309"/>
+      <c r="E74" s="283"/>
+      <c r="F74" s="285"/>
+      <c r="G74" s="285"/>
+      <c r="H74" s="287"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22703,7 +22232,7 @@
       <c r="O74" s="40"/>
       <c r="P74" s="40"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="82"/>
       <c r="B75" s="182" t="s">
         <v>45</v>
@@ -22739,7 +22268,7 @@
       <c r="O75" s="15"/>
       <c r="P75" s="15"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="82"/>
       <c r="B76" s="187" t="s">
         <v>46</v>
@@ -22777,7 +22306,7 @@
       <c r="O76" s="15"/>
       <c r="P76" s="15"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="82"/>
       <c r="B77" s="187" t="s">
         <v>90</v>
@@ -22815,7 +22344,7 @@
       <c r="O77" s="41"/>
       <c r="P77" s="41"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="82"/>
       <c r="B78" s="187" t="s">
         <v>47</v>
@@ -22853,7 +22382,7 @@
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
     </row>
-    <row r="79" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="190" t="s">
         <v>154</v>
       </c>
@@ -22890,7 +22419,7 @@
       <c r="O79" s="41"/>
       <c r="P79" s="41"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="54"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -22907,7 +22436,7 @@
       <c r="N80" s="41"/>
       <c r="O80" s="41"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="54"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -22924,7 +22453,7 @@
       <c r="N81" s="41"/>
       <c r="O81" s="41"/>
     </row>
-    <row r="82" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A82" s="54"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -22932,33 +22461,33 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="300"/>
-      <c r="I82" s="300"/>
-      <c r="J82" s="300"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
       <c r="N82" s="41"/>
     </row>
-    <row r="83" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="299" t="s">
+      <c r="B83" s="277" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="299"/>
-      <c r="D83" s="299"/>
-      <c r="E83" s="299"/>
-      <c r="F83" s="299"/>
-      <c r="G83" s="299"/>
-      <c r="H83" s="299"/>
-      <c r="I83" s="299"/>
-      <c r="J83" s="299"/>
-      <c r="K83" s="299"/>
-      <c r="L83" s="299"/>
+      <c r="C83" s="277"/>
+      <c r="D83" s="277"/>
+      <c r="E83" s="277"/>
+      <c r="F83" s="277"/>
+      <c r="G83" s="277"/>
+      <c r="H83" s="277"/>
+      <c r="I83" s="277"/>
+      <c r="J83" s="277"/>
+      <c r="K83" s="277"/>
+      <c r="L83" s="277"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="54"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -22974,7 +22503,7 @@
       <c r="M84" s="41"/>
       <c r="N84" s="41"/>
     </row>
-    <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="54"/>
       <c r="B85" s="150" t="s">
         <v>137</v>
@@ -22996,7 +22525,7 @@
       <c r="M85" s="41"/>
       <c r="N85" s="41"/>
     </row>
-    <row r="86" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="54"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -23012,7 +22541,7 @@
       <c r="M86" s="41"/>
       <c r="N86" s="41"/>
     </row>
-    <row r="87" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="54"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -23020,21 +22549,21 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="318" t="s">
+      <c r="H87" s="329" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="319"/>
+      <c r="I87" s="330"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="320" t="s">
+      <c r="K87" s="331" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="321"/>
+      <c r="L87" s="332"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
-    <row r="88" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="54"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -23042,29 +22571,29 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="322">
+      <c r="H88" s="333">
         <f>C75+H70</f>
         <v>3.0809215390131408</v>
       </c>
-      <c r="I88" s="323"/>
+      <c r="I88" s="334"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>5.8472728784905177E-2</v>
       </c>
-      <c r="K88" s="324">
+      <c r="K88" s="335">
         <f>E106+E122</f>
         <v>3.2610714285714288</v>
       </c>
-      <c r="L88" s="325"/>
+      <c r="L88" s="336"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
-    <row r="89" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D89" s="42"/>
       <c r="E89" s="42"/>
       <c r="F89" s="42"/>
     </row>
-    <row r="90" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="53"/>
       <c r="B90" s="155" t="s">
         <v>12</v>
@@ -23083,7 +22612,7 @@
       </c>
       <c r="P90" s="222"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B91" s="143" t="str">
         <f t="shared" ref="B91:B103" si="6">IF(ISTEXT(B25), B25, "")</f>
         <v>PET Transparent</v>
@@ -23105,7 +22634,7 @@
       </c>
       <c r="P91" s="222"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B92" s="146" t="str">
         <f t="shared" si="6"/>
         <v>All Colors</v>
@@ -23126,10 +22655,10 @@
         <v>9.8268600842302295E-2</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="306" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="306"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0398199127616214</v>
@@ -23138,7 +22667,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B93" s="146" t="str">
         <f t="shared" si="6"/>
         <v>Solvent Base</v>
@@ -23160,7 +22689,7 @@
       </c>
       <c r="P93" s="222"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B94" s="146" t="str">
         <f t="shared" si="6"/>
         <v>Aluminium Foil</v>
@@ -23187,12 +22716,12 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="310" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U94" s="311"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
         <f t="shared" si="6"/>
         <v>Solvent Less</v>
@@ -23224,16 +22753,16 @@
         <f>R95/S92</f>
         <v>0.7626383367438333</v>
       </c>
-      <c r="T95" s="269">
+      <c r="T95" s="307">
         <f>R96-R95</f>
         <v>0.18014988955828803</v>
       </c>
-      <c r="U95" s="271">
+      <c r="U95" s="309">
         <f>(R96-R95)/R95</f>
         <v>5.8472728784905177E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B96" s="146" t="str">
         <f t="shared" si="6"/>
         <v>LDPE Transparent</v>
@@ -23267,10 +22796,10 @@
         <f>R96/S92</f>
         <v>0.80723188136922663</v>
       </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
-    </row>
-    <row r="97" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="308"/>
+      <c r="U96" s="309"/>
+    </row>
+    <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
         <f t="shared" si="6"/>
         <v>Solvent Less</v>
@@ -23304,7 +22833,7 @@
         <v>0.23736166325616667</v>
       </c>
     </row>
-    <row r="98" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B98" s="146" t="str">
         <f t="shared" si="6"/>
         <v>LDPE Transparent</v>
@@ -23338,7 +22867,7 @@
         <v>0.19276811863077334</v>
       </c>
     </row>
-    <row r="99" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B99" s="146" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -23359,7 +22888,7 @@
       <c r="I99" s="3"/>
       <c r="P99" s="222"/>
     </row>
-    <row r="100" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B100" s="146" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -23379,7 +22908,7 @@
       </c>
       <c r="P100" s="222"/>
     </row>
-    <row r="101" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B101" s="146" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -23399,7 +22928,7 @@
       </c>
       <c r="P101" s="222"/>
     </row>
-    <row r="102" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B102" s="146" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -23419,7 +22948,7 @@
       </c>
       <c r="P102" s="222"/>
     </row>
-    <row r="103" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B103" s="146" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -23439,7 +22968,7 @@
       </c>
       <c r="P103" s="222"/>
     </row>
-    <row r="104" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="148" t="s">
         <v>139</v>
       </c>
@@ -23460,7 +22989,7 @@
       </c>
       <c r="P104" s="222"/>
     </row>
-    <row r="105" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
@@ -23468,7 +22997,7 @@
       </c>
       <c r="P105" s="222"/>
     </row>
-    <row r="106" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B106" s="41"/>
       <c r="D106" s="87" t="s">
         <v>141</v>
@@ -23479,7 +23008,7 @@
       </c>
       <c r="P106" s="222"/>
     </row>
-    <row r="107" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B107" s="41"/>
       <c r="D107" s="87" t="s">
         <v>142</v>
@@ -23490,16 +23019,16 @@
       </c>
       <c r="P107" s="222"/>
     </row>
-    <row r="108" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B108" s="41"/>
       <c r="P108" s="222"/>
     </row>
-    <row r="109" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B109" s="41"/>
       <c r="E109" s="4"/>
       <c r="P109" s="222"/>
     </row>
-    <row r="110" spans="2:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B110" s="155" t="s">
         <v>143</v>
       </c>
@@ -23517,7 +23046,7 @@
       </c>
       <c r="P110" s="222"/>
     </row>
-    <row r="111" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B111" s="143" t="str">
         <f t="shared" ref="B111:B120" si="10">IF(A60=TRUE, B60, "")</f>
         <v>Extrusion</v>
@@ -23539,7 +23068,7 @@
       </c>
       <c r="P111" s="222"/>
     </row>
-    <row r="112" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B112" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Printing</v>
@@ -23561,7 +23090,7 @@
       </c>
       <c r="P112" s="222"/>
     </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B113" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Rewinding</v>
@@ -23583,7 +23112,7 @@
       </c>
       <c r="P113" s="222"/>
     </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B114" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Lamination 1</v>
@@ -23605,7 +23134,7 @@
       </c>
       <c r="P114" s="222"/>
     </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B115" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Lamination 2</v>
@@ -23627,7 +23156,7 @@
       </c>
       <c r="P115" s="222"/>
     </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B116" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Lamination 3</v>
@@ -23649,7 +23178,7 @@
       </c>
       <c r="P116" s="222"/>
     </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B117" s="146" t="str">
         <f t="shared" si="10"/>
         <v>Slitting</v>
@@ -23671,7 +23200,7 @@
       </c>
       <c r="P117" s="222"/>
     </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B118" s="146" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -23691,7 +23220,7 @@
       </c>
       <c r="P118" s="222"/>
     </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B119" s="146" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -23711,7 +23240,7 @@
       </c>
       <c r="P119" s="222"/>
     </row>
-    <row r="120" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B120" s="148" t="str">
         <f t="shared" si="10"/>
         <v>Pouch Making</v>
@@ -23733,7 +23262,7 @@
       </c>
       <c r="P120" s="222"/>
     </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B121" s="41"/>
       <c r="E121" s="141">
         <f>SUM(E111:E120)</f>
@@ -23741,53 +23270,119 @@
       </c>
       <c r="P121" s="222"/>
     </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B122" s="298" t="s">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B122" s="276" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="298"/>
-      <c r="D122" s="298"/>
+      <c r="C122" s="276"/>
+      <c r="D122" s="276"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
       </c>
       <c r="P122" s="222"/>
     </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B123" s="298" t="s">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B123" s="276" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="298"/>
-      <c r="D123" s="298"/>
+      <c r="C123" s="276"/>
+      <c r="D123" s="276"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>9.8163656516668904E-2</v>
       </c>
       <c r="P123" s="222"/>
     </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P124" s="222"/>
     </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P125" s="222"/>
     </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P126" s="222"/>
     </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P127" s="222"/>
     </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P128" s="222"/>
     </row>
-    <row r="129" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="16:16" x14ac:dyDescent="0.3">
       <c r="P129" s="222"/>
     </row>
-    <row r="130" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="16:16" x14ac:dyDescent="0.3">
       <c r="P130" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -23801,72 +23396,6 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -23903,34 +23432,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56876A7-A503-4EE5-BF05-536BED17384A}">
   <dimension ref="B1:Q12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="G1" s="345" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="G1" s="346" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="345"/>
-      <c r="I1" s="345"/>
-      <c r="J1" s="345"/>
-      <c r="K1" s="345" t="s">
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="346" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="345"/>
-      <c r="M1" s="345"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
       <c r="N1" s="172"/>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>175</v>
       </c>
@@ -23968,7 +23497,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>175</v>
       </c>
@@ -24008,7 +23537,7 @@
       <c r="O5" s="19"/>
       <c r="P5" s="19"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N6" s="2" t="s">
         <v>203</v>
       </c>
@@ -24019,7 +23548,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N7" t="s">
         <v>209</v>
       </c>
@@ -24029,11 +23558,11 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="346" t="s">
+      <c r="Q7" s="347" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N8" t="s">
         <v>210</v>
       </c>
@@ -24043,9 +23572,9 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="346"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q8" s="347"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
         <v>211</v>
       </c>
@@ -24055,9 +23584,9 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="346"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q9" s="347"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
         <v>212</v>
       </c>
@@ -24067,9 +23596,9 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="346"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q10" s="347"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
         <v>213</v>
       </c>
@@ -24079,9 +23608,9 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="346"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q11" s="347"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
         <v>217</v>
       </c>
@@ -24091,7 +23620,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="346"/>
+      <c r="Q12" s="347"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">
@@ -24109,4 +23638,475 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941D5018-3274-429A-BC96-6832248D126F}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I1" s="233" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="233" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="233" t="s">
+        <v>220</v>
+      </c>
+      <c r="L1" s="233" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="233" t="s">
+        <v>221</v>
+      </c>
+      <c r="N1" s="233" t="s">
+        <v>222</v>
+      </c>
+      <c r="O1" s="233" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I2" s="234" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="236">
+        <v>100</v>
+      </c>
+      <c r="L2" s="236">
+        <v>2.7</v>
+      </c>
+      <c r="M2" s="236">
+        <v>5</v>
+      </c>
+      <c r="N2" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O2" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I3" s="234" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K3" s="236">
+        <v>100</v>
+      </c>
+      <c r="L3" s="236">
+        <v>0.91</v>
+      </c>
+      <c r="M3" s="236">
+        <v>5</v>
+      </c>
+      <c r="N3" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O3" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I4" s="234" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K4" s="236">
+        <v>100</v>
+      </c>
+      <c r="L4" s="236">
+        <v>0.91</v>
+      </c>
+      <c r="M4" s="236">
+        <v>5</v>
+      </c>
+      <c r="N4" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O4" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="239">
+        <v>0.91</v>
+      </c>
+      <c r="I5" s="234" t="s">
+        <v>227</v>
+      </c>
+      <c r="J5" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K5" s="236">
+        <v>100</v>
+      </c>
+      <c r="L5" s="236">
+        <v>0.95</v>
+      </c>
+      <c r="M5" s="236">
+        <v>5</v>
+      </c>
+      <c r="N5" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O5" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="240">
+        <v>1.4</v>
+      </c>
+      <c r="G6" s="231" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="234" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="235"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="237"/>
+      <c r="O6" s="238"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="239">
+        <v>0.91</v>
+      </c>
+      <c r="G7" s="231" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="234" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" s="236">
+        <v>100</v>
+      </c>
+      <c r="L7" s="236">
+        <v>0.92</v>
+      </c>
+      <c r="M7" s="236">
+        <v>5</v>
+      </c>
+      <c r="N7" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O7" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="240">
+        <v>2.7</v>
+      </c>
+      <c r="G8" s="231" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="234" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K8" s="236">
+        <v>100</v>
+      </c>
+      <c r="L8" s="236">
+        <v>0.92</v>
+      </c>
+      <c r="M8" s="236">
+        <v>5</v>
+      </c>
+      <c r="N8" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="239">
+        <v>0.92</v>
+      </c>
+      <c r="G9" s="231" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="234" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K9" s="236">
+        <v>100</v>
+      </c>
+      <c r="L9" s="236">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M9" s="236">
+        <v>5</v>
+      </c>
+      <c r="N9" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O9" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="240">
+        <v>0.93</v>
+      </c>
+      <c r="G10" s="231" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="234" t="s">
+        <v>241</v>
+      </c>
+      <c r="J10" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K10" s="236">
+        <v>100</v>
+      </c>
+      <c r="L10" s="236">
+        <v>1</v>
+      </c>
+      <c r="M10" s="236">
+        <v>8</v>
+      </c>
+      <c r="N10" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="239">
+        <v>1.24</v>
+      </c>
+      <c r="G11" s="231" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" s="234" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" s="236">
+        <v>100</v>
+      </c>
+      <c r="L11" s="236">
+        <v>1.38</v>
+      </c>
+      <c r="M11" s="236">
+        <v>5</v>
+      </c>
+      <c r="N11" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O11" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" s="240">
+        <v>0.92</v>
+      </c>
+      <c r="G12" s="231" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="234" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K12" s="236">
+        <v>100</v>
+      </c>
+      <c r="L12" s="236">
+        <v>1.38</v>
+      </c>
+      <c r="M12" s="236">
+        <v>5</v>
+      </c>
+      <c r="N12" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O12" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="239">
+        <v>1</v>
+      </c>
+      <c r="G13" s="229" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="234" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="240">
+        <v>1</v>
+      </c>
+      <c r="G14" s="231" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="234" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="239">
+        <v>1</v>
+      </c>
+      <c r="G15" s="231" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="231" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="241" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="242">
+        <v>1</v>
+      </c>
+      <c r="G16" s="230" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="231" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="231" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="234" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="231" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="234" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="229" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="229" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="230" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="231" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="232" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>249</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I2:O12">
+    <sortCondition ref="I2:I12"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5713E9E-8306-43E3-B4F7-3CF45A8A439D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC32DAD3-6D31-4FC6-93D8-5CD92083DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="3" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="PE Bag" sheetId="11" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="337">
   <si>
     <t>Roll</t>
   </si>
@@ -1133,6 +1133,21 @@
   </si>
   <si>
     <t>Claculate</t>
+  </si>
+  <si>
+    <t>Ethyl Acetate</t>
+  </si>
+  <si>
+    <t>Ethanol</t>
+  </si>
+  <si>
+    <t>IPA</t>
+  </si>
+  <si>
+    <t>MEK</t>
+  </si>
+  <si>
+    <t>Toluene</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2706,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="354">
+  <cellXfs count="356">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3313,8 +3328,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3325,89 +3346,26 @@
     <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3436,8 +3394,8 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3448,6 +3406,9 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3457,11 +3418,110 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3487,54 +3547,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3547,19 +3559,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3568,8 +3586,11 @@
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3581,401 +3602,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="88">
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="dashed">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="dashed">
-          <color indexed="64"/>
-        </right>
-        <top style="dashed">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dashed">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="dashed">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="dashed">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -5042,6 +4668,401 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="dashed">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="dashed">
+          <color indexed="64"/>
+        </right>
+        <top style="dashed">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dashed">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="dashed">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="dashed">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5975,10 +5996,10 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.44021325209444023</c:v>
+                  <c:v>0.43920972644376899</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10281797410510282</c:v>
+                  <c:v>0.10486322188449848</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -6011,7 +6032,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.45696877380045697</c:v>
+                  <c:v>0.45592705167173253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6153,10 +6174,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="13"/>
                       <c:pt idx="0">
-                        <c:v>0.44021325209444023</c:v>
+                        <c:v>0.43920972644376899</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.10281797410510282</c:v>
+                        <c:v>0.10486322188449848</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -6189,7 +6210,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>0.45696877380045697</c:v>
+                        <c:v>0.45592705167173253</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -6321,7 +6342,7 @@
                         <c:v>2890</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -6483,10 +6504,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="13"/>
                       <c:pt idx="0">
-                        <c:v>0.44021325209444023</c:v>
+                        <c:v>0.43920972644376899</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.10281797410510282</c:v>
+                        <c:v>0.10486322188449848</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -6519,7 +6540,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>0.45696877380045697</c:v>
+                        <c:v>0.45592705167173253</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7031,10 +7052,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.44021325209444023</c:v>
+                        <c:v>0.43920972644376899</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.10281797410510282</c:v>
+                        <c:v>0.10486322188449848</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7070,7 +7091,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.45696877380045697</c:v>
+                        <c:v>0.45592705167173253</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7159,7 +7180,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'PE Bag'!$B$111:$B$120</c15:sqref>
@@ -7194,7 +7215,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'PE Bag'!$E$91:$E$104</c15:sqref>
@@ -7208,7 +7229,7 @@
                         <c:v>2890</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7333,7 +7354,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'PE Bag'!$B$111:$B$120</c15:sqref>
@@ -7368,7 +7389,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'PE Bag'!$F$91:$F$104</c15:sqref>
@@ -7379,10 +7400,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.44021325209444023</c:v>
+                        <c:v>0.43920972644376899</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0.10281797410510282</c:v>
+                        <c:v>0.10486322188449848</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7418,7 +7439,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.45696877380045697</c:v>
+                        <c:v>0.45592705167173253</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -7763,16 +7784,16 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.12829059076559296</c:v>
+                  <c:v>0.12819384920884286</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.395927402618637E-2</c:v>
+                  <c:v>3.468774743298101E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.10196586464084924</c:v>
+                  <c:v>0.1018889740721656</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.58485416378432087</c:v>
+                  <c:v>0.58441313609913659</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -7799,7 +7820,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.15093010678305055</c:v>
+                  <c:v>0.15081629318687395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7947,16 +7968,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="13"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -7983,7 +8004,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -8121,7 +8142,7 @@
                         <c:v>2550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>2026.75</c:v>
@@ -8289,16 +8310,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="13"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -8325,7 +8346,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -8837,16 +8858,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -8876,7 +8897,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9014,7 +9035,7 @@
                         <c:v>2550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>2026.75</c:v>
@@ -9185,16 +9206,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -9224,7 +9245,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9563,10 +9584,10 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0.10323613646002601</c:v>
+                  <c:v>0.10336164612991984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88063321721809495</c:v>
+                  <c:v>0.88048809666228023</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -9593,7 +9614,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6130646321879064E-2</c:v>
+                  <c:v>1.6150257207799976E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9735,10 +9756,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="11"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -9765,7 +9786,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9897,7 +9918,7 @@
                         <c:v>2550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -10053,10 +10074,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="11"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -10083,7 +10104,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10577,16 +10598,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -10616,7 +10637,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10745,7 +10766,7 @@
                         <c:v>2550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>2026.75</c:v>
@@ -10907,16 +10928,16 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="14"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0.10196586464084924</c:v>
+                        <c:v>0.1018889740721656</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0.58485416378432087</c:v>
+                        <c:v>0.58441313609913659</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -10946,7 +10967,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -11294,19 +11315,19 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>7.4871314927468416E-2</c:v>
+                  <c:v>7.4708171206225679E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.8268600842302295E-2</c:v>
+                  <c:v>0.10023346303501944</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.29948525970987366</c:v>
+                  <c:v>0.29883268482490272</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9931367961316487E-2</c:v>
+                  <c:v>3.9844357976653699E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.3589143659335516E-2</c:v>
+                  <c:v>9.3385214007782102E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -11324,7 +11345,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.0191857744501637E-2</c:v>
+                  <c:v>7.0038910505836577E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11475,10 +11496,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="11"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -11505,7 +11526,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -11646,7 +11667,7 @@
                         <c:v>2550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>675</c:v>
+                        <c:v>690</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -11811,10 +11832,10 @@
                       <c:formatCode>0.0%</c:formatCode>
                       <c:ptCount val="11"/>
                       <c:pt idx="0">
-                        <c:v>0.12829059076559296</c:v>
+                        <c:v>0.12819384920884286</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>3.395927402618637E-2</c:v>
+                        <c:v>3.468774743298101E-2</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -11841,7 +11862,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>0.15093010678305055</c:v>
+                        <c:v>0.15081629318687395</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -16649,32 +16670,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="8" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="79">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="78">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="77">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="3" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="75">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table1713[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="74">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="73">
       <calculatedColumnFormula>table1713[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16683,42 +16704,42 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}" name="UT" displayName="UT" ref="M1:M6" totalsRowShown="0" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}" name="UT" displayName="UT" ref="M1:M6" totalsRowShown="0" dataDxfId="31">
   <autoFilter ref="M1:M6" xr:uid="{0ACB9144-FE8F-4434-B61E-D494EC9E3ABC}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{031412D9-180B-4257-B711-44F88C9C965F}" name="Units" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{031412D9-180B-4257-B711-44F88C9C965F}" name="Units" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C1F89DFF-92E0-4FAB-9769-7CF6CF9FC96F}" name="table1" displayName="table1" ref="A24:K30" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C1F89DFF-92E0-4FAB-9769-7CF6CF9FC96F}" name="table1" displayName="table1" ref="A24:K30" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{50FE5CD8-8F96-4285-BA9D-268C0CAD731A}" name="Type" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{CDABA659-5E06-4320-B16B-D8FC50A5EC4C}" name="Material" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{F30B7E1A-8EC0-487D-B51E-A83F6C0A7696}" name="Solid_x000a_%" dataDxfId="38" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{50FE5CD8-8F96-4285-BA9D-268C0CAD731A}" name="Type" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{CDABA659-5E06-4320-B16B-D8FC50A5EC4C}" name="Material" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{F30B7E1A-8EC0-487D-B51E-A83F6C0A7696}" name="Solid_x000a_%" dataDxfId="23" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EC6EB5B0-8D3E-431C-A41E-451AEDDF1CAB}" name="Micron" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{0E9EC9A2-097B-4038-90CC-10ACAA2D37C8}" name="Density" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{EC6EB5B0-8D3E-431C-A41E-451AEDDF1CAB}" name="Micron" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{0E9EC9A2-097B-4038-90CC-10ACAA2D37C8}" name="Density" dataDxfId="21">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6DE0F403-F045-4CB7-A93C-BBBB4C2CC36C}" name="Total GSM" dataDxfId="35">
+    <tableColumn id="6" xr3:uid="{6DE0F403-F045-4CB7-A93C-BBBB4C2CC36C}" name="Total GSM" dataDxfId="20">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6CFF6209-352B-43CE-920D-DA966F28BBF4}" name="Cost Per Kg" dataDxfId="34">
+    <tableColumn id="7" xr3:uid="{6CFF6209-352B-43CE-920D-DA966F28BBF4}" name="Cost Per Kg" dataDxfId="19">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6570658D-E7B6-433E-BD7F-58AB4E45B978}" name="Waste_x000a_%" dataDxfId="33" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{08E47AC7-5580-40EE-AA5E-E63B6D775F19}" name="Cost / M²" dataDxfId="32">
+    <tableColumn id="8" xr3:uid="{6570658D-E7B6-433E-BD7F-58AB4E45B978}" name="Waste_x000a_%" dataDxfId="18" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{08E47AC7-5580-40EE-AA5E-E63B6D775F19}" name="Cost / M²" dataDxfId="17">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table1[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6061D34F-C8DF-4EFA-905E-8BC988C9E100}" name="Est._x000a_Required Kgs" dataDxfId="31">
+    <tableColumn id="10" xr3:uid="{6061D34F-C8DF-4EFA-905E-8BC988C9E100}" name="Est._x000a_Required Kgs" dataDxfId="16">
       <calculatedColumnFormula>IF(A25="Substrate",((_xlfn.SINGLE(OQKG)*F25)/_xlfn.SINGLE(TGSM))*(1+H25),((_xlfn.SINGLE(OQKG)*D25)/_xlfn.SINGLE(TGSM))*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{34DD8AA7-3F81-4C57-9966-FA6A384BC52D}" name="Layer %" dataDxfId="30">
+    <tableColumn id="11" xr3:uid="{34DD8AA7-3F81-4C57-9966-FA6A384BC52D}" name="Layer %" dataDxfId="15">
       <calculatedColumnFormula>table1[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16727,32 +16748,32 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0D4C80BE-F4F8-4934-9879-F5555B90B675}" name="table111" displayName="table111" ref="A24:K32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0D4C80BE-F4F8-4934-9879-F5555B90B675}" name="table111" displayName="table111" ref="A24:K32" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C78D00EE-CC8D-4078-8CF3-F7CA276EB14E}" name="Type" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{1D84220D-1AC7-4C20-8698-133A4B852684}" name="Material" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{85EF343D-3E7B-4865-8D76-03D11AE9E519}" name="Solid_x000a_%" dataDxfId="23" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{C78D00EE-CC8D-4078-8CF3-F7CA276EB14E}" name="Type" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{1D84220D-1AC7-4C20-8698-133A4B852684}" name="Material" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{85EF343D-3E7B-4865-8D76-03D11AE9E519}" name="Solid_x000a_%" dataDxfId="8" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B0482690-6F47-4FE7-9C89-DA01552E21F8}" name="Micron" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{E7E60B92-AF49-4CC8-8113-82A5EF636877}" name="Density" dataDxfId="21">
+    <tableColumn id="4" xr3:uid="{B0482690-6F47-4FE7-9C89-DA01552E21F8}" name="Micron" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{E7E60B92-AF49-4CC8-8113-82A5EF636877}" name="Density" dataDxfId="6">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{94DD0504-F221-405D-81CF-F0738ECA1FCC}" name="Total GSM" dataDxfId="20">
+    <tableColumn id="6" xr3:uid="{94DD0504-F221-405D-81CF-F0738ECA1FCC}" name="Total GSM" dataDxfId="5">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2CA9B622-3087-468C-989B-788B5B5FA003}" name="Cost Per Kg" dataDxfId="19">
+    <tableColumn id="7" xr3:uid="{2CA9B622-3087-468C-989B-788B5B5FA003}" name="Cost Per Kg" dataDxfId="4">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{86908396-9795-4DE3-9FF0-383162A826B5}" name="Waste_x000a_%" dataDxfId="18" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{E189D7D2-A0B2-4FE3-8D31-A34B3D925414}" name="Cost / M²" dataDxfId="17">
+    <tableColumn id="8" xr3:uid="{86908396-9795-4DE3-9FF0-383162A826B5}" name="Waste_x000a_%" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{E189D7D2-A0B2-4FE3-8D31-A34B3D925414}" name="Cost / M²" dataDxfId="2">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table111[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F2A518A6-5B7C-4FF1-B5F2-B276433B3AE1}" name="Est._x000a_Required Kgs" dataDxfId="16">
+    <tableColumn id="10" xr3:uid="{F2A518A6-5B7C-4FF1-B5F2-B276433B3AE1}" name="Est._x000a_Required Kgs" dataDxfId="1">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{380643C8-6CF2-44AE-9796-D6CDAFCFF6FC}" name="Layer %" dataDxfId="15">
+    <tableColumn id="11" xr3:uid="{380643C8-6CF2-44AE-9796-D6CDAFCFF6FC}" name="Layer %" dataDxfId="0">
       <calculatedColumnFormula>table111[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16776,32 +16797,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="55" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="80"/>
-    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="79">
+    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="53">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="52">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="51">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="75">
+    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="50" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="49">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table17[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="74">
+    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="48">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="73">
+    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="47">
       <calculatedColumnFormula>table17[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16814,16 +16835,16 @@
   <autoFilter ref="D1:G33" xr:uid="{837835BF-F846-4004-BCD7-070D9DCCAD90}"/>
   <tableColumns count="4">
     <tableColumn id="2" xr3:uid="{9E3142C9-50FA-4916-9CEF-822169826878}" name="Material"/>
-    <tableColumn id="3" xr3:uid="{32A96633-FC6A-40F7-974B-25881602DB09}" name="Density" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{32A96633-FC6A-40F7-974B-25881602DB09}" name="Density" dataDxfId="46"/>
     <tableColumn id="4" xr3:uid="{705696B6-E241-4CE0-AFE1-37043FC331F9}" name="Solid" dataCellStyle="Percent"/>
-    <tableColumn id="1" xr3:uid="{69EE0737-5119-452D-80EC-62F1CE8D7933}" name="Cost Per Kg" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{69EE0737-5119-452D-80EC-62F1CE8D7933}" name="Cost Per Kg" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}" name="T" displayName="T" ref="P1:P5" totalsRowShown="0" headerRowDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}" name="T" displayName="T" ref="P1:P5" totalsRowShown="0" headerRowDxfId="44">
   <autoFilter ref="P1:P5" xr:uid="{ACEB8540-85B3-4847-8F20-81840BD67A79}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{128D7DDA-5198-45F5-9AC3-6316B0FAB04C}" name="Material Type"/>
@@ -16833,38 +16854,38 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}" name="Table3" displayName="Table3" ref="Q1:Q18" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}" name="Table3" displayName="Table3" ref="Q1:Q18" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="Q1:Q18" xr:uid="{5B46735D-3E62-4411-9491-B2CB027FCCD7}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9E980FBC-6C44-4579-9F83-F013225FDE31}" name="Substrate" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{9E980FBC-6C44-4579-9F83-F013225FDE31}" name="Substrate" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}" name="Table4" displayName="Table4" ref="R1:R9" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}" name="Table4" displayName="Table4" ref="R1:R9" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="R1:R9" xr:uid="{18F0352D-76C9-4FE0-B368-CC02D4B9A4DD}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6C1C3C3D-7FBA-4671-9A3E-6181E3719E8D}" name="Ink" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{6C1C3C3D-7FBA-4671-9A3E-6181E3719E8D}" name="Ink" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}" name="A" displayName="A" ref="S1:T4" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}" name="A" displayName="A" ref="S1:T4" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="S1:T4" xr:uid="{A0A7022A-2C20-43C3-AA8D-7A4D11FC446B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{012E7603-7A8C-46AD-914C-FAE7D12FAF3F}" name="Adhesive" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{4325B70E-CBBC-4618-9B76-FCD61F8B754A}" name="Packaging" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{012E7603-7A8C-46AD-914C-FAE7D12FAF3F}" name="Adhesive" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{4325B70E-CBBC-4618-9B76-FCD61F8B754A}" name="Packaging" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}" name="PTypeT" displayName="PTypeT" ref="K1:K4" totalsRowShown="0" headerRowDxfId="48" tableBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}" name="PTypeT" displayName="PTypeT" ref="K1:K4" totalsRowShown="0" headerRowDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="K1:K4" xr:uid="{679E0A2B-7D76-401E-A524-0A36C49CE947}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{15A59F61-F80E-4915-8496-D6FC380FA80A}" name="Product Type"/>
@@ -17239,20 +17260,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="316" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="283"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17280,26 +17301,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="317" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="317"/>
+      <c r="C3" s="318" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="284"/>
-      <c r="E3" s="284"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="317" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="284" t="s">
+      <c r="H3" s="317"/>
+      <c r="I3" s="318" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="284"/>
-      <c r="K3" s="284"/>
-      <c r="L3" s="284"/>
+      <c r="J3" s="318"/>
+      <c r="K3" s="318"/>
+      <c r="L3" s="318"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17324,28 +17345,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="317" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="317"/>
+      <c r="C5" s="319" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="317" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="317"/>
+      <c r="I5" s="320">
         <v>10000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="320"/>
+      <c r="K5" s="319" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="319"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17376,132 +17397,132 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="310" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="310"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="277" t="s">
+      <c r="A10" s="310" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
+      <c r="B10" s="310"/>
+      <c r="C10" s="310"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
+      <c r="O10" s="311"/>
+      <c r="P10" s="311"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="286" t="s">
+      <c r="A12" s="312" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="287"/>
-      <c r="C12" s="288"/>
+      <c r="B12" s="313"/>
+      <c r="C12" s="314"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="289"/>
-      <c r="J12" s="289"/>
-      <c r="K12" s="289"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
+      <c r="I12" s="315"/>
+      <c r="J12" s="315"/>
+      <c r="K12" s="315"/>
+      <c r="M12" s="315"/>
+      <c r="N12" s="315"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="281" t="s">
+      <c r="A13" s="308" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="282"/>
+      <c r="B13" s="309"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
+      <c r="E13" s="303"/>
+      <c r="F13" s="303"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
+      <c r="I13" s="303"/>
+      <c r="J13" s="303"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="290" t="s">
+      <c r="A14" s="306" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="291"/>
+      <c r="B14" s="307"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
+      <c r="E14" s="303"/>
+      <c r="F14" s="303"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
+      <c r="I14" s="303"/>
+      <c r="J14" s="303"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="278"/>
+      <c r="M14" s="303"/>
+      <c r="N14" s="303"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="290" t="s">
+      <c r="A15" s="306" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="291"/>
+      <c r="B15" s="307"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
+      <c r="E15" s="303"/>
+      <c r="F15" s="303"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
+      <c r="M15" s="303"/>
+      <c r="N15" s="303"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="290" t="s">
+      <c r="A16" s="306" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="291"/>
+      <c r="B16" s="307"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
+      <c r="I16" s="303"/>
+      <c r="J16" s="303"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
+      <c r="M16" s="303"/>
+      <c r="N16" s="303"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="292" t="s">
+      <c r="A17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="293"/>
+      <c r="B17" s="302"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
+      <c r="E17" s="303"/>
+      <c r="F17" s="303"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="278"/>
-      <c r="N17" s="278"/>
+      <c r="M17" s="303"/>
+      <c r="N17" s="303"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
         <v>10.656436487638533</v>
       </c>
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
+      <c r="M18" s="303"/>
+      <c r="N18" s="303"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L19">
@@ -17520,28 +17541,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="279"/>
+      <c r="C21" s="304"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="279"/>
-      <c r="F21" s="279"/>
-      <c r="G21" s="279"/>
-      <c r="H21" s="279"/>
+      <c r="E21" s="304"/>
+      <c r="F21" s="304"/>
+      <c r="G21" s="304"/>
+      <c r="H21" s="304"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="279"/>
+      <c r="C22" s="304"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="279"/>
+      <c r="E22" s="304"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="304"/>
+      <c r="H22" s="304"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="280"/>
+      <c r="C23" s="305"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="280"/>
-      <c r="F23" s="280"/>
-      <c r="G23" s="280"/>
-      <c r="H23" s="280"/>
+      <c r="E23" s="305"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="305"/>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -17613,11 +17634,11 @@
       </c>
       <c r="J25" s="179">
         <f>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</f>
-        <v>10000</v>
+        <v>9651.1932861264104</v>
       </c>
       <c r="K25" s="180">
         <f>table1713[[#This Row],[Total GSM]]/$B$37</f>
-        <v>1</v>
+        <v>0.96511932861264105</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -17629,10 +17650,10 @@
       </c>
       <c r="C26" s="173">
         <f>VLOOKUP(B26,Material[],3,FALSE)</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D26" s="174">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="E26" s="175">
         <f>VLOOKUP(B26,Material[],2,FALSE)</f>
@@ -17640,27 +17661,27 @@
       </c>
       <c r="F26" s="175">
         <f>IF(A26="Substrate",D26*E26,C26*D26)</f>
-        <v>0</v>
+        <v>1.9949999999999999</v>
       </c>
       <c r="G26" s="176">
         <f>VLOOKUP(B26,Material[],4,FALSE)</f>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H26" s="177">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="178">
         <f>(IF(A26="Substrate",(F26*G26)/1000,(D26*G26)/1000))*(1+table1713[[#This Row],[Waste
 %]])</f>
-        <v>0</v>
+        <v>2.622E-2</v>
       </c>
       <c r="J26" s="179">
         <f>IF(A26="Substrate",(($I$36*F26)/$B$37)*(1+H26),(($I$36*D26)/$B$37)*(1+H26))</f>
-        <v>0</v>
+        <v>996.59061106740103</v>
       </c>
       <c r="K26" s="180">
         <f>table1713[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0</v>
+        <v>3.4880671387359036E-2</v>
       </c>
       <c r="M26" s="101"/>
     </row>
@@ -17717,12 +17738,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="294" t="s">
+      <c r="A31" s="298" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="295"/>
-      <c r="C31" s="295"/>
-      <c r="D31" s="295"/>
+      <c r="B31" s="299"/>
+      <c r="C31" s="299"/>
+      <c r="D31" s="299"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17736,13 +17757,13 @@
       <c r="H31" s="62"/>
       <c r="I31" s="63">
         <f>((SUMIFS(table1713[Total GSM],table1713[Type],"ink")+SUMIFS(table1713[Total GSM],table1713[Material],"Solvent Base"))/$F$31)*G31/1000</f>
-        <v>0</v>
+        <v>2.9924999999999995E-3</v>
       </c>
       <c r="J31" s="125">
         <f>(SUMIFS(table1713[Est.
 Required Kgs],table1713[Type], "Ink") + SUMIFS(table1713[Est.
 Required Kgs],table1713[Material], "Solvent Base"))*$F$31</f>
-        <v>0</v>
+        <v>996.59061106740103</v>
       </c>
       <c r="K31" s="64"/>
     </row>
@@ -17784,21 +17805,21 @@
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
-        <v>0.92</v>
-      </c>
-      <c r="C35" s="296" t="s">
+        <v>0.92257440116138401</v>
+      </c>
+      <c r="C35" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="296"/>
+      <c r="D35" s="294"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
-        <v>724.63768115942025</v>
-      </c>
-      <c r="F35" s="296" t="s">
+        <v>699.36183232800067</v>
+      </c>
+      <c r="F35" s="294" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="296"/>
-      <c r="H35" s="296"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -17810,21 +17831,21 @@
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
-        <v>60</v>
-      </c>
-      <c r="C36" s="296" t="s">
+        <v>61.994999999999997</v>
+      </c>
+      <c r="C36" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="296"/>
+      <c r="D36" s="294"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
-        <v>1.3800000000000001</v>
-      </c>
-      <c r="F36" s="296" t="s">
+        <v>1.429875</v>
+      </c>
+      <c r="F36" s="294" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="296"/>
-      <c r="H36" s="296"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -17847,24 +17868,24 @@
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F30)</f>
-        <v>55.2</v>
-      </c>
-      <c r="C37" s="353" t="s">
+        <v>57.195</v>
+      </c>
+      <c r="C37" s="300" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="353"/>
+      <c r="D37" s="300"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
-        <v>18.115942028985508</v>
-      </c>
-      <c r="F37" s="296" t="s">
+        <v>17.484045808200019</v>
+      </c>
+      <c r="F37" s="294" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="296"/>
-      <c r="H37" s="296"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
-        <v>7246.3768115942021</v>
+        <v>6993.6183232800067</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -17873,34 +17894,34 @@
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
-        <v>9.3840000000000007E-2</v>
-      </c>
-      <c r="C38" s="296" t="s">
+        <v>0.1230525</v>
+      </c>
+      <c r="C38" s="294" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="296"/>
+      <c r="D38" s="294"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
-        <v>17.760727479397556</v>
-      </c>
-      <c r="F38" s="296" t="s">
+        <v>17.141221380588252</v>
+      </c>
+      <c r="F38" s="294" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="296"/>
-      <c r="H38" s="296"/>
+      <c r="G38" s="294"/>
+      <c r="H38" s="294"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
-        <v>177607.27479397555</v>
+        <v>171412.21380588252</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="296" t="s">
+      <c r="C39" s="294" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="296"/>
+      <c r="D39" s="294"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
-        <v>72.463768115942031</v>
+        <v>69.936183232800076</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -17954,11 +17975,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="313" t="s">
+      <c r="A44" s="295" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="314"/>
-      <c r="C44" s="315"/>
+      <c r="B44" s="296"/>
+      <c r="C44" s="297"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -17988,11 +18009,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="316" t="s">
+      <c r="A46" s="290" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="316"/>
-      <c r="C46" s="316"/>
+      <c r="B46" s="290"/>
+      <c r="C46" s="290"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18007,14 +18028,14 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="316" t="s">
+      <c r="A47" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="316"/>
-      <c r="C47" s="316"/>
+      <c r="B47" s="290"/>
+      <c r="C47" s="290"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
-        <v>59.435414422146863</v>
+        <v>59.60173029162047</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -18027,14 +18048,14 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="316" t="s">
+      <c r="A48" s="290" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="316"/>
-      <c r="C48" s="316"/>
+      <c r="B48" s="290"/>
+      <c r="C48" s="290"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
-        <v>4306.914088561367</v>
+        <v>4168.3175306666999</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -18047,11 +18068,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="316" t="s">
+      <c r="A49" s="290" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="316"/>
-      <c r="C49" s="316"/>
+      <c r="B49" s="290"/>
+      <c r="C49" s="290"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18067,14 +18088,14 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="316" t="s">
+      <c r="A50" s="290" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="316"/>
-      <c r="C50" s="316"/>
+      <c r="B50" s="290"/>
+      <c r="C50" s="290"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
-        <v>43069.14088561367</v>
+        <v>41683.175306666992</v>
       </c>
       <c r="E50" s="82"/>
       <c r="F50" s="82"/>
@@ -18102,11 +18123,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="316" t="s">
+      <c r="A52" s="290" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="316"/>
-      <c r="C52" s="316"/>
+      <c r="B52" s="290"/>
+      <c r="C52" s="290"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18121,14 +18142,14 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="316" t="s">
+      <c r="A53" s="290" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="316"/>
-      <c r="C53" s="316"/>
+      <c r="B53" s="290"/>
+      <c r="C53" s="290"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
-        <v>663.79739676972963</v>
+        <v>662.93579768320956</v>
       </c>
       <c r="E53" s="82"/>
       <c r="F53" s="82"/>
@@ -18262,18 +18283,18 @@
         <f>IF(A60=TRUE, (D60+(SUMIFS(table1713[Est.
 Required Kgs], table1713[Material], "LDPE Transparent") + SUMIFS(table1713[Est.
 Required Kgs], table1713[Material], "LDPE White"))/C60), "")</f>
-        <v>15.285714285714286</v>
+        <v>14.787418980180586</v>
       </c>
       <c r="F60" s="204">
         <v>300</v>
       </c>
       <c r="G60" s="207">
         <f>IFERROR(F60*E60,"")</f>
-        <v>4585.7142857142862</v>
-      </c>
-      <c r="H60" s="310">
+        <v>4436.2256940541756</v>
+      </c>
+      <c r="H60" s="291">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
-        <v>14420.065900756443</v>
+        <v>13971.149361338501</v>
       </c>
       <c r="I60" s="82"/>
       <c r="J60" s="82"/>
@@ -18296,16 +18317,16 @@
       </c>
       <c r="E61" s="106">
         <f t="shared" ref="E61:E66" si="0">IF(A61=TRUE, D61+(OQM/C61/60),"")</f>
-        <v>14.840484986265038</v>
+        <v>14.427480920392167</v>
       </c>
       <c r="F61" s="205">
         <v>300</v>
       </c>
       <c r="G61" s="208">
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
-        <v>4452.1454958795111</v>
-      </c>
-      <c r="H61" s="311"/>
+        <v>4328.2442761176499</v>
+      </c>
+      <c r="H61" s="292"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18327,16 +18348,16 @@
       </c>
       <c r="E62" s="106">
         <f t="shared" si="0"/>
-        <v>6.4202424931325188</v>
+        <v>6.2137404601960835</v>
       </c>
       <c r="F62" s="205">
         <v>50</v>
       </c>
       <c r="G62" s="208">
         <f t="shared" si="1"/>
-        <v>321.01212465662593</v>
-      </c>
-      <c r="H62" s="311"/>
+        <v>310.68702300980419</v>
+      </c>
+      <c r="H62" s="292"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18358,16 +18379,16 @@
       </c>
       <c r="E63" s="106">
         <f t="shared" si="0"/>
-        <v>15.800606232831296</v>
+        <v>15.28435115049021</v>
       </c>
       <c r="F63" s="205">
         <v>100</v>
       </c>
       <c r="G63" s="208">
         <f t="shared" si="1"/>
-        <v>1580.0606232831296</v>
-      </c>
-      <c r="H63" s="311"/>
+        <v>1528.4351150490211</v>
+      </c>
+      <c r="H63" s="292"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18389,16 +18410,16 @@
       </c>
       <c r="E64" s="106">
         <f t="shared" si="0"/>
-        <v>15.800606232831296</v>
+        <v>15.28435115049021</v>
       </c>
       <c r="F64" s="205">
         <v>100</v>
       </c>
       <c r="G64" s="208">
         <f t="shared" si="1"/>
-        <v>1580.0606232831296</v>
-      </c>
-      <c r="H64" s="311"/>
+        <v>1528.4351150490211</v>
+      </c>
+      <c r="H64" s="292"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18420,16 +18441,16 @@
       </c>
       <c r="E65" s="106">
         <f t="shared" si="0"/>
-        <v>15.800606232831296</v>
+        <v>15.28435115049021</v>
       </c>
       <c r="F65" s="205">
         <v>100</v>
       </c>
       <c r="G65" s="208">
         <f t="shared" si="1"/>
-        <v>1580.0606232831296</v>
-      </c>
-      <c r="H65" s="311"/>
+        <v>1528.4351150490211</v>
+      </c>
+      <c r="H65" s="292"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18451,16 +18472,16 @@
       </c>
       <c r="E66" s="106">
         <f t="shared" si="0"/>
-        <v>6.4202424931325188</v>
+        <v>6.2137404601960835</v>
       </c>
       <c r="F66" s="205">
         <v>50</v>
       </c>
       <c r="G66" s="208">
         <f t="shared" si="1"/>
-        <v>321.01212465662593</v>
-      </c>
-      <c r="H66" s="311"/>
+        <v>310.68702300980419</v>
+      </c>
+      <c r="H66" s="292"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18490,7 +18511,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="311"/>
+      <c r="H67" s="292"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18520,7 +18541,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="311"/>
+      <c r="H68" s="292"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18550,7 +18571,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="312"/>
+      <c r="H69" s="293"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18569,7 +18590,7 @@
       </c>
       <c r="H70" s="137">
         <f>H60/OQKG</f>
-        <v>1.4420065900756442</v>
+        <v>1.3971149361338502</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -18610,23 +18631,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="300"/>
-      <c r="C73" s="301" t="s">
+      <c r="B73" s="281"/>
+      <c r="C73" s="282" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="303" t="s">
+      <c r="E73" s="284" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="305" t="s">
+      <c r="F73" s="286" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="305" t="s">
+      <c r="G73" s="286" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="307" t="s">
+      <c r="H73" s="288" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18639,15 +18660,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="300"/>
-      <c r="C74" s="302"/>
+      <c r="B74" s="281"/>
+      <c r="C74" s="283"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="304"/>
-      <c r="F74" s="306"/>
-      <c r="G74" s="306"/>
-      <c r="H74" s="308"/>
+      <c r="E74" s="285"/>
+      <c r="F74" s="287"/>
+      <c r="G74" s="287"/>
+      <c r="H74" s="289"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -18663,11 +18684,11 @@
       </c>
       <c r="C75" s="183">
         <f>(B38/B37*1000)</f>
-        <v>1.7000000000000002</v>
+        <v>2.1514555468135326</v>
       </c>
       <c r="D75" s="183">
         <f>C75*D74</f>
-        <v>0.51</v>
+        <v>0.64543666404405975</v>
       </c>
       <c r="E75" s="184">
         <v>0.1</v>
@@ -18677,11 +18698,11 @@
       </c>
       <c r="G75" s="185">
         <f>H70</f>
-        <v>1.4420065900756442</v>
+        <v>1.3971149361338502</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>3.9520065900756443</v>
+        <v>4.4940071469914429</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -18698,27 +18719,27 @@
       </c>
       <c r="C76" s="91">
         <f>(C75/$E$35)*1000</f>
-        <v>2.3460000000000005</v>
+        <v>3.0763125000000002</v>
       </c>
       <c r="D76" s="91">
         <f>(D75/$E$35)*1000</f>
-        <v>0.70380000000000009</v>
+        <v>0.92289374999999996</v>
       </c>
       <c r="E76" s="91">
         <f>(E75/$E$35)*1000</f>
-        <v>0.13800000000000001</v>
+        <v>0.14298750000000002</v>
       </c>
       <c r="F76" s="91">
         <f>(F75/$E$35)*1000</f>
-        <v>0.27600000000000002</v>
+        <v>0.28597500000000003</v>
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
-        <v>1.9899690943043893</v>
+        <v>1.9976997193043891</v>
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>5.4537690943043904</v>
+        <v>6.4258684693043895</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -18735,27 +18756,27 @@
       </c>
       <c r="C77" s="92">
         <f>(C75/$E$37)</f>
-        <v>9.3840000000000007E-2</v>
+        <v>0.12305249999999998</v>
       </c>
       <c r="D77" s="92">
         <f t="shared" ref="D77:G77" si="2">(D75/$E$37)</f>
-        <v>2.8152E-2</v>
+        <v>3.6915749999999997E-2</v>
       </c>
       <c r="E77" s="92">
         <f t="shared" si="2"/>
-        <v>5.5199999999999997E-3</v>
+        <v>5.7194999999999998E-3</v>
       </c>
       <c r="F77" s="92">
         <f t="shared" si="2"/>
-        <v>1.1039999999999999E-2</v>
+        <v>1.1439E-2</v>
       </c>
       <c r="G77" s="92">
         <f t="shared" si="2"/>
-        <v>7.9598763772175563E-2</v>
+        <v>7.9907988772175559E-2</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.21815076377217557</v>
+        <v>0.25703473877217553</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -18772,27 +18793,27 @@
       </c>
       <c r="C78" s="92">
         <f>(C75/$E$39)</f>
-        <v>2.3460000000000002E-2</v>
+        <v>3.0763124999999995E-2</v>
       </c>
       <c r="D78" s="92">
         <f>(D75/$E$39)</f>
-        <v>7.038E-3</v>
+        <v>9.2289374999999993E-3</v>
       </c>
       <c r="E78" s="92">
         <f>(E75/$E$39)</f>
-        <v>1.3799999999999999E-3</v>
+        <v>1.4298749999999999E-3</v>
       </c>
       <c r="F78" s="92">
         <f>(F75/$E$39)</f>
-        <v>2.7599999999999999E-3</v>
+        <v>2.8597499999999999E-3</v>
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>1.9899690943043891E-2</v>
+        <v>1.997699719304389E-2</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>5.4537690943043893E-2</v>
+        <v>6.4258684693043883E-2</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -18808,27 +18829,27 @@
       </c>
       <c r="C79" s="191">
         <f>C78*500</f>
-        <v>11.73</v>
+        <v>15.381562499999998</v>
       </c>
       <c r="D79" s="191">
         <f>D78*500</f>
-        <v>3.5190000000000001</v>
+        <v>4.6144687499999995</v>
       </c>
       <c r="E79" s="191">
         <f t="shared" ref="E79:G79" si="3">E78*500</f>
-        <v>0.69</v>
+        <v>0.7149375</v>
       </c>
       <c r="F79" s="191">
         <f t="shared" si="3"/>
-        <v>1.38</v>
+        <v>1.429875</v>
       </c>
       <c r="G79" s="191">
         <f t="shared" si="3"/>
-        <v>9.9498454715219449</v>
+        <v>9.9884985965219446</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>27.268845471521942</v>
+        <v>32.129342346521945</v>
       </c>
       <c r="I79" s="220"/>
       <c r="J79" s="221"/>
@@ -18878,9 +18899,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="299"/>
-      <c r="I82" s="299"/>
-      <c r="J82" s="299"/>
+      <c r="H82" s="275"/>
+      <c r="I82" s="275"/>
+      <c r="J82" s="275"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -18888,19 +18909,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="298" t="s">
+      <c r="B83" s="276" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="298"/>
-      <c r="D83" s="298"/>
-      <c r="E83" s="298"/>
-      <c r="F83" s="298"/>
-      <c r="G83" s="298"/>
-      <c r="H83" s="298"/>
-      <c r="I83" s="298"/>
-      <c r="J83" s="298"/>
-      <c r="K83" s="298"/>
-      <c r="L83" s="298"/>
+      <c r="C83" s="276"/>
+      <c r="D83" s="276"/>
+      <c r="E83" s="276"/>
+      <c r="F83" s="276"/>
+      <c r="G83" s="276"/>
+      <c r="H83" s="276"/>
+      <c r="I83" s="276"/>
+      <c r="J83" s="276"/>
+      <c r="K83" s="276"/>
+      <c r="L83" s="276"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -18985,11 +19006,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="309"/>
-      <c r="I88" s="309"/>
+      <c r="H88" s="277"/>
+      <c r="I88" s="277"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="309"/>
-      <c r="L88" s="309"/>
+      <c r="K88" s="277"/>
+      <c r="L88" s="277"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19045,7 +19066,7 @@
       </c>
       <c r="F91" s="163">
         <f>IFERROR(E91/$E$105,"")</f>
-        <v>0.44021325209444023</v>
+        <v>0.43920972644376899</v>
       </c>
       <c r="G91" s="10"/>
       <c r="M91" s="41"/>
@@ -19065,27 +19086,27 @@
       </c>
       <c r="D92" s="142">
         <f t="shared" si="5"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E92" s="147">
         <f t="shared" ref="E92:E104" si="6">IFERROR(D92*C92,"")</f>
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="F92" s="163">
         <f t="shared" ref="F92:F104" si="7">IFERROR(E92/$E$105,"")</f>
-        <v>0.10281797410510282</v>
+        <v>0.10486322188449848</v>
       </c>
       <c r="G92" s="10"/>
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="278" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="278"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>3.9520065900756443</v>
+        <v>4.4940071469914429</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -19142,10 +19163,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="279" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
+      <c r="U94" s="280"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19172,19 +19193,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>3.1420065900756446</v>
+        <v>3.5485704829473828</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.79504082760537709</v>
-      </c>
-      <c r="T95" s="269">
+        <v>0.7896227947307578</v>
+      </c>
+      <c r="T95" s="271">
         <f>R96-R95</f>
-        <v>-1.5977208757899304</v>
-      </c>
-      <c r="U95" s="271">
+        <v>-2.0028561972330969</v>
+      </c>
+      <c r="U95" s="273">
         <f>(R96-R95)/R95</f>
-        <v>-0.50850334968631139</v>
+        <v>-0.56441212224973436</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
@@ -19212,14 +19233,14 @@
       </c>
       <c r="R96" s="175">
         <f>E106+E122</f>
-        <v>1.5442857142857143</v>
+        <v>1.5457142857142858</v>
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>0.39075990363066565</v>
-      </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
+        <v>0.34395011738000447</v>
+      </c>
+      <c r="T96" s="272"/>
+      <c r="U96" s="273"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -19245,11 +19266,11 @@
       </c>
       <c r="R97" s="217">
         <f>S92-R95</f>
-        <v>0.80999999999999961</v>
+        <v>0.94543666404406013</v>
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.20495917239462286</v>
+        <v>0.21037720526924217</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -19276,11 +19297,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>2.4077208757899298</v>
+        <v>2.9482928612771571</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>0.60924009636933429</v>
+        <v>0.65604988261999553</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -19400,14 +19421,14 @@
       </c>
       <c r="F104" s="163">
         <f t="shared" si="7"/>
-        <v>0.45696877380045697</v>
+        <v>0.45592705167173253</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
-        <v>6565</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
@@ -19417,7 +19438,7 @@
       </c>
       <c r="E106" s="140">
         <f>E105/C85</f>
-        <v>0.62523809523809526</v>
+        <v>0.62666666666666671</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
@@ -19427,7 +19448,7 @@
       </c>
       <c r="E107" s="159">
         <f>(E106-C75)/C75</f>
-        <v>-0.63221288515406171</v>
+        <v>-0.70872432498323878</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
@@ -19672,29 +19693,92 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="297" t="s">
+      <c r="B122" s="274" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="297"/>
-      <c r="D122" s="297"/>
+      <c r="C122" s="274"/>
+      <c r="D122" s="274"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="297" t="s">
+      <c r="B123" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="297"/>
-      <c r="D123" s="297"/>
+      <c r="C123" s="274"/>
+      <c r="D123" s="274"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>-0.36266059713402005</v>
+        <v>-0.34218180961486055</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
     <mergeCell ref="B122:D122"/>
@@ -19705,69 +19789,6 @@
     <mergeCell ref="K88:L88"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -19809,7 +19830,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64514EA5-211E-42DB-B908-1C8FEC7CF710}">
-  <dimension ref="G7:N17"/>
+  <dimension ref="G7:T25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="5" customWidth="1"/>
@@ -19820,94 +19841,179 @@
     <col min="12" max="12" width="7.21875" customWidth="1"/>
     <col min="13" max="13" width="6.33203125" customWidth="1"/>
     <col min="14" max="14" width="5.6640625" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="7:14" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="G7" s="350" t="s">
+      <c r="G7" s="270" t="s">
         <v>325</v>
       </c>
-      <c r="H7" s="350" t="s">
+      <c r="H7" s="270" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="350" t="s">
+      <c r="I7" s="270" t="s">
         <v>326</v>
       </c>
-      <c r="J7" s="350" t="s">
+      <c r="J7" s="270" t="s">
         <v>327</v>
       </c>
-      <c r="K7" s="350" t="s">
+      <c r="K7" s="270" t="s">
         <v>329</v>
       </c>
-      <c r="L7" s="350" t="s">
+      <c r="L7" s="270" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="350" t="s">
+      <c r="M7" s="270" t="s">
         <v>330</v>
       </c>
-      <c r="N7" s="350" t="s">
+      <c r="N7" s="270" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="7:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="351">
+      <c r="G8" s="352">
         <v>1</v>
       </c>
-      <c r="H8" s="352" t="s">
+      <c r="H8" s="353" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="352" t="s">
+      <c r="I8" s="353" t="s">
         <v>328</v>
       </c>
-      <c r="J8" s="352" t="s">
+      <c r="J8" s="353" t="s">
         <v>328</v>
       </c>
-      <c r="K8" s="352" t="s">
+      <c r="K8" s="353" t="s">
         <v>328</v>
       </c>
-      <c r="L8" s="352" t="s">
+      <c r="L8" s="353" t="s">
         <v>331</v>
       </c>
-      <c r="M8" s="352" t="s">
+      <c r="M8" s="353" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="352" t="s">
+      <c r="N8" s="353" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="7:14" x14ac:dyDescent="0.3">
-      <c r="G9" s="351"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="352"/>
-      <c r="K9" s="352"/>
-      <c r="L9" s="352"/>
-      <c r="M9" s="352"/>
-      <c r="N9" s="352"/>
-    </row>
-    <row r="17" spans="7:14" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="G17" s="348" t="s">
+      <c r="G9" s="352"/>
+      <c r="H9" s="353"/>
+      <c r="I9" s="353"/>
+      <c r="J9" s="353"/>
+      <c r="K9" s="353"/>
+      <c r="L9" s="353"/>
+      <c r="M9" s="353"/>
+      <c r="N9" s="353"/>
+    </row>
+    <row r="17" spans="7:20" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="G17" s="268" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="348" t="s">
+      <c r="H17" s="268" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="348" t="s">
+      <c r="I17" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="348" t="s">
+      <c r="J17" s="268" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="348" t="s">
+      <c r="K17" s="268" t="s">
         <v>17</v>
       </c>
-      <c r="L17" s="348" t="s">
+      <c r="L17" s="268" t="s">
         <v>18</v>
       </c>
-      <c r="M17" s="348" t="s">
+      <c r="M17" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="N17" s="349" t="s">
+      <c r="N17" s="269" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q20" s="354" t="s">
+        <v>326</v>
+      </c>
+      <c r="R20" s="354" t="s">
+        <v>203</v>
+      </c>
+      <c r="S20" s="354" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="354" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q21" s="355" t="s">
+        <v>238</v>
+      </c>
+      <c r="R21" s="355" t="s">
+        <v>332</v>
+      </c>
+      <c r="S21" s="355">
+        <v>0.9</v>
+      </c>
+      <c r="T21" s="355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q22" s="355" t="s">
+        <v>238</v>
+      </c>
+      <c r="R22" s="355" t="s">
+        <v>333</v>
+      </c>
+      <c r="S22" s="355">
+        <v>0.79</v>
+      </c>
+      <c r="T22" s="355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q23" s="355" t="s">
+        <v>238</v>
+      </c>
+      <c r="R23" s="355" t="s">
+        <v>334</v>
+      </c>
+      <c r="S23" s="355">
+        <v>0.79</v>
+      </c>
+      <c r="T23" s="355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q24" s="355" t="s">
+        <v>238</v>
+      </c>
+      <c r="R24" s="355" t="s">
+        <v>335</v>
+      </c>
+      <c r="S24" s="355">
+        <v>0.8</v>
+      </c>
+      <c r="T24" s="355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="7:20" x14ac:dyDescent="0.3">
+      <c r="Q25" s="355" t="s">
+        <v>238</v>
+      </c>
+      <c r="R25" s="355" t="s">
+        <v>336</v>
+      </c>
+      <c r="S25" s="355">
+        <v>0.87</v>
+      </c>
+      <c r="T25" s="355">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20854,20 +20960,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="316" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="283"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -20895,26 +21001,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="317" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="317"/>
+      <c r="C3" s="318" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="284"/>
-      <c r="E3" s="284"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="317" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="284" t="s">
+      <c r="H3" s="317"/>
+      <c r="I3" s="318" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="284"/>
-      <c r="K3" s="284"/>
-      <c r="L3" s="284"/>
+      <c r="J3" s="318"/>
+      <c r="K3" s="318"/>
+      <c r="L3" s="318"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -20939,28 +21045,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="317" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="317"/>
+      <c r="C5" s="319" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="317" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="317"/>
+      <c r="I5" s="320">
         <v>10000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="320"/>
+      <c r="K5" s="319" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="319"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -20991,128 +21097,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="310" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="310"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="277" t="s">
+      <c r="A10" s="310" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
+      <c r="B10" s="310"/>
+      <c r="C10" s="310"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
+      <c r="O10" s="311"/>
+      <c r="P10" s="311"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="286" t="s">
+      <c r="A12" s="312" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="287"/>
-      <c r="C12" s="288"/>
+      <c r="B12" s="313"/>
+      <c r="C12" s="314"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="289"/>
-      <c r="J12" s="289"/>
-      <c r="K12" s="289"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
+      <c r="I12" s="315"/>
+      <c r="J12" s="315"/>
+      <c r="K12" s="315"/>
+      <c r="M12" s="315"/>
+      <c r="N12" s="315"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="281" t="s">
+      <c r="A13" s="308" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="282"/>
+      <c r="B13" s="309"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
+      <c r="E13" s="303"/>
+      <c r="F13" s="303"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
+      <c r="I13" s="303"/>
+      <c r="J13" s="303"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="290" t="s">
+      <c r="A14" s="306" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="291"/>
+      <c r="B14" s="307"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
+      <c r="E14" s="303"/>
+      <c r="F14" s="303"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
+      <c r="I14" s="303"/>
+      <c r="J14" s="303"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="278"/>
+      <c r="M14" s="303"/>
+      <c r="N14" s="303"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="290" t="s">
+      <c r="A15" s="306" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="291"/>
+      <c r="B15" s="307"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
+      <c r="E15" s="303"/>
+      <c r="F15" s="303"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
+      <c r="M15" s="303"/>
+      <c r="N15" s="303"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="290" t="s">
+      <c r="A16" s="306" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="291"/>
+      <c r="B16" s="307"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
+      <c r="I16" s="303"/>
+      <c r="J16" s="303"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
+      <c r="M16" s="303"/>
+      <c r="N16" s="303"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="292" t="s">
+      <c r="A17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="293"/>
+      <c r="B17" s="302"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
+      <c r="E17" s="303"/>
+      <c r="F17" s="303"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="278"/>
-      <c r="N17" s="278"/>
+      <c r="M17" s="303"/>
+      <c r="N17" s="303"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
+      <c r="M18" s="303"/>
+      <c r="N18" s="303"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21123,28 +21229,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="279"/>
+      <c r="C21" s="304"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="279"/>
-      <c r="F21" s="279"/>
-      <c r="G21" s="279"/>
-      <c r="H21" s="279"/>
+      <c r="E21" s="304"/>
+      <c r="F21" s="304"/>
+      <c r="G21" s="304"/>
+      <c r="H21" s="304"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="279"/>
+      <c r="C22" s="304"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="279"/>
+      <c r="E22" s="304"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="304"/>
+      <c r="H22" s="304"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="280"/>
+      <c r="C23" s="305"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="280"/>
-      <c r="F23" s="280"/>
-      <c r="G23" s="280"/>
-      <c r="H23" s="280"/>
+      <c r="E23" s="305"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="305"/>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21217,11 +21323,11 @@
       </c>
       <c r="J25" s="179">
         <f>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</f>
-        <v>1609.7560975609756</v>
+        <v>1598.6159169550172</v>
       </c>
       <c r="K25" s="180">
         <f>table17[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.14634146341463414</v>
+        <v>0.14532871972318337</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -21233,7 +21339,7 @@
       </c>
       <c r="C26" s="173">
         <f>VLOOKUP(B26,Material[],3,FALSE)</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D26" s="174">
         <v>8</v>
@@ -21244,11 +21350,11 @@
       </c>
       <c r="F26" s="175">
         <f>IF(A26="Substrate",D26*E26,C26*D26)</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G26" s="176">
         <f>VLOOKUP(B26,Material[],4,FALSE)</f>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H26" s="177">
         <v>0.1</v>
@@ -21256,15 +21362,15 @@
       <c r="I26" s="178">
         <f>(IF(A26="Substrate",(F26*G26)/1000,(D26*G26)/1000))*(1+table17[[#This Row],[Waste
 %]])</f>
-        <v>3.9600000000000003E-2</v>
+        <v>4.0480000000000002E-2</v>
       </c>
       <c r="J26" s="179">
         <f>IF(A26="Substrate",(($I$36*F26)/$B$37)*(1+H26),(($I$36*D26)/$B$37)*(1+H26))</f>
-        <v>766.55052264808376</v>
+        <v>761.24567474048456</v>
       </c>
       <c r="K26" s="180">
         <f>table17[[#This Row],[Total GSM]]/$B$37</f>
-        <v>1.7421602787456445E-2</v>
+        <v>2.4221453287197232E-2</v>
       </c>
       <c r="M26" s="101"/>
     </row>
@@ -21287,7 +21393,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="175">
-        <f t="shared" ref="F26:F28" si="0">IF(A27="Substrate",D27*E27,C27*D27)</f>
+        <f t="shared" ref="F27:F28" si="0">IF(A27="Substrate",D27*E27,C27*D27)</f>
         <v>3</v>
       </c>
       <c r="G27" s="176">
@@ -21304,11 +21410,11 @@
       </c>
       <c r="J27" s="179">
         <f>IF(A27="Substrate",(($I$36*F27)/$B$37)*(1+H27),(($I$36*D27)/$B$37)*(1+H27))</f>
-        <v>574.91289198606285</v>
+        <v>570.93425605536333</v>
       </c>
       <c r="K27" s="180">
         <f>table17[[#This Row],[Total GSM]]/$B$37</f>
-        <v>2.6132404181184669E-2</v>
+        <v>2.5951557093425608E-2</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -21347,11 +21453,11 @@
       </c>
       <c r="J28" s="179">
         <f>IF(A28="Substrate",(($I$36*F28)/$B$37)*(1+H28),(($I$36*D28)/$B$37)*(1+H28))</f>
-        <v>8911.1498257839721</v>
+        <v>8849.4809688581317</v>
       </c>
       <c r="K28" s="180">
         <f>table17[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.81010452961672474</v>
+        <v>0.80449826989619377</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -21385,12 +21491,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="294" t="s">
+      <c r="A31" s="298" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="295"/>
-      <c r="C31" s="295"/>
-      <c r="D31" s="295"/>
+      <c r="B31" s="299"/>
+      <c r="C31" s="299"/>
+      <c r="D31" s="299"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21404,13 +21510,13 @@
       <c r="H31" s="62"/>
       <c r="I31" s="63">
         <f>((SUMIFS(table17[Total GSM],table17[Type],"ink")+SUMIFS(table17[Total GSM],table17[Material],"Solvent Base"))/$F$31)*G31/1000</f>
-        <v>5.0000000000000001E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="J31" s="125">
         <f>(SUMIFS(table17[Est.
 Required Kgs],table17[Type], "Ink") + SUMIFS(table17[Est.
 Required Kgs],table17[Material], "Solvent Base"))*$F$31</f>
-        <v>2012.1951219512198</v>
+        <v>1998.2698961937717</v>
       </c>
       <c r="K31" s="64"/>
     </row>
@@ -21451,21 +21557,21 @@
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
-        <v>0.98119658119658115</v>
-      </c>
-      <c r="C35" s="296" t="s">
+        <v>0.9813242784380305</v>
+      </c>
+      <c r="C35" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="296"/>
+      <c r="D35" s="294"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
-        <v>348.43205574912889</v>
-      </c>
-      <c r="F35" s="296" t="s">
+        <v>346.02076124567475</v>
+      </c>
+      <c r="F35" s="294" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="296"/>
-      <c r="H35" s="296"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21477,21 +21583,21 @@
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
-        <v>117</v>
-      </c>
-      <c r="C36" s="296" t="s">
+        <v>117.8</v>
+      </c>
+      <c r="C36" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="296"/>
+      <c r="D36" s="294"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
-        <v>2.87</v>
-      </c>
-      <c r="F36" s="296" t="s">
+        <v>2.89</v>
+      </c>
+      <c r="F36" s="294" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="296"/>
-      <c r="H36" s="296"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21514,24 +21620,24 @@
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F30)</f>
-        <v>114.8</v>
-      </c>
-      <c r="C37" s="296" t="s">
+        <v>115.6</v>
+      </c>
+      <c r="C37" s="294" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="296"/>
+      <c r="D37" s="294"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
-        <v>8.7108013937282234</v>
-      </c>
-      <c r="F37" s="296" t="s">
+        <v>8.6505190311418687</v>
+      </c>
+      <c r="F37" s="294" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="296"/>
-      <c r="H37" s="296"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
-        <v>3484.320557491289</v>
+        <v>3460.2076124567475</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -21540,34 +21646,34 @@
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
-        <v>0.22230500000000003</v>
-      </c>
-      <c r="C38" s="296" t="s">
+        <v>0.22398500000000002</v>
+      </c>
+      <c r="C38" s="294" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="296"/>
+      <c r="D38" s="294"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
-        <v>8.5400013664002188</v>
-      </c>
-      <c r="F38" s="296" t="s">
+        <v>8.4809010109234002</v>
+      </c>
+      <c r="F38" s="294" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="296"/>
-      <c r="H38" s="296"/>
+      <c r="G38" s="294"/>
+      <c r="H38" s="294"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
-        <v>85400.013664002181</v>
+        <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="296" t="s">
+      <c r="C39" s="294" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="296"/>
+      <c r="D39" s="294"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
-        <v>34.843205574912893</v>
+        <v>34.602076124567475</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -21621,11 +21727,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="313" t="s">
+      <c r="A44" s="295" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="314"/>
-      <c r="C44" s="315"/>
+      <c r="B44" s="296"/>
+      <c r="C44" s="297"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -21655,11 +21761,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="316" t="s">
+      <c r="A46" s="290" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="316"/>
-      <c r="C46" s="316"/>
+      <c r="B46" s="290"/>
+      <c r="C46" s="290"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -21674,14 +21780,14 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="316" t="s">
+      <c r="A47" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="316"/>
-      <c r="C47" s="316"/>
+      <c r="B47" s="290"/>
+      <c r="C47" s="290"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
-        <v>63.388940688057041</v>
+        <v>63.397190403781075</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -21694,14 +21800,14 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="316" t="s">
+      <c r="A48" s="290" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="316"/>
-      <c r="C48" s="316"/>
+      <c r="B48" s="290"/>
+      <c r="C48" s="290"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
-        <v>2208.673891569932</v>
+        <v>2193.6744084353313</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -21714,11 +21820,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="316" t="s">
+      <c r="A49" s="290" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="316"/>
-      <c r="C49" s="316"/>
+      <c r="B49" s="290"/>
+      <c r="C49" s="290"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -21734,14 +21840,14 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="316" t="s">
+      <c r="A50" s="290" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="316"/>
-      <c r="C50" s="316"/>
+      <c r="B50" s="290"/>
+      <c r="C50" s="290"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
-        <v>22086.738915699316</v>
+        <v>21936.744084353315</v>
       </c>
       <c r="E50" s="82"/>
       <c r="F50" s="82"/>
@@ -21769,11 +21875,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="316" t="s">
+      <c r="A52" s="290" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="316"/>
-      <c r="C52" s="316"/>
+      <c r="B52" s="290"/>
+      <c r="C52" s="290"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -21788,14 +21894,14 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="316" t="s">
+      <c r="A53" s="290" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="316"/>
-      <c r="C53" s="316"/>
+      <c r="B53" s="290"/>
+      <c r="C53" s="290"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
-        <v>644.26494805034054</v>
+        <v>644.22615683819515</v>
       </c>
       <c r="E53" s="82"/>
       <c r="F53" s="82"/>
@@ -21929,18 +22035,18 @@
         <f>IF(A60=TRUE, (D60+(SUMIFS(table17[Est.
 Required Kgs], table17[Material], "LDPE Transparent") + SUMIFS(table17[Est.
 Required Kgs], table17[Material], "LDPE White"))/C60), "")</f>
-        <v>13.730214036834246</v>
+        <v>13.642115669797331</v>
       </c>
       <c r="F60" s="204">
         <v>300</v>
       </c>
       <c r="G60" s="207">
         <f>IFERROR(F60*E60,"")</f>
-        <v>4119.064211050274</v>
-      </c>
-      <c r="H60" s="310">
+        <v>4092.6347009391993</v>
+      </c>
+      <c r="H60" s="291">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
-        <v>9496.7315381437129</v>
+        <v>9441.736856218844</v>
       </c>
       <c r="I60" s="82"/>
       <c r="J60" s="82"/>
@@ -21963,16 +22069,16 @@
       </c>
       <c r="E61" s="106">
         <f t="shared" ref="E61:E66" si="1">IF(A61=TRUE, D61+(OQM/C61/60),"")</f>
-        <v>8.6933342442668113</v>
+        <v>8.6539340072822668</v>
       </c>
       <c r="F61" s="205">
         <v>300</v>
       </c>
       <c r="G61" s="208">
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
-        <v>2608.0002732800435</v>
-      </c>
-      <c r="H61" s="311"/>
+        <v>2596.1802021846802</v>
+      </c>
+      <c r="H61" s="292"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -21994,16 +22100,16 @@
       </c>
       <c r="E62" s="106">
         <f t="shared" si="1"/>
-        <v>3.3466671221334061</v>
+        <v>3.3269670036411338</v>
       </c>
       <c r="F62" s="205">
         <v>50</v>
       </c>
       <c r="G62" s="208">
         <f t="shared" si="2"/>
-        <v>167.33335610667029</v>
-      </c>
-      <c r="H62" s="311"/>
+        <v>166.34835018205669</v>
+      </c>
+      <c r="H62" s="292"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22025,16 +22131,16 @@
       </c>
       <c r="E63" s="106">
         <f t="shared" si="1"/>
-        <v>8.1166678053335151</v>
+        <v>8.0674175091028353</v>
       </c>
       <c r="F63" s="205">
         <v>100</v>
       </c>
       <c r="G63" s="208">
         <f t="shared" si="2"/>
-        <v>811.66678053335147</v>
-      </c>
-      <c r="H63" s="311"/>
+        <v>806.74175091028349</v>
+      </c>
+      <c r="H63" s="292"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22056,16 +22162,16 @@
       </c>
       <c r="E64" s="106">
         <f t="shared" si="1"/>
-        <v>8.1166678053335151</v>
+        <v>8.0674175091028353</v>
       </c>
       <c r="F64" s="205">
         <v>100</v>
       </c>
       <c r="G64" s="208">
         <f t="shared" si="2"/>
-        <v>811.66678053335147</v>
-      </c>
-      <c r="H64" s="311"/>
+        <v>806.74175091028349</v>
+      </c>
+      <c r="H64" s="292"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22087,16 +22193,16 @@
       </c>
       <c r="E65" s="106">
         <f t="shared" si="1"/>
-        <v>8.1166678053335151</v>
+        <v>8.0674175091028353</v>
       </c>
       <c r="F65" s="205">
         <v>100</v>
       </c>
       <c r="G65" s="208">
         <f t="shared" si="2"/>
-        <v>811.66678053335147</v>
-      </c>
-      <c r="H65" s="311"/>
+        <v>806.74175091028349</v>
+      </c>
+      <c r="H65" s="292"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22118,16 +22224,16 @@
       </c>
       <c r="E66" s="106">
         <f t="shared" si="1"/>
-        <v>3.3466671221334061</v>
+        <v>3.3269670036411338</v>
       </c>
       <c r="F66" s="205">
         <v>50</v>
       </c>
       <c r="G66" s="208">
         <f t="shared" si="2"/>
-        <v>167.33335610667029</v>
-      </c>
-      <c r="H66" s="311"/>
+        <v>166.34835018205669</v>
+      </c>
+      <c r="H66" s="292"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22157,7 +22263,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="311"/>
+      <c r="H67" s="292"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22187,7 +22293,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="311"/>
+      <c r="H68" s="292"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22217,7 +22323,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="312"/>
+      <c r="H69" s="293"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22236,7 +22342,7 @@
       </c>
       <c r="H70" s="137">
         <f>H60/OQKG</f>
-        <v>0.94967315381437134</v>
+        <v>0.94417368562188442</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -22277,23 +22383,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="300"/>
-      <c r="C73" s="301" t="s">
+      <c r="B73" s="281"/>
+      <c r="C73" s="282" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="303" t="s">
+      <c r="E73" s="284" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="305" t="s">
+      <c r="F73" s="286" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="305" t="s">
+      <c r="G73" s="286" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="307" t="s">
+      <c r="H73" s="288" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22306,15 +22412,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="300"/>
-      <c r="C74" s="302"/>
+      <c r="B74" s="281"/>
+      <c r="C74" s="283"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="304"/>
-      <c r="F74" s="306"/>
-      <c r="G74" s="306"/>
-      <c r="H74" s="308"/>
+      <c r="E74" s="285"/>
+      <c r="F74" s="287"/>
+      <c r="G74" s="287"/>
+      <c r="H74" s="289"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22330,11 +22436,11 @@
       </c>
       <c r="C75" s="183">
         <f>(B38/B37*1000)</f>
-        <v>1.9364547038327529</v>
+        <v>1.9375865051903116</v>
       </c>
       <c r="D75" s="183">
         <f>C75*D74</f>
-        <v>0.58093641114982586</v>
+        <v>0.58127595155709344</v>
       </c>
       <c r="E75" s="184">
         <v>0.1</v>
@@ -22344,11 +22450,11 @@
       </c>
       <c r="G75" s="185">
         <f>H70</f>
-        <v>0.94967315381437134</v>
+        <v>0.94417368562188442</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>3.7670642687969504</v>
+        <v>3.7630361423692897</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -22365,27 +22471,27 @@
       </c>
       <c r="C76" s="91">
         <f>(C75/$E$35)*1000</f>
-        <v>5.5576250000000007</v>
+        <v>5.5996250000000005</v>
       </c>
       <c r="D76" s="91">
         <f>(D75/$E$35)*1000</f>
-        <v>1.6672875000000003</v>
+        <v>1.6798875</v>
       </c>
       <c r="E76" s="91">
         <f>(E75/$E$35)*1000</f>
-        <v>0.28700000000000003</v>
+        <v>0.28900000000000003</v>
       </c>
       <c r="F76" s="91">
         <f>(F75/$E$35)*1000</f>
-        <v>0.57400000000000007</v>
+        <v>0.57800000000000007</v>
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
-        <v>2.7255619514472462</v>
+        <v>2.7286619514472461</v>
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>10.811474451447246</v>
+        <v>10.875174451447247</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -22402,27 +22508,27 @@
       </c>
       <c r="C77" s="92">
         <f>(C75/$E$37)</f>
-        <v>0.22230500000000003</v>
+        <v>0.22398500000000002</v>
       </c>
       <c r="D77" s="92">
         <f t="shared" ref="D77:G77" si="3">(D75/$E$37)</f>
-        <v>6.6691500000000001E-2</v>
+        <v>6.7195500000000005E-2</v>
       </c>
       <c r="E77" s="92">
         <f t="shared" si="3"/>
-        <v>1.1480000000000001E-2</v>
+        <v>1.1560000000000001E-2</v>
       </c>
       <c r="F77" s="92">
         <f t="shared" si="3"/>
-        <v>2.2960000000000001E-2</v>
+        <v>2.3120000000000002E-2</v>
       </c>
       <c r="G77" s="92">
         <f t="shared" si="3"/>
-        <v>0.10902247805788982</v>
+        <v>0.10914647805788984</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.43245897805788985</v>
+        <v>0.43500697805788985</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -22439,27 +22545,27 @@
       </c>
       <c r="C78" s="92">
         <f>(C75/$E$39)</f>
-        <v>5.5576250000000008E-2</v>
+        <v>5.5996250000000004E-2</v>
       </c>
       <c r="D78" s="92">
         <f>(D75/$E$39)</f>
-        <v>1.6672875E-2</v>
+        <v>1.6798875000000001E-2</v>
       </c>
       <c r="E78" s="92">
         <f>(E75/$E$39)</f>
-        <v>2.8700000000000002E-3</v>
+        <v>2.8900000000000002E-3</v>
       </c>
       <c r="F78" s="92">
         <f>(F75/$E$39)</f>
-        <v>5.7400000000000003E-3</v>
+        <v>5.7800000000000004E-3</v>
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>2.7255619514472456E-2</v>
+        <v>2.7286619514472459E-2</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>0.10811474451447246</v>
+        <v>0.10875174451447246</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -22475,27 +22581,27 @@
       </c>
       <c r="C79" s="191">
         <f>C78*500</f>
-        <v>27.788125000000004</v>
+        <v>27.998125000000002</v>
       </c>
       <c r="D79" s="191">
         <f>D78*500</f>
-        <v>8.3364375000000006</v>
+        <v>8.3994375000000012</v>
       </c>
       <c r="E79" s="191">
         <f t="shared" ref="E79:G79" si="4">E78*500</f>
-        <v>1.4350000000000001</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="F79" s="191">
         <f t="shared" si="4"/>
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="G79" s="191">
         <f t="shared" si="4"/>
-        <v>13.627809757236228</v>
+        <v>13.64330975723623</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>54.057372257236231</v>
+        <v>54.375872257236239</v>
       </c>
       <c r="I79" s="220"/>
       <c r="J79" s="221"/>
@@ -22545,9 +22651,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="299"/>
-      <c r="I82" s="299"/>
-      <c r="J82" s="299"/>
+      <c r="H82" s="275"/>
+      <c r="I82" s="275"/>
+      <c r="J82" s="275"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22555,19 +22661,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="298" t="s">
+      <c r="B83" s="276" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="298"/>
-      <c r="D83" s="298"/>
-      <c r="E83" s="298"/>
-      <c r="F83" s="298"/>
-      <c r="G83" s="298"/>
-      <c r="H83" s="298"/>
-      <c r="I83" s="298"/>
-      <c r="J83" s="298"/>
-      <c r="K83" s="298"/>
-      <c r="L83" s="298"/>
+      <c r="C83" s="276"/>
+      <c r="D83" s="276"/>
+      <c r="E83" s="276"/>
+      <c r="F83" s="276"/>
+      <c r="G83" s="276"/>
+      <c r="H83" s="276"/>
+      <c r="I83" s="276"/>
+      <c r="J83" s="276"/>
+      <c r="K83" s="276"/>
+      <c r="L83" s="276"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -22652,11 +22758,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="309"/>
-      <c r="I88" s="309"/>
+      <c r="H88" s="277"/>
+      <c r="I88" s="277"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="309"/>
-      <c r="L88" s="309"/>
+      <c r="K88" s="277"/>
+      <c r="L88" s="277"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -22712,7 +22818,7 @@
       </c>
       <c r="F91" s="163">
         <f>IFERROR(E91/$E$105,"")</f>
-        <v>0.12829059076559296</v>
+        <v>0.12819384920884286</v>
       </c>
       <c r="G91" s="10"/>
       <c r="M91" s="41"/>
@@ -22732,27 +22838,27 @@
       </c>
       <c r="D92" s="142">
         <f t="shared" si="6"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E92" s="147">
         <f t="shared" ref="E92:E104" si="7">IFERROR(D92*C92,"")</f>
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="F92" s="163">
         <f t="shared" ref="F92:F104" si="8">IFERROR(E92/$E$105,"")</f>
-        <v>3.395927402618637E-2</v>
+        <v>3.468774743298101E-2</v>
       </c>
       <c r="G92" s="10"/>
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="278" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="278"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>3.7670642687969504</v>
+        <v>3.7630361423692897</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -22776,7 +22882,7 @@
       </c>
       <c r="F93" s="163">
         <f t="shared" si="8"/>
-        <v>0.10196586464084924</v>
+        <v>0.1018889740721656</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
@@ -22800,7 +22906,7 @@
       </c>
       <c r="F94" s="163">
         <f t="shared" si="8"/>
-        <v>0.58485416378432087</v>
+        <v>0.58441313609913659</v>
       </c>
       <c r="L94" s="43"/>
       <c r="R94" s="215" t="s">
@@ -22809,10 +22915,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="279" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
+      <c r="U94" s="280"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -22839,19 +22945,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>2.8861278576471241</v>
+        <v>2.8817601908121961</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.76614776168096488</v>
-      </c>
-      <c r="T95" s="269">
+        <v>0.76580720508248346</v>
+      </c>
+      <c r="T95" s="271">
         <f>R96-R95</f>
-        <v>-7.405642907569554E-2</v>
-      </c>
-      <c r="U95" s="271">
+        <v>-6.8260190812196253E-2</v>
+      </c>
+      <c r="U95" s="273">
         <f>(R96-R95)/R95</f>
-        <v>-2.565944155227725E-2</v>
+        <v>-2.368697819819552E-2</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
@@ -22879,14 +22985,14 @@
       </c>
       <c r="R96" s="175">
         <f>E106+E122</f>
-        <v>2.8120714285714286</v>
+        <v>2.8134999999999999</v>
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>0.74648883796970411</v>
-      </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
+        <v>0.74766754651167366</v>
+      </c>
+      <c r="T96" s="272"/>
+      <c r="U96" s="273"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -22912,11 +23018,11 @@
       </c>
       <c r="R97" s="217">
         <f>S92-R95</f>
-        <v>0.88093641114982635</v>
+        <v>0.8812759515570936</v>
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.23385223831903515</v>
+        <v>0.23419279491751652</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -22943,11 +23049,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>0.95499284022552189</v>
+        <v>0.94953614236928985</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>0.25351116203029589</v>
+        <v>0.25233245348832634</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -23067,14 +23173,14 @@
       </c>
       <c r="F104" s="163">
         <f t="shared" si="8"/>
-        <v>0.15093010678305055</v>
+        <v>0.15081629318687395</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
-        <v>19876.75</v>
+        <v>19891.75</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
@@ -23084,7 +23190,7 @@
       </c>
       <c r="E106" s="140">
         <f>E105/C85</f>
-        <v>1.8930238095238094</v>
+        <v>1.894452380952381</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
@@ -23094,7 +23200,7 @@
       </c>
       <c r="E107" s="159">
         <f>(E106-C75)/C75</f>
-        <v>-2.2428045553031666E-2</v>
+        <v>-2.2261779859833377E-2</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
@@ -23339,86 +23445,29 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="297" t="s">
+      <c r="B122" s="274" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="297"/>
-      <c r="D122" s="297"/>
+      <c r="C122" s="274"/>
+      <c r="D122" s="274"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="297" t="s">
+      <c r="B123" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="297"/>
-      <c r="D123" s="297"/>
+      <c r="C123" s="274"/>
+      <c r="D123" s="274"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>-3.2248500069465565E-2</v>
+        <v>-2.6611699687135438E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23435,6 +23484,63 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -23541,16 +23647,16 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="317" t="s">
+      <c r="W1" s="321" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="317"/>
-      <c r="Y1" s="317"/>
-      <c r="Z1" s="317"/>
-      <c r="AA1" s="317"/>
-      <c r="AB1" s="317"/>
-      <c r="AC1" s="317"/>
-      <c r="AD1" s="317"/>
+      <c r="X1" s="321"/>
+      <c r="Y1" s="321"/>
+      <c r="Z1" s="321"/>
+      <c r="AA1" s="321"/>
+      <c r="AB1" s="321"/>
+      <c r="AC1" s="321"/>
+      <c r="AD1" s="321"/>
     </row>
     <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
@@ -24088,10 +24194,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="5">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G19" s="103">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="20" spans="4:17" x14ac:dyDescent="0.3">
@@ -24319,20 +24425,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="316" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="283"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24362,26 +24468,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="317" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="317"/>
+      <c r="C3" s="318" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="284"/>
-      <c r="E3" s="284"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="317" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="284" t="s">
+      <c r="H3" s="317"/>
+      <c r="I3" s="318" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="284"/>
-      <c r="K3" s="284"/>
-      <c r="L3" s="284"/>
+      <c r="J3" s="318"/>
+      <c r="K3" s="318"/>
+      <c r="L3" s="318"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24408,28 +24514,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="317" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="317"/>
+      <c r="C5" s="319" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="317" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="317"/>
+      <c r="I5" s="320">
         <v>20000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="320"/>
+      <c r="K5" s="319" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="319"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24462,105 +24568,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="310" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="310"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="277" t="s">
+      <c r="A10" s="310" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
+      <c r="B10" s="310"/>
+      <c r="C10" s="310"/>
+      <c r="N10" s="311"/>
+      <c r="O10" s="311"/>
+      <c r="P10" s="311"/>
+      <c r="Q10" s="311"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="289"/>
-      <c r="B12" s="289"/>
-      <c r="C12" s="289"/>
-      <c r="E12" s="331" t="s">
+      <c r="A12" s="315"/>
+      <c r="B12" s="315"/>
+      <c r="C12" s="315"/>
+      <c r="E12" s="325" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="332"/>
-      <c r="G12" s="333"/>
-      <c r="I12" s="289"/>
-      <c r="J12" s="289"/>
-      <c r="K12" s="289"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
-      <c r="O12" s="289"/>
+      <c r="F12" s="326"/>
+      <c r="G12" s="327"/>
+      <c r="I12" s="315"/>
+      <c r="J12" s="315"/>
+      <c r="K12" s="315"/>
+      <c r="M12" s="315"/>
+      <c r="N12" s="315"/>
+      <c r="O12" s="315"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="278"/>
-      <c r="B13" s="278"/>
+      <c r="A13" s="303"/>
+      <c r="B13" s="303"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="334" t="s">
+      <c r="E13" s="328" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="335"/>
+      <c r="F13" s="329"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
+      <c r="I13" s="303"/>
+      <c r="J13" s="303"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="278"/>
-      <c r="N13" s="278"/>
+      <c r="M13" s="303"/>
+      <c r="N13" s="303"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="278"/>
-      <c r="B14" s="278"/>
+      <c r="A14" s="303"/>
+      <c r="B14" s="303"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="290" t="s">
+      <c r="E14" s="306" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="291"/>
+      <c r="F14" s="307"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
+      <c r="I14" s="303"/>
+      <c r="J14" s="303"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="278"/>
+      <c r="M14" s="303"/>
+      <c r="N14" s="303"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="278"/>
-      <c r="B15" s="278"/>
+      <c r="A15" s="303"/>
+      <c r="B15" s="303"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="329" t="s">
+      <c r="E15" s="323" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="330"/>
+      <c r="F15" s="324"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="278"/>
-      <c r="N15" s="278"/>
+      <c r="M15" s="303"/>
+      <c r="N15" s="303"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="278"/>
-      <c r="B16" s="278"/>
+      <c r="A16" s="303"/>
+      <c r="B16" s="303"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -24569,74 +24675,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
+      <c r="I16" s="303"/>
+      <c r="J16" s="303"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="278"/>
-      <c r="N16" s="278"/>
+      <c r="M16" s="303"/>
+      <c r="N16" s="303"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="278"/>
-      <c r="B17" s="278"/>
+      <c r="A17" s="303"/>
+      <c r="B17" s="303"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="292" t="s">
+      <c r="E17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="293"/>
+      <c r="F17" s="302"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="278"/>
-      <c r="N17" s="278"/>
+      <c r="M17" s="303"/>
+      <c r="N17" s="303"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="278"/>
-      <c r="N18" s="278"/>
+      <c r="M18" s="303"/>
+      <c r="N18" s="303"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="336"/>
-      <c r="N19" s="336"/>
+      <c r="M19" s="322"/>
+      <c r="N19" s="322"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="336"/>
-      <c r="N20" s="336"/>
+      <c r="M20" s="322"/>
+      <c r="N20" s="322"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="279" t="s">
+      <c r="C21" s="304" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="279" t="s">
+      <c r="E21" s="304" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="279"/>
-      <c r="G21" s="279" t="s">
+      <c r="F21" s="304"/>
+      <c r="G21" s="304" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="279" t="s">
+      <c r="H21" s="304" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="279"/>
+      <c r="C22" s="304"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="279"/>
+      <c r="E22" s="304"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="304"/>
+      <c r="H22" s="304"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="280"/>
+      <c r="C23" s="305"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="280"/>
-      <c r="F23" s="280"/>
-      <c r="G23" s="280"/>
-      <c r="H23" s="280"/>
+      <c r="E23" s="305"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="305"/>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -24709,11 +24815,11 @@
       </c>
       <c r="J25" s="74">
         <f>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</f>
-        <v>20700.147710487447</v>
+        <v>20222.222222222226</v>
       </c>
       <c r="K25" s="75">
         <f>table1[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.94091580502215655</v>
+        <v>0.91919191919191923</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -24725,7 +24831,7 @@
       </c>
       <c r="C26" s="48">
         <f>VLOOKUP(B26,Material[],3,FALSE)</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D26" s="49">
         <v>8</v>
@@ -24736,11 +24842,11 @@
       </c>
       <c r="F26" s="50">
         <f t="shared" ref="F26" si="0">IF(A26="Substrate",D26*E26,C26*D26)</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G26" s="71">
         <f>VLOOKUP(B26,Material[],4,FALSE)</f>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H26" s="51">
         <v>0.1</v>
@@ -24748,15 +24854,15 @@
       <c r="I26" s="47">
         <f>(IF(A26="Substrate",(F26*G26)/1000,(D26*G26)/1000))*(1+table1[[#This Row],[Waste
 %]])</f>
-        <v>3.9600000000000003E-2</v>
+        <v>4.0480000000000002E-2</v>
       </c>
       <c r="J26" s="52">
         <f t="shared" ref="J26" si="1">IF(A26="Substrate",(($I$36*F26)/$B$37)*(1+H26),(($I$36*D26)/$B$37)*(1+H26))</f>
-        <v>5199.4091580502218</v>
+        <v>5079.3650793650795</v>
       </c>
       <c r="K26" s="58">
         <f>table1[[#This Row],[Total GSM]]/$B$37</f>
-        <v>5.9084194977843424E-2</v>
+        <v>8.0808080808080801E-2</v>
       </c>
       <c r="M26" s="14"/>
     </row>
@@ -24813,12 +24919,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="294" t="s">
+      <c r="A31" s="298" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="295"/>
-      <c r="C31" s="295"/>
-      <c r="D31" s="295"/>
+      <c r="B31" s="299"/>
+      <c r="C31" s="299"/>
+      <c r="D31" s="299"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -24832,13 +24938,13 @@
       <c r="H31" s="62"/>
       <c r="I31" s="63">
         <f>((SUMIFS(table1[Total GSM],table1[Type],"ink")+SUMIFS(table1[Total GSM],table1[Material],"Solvent Base"))/$F$31)*G31/1000</f>
-        <v>2E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="J31" s="125">
         <f>(SUMIFS(table1[Est.
 Required Kgs],table1[Type], "Ink") + SUMIFS(table1[Est.
 Required Kgs],table1[Material], "Solvent Base"))*$F$31</f>
-        <v>7799.1137370753331</v>
+        <v>7619.0476190476193</v>
       </c>
       <c r="K31" s="64"/>
     </row>
@@ -24879,21 +24985,21 @@
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
-        <v>0.91486486486486496</v>
-      </c>
-      <c r="C35" s="296" t="s">
+        <v>0.91666666666666674</v>
+      </c>
+      <c r="C35" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="296"/>
+      <c r="D35" s="294"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
-        <v>5560.3420833656528</v>
-      </c>
-      <c r="F35" s="296" t="s">
+        <v>5431.9647769676003</v>
+      </c>
+      <c r="F35" s="294" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="296"/>
-      <c r="H35" s="296"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -24905,21 +25011,21 @@
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
-        <v>37</v>
-      </c>
-      <c r="C36" s="296" t="s">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C36" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="296"/>
+      <c r="D36" s="294"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
-        <v>0.17984505000000001</v>
-      </c>
-      <c r="F36" s="296" t="s">
+        <v>0.18409544999999999</v>
+      </c>
+      <c r="F36" s="294" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="296"/>
-      <c r="H36" s="296"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -24936,24 +25042,24 @@
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F30)</f>
-        <v>33.85</v>
-      </c>
-      <c r="C37" s="296" t="s">
+        <v>34.65</v>
+      </c>
+      <c r="C37" s="294" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="296"/>
+      <c r="D37" s="294"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
-        <v>29.542097488921712</v>
-      </c>
-      <c r="F37" s="296" t="s">
+        <v>28.860028860028862</v>
+      </c>
+      <c r="F37" s="294" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="296"/>
-      <c r="H37" s="296"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
-        <v>111206.84166731306</v>
+        <v>108639.29553935201</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -24962,39 +25068,39 @@
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
-        <v>0.10466300000000001</v>
-      </c>
-      <c r="C38" s="296" t="s">
+        <v>0.10634300000000001</v>
+      </c>
+      <c r="C38" s="294" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="296"/>
+      <c r="D38" s="294"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
-        <v>29.249601474179915</v>
-      </c>
-      <c r="F38" s="296" t="s">
+        <v>28.574286000028575</v>
+      </c>
+      <c r="F38" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="296"/>
-      <c r="H38" s="296"/>
+      <c r="G38" s="294"/>
+      <c r="H38" s="294"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
-        <v>584992.02948359831</v>
+        <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="296" t="s">
+      <c r="C39" s="294" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="296"/>
+      <c r="D39" s="294"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
-        <v>895.2150754218701</v>
+        <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="296"/>
-      <c r="D40" s="296"/>
+      <c r="C40" s="294"/>
+      <c r="D40" s="294"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25044,11 +25150,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="313" t="s">
+      <c r="A44" s="295" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="314"/>
-      <c r="C44" s="315"/>
+      <c r="B44" s="296"/>
+      <c r="C44" s="297"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25078,11 +25184,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="316" t="s">
+      <c r="A46" s="290" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="316"/>
-      <c r="C46" s="316"/>
+      <c r="B46" s="290"/>
+      <c r="C46" s="290"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25097,14 +25203,14 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="316" t="s">
+      <c r="A47" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="316"/>
-      <c r="C47" s="316"/>
+      <c r="B47" s="290"/>
+      <c r="C47" s="290"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
-        <v>7.801683863720231</v>
+        <v>7.8170490707388822</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -25117,14 +25223,14 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="316" t="s">
+      <c r="A48" s="290" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="316"/>
-      <c r="C48" s="316"/>
+      <c r="B48" s="290"/>
+      <c r="C48" s="290"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
-        <v>6984.1850084778926</v>
+        <v>6836.3715691450298</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -25137,11 +25243,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="316" t="s">
+      <c r="A49" s="290" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="316"/>
-      <c r="C49" s="316"/>
+      <c r="B49" s="290"/>
+      <c r="C49" s="290"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25157,14 +25263,14 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="316" t="s">
+      <c r="A50" s="290" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="316"/>
-      <c r="C50" s="316"/>
+      <c r="B50" s="290"/>
+      <c r="C50" s="290"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
-        <v>43380.031108558345</v>
+        <v>42461.93521208092</v>
       </c>
       <c r="E50" s="82"/>
       <c r="F50" s="82"/>
@@ -25192,11 +25298,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="316" t="s">
+      <c r="A52" s="290" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="316"/>
-      <c r="C52" s="316"/>
+      <c r="B52" s="290"/>
+      <c r="C52" s="290"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25211,14 +25317,14 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="316" t="s">
+      <c r="A53" s="290" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="316"/>
-      <c r="C53" s="316"/>
+      <c r="B53" s="290"/>
+      <c r="C53" s="290"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
-        <v>1739.3365512543585</v>
+        <v>1737.6438086744588</v>
       </c>
       <c r="E53" s="82"/>
       <c r="F53" s="82"/>
@@ -25358,9 +25464,9 @@
         <f>F60*E60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="326">
+      <c r="H60" s="330">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
-        <v>145298.03393928759</v>
+        <v>141966.47760014096</v>
       </c>
       <c r="I60" s="82"/>
       <c r="J60" s="82"/>
@@ -25383,16 +25489,16 @@
       </c>
       <c r="E61" s="106">
         <f t="shared" ref="E61:E66" si="2">D61+(OQM/C61/60)</f>
-        <v>41.999468632239889</v>
+        <v>41.099048000038096</v>
       </c>
       <c r="F61" s="113">
         <v>300</v>
       </c>
       <c r="G61" s="114">
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
-        <v>12599.840589671967</v>
-      </c>
-      <c r="H61" s="327"/>
+        <v>12329.714400011429</v>
+      </c>
+      <c r="H61" s="331"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -25422,7 +25528,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H62" s="327"/>
+      <c r="H62" s="331"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -25452,7 +25558,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H63" s="327"/>
+      <c r="H63" s="331"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -25482,7 +25588,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H64" s="327"/>
+      <c r="H64" s="331"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -25512,7 +25618,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H65" s="327"/>
+      <c r="H65" s="331"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -25534,16 +25640,16 @@
       </c>
       <c r="E66" s="106">
         <f t="shared" si="2"/>
-        <v>19.999734316119945</v>
+        <v>19.549524000019048</v>
       </c>
       <c r="F66" s="113">
         <v>50</v>
       </c>
       <c r="G66" s="114">
         <f t="shared" si="3"/>
-        <v>999.98671580599728</v>
-      </c>
-      <c r="H66" s="327"/>
+        <v>977.47620000095242</v>
+      </c>
+      <c r="H66" s="331"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -25565,16 +25671,16 @@
       </c>
       <c r="E67" s="106">
         <f>D67+(OQM*Nb_Ups_Sleeve/C67/60)</f>
-        <v>585.49202948359846</v>
+        <v>571.98572000057152</v>
       </c>
       <c r="F67" s="113">
         <v>100</v>
       </c>
       <c r="G67" s="114">
         <f t="shared" si="3"/>
-        <v>58549.202948359845</v>
-      </c>
-      <c r="H67" s="327"/>
+        <v>57198.572000057153</v>
+      </c>
+      <c r="H67" s="331"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -25597,16 +25703,16 @@
       </c>
       <c r="E68" s="106">
         <f>D68+(OQM*Nb_Ups_Sleeve/C68/60)</f>
-        <v>1462.9800737089959</v>
+        <v>1429.2143000014289</v>
       </c>
       <c r="F68" s="113">
         <v>50</v>
       </c>
       <c r="G68" s="114">
         <f t="shared" si="3"/>
-        <v>73149.003685449788</v>
-      </c>
-      <c r="H68" s="327"/>
+        <v>71460.715000071446</v>
+      </c>
+      <c r="H68" s="331"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -25636,7 +25742,7 @@
         <f>F69*E69</f>
         <v>0</v>
       </c>
-      <c r="H69" s="328"/>
+      <c r="H69" s="332"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -25655,7 +25761,7 @@
       </c>
       <c r="H70" s="124">
         <f>H60/OQKG</f>
-        <v>7.2649016969643796</v>
+        <v>7.0983238800070483</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -25696,23 +25802,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="300"/>
-      <c r="C73" s="301" t="s">
+      <c r="B73" s="281"/>
+      <c r="C73" s="282" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="303" t="s">
+      <c r="E73" s="284" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="305" t="s">
+      <c r="F73" s="286" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="305" t="s">
+      <c r="G73" s="286" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="307" t="s">
+      <c r="H73" s="288" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -25726,15 +25832,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="300"/>
-      <c r="C74" s="302"/>
+      <c r="B74" s="281"/>
+      <c r="C74" s="283"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="304"/>
-      <c r="F74" s="306"/>
-      <c r="G74" s="306"/>
-      <c r="H74" s="308"/>
+      <c r="E74" s="285"/>
+      <c r="F74" s="287"/>
+      <c r="G74" s="287"/>
+      <c r="H74" s="289"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -25751,11 +25857,11 @@
       </c>
       <c r="C75" s="183">
         <f>(B38/B37*1000)</f>
-        <v>3.0919645494830132</v>
+        <v>3.0690620490620497</v>
       </c>
       <c r="D75" s="183">
         <f>C75*D74</f>
-        <v>0.92758936484490395</v>
+        <v>0.92071861471861483</v>
       </c>
       <c r="E75" s="184">
         <v>0.1</v>
@@ -25765,11 +25871,11 @@
       </c>
       <c r="G75" s="184">
         <f>H70</f>
-        <v>7.2649016969643796</v>
+        <v>7.0983238800070483</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>11.584455611292297</v>
+        <v>11.388104543787712</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -25787,27 +25893,27 @@
       </c>
       <c r="C76" s="91">
         <f>(C75/$E$35)*1000</f>
-        <v>0.55607451900000004</v>
+        <v>0.56500035900000012</v>
       </c>
       <c r="D76" s="91">
         <f>(D75/$E$35)*1000</f>
-        <v>0.16682235569999998</v>
+        <v>0.16950010770000001</v>
       </c>
       <c r="E76" s="91">
         <f>(E75/$E$35)*1000</f>
-        <v>1.7984505000000001E-2</v>
+        <v>1.8409544999999999E-2</v>
       </c>
       <c r="F76" s="91">
         <f>(F75/$E$35)*1000</f>
-        <v>3.5969010000000003E-2</v>
+        <v>3.6819089999999999E-2</v>
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
-        <v>1.3065566089356435</v>
+        <v>1.3067691289356436</v>
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>2.0834069986356436</v>
+        <v>2.0964982306356434</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -25825,27 +25931,27 @@
       </c>
       <c r="C77" s="92">
         <f>(C75/$E$37)</f>
-        <v>0.10466300000000001</v>
+        <v>0.10634300000000002</v>
       </c>
       <c r="D77" s="92">
         <f t="shared" ref="D77:F77" si="4">(D75/$E$37)</f>
-        <v>3.13989E-2</v>
+        <v>3.1902899999999998E-2</v>
       </c>
       <c r="E77" s="92">
         <f t="shared" si="4"/>
-        <v>3.3850000000000004E-3</v>
+        <v>3.4649999999999998E-3</v>
       </c>
       <c r="F77" s="92">
         <f t="shared" si="4"/>
-        <v>6.7700000000000008E-3</v>
+        <v>6.9299999999999995E-3</v>
       </c>
       <c r="G77" s="92">
         <f t="shared" ref="G77" si="5">(G75/$E$37)</f>
-        <v>0.24591692244224425</v>
+        <v>0.24595692244224421</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.39213382244224426</v>
+        <v>0.39459782244224423</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -25863,27 +25969,27 @@
       </c>
       <c r="C78" s="92">
         <f>(C75/$E$39)</f>
-        <v>3.453879E-3</v>
+        <v>3.5093190000000008E-3</v>
       </c>
       <c r="D78" s="92">
         <f>(D75/$E$39)</f>
-        <v>1.0361636999999999E-3</v>
+        <v>1.0527957000000001E-3</v>
       </c>
       <c r="E78" s="92">
         <f>(E75/$E$39)</f>
-        <v>1.11705E-4</v>
+        <v>1.14345E-4</v>
       </c>
       <c r="F78" s="92">
         <f>(F75/$E$39)</f>
-        <v>2.2341E-4</v>
+        <v>2.2869000000000001E-4</v>
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>8.1152584405940597E-3</v>
+        <v>8.1165784405940588E-3</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>1.294041614059406E-2</v>
+        <v>1.302172814059406E-2</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -25900,27 +26006,27 @@
       </c>
       <c r="C79" s="191">
         <f>C78*500</f>
-        <v>1.7269395000000001</v>
+        <v>1.7546595000000005</v>
       </c>
       <c r="D79" s="191">
         <f>D78*500</f>
-        <v>0.51808184999999995</v>
+        <v>0.52639785000000006</v>
       </c>
       <c r="E79" s="191">
         <f t="shared" ref="E79:G79" si="6">E78*500</f>
-        <v>5.5852499999999999E-2</v>
+        <v>5.7172500000000001E-2</v>
       </c>
       <c r="F79" s="191">
         <f t="shared" si="6"/>
-        <v>0.111705</v>
+        <v>0.114345</v>
       </c>
       <c r="G79" s="191">
         <f t="shared" si="6"/>
-        <v>4.0576292202970299</v>
+        <v>4.0582892202970298</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>6.4702080702970299</v>
+        <v>6.5108640702970302</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="41"/>
@@ -25973,9 +26079,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="299"/>
-      <c r="I82" s="299"/>
-      <c r="J82" s="299"/>
+      <c r="H82" s="275"/>
+      <c r="I82" s="275"/>
+      <c r="J82" s="275"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -25983,19 +26089,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="298" t="s">
+      <c r="B83" s="276" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="298"/>
-      <c r="D83" s="298"/>
-      <c r="E83" s="298"/>
-      <c r="F83" s="298"/>
-      <c r="G83" s="298"/>
-      <c r="H83" s="298"/>
-      <c r="I83" s="298"/>
-      <c r="J83" s="298"/>
-      <c r="K83" s="298"/>
-      <c r="L83" s="298"/>
+      <c r="C83" s="276"/>
+      <c r="D83" s="276"/>
+      <c r="E83" s="276"/>
+      <c r="F83" s="276"/>
+      <c r="G83" s="276"/>
+      <c r="H83" s="276"/>
+      <c r="I83" s="276"/>
+      <c r="J83" s="276"/>
+      <c r="K83" s="276"/>
+      <c r="L83" s="276"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26061,17 +26167,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="318" t="s">
+      <c r="H87" s="333" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="319"/>
+      <c r="I87" s="334"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="320" t="s">
+      <c r="K87" s="335" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="321"/>
+      <c r="L87" s="336"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26083,20 +26189,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="322">
+      <c r="H88" s="337">
         <f>C75+H70</f>
-        <v>10.356866246447392</v>
-      </c>
-      <c r="I88" s="323"/>
+        <v>10.167385929069098</v>
+      </c>
+      <c r="I88" s="338"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
-        <v>0.95343569181762111</v>
-      </c>
-      <c r="K88" s="324">
+        <v>0.98761894452246557</v>
+      </c>
+      <c r="K88" s="339">
         <f>E106+E122</f>
-        <v>20.231472181191531</v>
-      </c>
-      <c r="L88" s="325"/>
+        <v>20.20888888888889</v>
+      </c>
+      <c r="L88" s="340"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26142,7 +26248,7 @@
       </c>
       <c r="F91" s="163">
         <f>IFERROR(E91/$E$105,"")</f>
-        <v>0.10323613646002601</v>
+        <v>0.10336164612991984</v>
       </c>
       <c r="P91" s="222"/>
     </row>
@@ -26153,28 +26259,28 @@
       </c>
       <c r="C92" s="153">
         <f t="shared" ref="C92" si="9">J26*1.05</f>
-        <v>5459.3796159527328</v>
+        <v>5333.3333333333339</v>
       </c>
       <c r="D92" s="142">
         <f t="shared" si="8"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E92" s="147">
         <f t="shared" ref="E92:E104" si="10">IFERROR(D92*C92,"")</f>
-        <v>24567.208271787298</v>
+        <v>24533.333333333336</v>
       </c>
       <c r="F92" s="163">
         <f t="shared" ref="F92:F104" si="11">IFERROR(E92/$E$105,"")</f>
-        <v>0.88063321721809495</v>
+        <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="278" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="278"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>11.584455611292297</v>
+        <v>11.388104543787712</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -26225,10 +26331,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="279" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
+      <c r="U94" s="280"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26254,19 +26360,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>10.356866246447392</v>
+        <v>10.167385929069098</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.89403132904680693</v>
-      </c>
-      <c r="T95" s="269">
+        <v>0.89280756863225985</v>
+      </c>
+      <c r="T95" s="271">
         <f>R96-R95</f>
-        <v>9.8746059347441388</v>
-      </c>
-      <c r="U95" s="271">
+        <v>10.041502959819791</v>
+      </c>
+      <c r="U95" s="273">
         <f>(R96-R95)/R95</f>
-        <v>0.95343569181762111</v>
+        <v>0.98761894452246557</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.3">
@@ -26295,14 +26401,14 @@
       </c>
       <c r="R96" s="175">
         <f>E106+E122</f>
-        <v>20.231472181191531</v>
+        <v>20.20888888888889</v>
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>1.7464327077631765</v>
-      </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
+        <v>1.7745612372265211</v>
+      </c>
+      <c r="T96" s="272"/>
+      <c r="U96" s="273"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -26329,11 +26435,11 @@
       </c>
       <c r="R97" s="217">
         <f>S92-R95</f>
-        <v>1.2275893648449046</v>
+        <v>1.2207186147186135</v>
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.10596867095319308</v>
+        <v>0.10719243136774011</v>
       </c>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.3">
@@ -26361,11 +26467,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>-8.6470165698992343</v>
+        <v>-8.8207843451011776</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>-0.74643270776317661</v>
+        <v>-0.77456123722652115</v>
       </c>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.3">
@@ -26486,7 +26592,7 @@
       </c>
       <c r="F104" s="163">
         <f t="shared" si="11"/>
-        <v>1.6130646321879064E-2</v>
+        <v>1.6150257207799976E-2</v>
       </c>
       <c r="P104" s="222"/>
     </row>
@@ -26494,7 +26600,7 @@
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
-        <v>27897.208271787298</v>
+        <v>27863.333333333336</v>
       </c>
       <c r="P105" s="222"/>
     </row>
@@ -26505,7 +26611,7 @@
       </c>
       <c r="E106" s="140">
         <f>E105/C85</f>
-        <v>18.598138847858198</v>
+        <v>18.575555555555557</v>
       </c>
       <c r="P106" s="222"/>
     </row>
@@ -26516,7 +26622,7 @@
       </c>
       <c r="E107" s="159">
         <f>(E106-C75)/C75</f>
-        <v>5.0149909710212786</v>
+        <v>5.0525187365411917</v>
       </c>
       <c r="P107" s="222"/>
     </row>
@@ -26764,11 +26870,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="297" t="s">
+      <c r="B122" s="274" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="297"/>
-      <c r="D122" s="297"/>
+      <c r="C122" s="274"/>
+      <c r="D122" s="274"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -26776,14 +26882,14 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="297" t="s">
+      <c r="B123" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="297"/>
-      <c r="D123" s="297"/>
+      <c r="C123" s="274"/>
+      <c r="D123" s="274"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>-0.77517475095143862</v>
+        <v>-0.76989873089142391</v>
       </c>
       <c r="P123" s="222"/>
     </row>
@@ -26810,29 +26916,47 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="A1:L1"/>
@@ -26849,47 +26973,29 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -26961,20 +27067,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="316" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="283"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27004,26 +27110,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="317" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="284" t="s">
+      <c r="B3" s="317"/>
+      <c r="C3" s="318" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="284"/>
-      <c r="E3" s="284"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="317" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="284" t="s">
+      <c r="H3" s="317"/>
+      <c r="I3" s="318" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="284"/>
-      <c r="K3" s="284"/>
-      <c r="L3" s="284"/>
+      <c r="J3" s="318"/>
+      <c r="K3" s="318"/>
+      <c r="L3" s="318"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27050,28 +27156,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="317" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="317"/>
+      <c r="C5" s="319" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="319"/>
+      <c r="E5" s="319"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="317" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="317"/>
+      <c r="I5" s="320">
         <v>500</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="320"/>
+      <c r="K5" s="319" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="319"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27104,86 +27210,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="310" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="310"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="277" t="s">
+      <c r="A10" s="310" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
+      <c r="B10" s="310"/>
+      <c r="C10" s="310"/>
+      <c r="N10" s="311"/>
+      <c r="O10" s="311"/>
+      <c r="P10" s="311"/>
+      <c r="Q10" s="311"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="289"/>
-      <c r="B12" s="289"/>
-      <c r="C12" s="289"/>
-      <c r="E12" s="289"/>
-      <c r="F12" s="289"/>
-      <c r="G12" s="289"/>
-      <c r="I12" s="337" t="s">
+      <c r="A12" s="315"/>
+      <c r="B12" s="315"/>
+      <c r="C12" s="315"/>
+      <c r="E12" s="315"/>
+      <c r="F12" s="315"/>
+      <c r="G12" s="315"/>
+      <c r="I12" s="347" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="338"/>
-      <c r="K12" s="339"/>
-      <c r="M12" s="337" t="s">
+      <c r="J12" s="348"/>
+      <c r="K12" s="349"/>
+      <c r="M12" s="347" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="338"/>
-      <c r="O12" s="339"/>
+      <c r="N12" s="348"/>
+      <c r="O12" s="349"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="278"/>
-      <c r="B13" s="278"/>
+      <c r="A13" s="303"/>
+      <c r="B13" s="303"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
+      <c r="E13" s="303"/>
+      <c r="F13" s="303"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="334" t="s">
+      <c r="I13" s="328" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="335"/>
+      <c r="J13" s="329"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="334" t="s">
+      <c r="M13" s="328" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="335"/>
+      <c r="N13" s="329"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="278"/>
-      <c r="B14" s="278"/>
+      <c r="A14" s="303"/>
+      <c r="B14" s="303"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
+      <c r="E14" s="303"/>
+      <c r="F14" s="303"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="290" t="s">
+      <c r="I14" s="306" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="291"/>
+      <c r="J14" s="307"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="290" t="s">
+      <c r="M14" s="306" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="291"/>
+      <c r="N14" s="307"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27191,11 +27297,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="278"/>
-      <c r="B15" s="278"/>
+      <c r="A15" s="303"/>
+      <c r="B15" s="303"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
+      <c r="E15" s="303"/>
+      <c r="F15" s="303"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27204,10 +27310,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="290" t="s">
+      <c r="M15" s="306" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="291"/>
+      <c r="N15" s="307"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27216,103 +27322,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="278"/>
-      <c r="B16" s="278"/>
+      <c r="A16" s="303"/>
+      <c r="B16" s="303"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="292" t="s">
+      <c r="I16" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="293"/>
+      <c r="J16" s="302"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="290" t="s">
+      <c r="M16" s="306" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="291"/>
+      <c r="N16" s="307"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="278"/>
-      <c r="B17" s="278"/>
+      <c r="A17" s="303"/>
+      <c r="B17" s="303"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
+      <c r="E17" s="303"/>
+      <c r="F17" s="303"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="290" t="s">
+      <c r="M17" s="306" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="291"/>
+      <c r="N17" s="307"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="290" t="s">
+      <c r="M18" s="306" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="291"/>
+      <c r="N18" s="307"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
-        <v>2.0095041508317739</v>
+        <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="342" t="s">
+      <c r="M19" s="341" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="343"/>
+      <c r="N19" s="342"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="344"/>
-      <c r="N20" s="345"/>
+      <c r="M20" s="343"/>
+      <c r="N20" s="344"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="279" t="s">
+      <c r="C21" s="304" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="279" t="s">
+      <c r="E21" s="304" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="279"/>
-      <c r="G21" s="279" t="s">
+      <c r="F21" s="304"/>
+      <c r="G21" s="304" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="279" t="s">
+      <c r="H21" s="304" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="279"/>
+      <c r="C22" s="304"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="279"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="279"/>
+      <c r="E22" s="304"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="304"/>
+      <c r="H22" s="304"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="280"/>
+      <c r="C23" s="305"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="280"/>
-      <c r="F23" s="280"/>
-      <c r="G23" s="280"/>
-      <c r="H23" s="280"/>
+      <c r="E23" s="305"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="305"/>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -27389,7 +27495,7 @@
       </c>
       <c r="K25" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>9.7227848833844541E-2</v>
+        <v>9.6779768419839832E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -27401,7 +27507,7 @@
       </c>
       <c r="C26" s="173">
         <f>VLOOKUP(B26,Material[],3,FALSE)</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D26" s="174">
         <v>8</v>
@@ -27412,11 +27518,11 @@
       </c>
       <c r="F26" s="175">
         <f t="shared" ref="F26:F30" si="1">IF(A26="Substrate",D26*E26,C26*D26)</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G26" s="176">
         <f>VLOOKUP(B26,Material[],4,FALSE)</f>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H26" s="177">
         <v>0.1</v>
@@ -27424,15 +27530,15 @@
       <c r="I26" s="178">
         <f>(IF(A26="Substrate",(F26*G26)/1000,(D26*G26)/1000))*(1+table111[[#This Row],[Waste
 %]])</f>
-        <v>3.9600000000000003E-2</v>
+        <v>4.0480000000000002E-2</v>
       </c>
       <c r="J26" s="179">
         <f t="shared" si="0"/>
-        <v>982.08000000000015</v>
+        <v>982.08</v>
       </c>
       <c r="K26" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>1.1574743908791018E-2</v>
+        <v>1.612996140330664E-2</v>
       </c>
       <c r="M26" s="14"/>
     </row>
@@ -27476,7 +27582,7 @@
       </c>
       <c r="K27" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>1.7362115863186527E-2</v>
+        <v>1.728210150354283E-2</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -27515,11 +27621,11 @@
       </c>
       <c r="J28" s="179">
         <f t="shared" si="0"/>
-        <v>2994.1164000000008</v>
+        <v>2994.1164000000003</v>
       </c>
       <c r="K28" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.14115400196770647</v>
+        <v>0.14050348522380321</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -27562,7 +27668,7 @@
       </c>
       <c r="K29" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>1.7362115863186527E-2</v>
+        <v>1.728210150354283E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -27605,7 +27711,7 @@
       </c>
       <c r="K30" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.53243821980438688</v>
+        <v>0.52998444610864681</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -27644,11 +27750,11 @@
       </c>
       <c r="J31" s="179">
         <f t="shared" si="0"/>
-        <v>491.04000000000008</v>
+        <v>491.04</v>
       </c>
       <c r="K31" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>2.3149487817582037E-2</v>
+        <v>2.3042802004723775E-2</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -27691,16 +27797,16 @@
       </c>
       <c r="K32" s="180">
         <f>table111[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.15973146594131607</v>
+        <v>0.15899533383259404</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="340" t="s">
+      <c r="A33" s="345" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="341"/>
-      <c r="C33" s="341"/>
-      <c r="D33" s="341"/>
+      <c r="B33" s="346"/>
+      <c r="C33" s="346"/>
+      <c r="D33" s="346"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -27714,13 +27820,13 @@
       <c r="H33" s="197"/>
       <c r="I33" s="198">
         <f>((SUMIFS(table111[Total GSM],table111[Type],"ink")+SUMIFS(table111[Total GSM],table111[Material],"Solvent Base"))/$F$33)*G33/1000</f>
-        <v>7.4999999999999997E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="J33" s="199">
         <f>(SUMIFS(table111[Est.
 Required Kgs],table111[Type], "Ink") + SUMIFS(table111[Est.
 Required Kgs],table111[Material], "Solvent Base"))*$F$33</f>
-        <v>1718.6400000000003</v>
+        <v>1718.64</v>
       </c>
       <c r="K33" s="200"/>
     </row>
@@ -27744,21 +27850,21 @@
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
-        <v>1.0600613496932514</v>
-      </c>
-      <c r="C35" s="296" t="s">
+        <v>1.0597680097680098</v>
+      </c>
+      <c r="C35" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="296"/>
+      <c r="D35" s="294"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
-        <v>25.929085817184177</v>
-      </c>
-      <c r="F35" s="296" t="s">
+        <v>25.809590059054404</v>
+      </c>
+      <c r="F35" s="294" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="296"/>
-      <c r="H35" s="296"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -27770,28 +27876,28 @@
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
-        <v>163</v>
-      </c>
-      <c r="C36" s="296" t="s">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="C36" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="296"/>
+      <c r="D36" s="294"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
-        <v>38.566728000000005</v>
-      </c>
-      <c r="F36" s="296" t="s">
+        <v>38.745288000000002</v>
+      </c>
+      <c r="F36" s="294" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="296"/>
-      <c r="H36" s="296"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
  IF(UnitsDD="SQM", I5/E37,
  IF(UnitsDD="LM", I5/E39,
  IF(UnitsDD="Roll 500 LM", (I5/E39)*500, "")))))</f>
-        <v>19283.364000000001</v>
+        <v>19372.644</v>
       </c>
       <c r="K36" s="13"/>
     </row>
@@ -27801,24 +27907,24 @@
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F32)</f>
-        <v>172.79</v>
-      </c>
-      <c r="C37" s="296" t="s">
+        <v>173.59</v>
+      </c>
+      <c r="C37" s="294" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="296"/>
+      <c r="D37" s="294"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
-        <v>5.7873719543955096</v>
-      </c>
-      <c r="F37" s="296" t="s">
+        <v>5.7607005011809438</v>
+      </c>
+      <c r="F37" s="294" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="296"/>
-      <c r="H37" s="296"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
-        <v>499.99999999999994</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -27827,34 +27933,34 @@
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I32)+I33</f>
-        <v>0.37950350000000005</v>
-      </c>
-      <c r="C38" s="296" t="s">
+        <v>0.38158350000000002</v>
+      </c>
+      <c r="C38" s="294" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="296"/>
+      <c r="D38" s="294"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
-        <v>6.0919704783110626</v>
-      </c>
-      <c r="F38" s="296" t="s">
+        <v>6.063895264400994</v>
+      </c>
+      <c r="F38" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="296"/>
-      <c r="H38" s="296"/>
+      <c r="G38" s="294"/>
+      <c r="H38" s="294"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="296" t="s">
+      <c r="C39" s="294" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="296"/>
+      <c r="D39" s="294"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
-        <v>8.0380166033270974</v>
+        <v>8.0009729183068661</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -27905,11 +28011,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="313" t="s">
+      <c r="A44" s="295" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="314"/>
-      <c r="C44" s="315"/>
+      <c r="B44" s="296"/>
+      <c r="C44" s="297"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -27939,11 +28045,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="316" t="s">
+      <c r="A46" s="290" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="316"/>
-      <c r="C46" s="316"/>
+      <c r="B46" s="290"/>
+      <c r="C46" s="290"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -27958,14 +28064,14 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="316" t="s">
+      <c r="A47" s="290" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="316"/>
-      <c r="C47" s="316"/>
+      <c r="B47" s="290"/>
+      <c r="C47" s="290"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
-        <v>35.381970487307228</v>
+        <v>35.372179596826548</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -27978,14 +28084,14 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="316" t="s">
+      <c r="A48" s="290" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="316"/>
-      <c r="C48" s="316"/>
+      <c r="B48" s="290"/>
+      <c r="C48" s="290"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
-        <v>284.40086623540481</v>
+        <v>283.01185101569587</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -27998,11 +28104,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="316" t="s">
+      <c r="A49" s="290" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="316"/>
-      <c r="C49" s="316"/>
+      <c r="B49" s="290"/>
+      <c r="C49" s="290"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28018,14 +28124,14 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="316" t="s">
+      <c r="A50" s="290" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="316"/>
-      <c r="C50" s="316"/>
+      <c r="B50" s="290"/>
+      <c r="C50" s="290"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
-        <v>917.42214914646695</v>
+        <v>912.94145488934146</v>
       </c>
       <c r="E50" s="82"/>
       <c r="F50" s="82"/>
@@ -28053,11 +28159,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="316" t="s">
+      <c r="A52" s="290" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="316"/>
-      <c r="C52" s="316"/>
+      <c r="B52" s="290"/>
+      <c r="C52" s="290"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28072,14 +28178,14 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="316" t="s">
+      <c r="A53" s="290" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="316"/>
-      <c r="C53" s="316"/>
+      <c r="B53" s="290"/>
+      <c r="C53" s="290"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
-        <v>632.17634485576332</v>
+        <v>632.25705038862782</v>
       </c>
       <c r="E53" s="82"/>
       <c r="F53" s="82"/>
@@ -28222,7 +28328,7 @@
         <f>F60*E60</f>
         <v>6892.3268571428589</v>
       </c>
-      <c r="H60" s="326">
+      <c r="H60" s="330">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>17057.940892230581</v>
       </c>
@@ -28256,7 +28362,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>3249.4736842105267</v>
       </c>
-      <c r="H61" s="327"/>
+      <c r="H61" s="331"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -28287,7 +28393,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H62" s="327"/>
+      <c r="H62" s="331"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -28318,7 +28424,7 @@
         <f t="shared" si="3"/>
         <v>1078.9473684210527</v>
       </c>
-      <c r="H63" s="327"/>
+      <c r="H63" s="331"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -28349,7 +28455,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H64" s="327"/>
+      <c r="H64" s="331"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -28380,7 +28486,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H65" s="327"/>
+      <c r="H65" s="331"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -28411,7 +28517,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H66" s="327"/>
+      <c r="H66" s="331"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -28441,7 +28547,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H67" s="327"/>
+      <c r="H67" s="331"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -28472,7 +28578,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="327"/>
+      <c r="H68" s="331"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -28494,7 +28600,7 @@
       </c>
       <c r="E69" s="126">
         <f>D69+(((I37*1000)/C69)/60)</f>
-        <v>42.166666666666657</v>
+        <v>42.166666666666664</v>
       </c>
       <c r="F69" s="122">
         <v>100</v>
@@ -28503,7 +28609,7 @@
         <f>F69*E69</f>
         <v>4216.6666666666661</v>
       </c>
-      <c r="H69" s="328"/>
+      <c r="H69" s="332"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -28522,7 +28628,7 @@
       </c>
       <c r="H70" s="124">
         <f>H60/OQKG</f>
-        <v>0.88459362651820395</v>
+        <v>0.88051692336010412</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -28563,23 +28669,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="300"/>
-      <c r="C73" s="301" t="s">
+      <c r="B73" s="281"/>
+      <c r="C73" s="282" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="303" t="s">
+      <c r="E73" s="284" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="305" t="s">
+      <c r="F73" s="286" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="305" t="s">
+      <c r="G73" s="286" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="307" t="s">
+      <c r="H73" s="288" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -28593,15 +28699,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="300"/>
-      <c r="C74" s="302"/>
+      <c r="B74" s="281"/>
+      <c r="C74" s="283"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="304"/>
-      <c r="F74" s="306"/>
-      <c r="G74" s="306"/>
-      <c r="H74" s="308"/>
+      <c r="E74" s="285"/>
+      <c r="F74" s="287"/>
+      <c r="G74" s="287"/>
+      <c r="H74" s="289"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -28618,11 +28724,11 @@
       </c>
       <c r="C75" s="183">
         <f>(B38/B37*1000)</f>
-        <v>2.1963279124949366</v>
+        <v>2.1981882596923783</v>
       </c>
       <c r="D75" s="183">
         <f>C75*D74</f>
-        <v>0.65889837374848093</v>
+        <v>0.65945647790771345</v>
       </c>
       <c r="E75" s="184">
         <v>0.1</v>
@@ -28632,11 +28738,11 @@
       </c>
       <c r="G75" s="184">
         <f>H70</f>
-        <v>0.88459362651820395</v>
+        <v>0.88051692336010412</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>4.0398199127616214</v>
+        <v>4.0381616609601965</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -28654,19 +28760,19 @@
       </c>
       <c r="C76" s="91">
         <f>(C75/$E$35)*1000</f>
-        <v>84.705181200000041</v>
+        <v>85.169437200000004</v>
       </c>
       <c r="D76" s="91">
         <f>(D75/$E$35)*1000</f>
-        <v>25.411554360000007</v>
+        <v>25.550831159999998</v>
       </c>
       <c r="E76" s="91">
         <f>(E75/$E$35)*1000</f>
-        <v>3.8566728000000006</v>
+        <v>3.8745288000000007</v>
       </c>
       <c r="F76" s="91">
         <f>(F75/$E$35)*1000</f>
-        <v>7.7133456000000011</v>
+        <v>7.7490576000000013</v>
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
@@ -28674,7 +28780,7 @@
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>155.80263574446121</v>
+        <v>156.45973654446118</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -28692,27 +28798,27 @@
       </c>
       <c r="C77" s="92">
         <f>(C75/$E$37)</f>
-        <v>0.37950350000000005</v>
+        <v>0.38158349999999991</v>
       </c>
       <c r="D77" s="92">
         <f t="shared" ref="D77:G77" si="4">(D75/$E$37)</f>
-        <v>0.11385105000000001</v>
+        <v>0.11447504999999997</v>
       </c>
       <c r="E77" s="92">
         <f t="shared" si="4"/>
-        <v>1.7278999999999999E-2</v>
+        <v>1.7358999999999999E-2</v>
       </c>
       <c r="F77" s="92">
         <f t="shared" si="4"/>
-        <v>3.4557999999999998E-2</v>
+        <v>3.4717999999999999E-2</v>
       </c>
       <c r="G77" s="92">
         <f t="shared" si="4"/>
-        <v>0.15284893272608044</v>
+        <v>0.15284893272608047</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.69804048272608055</v>
+        <v>0.70098448272608038</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -28730,27 +28836,27 @@
       </c>
       <c r="C78" s="92">
         <f>(C75/$E$39)</f>
-        <v>0.27324252000000004</v>
+        <v>0.27474011999999998</v>
       </c>
       <c r="D78" s="92">
         <f>(D75/$E$39)</f>
-        <v>8.1972755999999994E-2</v>
+        <v>8.242203599999999E-2</v>
       </c>
       <c r="E78" s="92">
         <f>(E75/$E$39)</f>
-        <v>1.2440879999999998E-2</v>
+        <v>1.2498480000000001E-2</v>
       </c>
       <c r="F78" s="92">
         <f>(F75/$E$39)</f>
-        <v>2.4881759999999996E-2</v>
+        <v>2.4996960000000002E-2</v>
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>0.11005123156277791</v>
+        <v>0.11005123156277795</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>0.50258914756277795</v>
+        <v>0.50470882756277791</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -28767,27 +28873,27 @@
       </c>
       <c r="C79" s="191">
         <f>C78*500</f>
-        <v>136.62126000000004</v>
+        <v>137.37006</v>
       </c>
       <c r="D79" s="191">
         <f>D78*500</f>
-        <v>40.986377999999995</v>
+        <v>41.211017999999996</v>
       </c>
       <c r="E79" s="191">
         <f t="shared" ref="E79:G79" si="5">E78*500</f>
-        <v>6.2204399999999991</v>
+        <v>6.2492400000000004</v>
       </c>
       <c r="F79" s="191">
         <f t="shared" si="5"/>
-        <v>12.440879999999998</v>
+        <v>12.498480000000001</v>
       </c>
       <c r="G79" s="191">
         <f t="shared" si="5"/>
-        <v>55.02561578138895</v>
+        <v>55.025615781388971</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>251.29457378138898</v>
+        <v>252.35441378138896</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="41"/>
@@ -28840,9 +28946,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="299"/>
-      <c r="I82" s="299"/>
-      <c r="J82" s="299"/>
+      <c r="H82" s="275"/>
+      <c r="I82" s="275"/>
+      <c r="J82" s="275"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -28850,19 +28956,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="298" t="s">
+      <c r="B83" s="276" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="298"/>
-      <c r="D83" s="298"/>
-      <c r="E83" s="298"/>
-      <c r="F83" s="298"/>
-      <c r="G83" s="298"/>
-      <c r="H83" s="298"/>
-      <c r="I83" s="298"/>
-      <c r="J83" s="298"/>
-      <c r="K83" s="298"/>
-      <c r="L83" s="298"/>
+      <c r="C83" s="276"/>
+      <c r="D83" s="276"/>
+      <c r="E83" s="276"/>
+      <c r="F83" s="276"/>
+      <c r="G83" s="276"/>
+      <c r="H83" s="276"/>
+      <c r="I83" s="276"/>
+      <c r="J83" s="276"/>
+      <c r="K83" s="276"/>
+      <c r="L83" s="276"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -28928,17 +29034,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="318" t="s">
+      <c r="H87" s="333" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="319"/>
+      <c r="I87" s="334"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="320" t="s">
+      <c r="K87" s="335" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="321"/>
+      <c r="L87" s="336"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -28950,20 +29056,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="322">
+      <c r="H88" s="337">
         <f>C75+H70</f>
-        <v>3.0809215390131408</v>
-      </c>
-      <c r="I88" s="323"/>
+        <v>3.0787051830524823</v>
+      </c>
+      <c r="I88" s="338"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
-        <v>5.8472728784905177E-2</v>
-      </c>
-      <c r="K88" s="324">
+        <v>6.0858781331305026E-2</v>
+      </c>
+      <c r="K88" s="339">
         <f>E106+E122</f>
-        <v>3.2610714285714288</v>
-      </c>
-      <c r="L88" s="325"/>
+        <v>3.2660714285714287</v>
+      </c>
+      <c r="L88" s="340"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29009,7 +29115,7 @@
       </c>
       <c r="F91" s="163">
         <f>IFERROR(E91/$E$105,"")</f>
-        <v>7.4871314927468416E-2</v>
+        <v>7.4708171206225679E-2</v>
       </c>
       <c r="P91" s="222"/>
     </row>
@@ -29023,24 +29129,24 @@
       </c>
       <c r="D92" s="142">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E92" s="147">
         <f t="shared" ref="E92:E104" si="8">IFERROR(D92*C92,"")</f>
-        <v>3150</v>
+        <v>3219.9999999999995</v>
       </c>
       <c r="F92" s="163">
         <f t="shared" ref="F92:F104" si="9">IFERROR(E92/$E$105,"")</f>
-        <v>9.8268600842302295E-2</v>
+        <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="268" t="s">
+      <c r="Q92" s="278" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="268"/>
+      <c r="R92" s="278"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>4.0398199127616214</v>
+        <v>4.0381616609601965</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -29064,7 +29170,7 @@
       </c>
       <c r="F93" s="163">
         <f t="shared" si="9"/>
-        <v>5.2253938543129E-2</v>
+        <v>5.2140077821011675E-2</v>
       </c>
       <c r="P93" s="222"/>
     </row>
@@ -29086,7 +29192,7 @@
       </c>
       <c r="F94" s="163">
         <f t="shared" si="9"/>
-        <v>0.2402121353922945</v>
+        <v>0.2396887159533074</v>
       </c>
       <c r="P94" s="222"/>
       <c r="R94" s="215" t="s">
@@ -29095,10 +29201,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="272" t="s">
+      <c r="T94" s="279" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="273"/>
+      <c r="U94" s="280"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29118,7 +29224,7 @@
       </c>
       <c r="F95" s="163">
         <f t="shared" si="9"/>
-        <v>3.1196381219778507E-2</v>
+        <v>3.1128404669260701E-2</v>
       </c>
       <c r="P95" s="222"/>
       <c r="Q95" s="212" t="s">
@@ -29126,19 +29232,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>3.0809215390131408</v>
+        <v>3.0787051830524823</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.7626383367438333</v>
-      </c>
-      <c r="T95" s="269">
+        <v>0.76240265782733074</v>
+      </c>
+      <c r="T95" s="271">
         <f>R96-R95</f>
-        <v>0.18014988955828803</v>
-      </c>
-      <c r="U95" s="271">
+        <v>0.18736624551894643</v>
+      </c>
+      <c r="U95" s="273">
         <f>(R96-R95)/R95</f>
-        <v>5.8472728784905177E-2</v>
+        <v>6.0858781331305026E-2</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.3">
@@ -29159,7 +29265,7 @@
       </c>
       <c r="F96" s="163">
         <f t="shared" si="9"/>
-        <v>0.29948525970987366</v>
+        <v>0.29883268482490272</v>
       </c>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
@@ -29169,14 +29275,14 @@
       </c>
       <c r="R96" s="175">
         <f>E106+E122</f>
-        <v>3.2610714285714288</v>
+        <v>3.2660714285714287</v>
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>0.80723188136922663</v>
-      </c>
-      <c r="T96" s="270"/>
-      <c r="U96" s="271"/>
+        <v>0.80880155446645008</v>
+      </c>
+      <c r="T96" s="272"/>
+      <c r="U96" s="273"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -29196,7 +29302,7 @@
       </c>
       <c r="F97" s="163">
         <f t="shared" si="9"/>
-        <v>3.9931367961316487E-2</v>
+        <v>3.9844357976653699E-2</v>
       </c>
       <c r="L97" s="43"/>
       <c r="P97" s="222"/>
@@ -29205,11 +29311,11 @@
       </c>
       <c r="R97" s="217">
         <f>S92-R95</f>
-        <v>0.95889837374848064</v>
+        <v>0.95945647790771416</v>
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.23736166325616667</v>
+        <v>0.23759734217266923</v>
       </c>
     </row>
     <row r="98" spans="2:19" x14ac:dyDescent="0.3">
@@ -29230,7 +29336,7 @@
       </c>
       <c r="F98" s="163">
         <f t="shared" si="9"/>
-        <v>9.3589143659335516E-2</v>
+        <v>9.3385214007782102E-2</v>
       </c>
       <c r="I98" s="3"/>
       <c r="P98" s="222"/>
@@ -29239,11 +29345,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>0.7787484841901926</v>
+        <v>0.77209023238876773</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>0.19276811863077334</v>
+        <v>0.19119844553354995</v>
       </c>
     </row>
     <row r="99" spans="2:19" x14ac:dyDescent="0.3">
@@ -29364,7 +29470,7 @@
       </c>
       <c r="F104" s="163">
         <f t="shared" si="9"/>
-        <v>7.0191857744501637E-2</v>
+        <v>7.0038910505836577E-2</v>
       </c>
       <c r="P104" s="222"/>
     </row>
@@ -29372,7 +29478,7 @@
       <c r="B105" s="41"/>
       <c r="E105" s="141">
         <f>SUM(E91:E104)</f>
-        <v>32055</v>
+        <v>32125</v>
       </c>
       <c r="P105" s="222"/>
     </row>
@@ -29383,7 +29489,7 @@
       </c>
       <c r="E106" s="140">
         <f>E105/C85</f>
-        <v>2.2896428571428573</v>
+        <v>2.2946428571428572</v>
       </c>
       <c r="P106" s="222"/>
     </row>
@@ -29394,7 +29500,7 @@
       </c>
       <c r="E107" s="159">
         <f>(E106-C75)/C75</f>
-        <v>4.2486799952343543E-2</v>
+        <v>4.3879134112005988E-2</v>
       </c>
       <c r="P107" s="222"/>
     </row>
@@ -29650,11 +29756,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="297" t="s">
+      <c r="B122" s="274" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="297"/>
-      <c r="D122" s="297"/>
+      <c r="C122" s="274"/>
+      <c r="D122" s="274"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -29662,14 +29768,14 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="297" t="s">
+      <c r="B123" s="274" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="297"/>
-      <c r="D123" s="297"/>
+      <c r="C123" s="274"/>
+      <c r="D123" s="274"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>9.8163656516668904E-2</v>
+        <v>0.10324804175431759</v>
       </c>
       <c r="P123" s="222"/>
     </row>
@@ -29696,6 +29802,72 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -29709,72 +29881,6 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -29825,17 +29931,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G1" s="346" t="s">
+      <c r="G1" s="350" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
-      <c r="K1" s="346" t="s">
+      <c r="H1" s="350"/>
+      <c r="I1" s="350"/>
+      <c r="J1" s="350"/>
+      <c r="K1" s="350" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="346"/>
-      <c r="M1" s="346"/>
+      <c r="L1" s="350"/>
+      <c r="M1" s="350"/>
       <c r="N1" s="172"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
@@ -29937,7 +30043,7 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="347" t="s">
+      <c r="Q7" s="351" t="s">
         <v>218</v>
       </c>
     </row>
@@ -29951,7 +30057,7 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="347"/>
+      <c r="Q8" s="351"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
@@ -29963,7 +30069,7 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="347"/>
+      <c r="Q9" s="351"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
@@ -29975,7 +30081,7 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="347"/>
+      <c r="Q10" s="351"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
@@ -29987,7 +30093,7 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="347"/>
+      <c r="Q11" s="351"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
@@ -29999,7 +30105,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="347"/>
+      <c r="Q12" s="351"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC32DAD3-6D31-4FC6-93D8-5CD92083DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C54ED6-92D1-4E55-8F98-AF96D22A2137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="3" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="PE Bag" sheetId="11" r:id="rId1"/>
@@ -2706,7 +2706,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="356">
+  <cellXfs count="357">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3337,6 +3337,15 @@
     <xf numFmtId="0" fontId="50" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3346,26 +3355,89 @@
     <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3394,8 +3466,8 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3406,9 +3478,6 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3418,110 +3487,14 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3547,6 +3520,54 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3558,21 +3579,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3586,12 +3592,7 @@
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -4668,6 +4669,328 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -5060,328 +5383,6 @@
           <color rgb="FF000000"/>
         </vertical>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF003366"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -16652,6 +16653,99 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>440871</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>45719</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>594918</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>42609</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D6A5981-F640-E0D0-A92C-F71EB9A51CA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3488871" y="971005"/>
+          <a:ext cx="7926447" cy="5058747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>58264</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>72665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13C73FAC-99C2-B66B-F79F-D83BD0C8A207}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11430000" y="1589315"/>
+          <a:ext cx="7983064" cy="3915321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
 <FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
   <bag type="Checkbox"/>
@@ -16670,32 +16764,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="66" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="80"/>
-    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="79">
+    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="64">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="63">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="62">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="75">
+    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="61" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="60">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table1713[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="74">
+    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="59">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="73">
+    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="58">
       <calculatedColumnFormula>table1713[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16782,47 +16876,47 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69" totalsRowBorderDxfId="68" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:F46" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="67" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="66" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="65" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="64" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="63" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="62" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="52" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="51" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="50" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="49" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="48" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="47" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="55" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="53">
+    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="79">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="52">
+    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="78">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="51">
+    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="77">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="50" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="49">
+    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="75">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table17[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="48">
+    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="74">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="47">
+    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="73">
       <calculatedColumnFormula>table17[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -17260,20 +17354,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="289" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17301,26 +17395,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="318" t="s">
+      <c r="B3" s="279"/>
+      <c r="C3" s="290" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="318"/>
-      <c r="E3" s="318"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="317" t="s">
+      <c r="G3" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="317"/>
-      <c r="I3" s="318" t="s">
+      <c r="H3" s="279"/>
+      <c r="I3" s="290" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="318"/>
-      <c r="K3" s="318"/>
-      <c r="L3" s="318"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17345,28 +17439,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="317" t="s">
+      <c r="A5" s="279" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="317"/>
-      <c r="C5" s="319" t="s">
+      <c r="B5" s="279"/>
+      <c r="C5" s="280" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="319"/>
-      <c r="E5" s="319"/>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="317" t="s">
+      <c r="G5" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="317"/>
-      <c r="I5" s="320">
+      <c r="H5" s="279"/>
+      <c r="I5" s="281">
         <v>10000</v>
       </c>
-      <c r="J5" s="320"/>
-      <c r="K5" s="319" t="s">
+      <c r="J5" s="281"/>
+      <c r="K5" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="319"/>
+      <c r="L5" s="280"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17397,132 +17491,132 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="282"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="310" t="s">
+      <c r="A10" s="282" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="310"/>
-      <c r="C10" s="310"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="282"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="311"/>
-      <c r="P10" s="311"/>
+      <c r="O10" s="288"/>
+      <c r="P10" s="288"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="312" t="s">
+      <c r="A12" s="291" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="313"/>
-      <c r="C12" s="314"/>
+      <c r="B12" s="292"/>
+      <c r="C12" s="293"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="315"/>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="M12" s="315"/>
-      <c r="N12" s="315"/>
+      <c r="I12" s="294"/>
+      <c r="J12" s="294"/>
+      <c r="K12" s="294"/>
+      <c r="M12" s="294"/>
+      <c r="N12" s="294"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="308" t="s">
+      <c r="A13" s="286" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="309"/>
+      <c r="B13" s="287"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="303"/>
-      <c r="F13" s="303"/>
+      <c r="E13" s="283"/>
+      <c r="F13" s="283"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="303"/>
-      <c r="J13" s="303"/>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="306" t="s">
+      <c r="A14" s="295" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="307"/>
+      <c r="B14" s="296"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
+      <c r="E14" s="283"/>
+      <c r="F14" s="283"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="303"/>
-      <c r="J14" s="303"/>
+      <c r="I14" s="283"/>
+      <c r="J14" s="283"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="303"/>
-      <c r="N14" s="303"/>
+      <c r="M14" s="283"/>
+      <c r="N14" s="283"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="306" t="s">
+      <c r="A15" s="295" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="307"/>
+      <c r="B15" s="296"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="303"/>
-      <c r="F15" s="303"/>
+      <c r="E15" s="283"/>
+      <c r="F15" s="283"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="303"/>
-      <c r="N15" s="303"/>
+      <c r="M15" s="283"/>
+      <c r="N15" s="283"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="306" t="s">
+      <c r="A16" s="295" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="307"/>
+      <c r="B16" s="296"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="303"/>
-      <c r="J16" s="303"/>
+      <c r="I16" s="283"/>
+      <c r="J16" s="283"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="303"/>
-      <c r="N16" s="303"/>
+      <c r="M16" s="283"/>
+      <c r="N16" s="283"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="301" t="s">
+      <c r="A17" s="297" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="302"/>
+      <c r="B17" s="298"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="303"/>
-      <c r="F17" s="303"/>
+      <c r="E17" s="283"/>
+      <c r="F17" s="283"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="303"/>
-      <c r="N17" s="303"/>
+      <c r="M17" s="283"/>
+      <c r="N17" s="283"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
         <v>10.656436487638533</v>
       </c>
-      <c r="M18" s="303"/>
-      <c r="N18" s="303"/>
+      <c r="M18" s="283"/>
+      <c r="N18" s="283"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L19">
@@ -17541,28 +17635,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="304"/>
+      <c r="C21" s="284"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="304"/>
-      <c r="F21" s="304"/>
-      <c r="G21" s="304"/>
-      <c r="H21" s="304"/>
+      <c r="E21" s="284"/>
+      <c r="F21" s="284"/>
+      <c r="G21" s="284"/>
+      <c r="H21" s="284"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="304"/>
+      <c r="C22" s="284"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="304"/>
-      <c r="F22" s="304"/>
-      <c r="G22" s="304"/>
-      <c r="H22" s="304"/>
+      <c r="E22" s="284"/>
+      <c r="F22" s="284"/>
+      <c r="G22" s="284"/>
+      <c r="H22" s="284"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="305"/>
+      <c r="C23" s="285"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="305"/>
-      <c r="F23" s="305"/>
-      <c r="G23" s="305"/>
-      <c r="H23" s="305"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="285"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="285"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -17738,12 +17832,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="298" t="s">
+      <c r="A31" s="299" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="299"/>
-      <c r="C31" s="299"/>
-      <c r="D31" s="299"/>
+      <c r="B31" s="300"/>
+      <c r="C31" s="300"/>
+      <c r="D31" s="300"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17800,52 +17894,52 @@
       <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="356" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
         <v>0.92257440116138401</v>
       </c>
-      <c r="C35" s="294" t="s">
+      <c r="C35" s="301" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="294"/>
+      <c r="D35" s="301"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>699.36183232800067</v>
       </c>
-      <c r="F35" s="294" t="s">
+      <c r="F35" s="301" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="294"/>
-      <c r="H35" s="294"/>
+      <c r="G35" s="301"/>
+      <c r="H35" s="301"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="356" t="s">
         <v>82</v>
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
         <v>61.994999999999997</v>
       </c>
-      <c r="C36" s="294" t="s">
+      <c r="C36" s="301" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="294"/>
+      <c r="D36" s="301"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>1.429875</v>
       </c>
-      <c r="F36" s="294" t="s">
+      <c r="F36" s="301" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="294"/>
-      <c r="H36" s="294"/>
+      <c r="G36" s="301"/>
+      <c r="H36" s="301"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -17863,62 +17957,62 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="356" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F30)</f>
         <v>57.195</v>
       </c>
-      <c r="C37" s="300" t="s">
+      <c r="C37" s="322" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="300"/>
+      <c r="D37" s="322"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>17.484045808200019</v>
       </c>
-      <c r="F37" s="294" t="s">
+      <c r="F37" s="301" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="294"/>
-      <c r="H37" s="294"/>
+      <c r="G37" s="301"/>
+      <c r="H37" s="301"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>6993.6183232800067</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="356" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
         <v>0.1230525</v>
       </c>
-      <c r="C38" s="294" t="s">
+      <c r="C38" s="301" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="294"/>
+      <c r="D38" s="301"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>17.141221380588252</v>
       </c>
-      <c r="F38" s="294" t="s">
+      <c r="F38" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="294"/>
-      <c r="H38" s="294"/>
+      <c r="G38" s="301"/>
+      <c r="H38" s="301"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>171412.21380588252</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="294" t="s">
+      <c r="C39" s="301" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="294"/>
+      <c r="D39" s="301"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>69.936183232800076</v>
@@ -17975,11 +18069,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="295" t="s">
+      <c r="A44" s="318" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="296"/>
-      <c r="C44" s="297"/>
+      <c r="B44" s="319"/>
+      <c r="C44" s="320"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -18009,11 +18103,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="290"/>
-      <c r="C46" s="290"/>
+      <c r="B46" s="321"/>
+      <c r="C46" s="321"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18028,11 +18122,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="321" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="290"/>
-      <c r="C47" s="290"/>
+      <c r="B47" s="321"/>
+      <c r="C47" s="321"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>59.60173029162047</v>
@@ -18048,11 +18142,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="290" t="s">
+      <c r="A48" s="321" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="290"/>
-      <c r="C48" s="290"/>
+      <c r="B48" s="321"/>
+      <c r="C48" s="321"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>4168.3175306666999</v>
@@ -18068,11 +18162,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="321" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="290"/>
-      <c r="C49" s="290"/>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18088,11 +18182,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="290" t="s">
+      <c r="A50" s="321" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="290"/>
-      <c r="C50" s="290"/>
+      <c r="B50" s="321"/>
+      <c r="C50" s="321"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>41683.175306666992</v>
@@ -18123,11 +18217,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="290" t="s">
+      <c r="A52" s="321" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="290"/>
-      <c r="C52" s="290"/>
+      <c r="B52" s="321"/>
+      <c r="C52" s="321"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18142,11 +18236,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="290" t="s">
+      <c r="A53" s="321" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="290"/>
-      <c r="C53" s="290"/>
+      <c r="B53" s="321"/>
+      <c r="C53" s="321"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>662.93579768320956</v>
@@ -18292,7 +18386,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4436.2256940541756</v>
       </c>
-      <c r="H60" s="291">
+      <c r="H60" s="315">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>13971.149361338501</v>
       </c>
@@ -18326,7 +18420,7 @@
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
         <v>4328.2442761176499</v>
       </c>
-      <c r="H61" s="292"/>
+      <c r="H61" s="316"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18357,7 +18451,7 @@
         <f t="shared" si="1"/>
         <v>310.68702300980419</v>
       </c>
-      <c r="H62" s="292"/>
+      <c r="H62" s="316"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18388,7 +18482,7 @@
         <f t="shared" si="1"/>
         <v>1528.4351150490211</v>
       </c>
-      <c r="H63" s="292"/>
+      <c r="H63" s="316"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18419,7 +18513,7 @@
         <f t="shared" si="1"/>
         <v>1528.4351150490211</v>
       </c>
-      <c r="H64" s="292"/>
+      <c r="H64" s="316"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18450,7 +18544,7 @@
         <f t="shared" si="1"/>
         <v>1528.4351150490211</v>
       </c>
-      <c r="H65" s="292"/>
+      <c r="H65" s="316"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18481,7 +18575,7 @@
         <f t="shared" si="1"/>
         <v>310.68702300980419</v>
       </c>
-      <c r="H66" s="292"/>
+      <c r="H66" s="316"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18511,7 +18605,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="292"/>
+      <c r="H67" s="316"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18541,7 +18635,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="292"/>
+      <c r="H68" s="316"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18571,7 +18665,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="293"/>
+      <c r="H69" s="317"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18631,23 +18725,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="281"/>
-      <c r="C73" s="282" t="s">
+      <c r="B73" s="305"/>
+      <c r="C73" s="306" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="284" t="s">
+      <c r="E73" s="308" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="286" t="s">
+      <c r="F73" s="310" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="286" t="s">
+      <c r="G73" s="310" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="288" t="s">
+      <c r="H73" s="312" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18660,15 +18754,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="281"/>
-      <c r="C74" s="283"/>
+      <c r="B74" s="305"/>
+      <c r="C74" s="307"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="285"/>
-      <c r="F74" s="287"/>
-      <c r="G74" s="287"/>
-      <c r="H74" s="289"/>
+      <c r="E74" s="309"/>
+      <c r="F74" s="311"/>
+      <c r="G74" s="311"/>
+      <c r="H74" s="313"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -18899,9 +18993,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="275"/>
-      <c r="I82" s="275"/>
-      <c r="J82" s="275"/>
+      <c r="H82" s="304"/>
+      <c r="I82" s="304"/>
+      <c r="J82" s="304"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -18909,19 +19003,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="276" t="s">
+      <c r="B83" s="303" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="276"/>
-      <c r="D83" s="276"/>
-      <c r="E83" s="276"/>
-      <c r="F83" s="276"/>
-      <c r="G83" s="276"/>
-      <c r="H83" s="276"/>
-      <c r="I83" s="276"/>
-      <c r="J83" s="276"/>
-      <c r="K83" s="276"/>
-      <c r="L83" s="276"/>
+      <c r="C83" s="303"/>
+      <c r="D83" s="303"/>
+      <c r="E83" s="303"/>
+      <c r="F83" s="303"/>
+      <c r="G83" s="303"/>
+      <c r="H83" s="303"/>
+      <c r="I83" s="303"/>
+      <c r="J83" s="303"/>
+      <c r="K83" s="303"/>
+      <c r="L83" s="303"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -19006,11 +19100,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="277"/>
-      <c r="I88" s="277"/>
+      <c r="H88" s="314"/>
+      <c r="I88" s="314"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="277"/>
-      <c r="L88" s="277"/>
+      <c r="K88" s="314"/>
+      <c r="L88" s="314"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19100,10 +19194,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="278" t="s">
+      <c r="Q92" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="278"/>
+      <c r="R92" s="273"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.4940071469914429</v>
@@ -19163,10 +19257,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="279" t="s">
+      <c r="T94" s="277" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="280"/>
+      <c r="U94" s="278"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19199,11 +19293,11 @@
         <f>R95/S92</f>
         <v>0.7896227947307578</v>
       </c>
-      <c r="T95" s="271">
+      <c r="T95" s="274">
         <f>R96-R95</f>
         <v>-2.0028561972330969</v>
       </c>
-      <c r="U95" s="273">
+      <c r="U95" s="276">
         <f>(R96-R95)/R95</f>
         <v>-0.56441212224973436</v>
       </c>
@@ -19239,8 +19333,8 @@
         <f>R96/S92</f>
         <v>0.34395011738000447</v>
       </c>
-      <c r="T96" s="272"/>
-      <c r="U96" s="273"/>
+      <c r="T96" s="275"/>
+      <c r="U96" s="276"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -19693,22 +19787,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="274" t="s">
+      <c r="B122" s="302" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="274"/>
-      <c r="D122" s="274"/>
+      <c r="C122" s="302"/>
+      <c r="D122" s="302"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="274" t="s">
+      <c r="B123" s="302" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="274"/>
-      <c r="D123" s="274"/>
+      <c r="C123" s="302"/>
+      <c r="D123" s="302"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.34218180961486055</v>
@@ -19716,44 +19810,28 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="C35:D35"/>
@@ -19767,28 +19845,44 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -19871,40 +19965,40 @@
       </c>
     </row>
     <row r="8" spans="7:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="352">
+      <c r="G8" s="354">
         <v>1</v>
       </c>
-      <c r="H8" s="353" t="s">
+      <c r="H8" s="355" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="353" t="s">
+      <c r="I8" s="355" t="s">
         <v>328</v>
       </c>
-      <c r="J8" s="353" t="s">
+      <c r="J8" s="355" t="s">
         <v>328</v>
       </c>
-      <c r="K8" s="353" t="s">
+      <c r="K8" s="355" t="s">
         <v>328</v>
       </c>
-      <c r="L8" s="353" t="s">
+      <c r="L8" s="355" t="s">
         <v>331</v>
       </c>
-      <c r="M8" s="353" t="s">
+      <c r="M8" s="355" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="353" t="s">
+      <c r="N8" s="355" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="7:14" x14ac:dyDescent="0.3">
-      <c r="G9" s="352"/>
-      <c r="H9" s="353"/>
-      <c r="I9" s="353"/>
-      <c r="J9" s="353"/>
-      <c r="K9" s="353"/>
-      <c r="L9" s="353"/>
-      <c r="M9" s="353"/>
-      <c r="N9" s="353"/>
+      <c r="G9" s="354"/>
+      <c r="H9" s="355"/>
+      <c r="I9" s="355"/>
+      <c r="J9" s="355"/>
+      <c r="K9" s="355"/>
+      <c r="L9" s="355"/>
+      <c r="M9" s="355"/>
+      <c r="N9" s="355"/>
     </row>
     <row r="17" spans="7:20" ht="55.2" x14ac:dyDescent="0.3">
       <c r="G17" s="268" t="s">
@@ -19933,86 +20027,86 @@
       </c>
     </row>
     <row r="20" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q20" s="354" t="s">
+      <c r="Q20" s="271" t="s">
         <v>326</v>
       </c>
-      <c r="R20" s="354" t="s">
+      <c r="R20" s="271" t="s">
         <v>203</v>
       </c>
-      <c r="S20" s="354" t="s">
+      <c r="S20" s="271" t="s">
         <v>14</v>
       </c>
-      <c r="T20" s="354" t="s">
+      <c r="T20" s="271" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="21" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q21" s="355" t="s">
+      <c r="Q21" s="272" t="s">
         <v>238</v>
       </c>
-      <c r="R21" s="355" t="s">
+      <c r="R21" s="272" t="s">
         <v>332</v>
       </c>
-      <c r="S21" s="355">
+      <c r="S21" s="272">
         <v>0.9</v>
       </c>
-      <c r="T21" s="355">
+      <c r="T21" s="272">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q22" s="355" t="s">
+      <c r="Q22" s="272" t="s">
         <v>238</v>
       </c>
-      <c r="R22" s="355" t="s">
+      <c r="R22" s="272" t="s">
         <v>333</v>
       </c>
-      <c r="S22" s="355">
+      <c r="S22" s="272">
         <v>0.79</v>
       </c>
-      <c r="T22" s="355">
+      <c r="T22" s="272">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q23" s="355" t="s">
+      <c r="Q23" s="272" t="s">
         <v>238</v>
       </c>
-      <c r="R23" s="355" t="s">
+      <c r="R23" s="272" t="s">
         <v>334</v>
       </c>
-      <c r="S23" s="355">
+      <c r="S23" s="272">
         <v>0.79</v>
       </c>
-      <c r="T23" s="355">
+      <c r="T23" s="272">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q24" s="355" t="s">
+      <c r="Q24" s="272" t="s">
         <v>238</v>
       </c>
-      <c r="R24" s="355" t="s">
+      <c r="R24" s="272" t="s">
         <v>335</v>
       </c>
-      <c r="S24" s="355">
+      <c r="S24" s="272">
         <v>0.8</v>
       </c>
-      <c r="T24" s="355">
+      <c r="T24" s="272">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="7:20" x14ac:dyDescent="0.3">
-      <c r="Q25" s="355" t="s">
+      <c r="Q25" s="272" t="s">
         <v>238</v>
       </c>
-      <c r="R25" s="355" t="s">
+      <c r="R25" s="272" t="s">
         <v>336</v>
       </c>
-      <c r="S25" s="355">
+      <c r="S25" s="272">
         <v>0.87</v>
       </c>
-      <c r="T25" s="355">
+      <c r="T25" s="272">
         <v>0</v>
       </c>
     </row>
@@ -20028,6 +20122,7 @@
     <mergeCell ref="L8:L9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20960,20 +21055,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="289" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21001,26 +21096,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="318" t="s">
+      <c r="B3" s="279"/>
+      <c r="C3" s="290" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="318"/>
-      <c r="E3" s="318"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="317" t="s">
+      <c r="G3" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="317"/>
-      <c r="I3" s="318" t="s">
+      <c r="H3" s="279"/>
+      <c r="I3" s="290" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="318"/>
-      <c r="K3" s="318"/>
-      <c r="L3" s="318"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -21045,28 +21140,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="317" t="s">
+      <c r="A5" s="279" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="317"/>
-      <c r="C5" s="319" t="s">
+      <c r="B5" s="279"/>
+      <c r="C5" s="280" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="319"/>
-      <c r="E5" s="319"/>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="317" t="s">
+      <c r="G5" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="317"/>
-      <c r="I5" s="320">
+      <c r="H5" s="279"/>
+      <c r="I5" s="281">
         <v>10000</v>
       </c>
-      <c r="J5" s="320"/>
-      <c r="K5" s="319" t="s">
+      <c r="J5" s="281"/>
+      <c r="K5" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="319"/>
+      <c r="L5" s="280"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -21097,128 +21192,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="282"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="310" t="s">
+      <c r="A10" s="282" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="310"/>
-      <c r="C10" s="310"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="282"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="311"/>
-      <c r="P10" s="311"/>
+      <c r="O10" s="288"/>
+      <c r="P10" s="288"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="312" t="s">
+      <c r="A12" s="291" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="313"/>
-      <c r="C12" s="314"/>
+      <c r="B12" s="292"/>
+      <c r="C12" s="293"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="315"/>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="M12" s="315"/>
-      <c r="N12" s="315"/>
+      <c r="I12" s="294"/>
+      <c r="J12" s="294"/>
+      <c r="K12" s="294"/>
+      <c r="M12" s="294"/>
+      <c r="N12" s="294"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="308" t="s">
+      <c r="A13" s="286" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="309"/>
+      <c r="B13" s="287"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="303"/>
-      <c r="F13" s="303"/>
+      <c r="E13" s="283"/>
+      <c r="F13" s="283"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="303"/>
-      <c r="J13" s="303"/>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="306" t="s">
+      <c r="A14" s="295" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="307"/>
+      <c r="B14" s="296"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
+      <c r="E14" s="283"/>
+      <c r="F14" s="283"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="303"/>
-      <c r="J14" s="303"/>
+      <c r="I14" s="283"/>
+      <c r="J14" s="283"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="303"/>
-      <c r="N14" s="303"/>
+      <c r="M14" s="283"/>
+      <c r="N14" s="283"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="306" t="s">
+      <c r="A15" s="295" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="307"/>
+      <c r="B15" s="296"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="303"/>
-      <c r="F15" s="303"/>
+      <c r="E15" s="283"/>
+      <c r="F15" s="283"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="303"/>
-      <c r="N15" s="303"/>
+      <c r="M15" s="283"/>
+      <c r="N15" s="283"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="306" t="s">
+      <c r="A16" s="295" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="307"/>
+      <c r="B16" s="296"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="303"/>
-      <c r="J16" s="303"/>
+      <c r="I16" s="283"/>
+      <c r="J16" s="283"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="303"/>
-      <c r="N16" s="303"/>
+      <c r="M16" s="283"/>
+      <c r="N16" s="283"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="301" t="s">
+      <c r="A17" s="297" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="302"/>
+      <c r="B17" s="298"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="303"/>
-      <c r="F17" s="303"/>
+      <c r="E17" s="283"/>
+      <c r="F17" s="283"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="303"/>
-      <c r="N17" s="303"/>
+      <c r="M17" s="283"/>
+      <c r="N17" s="283"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="303"/>
-      <c r="N18" s="303"/>
+      <c r="M18" s="283"/>
+      <c r="N18" s="283"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21229,28 +21324,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="304"/>
+      <c r="C21" s="284"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="304"/>
-      <c r="F21" s="304"/>
-      <c r="G21" s="304"/>
-      <c r="H21" s="304"/>
+      <c r="E21" s="284"/>
+      <c r="F21" s="284"/>
+      <c r="G21" s="284"/>
+      <c r="H21" s="284"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="304"/>
+      <c r="C22" s="284"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="304"/>
-      <c r="F22" s="304"/>
-      <c r="G22" s="304"/>
-      <c r="H22" s="304"/>
+      <c r="E22" s="284"/>
+      <c r="F22" s="284"/>
+      <c r="G22" s="284"/>
+      <c r="H22" s="284"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="305"/>
+      <c r="C23" s="285"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="305"/>
-      <c r="F23" s="305"/>
-      <c r="G23" s="305"/>
-      <c r="H23" s="305"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="285"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="285"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21491,12 +21586,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="298" t="s">
+      <c r="A31" s="299" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="299"/>
-      <c r="C31" s="299"/>
-      <c r="D31" s="299"/>
+      <c r="B31" s="300"/>
+      <c r="C31" s="300"/>
+      <c r="D31" s="300"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21559,19 +21654,19 @@
         <f>B37/B36</f>
         <v>0.9813242784380305</v>
       </c>
-      <c r="C35" s="294" t="s">
+      <c r="C35" s="301" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="294"/>
+      <c r="D35" s="301"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>346.02076124567475</v>
       </c>
-      <c r="F35" s="294" t="s">
+      <c r="F35" s="301" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="294"/>
-      <c r="H35" s="294"/>
+      <c r="G35" s="301"/>
+      <c r="H35" s="301"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21585,19 +21680,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117.8</v>
       </c>
-      <c r="C36" s="294" t="s">
+      <c r="C36" s="301" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="294"/>
+      <c r="D36" s="301"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.89</v>
       </c>
-      <c r="F36" s="294" t="s">
+      <c r="F36" s="301" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="294"/>
-      <c r="H36" s="294"/>
+      <c r="G36" s="301"/>
+      <c r="H36" s="301"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21622,19 +21717,19 @@
         <f>SUM(F25:F30)</f>
         <v>115.6</v>
       </c>
-      <c r="C37" s="294" t="s">
+      <c r="C37" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="294"/>
+      <c r="D37" s="301"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.6505190311418687</v>
       </c>
-      <c r="F37" s="294" t="s">
+      <c r="F37" s="301" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="294"/>
-      <c r="H37" s="294"/>
+      <c r="G37" s="301"/>
+      <c r="H37" s="301"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3460.2076124567475</v>
@@ -21648,29 +21743,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22398500000000002</v>
       </c>
-      <c r="C38" s="294" t="s">
+      <c r="C38" s="301" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="294"/>
+      <c r="D38" s="301"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.4809010109234002</v>
       </c>
-      <c r="F38" s="294" t="s">
+      <c r="F38" s="301" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="294"/>
-      <c r="H38" s="294"/>
+      <c r="G38" s="301"/>
+      <c r="H38" s="301"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="294" t="s">
+      <c r="C39" s="301" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="294"/>
+      <c r="D39" s="301"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.602076124567475</v>
@@ -21727,11 +21822,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="295" t="s">
+      <c r="A44" s="318" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="296"/>
-      <c r="C44" s="297"/>
+      <c r="B44" s="319"/>
+      <c r="C44" s="320"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -21761,11 +21856,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="290"/>
-      <c r="C46" s="290"/>
+      <c r="B46" s="321"/>
+      <c r="C46" s="321"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -21780,11 +21875,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="321" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="290"/>
-      <c r="C47" s="290"/>
+      <c r="B47" s="321"/>
+      <c r="C47" s="321"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.397190403781075</v>
@@ -21800,11 +21895,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="290" t="s">
+      <c r="A48" s="321" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="290"/>
-      <c r="C48" s="290"/>
+      <c r="B48" s="321"/>
+      <c r="C48" s="321"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2193.6744084353313</v>
@@ -21820,11 +21915,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="321" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="290"/>
-      <c r="C49" s="290"/>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -21840,11 +21935,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="290" t="s">
+      <c r="A50" s="321" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="290"/>
-      <c r="C50" s="290"/>
+      <c r="B50" s="321"/>
+      <c r="C50" s="321"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>21936.744084353315</v>
@@ -21875,11 +21970,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="290" t="s">
+      <c r="A52" s="321" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="290"/>
-      <c r="C52" s="290"/>
+      <c r="B52" s="321"/>
+      <c r="C52" s="321"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -21894,11 +21989,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="290" t="s">
+      <c r="A53" s="321" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="290"/>
-      <c r="C53" s="290"/>
+      <c r="B53" s="321"/>
+      <c r="C53" s="321"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.22615683819515</v>
@@ -22044,7 +22139,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4092.6347009391993</v>
       </c>
-      <c r="H60" s="291">
+      <c r="H60" s="315">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9441.736856218844</v>
       </c>
@@ -22078,7 +22173,7 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2596.1802021846802</v>
       </c>
-      <c r="H61" s="292"/>
+      <c r="H61" s="316"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -22109,7 +22204,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H62" s="292"/>
+      <c r="H62" s="316"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22140,7 +22235,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H63" s="292"/>
+      <c r="H63" s="316"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22171,7 +22266,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H64" s="292"/>
+      <c r="H64" s="316"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22202,7 +22297,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H65" s="292"/>
+      <c r="H65" s="316"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22233,7 +22328,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H66" s="292"/>
+      <c r="H66" s="316"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22263,7 +22358,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="292"/>
+      <c r="H67" s="316"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22293,7 +22388,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="292"/>
+      <c r="H68" s="316"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22323,7 +22418,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="293"/>
+      <c r="H69" s="317"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22383,23 +22478,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="281"/>
-      <c r="C73" s="282" t="s">
+      <c r="B73" s="305"/>
+      <c r="C73" s="306" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="284" t="s">
+      <c r="E73" s="308" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="286" t="s">
+      <c r="F73" s="310" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="286" t="s">
+      <c r="G73" s="310" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="288" t="s">
+      <c r="H73" s="312" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22412,15 +22507,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="281"/>
-      <c r="C74" s="283"/>
+      <c r="B74" s="305"/>
+      <c r="C74" s="307"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="285"/>
-      <c r="F74" s="287"/>
-      <c r="G74" s="287"/>
-      <c r="H74" s="289"/>
+      <c r="E74" s="309"/>
+      <c r="F74" s="311"/>
+      <c r="G74" s="311"/>
+      <c r="H74" s="313"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22651,9 +22746,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="275"/>
-      <c r="I82" s="275"/>
-      <c r="J82" s="275"/>
+      <c r="H82" s="304"/>
+      <c r="I82" s="304"/>
+      <c r="J82" s="304"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22661,19 +22756,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="276" t="s">
+      <c r="B83" s="303" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="276"/>
-      <c r="D83" s="276"/>
-      <c r="E83" s="276"/>
-      <c r="F83" s="276"/>
-      <c r="G83" s="276"/>
-      <c r="H83" s="276"/>
-      <c r="I83" s="276"/>
-      <c r="J83" s="276"/>
-      <c r="K83" s="276"/>
-      <c r="L83" s="276"/>
+      <c r="C83" s="303"/>
+      <c r="D83" s="303"/>
+      <c r="E83" s="303"/>
+      <c r="F83" s="303"/>
+      <c r="G83" s="303"/>
+      <c r="H83" s="303"/>
+      <c r="I83" s="303"/>
+      <c r="J83" s="303"/>
+      <c r="K83" s="303"/>
+      <c r="L83" s="303"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -22758,11 +22853,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="277"/>
-      <c r="I88" s="277"/>
+      <c r="H88" s="314"/>
+      <c r="I88" s="314"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="277"/>
-      <c r="L88" s="277"/>
+      <c r="K88" s="314"/>
+      <c r="L88" s="314"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -22852,10 +22947,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="278" t="s">
+      <c r="Q92" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="278"/>
+      <c r="R92" s="273"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7630361423692897</v>
@@ -22915,10 +23010,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="279" t="s">
+      <c r="T94" s="277" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="280"/>
+      <c r="U94" s="278"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -22951,11 +23046,11 @@
         <f>R95/S92</f>
         <v>0.76580720508248346</v>
       </c>
-      <c r="T95" s="271">
+      <c r="T95" s="274">
         <f>R96-R95</f>
         <v>-6.8260190812196253E-2</v>
       </c>
-      <c r="U95" s="273">
+      <c r="U95" s="276">
         <f>(R96-R95)/R95</f>
         <v>-2.368697819819552E-2</v>
       </c>
@@ -22991,8 +23086,8 @@
         <f>R96/S92</f>
         <v>0.74766754651167366</v>
       </c>
-      <c r="T96" s="272"/>
-      <c r="U96" s="273"/>
+      <c r="T96" s="275"/>
+      <c r="U96" s="276"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -23445,22 +23540,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="274" t="s">
+      <c r="B122" s="302" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="274"/>
-      <c r="D122" s="274"/>
+      <c r="C122" s="302"/>
+      <c r="D122" s="302"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="274" t="s">
+      <c r="B123" s="302" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="274"/>
-      <c r="D123" s="274"/>
+      <c r="C123" s="302"/>
+      <c r="D123" s="302"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-2.6611699687135438E-2</v>
@@ -23468,6 +23563,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23484,63 +23636,6 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -23647,16 +23742,16 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="321" t="s">
+      <c r="W1" s="323" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="321"/>
-      <c r="Y1" s="321"/>
-      <c r="Z1" s="321"/>
-      <c r="AA1" s="321"/>
-      <c r="AB1" s="321"/>
-      <c r="AC1" s="321"/>
-      <c r="AD1" s="321"/>
+      <c r="X1" s="323"/>
+      <c r="Y1" s="323"/>
+      <c r="Z1" s="323"/>
+      <c r="AA1" s="323"/>
+      <c r="AB1" s="323"/>
+      <c r="AC1" s="323"/>
+      <c r="AD1" s="323"/>
     </row>
     <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
@@ -24425,20 +24520,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="289" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24468,26 +24563,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="318" t="s">
+      <c r="B3" s="279"/>
+      <c r="C3" s="290" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="318"/>
-      <c r="E3" s="318"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="317" t="s">
+      <c r="G3" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="317"/>
-      <c r="I3" s="318" t="s">
+      <c r="H3" s="279"/>
+      <c r="I3" s="290" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="318"/>
-      <c r="K3" s="318"/>
-      <c r="L3" s="318"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24514,28 +24609,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="317" t="s">
+      <c r="A5" s="279" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="317"/>
-      <c r="C5" s="319" t="s">
+      <c r="B5" s="279"/>
+      <c r="C5" s="280" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="319"/>
-      <c r="E5" s="319"/>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="317" t="s">
+      <c r="G5" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="317"/>
-      <c r="I5" s="320">
+      <c r="H5" s="279"/>
+      <c r="I5" s="281">
         <v>20000</v>
       </c>
-      <c r="J5" s="320"/>
-      <c r="K5" s="319" t="s">
+      <c r="J5" s="281"/>
+      <c r="K5" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="319"/>
+      <c r="L5" s="280"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24568,105 +24663,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="282"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="310" t="s">
+      <c r="A10" s="282" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="310"/>
-      <c r="C10" s="310"/>
-      <c r="N10" s="311"/>
-      <c r="O10" s="311"/>
-      <c r="P10" s="311"/>
-      <c r="Q10" s="311"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="282"/>
+      <c r="N10" s="288"/>
+      <c r="O10" s="288"/>
+      <c r="P10" s="288"/>
+      <c r="Q10" s="288"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="315"/>
-      <c r="B12" s="315"/>
-      <c r="C12" s="315"/>
-      <c r="E12" s="325" t="s">
+      <c r="A12" s="294"/>
+      <c r="B12" s="294"/>
+      <c r="C12" s="294"/>
+      <c r="E12" s="337" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="326"/>
-      <c r="G12" s="327"/>
-      <c r="I12" s="315"/>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="M12" s="315"/>
-      <c r="N12" s="315"/>
-      <c r="O12" s="315"/>
+      <c r="F12" s="338"/>
+      <c r="G12" s="339"/>
+      <c r="I12" s="294"/>
+      <c r="J12" s="294"/>
+      <c r="K12" s="294"/>
+      <c r="M12" s="294"/>
+      <c r="N12" s="294"/>
+      <c r="O12" s="294"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="303"/>
-      <c r="B13" s="303"/>
+      <c r="A13" s="283"/>
+      <c r="B13" s="283"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="328" t="s">
+      <c r="E13" s="340" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="329"/>
+      <c r="F13" s="341"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="303"/>
-      <c r="J13" s="303"/>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="303"/>
-      <c r="N13" s="303"/>
+      <c r="M13" s="283"/>
+      <c r="N13" s="283"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="303"/>
-      <c r="B14" s="303"/>
+      <c r="A14" s="283"/>
+      <c r="B14" s="283"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="306" t="s">
+      <c r="E14" s="295" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="307"/>
+      <c r="F14" s="296"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="303"/>
-      <c r="J14" s="303"/>
+      <c r="I14" s="283"/>
+      <c r="J14" s="283"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="303"/>
-      <c r="N14" s="303"/>
+      <c r="M14" s="283"/>
+      <c r="N14" s="283"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="303"/>
-      <c r="B15" s="303"/>
+      <c r="A15" s="283"/>
+      <c r="B15" s="283"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="323" t="s">
+      <c r="E15" s="335" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="324"/>
+      <c r="F15" s="336"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="303"/>
-      <c r="N15" s="303"/>
+      <c r="M15" s="283"/>
+      <c r="N15" s="283"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="303"/>
-      <c r="B16" s="303"/>
+      <c r="A16" s="283"/>
+      <c r="B16" s="283"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -24675,74 +24770,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="303"/>
-      <c r="J16" s="303"/>
+      <c r="I16" s="283"/>
+      <c r="J16" s="283"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="303"/>
-      <c r="N16" s="303"/>
+      <c r="M16" s="283"/>
+      <c r="N16" s="283"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="303"/>
-      <c r="B17" s="303"/>
+      <c r="A17" s="283"/>
+      <c r="B17" s="283"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="301" t="s">
+      <c r="E17" s="297" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="302"/>
+      <c r="F17" s="298"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="303"/>
-      <c r="N17" s="303"/>
+      <c r="M17" s="283"/>
+      <c r="N17" s="283"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="303"/>
-      <c r="N18" s="303"/>
+      <c r="M18" s="283"/>
+      <c r="N18" s="283"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="322"/>
-      <c r="N19" s="322"/>
+      <c r="M19" s="342"/>
+      <c r="N19" s="342"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="322"/>
-      <c r="N20" s="322"/>
+      <c r="M20" s="342"/>
+      <c r="N20" s="342"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="304" t="s">
+      <c r="C21" s="284" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="304" t="s">
+      <c r="E21" s="284" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="304"/>
-      <c r="G21" s="304" t="s">
+      <c r="F21" s="284"/>
+      <c r="G21" s="284" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="304" t="s">
+      <c r="H21" s="284" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="304"/>
+      <c r="C22" s="284"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="304"/>
-      <c r="F22" s="304"/>
-      <c r="G22" s="304"/>
-      <c r="H22" s="304"/>
+      <c r="E22" s="284"/>
+      <c r="F22" s="284"/>
+      <c r="G22" s="284"/>
+      <c r="H22" s="284"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="305"/>
+      <c r="C23" s="285"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="305"/>
-      <c r="F23" s="305"/>
-      <c r="G23" s="305"/>
-      <c r="H23" s="305"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="285"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="285"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -24919,12 +25014,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="298" t="s">
+      <c r="A31" s="299" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="299"/>
-      <c r="C31" s="299"/>
-      <c r="D31" s="299"/>
+      <c r="B31" s="300"/>
+      <c r="C31" s="300"/>
+      <c r="D31" s="300"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -24987,19 +25082,19 @@
         <f>B37/B36</f>
         <v>0.91666666666666674</v>
       </c>
-      <c r="C35" s="294" t="s">
+      <c r="C35" s="301" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="294"/>
+      <c r="D35" s="301"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5431.9647769676003</v>
       </c>
-      <c r="F35" s="294" t="s">
+      <c r="F35" s="301" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="294"/>
-      <c r="H35" s="294"/>
+      <c r="G35" s="301"/>
+      <c r="H35" s="301"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -25013,19 +25108,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37.799999999999997</v>
       </c>
-      <c r="C36" s="294" t="s">
+      <c r="C36" s="301" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="294"/>
+      <c r="D36" s="301"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.18409544999999999</v>
       </c>
-      <c r="F36" s="294" t="s">
+      <c r="F36" s="301" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="294"/>
-      <c r="H36" s="294"/>
+      <c r="G36" s="301"/>
+      <c r="H36" s="301"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -25044,19 +25139,19 @@
         <f>SUM(F25:F30)</f>
         <v>34.65</v>
       </c>
-      <c r="C37" s="294" t="s">
+      <c r="C37" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="294"/>
+      <c r="D37" s="301"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>28.860028860028862</v>
       </c>
-      <c r="F37" s="294" t="s">
+      <c r="F37" s="301" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="294"/>
-      <c r="H37" s="294"/>
+      <c r="G37" s="301"/>
+      <c r="H37" s="301"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>108639.29553935201</v>
@@ -25070,37 +25165,37 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10634300000000001</v>
       </c>
-      <c r="C38" s="294" t="s">
+      <c r="C38" s="301" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="294"/>
+      <c r="D38" s="301"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>28.574286000028575</v>
       </c>
-      <c r="F38" s="294" t="s">
+      <c r="F38" s="301" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="294"/>
-      <c r="H38" s="294"/>
+      <c r="G38" s="301"/>
+      <c r="H38" s="301"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="294" t="s">
+      <c r="C39" s="301" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="294"/>
+      <c r="D39" s="301"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="294"/>
-      <c r="D40" s="294"/>
+      <c r="C40" s="301"/>
+      <c r="D40" s="301"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25150,11 +25245,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="295" t="s">
+      <c r="A44" s="318" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="296"/>
-      <c r="C44" s="297"/>
+      <c r="B44" s="319"/>
+      <c r="C44" s="320"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25184,11 +25279,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="290"/>
-      <c r="C46" s="290"/>
+      <c r="B46" s="321"/>
+      <c r="C46" s="321"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25203,11 +25298,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="321" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="290"/>
-      <c r="C47" s="290"/>
+      <c r="B47" s="321"/>
+      <c r="C47" s="321"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.8170490707388822</v>
@@ -25223,11 +25318,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="290" t="s">
+      <c r="A48" s="321" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="290"/>
-      <c r="C48" s="290"/>
+      <c r="B48" s="321"/>
+      <c r="C48" s="321"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6836.3715691450298</v>
@@ -25243,11 +25338,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="321" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="290"/>
-      <c r="C49" s="290"/>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25263,11 +25358,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="290" t="s">
+      <c r="A50" s="321" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="290"/>
-      <c r="C50" s="290"/>
+      <c r="B50" s="321"/>
+      <c r="C50" s="321"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>42461.93521208092</v>
@@ -25298,11 +25393,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="290" t="s">
+      <c r="A52" s="321" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="290"/>
-      <c r="C52" s="290"/>
+      <c r="B52" s="321"/>
+      <c r="C52" s="321"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25317,11 +25412,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="290" t="s">
+      <c r="A53" s="321" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="290"/>
-      <c r="C53" s="290"/>
+      <c r="B53" s="321"/>
+      <c r="C53" s="321"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1737.6438086744588</v>
@@ -25464,7 +25559,7 @@
         <f>F60*E60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="330">
+      <c r="H60" s="332">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>141966.47760014096</v>
       </c>
@@ -25498,7 +25593,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>12329.714400011429</v>
       </c>
-      <c r="H61" s="331"/>
+      <c r="H61" s="333"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -25528,7 +25623,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H62" s="331"/>
+      <c r="H62" s="333"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -25558,7 +25653,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H63" s="331"/>
+      <c r="H63" s="333"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -25588,7 +25683,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H64" s="331"/>
+      <c r="H64" s="333"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -25618,7 +25713,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H65" s="331"/>
+      <c r="H65" s="333"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -25649,7 +25744,7 @@
         <f t="shared" si="3"/>
         <v>977.47620000095242</v>
       </c>
-      <c r="H66" s="331"/>
+      <c r="H66" s="333"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -25680,7 +25775,7 @@
         <f t="shared" si="3"/>
         <v>57198.572000057153</v>
       </c>
-      <c r="H67" s="331"/>
+      <c r="H67" s="333"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -25712,7 +25807,7 @@
         <f t="shared" si="3"/>
         <v>71460.715000071446</v>
       </c>
-      <c r="H68" s="331"/>
+      <c r="H68" s="333"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -25742,7 +25837,7 @@
         <f>F69*E69</f>
         <v>0</v>
       </c>
-      <c r="H69" s="332"/>
+      <c r="H69" s="334"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -25802,23 +25897,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="281"/>
-      <c r="C73" s="282" t="s">
+      <c r="B73" s="305"/>
+      <c r="C73" s="306" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="284" t="s">
+      <c r="E73" s="308" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="286" t="s">
+      <c r="F73" s="310" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="286" t="s">
+      <c r="G73" s="310" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="288" t="s">
+      <c r="H73" s="312" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -25832,15 +25927,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="281"/>
-      <c r="C74" s="283"/>
+      <c r="B74" s="305"/>
+      <c r="C74" s="307"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="285"/>
-      <c r="F74" s="287"/>
-      <c r="G74" s="287"/>
-      <c r="H74" s="289"/>
+      <c r="E74" s="309"/>
+      <c r="F74" s="311"/>
+      <c r="G74" s="311"/>
+      <c r="H74" s="313"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -26079,9 +26174,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="275"/>
-      <c r="I82" s="275"/>
-      <c r="J82" s="275"/>
+      <c r="H82" s="304"/>
+      <c r="I82" s="304"/>
+      <c r="J82" s="304"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -26089,19 +26184,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="276" t="s">
+      <c r="B83" s="303" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="276"/>
-      <c r="D83" s="276"/>
-      <c r="E83" s="276"/>
-      <c r="F83" s="276"/>
-      <c r="G83" s="276"/>
-      <c r="H83" s="276"/>
-      <c r="I83" s="276"/>
-      <c r="J83" s="276"/>
-      <c r="K83" s="276"/>
-      <c r="L83" s="276"/>
+      <c r="C83" s="303"/>
+      <c r="D83" s="303"/>
+      <c r="E83" s="303"/>
+      <c r="F83" s="303"/>
+      <c r="G83" s="303"/>
+      <c r="H83" s="303"/>
+      <c r="I83" s="303"/>
+      <c r="J83" s="303"/>
+      <c r="K83" s="303"/>
+      <c r="L83" s="303"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26167,17 +26262,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="333" t="s">
+      <c r="H87" s="324" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="334"/>
+      <c r="I87" s="325"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="335" t="s">
+      <c r="K87" s="326" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="336"/>
+      <c r="L87" s="327"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26189,20 +26284,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="337">
+      <c r="H88" s="328">
         <f>C75+H70</f>
         <v>10.167385929069098</v>
       </c>
-      <c r="I88" s="338"/>
+      <c r="I88" s="329"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.98761894452246557</v>
       </c>
-      <c r="K88" s="339">
+      <c r="K88" s="330">
         <f>E106+E122</f>
         <v>20.20888888888889</v>
       </c>
-      <c r="L88" s="340"/>
+      <c r="L88" s="331"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26274,10 +26369,10 @@
         <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="278" t="s">
+      <c r="Q92" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="278"/>
+      <c r="R92" s="273"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.388104543787712</v>
@@ -26331,10 +26426,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="279" t="s">
+      <c r="T94" s="277" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="280"/>
+      <c r="U94" s="278"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26366,11 +26461,11 @@
         <f>R95/S92</f>
         <v>0.89280756863225985</v>
       </c>
-      <c r="T95" s="271">
+      <c r="T95" s="274">
         <f>R96-R95</f>
         <v>10.041502959819791</v>
       </c>
-      <c r="U95" s="273">
+      <c r="U95" s="276">
         <f>(R96-R95)/R95</f>
         <v>0.98761894452246557</v>
       </c>
@@ -26407,8 +26502,8 @@
         <f>R96/S92</f>
         <v>1.7745612372265211</v>
       </c>
-      <c r="T96" s="272"/>
-      <c r="U96" s="273"/>
+      <c r="T96" s="275"/>
+      <c r="U96" s="276"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -26870,11 +26965,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="274" t="s">
+      <c r="B122" s="302" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="274"/>
-      <c r="D122" s="274"/>
+      <c r="C122" s="302"/>
+      <c r="D122" s="302"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -26882,11 +26977,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="274" t="s">
+      <c r="B123" s="302" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="274"/>
-      <c r="D123" s="274"/>
+      <c r="C123" s="302"/>
+      <c r="D123" s="302"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.76989873089142391</v>
@@ -26916,31 +27011,45 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="A47:C47"/>
@@ -26957,45 +27066,31 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -27067,20 +27162,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="289" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="289"/>
+      <c r="H1" s="289"/>
+      <c r="I1" s="289"/>
+      <c r="J1" s="289"/>
+      <c r="K1" s="289"/>
+      <c r="L1" s="289"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27110,26 +27205,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="317" t="s">
+      <c r="A3" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="318" t="s">
+      <c r="B3" s="279"/>
+      <c r="C3" s="290" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="318"/>
-      <c r="E3" s="318"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="317" t="s">
+      <c r="G3" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="317"/>
-      <c r="I3" s="318" t="s">
+      <c r="H3" s="279"/>
+      <c r="I3" s="290" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="318"/>
-      <c r="K3" s="318"/>
-      <c r="L3" s="318"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27156,28 +27251,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="317" t="s">
+      <c r="A5" s="279" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="317"/>
-      <c r="C5" s="319" t="s">
+      <c r="B5" s="279"/>
+      <c r="C5" s="280" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="319"/>
-      <c r="E5" s="319"/>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="317" t="s">
+      <c r="G5" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="317"/>
-      <c r="I5" s="320">
+      <c r="H5" s="279"/>
+      <c r="I5" s="281">
         <v>500</v>
       </c>
-      <c r="J5" s="320"/>
-      <c r="K5" s="319" t="s">
+      <c r="J5" s="281"/>
+      <c r="K5" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="319"/>
+      <c r="L5" s="280"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27210,86 +27305,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="282"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="310" t="s">
+      <c r="A10" s="282" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="310"/>
-      <c r="C10" s="310"/>
-      <c r="N10" s="311"/>
-      <c r="O10" s="311"/>
-      <c r="P10" s="311"/>
-      <c r="Q10" s="311"/>
+      <c r="B10" s="282"/>
+      <c r="C10" s="282"/>
+      <c r="N10" s="288"/>
+      <c r="O10" s="288"/>
+      <c r="P10" s="288"/>
+      <c r="Q10" s="288"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="315"/>
-      <c r="B12" s="315"/>
-      <c r="C12" s="315"/>
-      <c r="E12" s="315"/>
-      <c r="F12" s="315"/>
-      <c r="G12" s="315"/>
-      <c r="I12" s="347" t="s">
+      <c r="A12" s="294"/>
+      <c r="B12" s="294"/>
+      <c r="C12" s="294"/>
+      <c r="E12" s="294"/>
+      <c r="F12" s="294"/>
+      <c r="G12" s="294"/>
+      <c r="I12" s="343" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="348"/>
-      <c r="K12" s="349"/>
-      <c r="M12" s="347" t="s">
+      <c r="J12" s="344"/>
+      <c r="K12" s="345"/>
+      <c r="M12" s="343" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="348"/>
-      <c r="O12" s="349"/>
+      <c r="N12" s="344"/>
+      <c r="O12" s="345"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="303"/>
-      <c r="B13" s="303"/>
+      <c r="A13" s="283"/>
+      <c r="B13" s="283"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="303"/>
-      <c r="F13" s="303"/>
+      <c r="E13" s="283"/>
+      <c r="F13" s="283"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="328" t="s">
+      <c r="I13" s="340" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="329"/>
+      <c r="J13" s="341"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="328" t="s">
+      <c r="M13" s="340" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="329"/>
+      <c r="N13" s="341"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="303"/>
-      <c r="B14" s="303"/>
+      <c r="A14" s="283"/>
+      <c r="B14" s="283"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
+      <c r="E14" s="283"/>
+      <c r="F14" s="283"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="306" t="s">
+      <c r="I14" s="295" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="307"/>
+      <c r="J14" s="296"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="306" t="s">
+      <c r="M14" s="295" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="307"/>
+      <c r="N14" s="296"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27297,11 +27392,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="303"/>
-      <c r="B15" s="303"/>
+      <c r="A15" s="283"/>
+      <c r="B15" s="283"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="303"/>
-      <c r="F15" s="303"/>
+      <c r="E15" s="283"/>
+      <c r="F15" s="283"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27310,10 +27405,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="306" t="s">
+      <c r="M15" s="295" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="307"/>
+      <c r="N15" s="296"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27322,103 +27417,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="303"/>
-      <c r="B16" s="303"/>
+      <c r="A16" s="283"/>
+      <c r="B16" s="283"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="301" t="s">
+      <c r="I16" s="297" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="302"/>
+      <c r="J16" s="298"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="306" t="s">
+      <c r="M16" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="307"/>
+      <c r="N16" s="296"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="303"/>
-      <c r="B17" s="303"/>
+      <c r="A17" s="283"/>
+      <c r="B17" s="283"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="303"/>
-      <c r="F17" s="303"/>
+      <c r="E17" s="283"/>
+      <c r="F17" s="283"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="306" t="s">
+      <c r="M17" s="295" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="307"/>
+      <c r="N17" s="296"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="306" t="s">
+      <c r="M18" s="295" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="307"/>
+      <c r="N18" s="296"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="341" t="s">
+      <c r="M19" s="348" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="342"/>
+      <c r="N19" s="349"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="343"/>
-      <c r="N20" s="344"/>
+      <c r="M20" s="350"/>
+      <c r="N20" s="351"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="304" t="s">
+      <c r="C21" s="284" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="304" t="s">
+      <c r="E21" s="284" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="304"/>
-      <c r="G21" s="304" t="s">
+      <c r="F21" s="284"/>
+      <c r="G21" s="284" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="304" t="s">
+      <c r="H21" s="284" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="304"/>
+      <c r="C22" s="284"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="304"/>
-      <c r="F22" s="304"/>
-      <c r="G22" s="304"/>
-      <c r="H22" s="304"/>
+      <c r="E22" s="284"/>
+      <c r="F22" s="284"/>
+      <c r="G22" s="284"/>
+      <c r="H22" s="284"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="305"/>
+      <c r="C23" s="285"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="305"/>
-      <c r="F23" s="305"/>
-      <c r="G23" s="305"/>
-      <c r="H23" s="305"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="285"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="285"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -27801,12 +27896,12 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="345" t="s">
+      <c r="A33" s="346" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="346"/>
-      <c r="C33" s="346"/>
-      <c r="D33" s="346"/>
+      <c r="B33" s="347"/>
+      <c r="C33" s="347"/>
+      <c r="D33" s="347"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -27852,19 +27947,19 @@
         <f>B37/B36</f>
         <v>1.0597680097680098</v>
       </c>
-      <c r="C35" s="294" t="s">
+      <c r="C35" s="301" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="294"/>
+      <c r="D35" s="301"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.809590059054404</v>
       </c>
-      <c r="F35" s="294" t="s">
+      <c r="F35" s="301" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="294"/>
-      <c r="H35" s="294"/>
+      <c r="G35" s="301"/>
+      <c r="H35" s="301"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -27878,19 +27973,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163.80000000000001</v>
       </c>
-      <c r="C36" s="294" t="s">
+      <c r="C36" s="301" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="294"/>
+      <c r="D36" s="301"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.745288000000002</v>
       </c>
-      <c r="F36" s="294" t="s">
+      <c r="F36" s="301" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="294"/>
-      <c r="H36" s="294"/>
+      <c r="G36" s="301"/>
+      <c r="H36" s="301"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -27909,19 +28004,19 @@
         <f>SUM(F25:F32)</f>
         <v>173.59</v>
       </c>
-      <c r="C37" s="294" t="s">
+      <c r="C37" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="294"/>
+      <c r="D37" s="301"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7607005011809438</v>
       </c>
-      <c r="F37" s="294" t="s">
+      <c r="F37" s="301" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="294"/>
-      <c r="H37" s="294"/>
+      <c r="G37" s="301"/>
+      <c r="H37" s="301"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>500</v>
@@ -27935,29 +28030,29 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.38158350000000002</v>
       </c>
-      <c r="C38" s="294" t="s">
+      <c r="C38" s="301" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="294"/>
+      <c r="D38" s="301"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.063895264400994</v>
       </c>
-      <c r="F38" s="294" t="s">
+      <c r="F38" s="301" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="294"/>
-      <c r="H38" s="294"/>
+      <c r="G38" s="301"/>
+      <c r="H38" s="301"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="294" t="s">
+      <c r="C39" s="301" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="294"/>
+      <c r="D39" s="301"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0009729183068661</v>
@@ -28011,11 +28106,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="295" t="s">
+      <c r="A44" s="318" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="296"/>
-      <c r="C44" s="297"/>
+      <c r="B44" s="319"/>
+      <c r="C44" s="320"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -28045,11 +28140,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="290"/>
-      <c r="C46" s="290"/>
+      <c r="B46" s="321"/>
+      <c r="C46" s="321"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -28064,11 +28159,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="321" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="290"/>
-      <c r="C47" s="290"/>
+      <c r="B47" s="321"/>
+      <c r="C47" s="321"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.372179596826548</v>
@@ -28084,11 +28179,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="290" t="s">
+      <c r="A48" s="321" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="290"/>
-      <c r="C48" s="290"/>
+      <c r="B48" s="321"/>
+      <c r="C48" s="321"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>283.01185101569587</v>
@@ -28104,11 +28199,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="321" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="290"/>
-      <c r="C49" s="290"/>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28124,11 +28219,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="290" t="s">
+      <c r="A50" s="321" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="290"/>
-      <c r="C50" s="290"/>
+      <c r="B50" s="321"/>
+      <c r="C50" s="321"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>912.94145488934146</v>
@@ -28159,11 +28254,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="290" t="s">
+      <c r="A52" s="321" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="290"/>
-      <c r="C52" s="290"/>
+      <c r="B52" s="321"/>
+      <c r="C52" s="321"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28178,11 +28273,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="290" t="s">
+      <c r="A53" s="321" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="290"/>
-      <c r="C53" s="290"/>
+      <c r="B53" s="321"/>
+      <c r="C53" s="321"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.25705038862782</v>
@@ -28328,7 +28423,7 @@
         <f>F60*E60</f>
         <v>6892.3268571428589</v>
       </c>
-      <c r="H60" s="330">
+      <c r="H60" s="332">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>17057.940892230581</v>
       </c>
@@ -28362,7 +28457,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>3249.4736842105267</v>
       </c>
-      <c r="H61" s="331"/>
+      <c r="H61" s="333"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -28393,7 +28488,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H62" s="331"/>
+      <c r="H62" s="333"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -28424,7 +28519,7 @@
         <f t="shared" si="3"/>
         <v>1078.9473684210527</v>
       </c>
-      <c r="H63" s="331"/>
+      <c r="H63" s="333"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -28455,7 +28550,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H64" s="331"/>
+      <c r="H64" s="333"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -28486,7 +28581,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H65" s="331"/>
+      <c r="H65" s="333"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -28517,7 +28612,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H66" s="331"/>
+      <c r="H66" s="333"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -28547,7 +28642,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H67" s="331"/>
+      <c r="H67" s="333"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -28578,7 +28673,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="331"/>
+      <c r="H68" s="333"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -28609,7 +28704,7 @@
         <f>F69*E69</f>
         <v>4216.6666666666661</v>
       </c>
-      <c r="H69" s="332"/>
+      <c r="H69" s="334"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -28669,23 +28764,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="281"/>
-      <c r="C73" s="282" t="s">
+      <c r="B73" s="305"/>
+      <c r="C73" s="306" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="284" t="s">
+      <c r="E73" s="308" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="286" t="s">
+      <c r="F73" s="310" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="286" t="s">
+      <c r="G73" s="310" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="288" t="s">
+      <c r="H73" s="312" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -28699,15 +28794,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="281"/>
-      <c r="C74" s="283"/>
+      <c r="B74" s="305"/>
+      <c r="C74" s="307"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="285"/>
-      <c r="F74" s="287"/>
-      <c r="G74" s="287"/>
-      <c r="H74" s="289"/>
+      <c r="E74" s="309"/>
+      <c r="F74" s="311"/>
+      <c r="G74" s="311"/>
+      <c r="H74" s="313"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -28946,9 +29041,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="275"/>
-      <c r="I82" s="275"/>
-      <c r="J82" s="275"/>
+      <c r="H82" s="304"/>
+      <c r="I82" s="304"/>
+      <c r="J82" s="304"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -28956,19 +29051,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="276" t="s">
+      <c r="B83" s="303" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="276"/>
-      <c r="D83" s="276"/>
-      <c r="E83" s="276"/>
-      <c r="F83" s="276"/>
-      <c r="G83" s="276"/>
-      <c r="H83" s="276"/>
-      <c r="I83" s="276"/>
-      <c r="J83" s="276"/>
-      <c r="K83" s="276"/>
-      <c r="L83" s="276"/>
+      <c r="C83" s="303"/>
+      <c r="D83" s="303"/>
+      <c r="E83" s="303"/>
+      <c r="F83" s="303"/>
+      <c r="G83" s="303"/>
+      <c r="H83" s="303"/>
+      <c r="I83" s="303"/>
+      <c r="J83" s="303"/>
+      <c r="K83" s="303"/>
+      <c r="L83" s="303"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -29034,17 +29129,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="333" t="s">
+      <c r="H87" s="324" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="334"/>
+      <c r="I87" s="325"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="335" t="s">
+      <c r="K87" s="326" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="336"/>
+      <c r="L87" s="327"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -29056,20 +29151,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="337">
+      <c r="H88" s="328">
         <f>C75+H70</f>
         <v>3.0787051830524823</v>
       </c>
-      <c r="I88" s="338"/>
+      <c r="I88" s="329"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>6.0858781331305026E-2</v>
       </c>
-      <c r="K88" s="339">
+      <c r="K88" s="330">
         <f>E106+E122</f>
         <v>3.2660714285714287</v>
       </c>
-      <c r="L88" s="340"/>
+      <c r="L88" s="331"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29140,10 +29235,10 @@
         <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="278" t="s">
+      <c r="Q92" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="278"/>
+      <c r="R92" s="273"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0381616609601965</v>
@@ -29201,10 +29296,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="279" t="s">
+      <c r="T94" s="277" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="280"/>
+      <c r="U94" s="278"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29238,11 +29333,11 @@
         <f>R95/S92</f>
         <v>0.76240265782733074</v>
       </c>
-      <c r="T95" s="271">
+      <c r="T95" s="274">
         <f>R96-R95</f>
         <v>0.18736624551894643</v>
       </c>
-      <c r="U95" s="273">
+      <c r="U95" s="276">
         <f>(R96-R95)/R95</f>
         <v>6.0858781331305026E-2</v>
       </c>
@@ -29281,8 +29376,8 @@
         <f>R96/S92</f>
         <v>0.80880155446645008</v>
       </c>
-      <c r="T96" s="272"/>
-      <c r="U96" s="273"/>
+      <c r="T96" s="275"/>
+      <c r="U96" s="276"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -29756,11 +29851,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="274" t="s">
+      <c r="B122" s="302" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="274"/>
-      <c r="D122" s="274"/>
+      <c r="C122" s="302"/>
+      <c r="D122" s="302"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -29768,11 +29863,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="274" t="s">
+      <c r="B123" s="302" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="274"/>
-      <c r="D123" s="274"/>
+      <c r="C123" s="302"/>
+      <c r="D123" s="302"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>0.10324804175431759</v>
@@ -29802,72 +29897,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -29881,6 +29910,72 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -29931,17 +30026,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G1" s="350" t="s">
+      <c r="G1" s="352" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="350"/>
-      <c r="I1" s="350"/>
-      <c r="J1" s="350"/>
-      <c r="K1" s="350" t="s">
+      <c r="H1" s="352"/>
+      <c r="I1" s="352"/>
+      <c r="J1" s="352"/>
+      <c r="K1" s="352" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="350"/>
-      <c r="M1" s="350"/>
+      <c r="L1" s="352"/>
+      <c r="M1" s="352"/>
       <c r="N1" s="172"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
@@ -30043,7 +30138,7 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="351" t="s">
+      <c r="Q7" s="353" t="s">
         <v>218</v>
       </c>
     </row>
@@ -30057,7 +30152,7 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="351"/>
+      <c r="Q8" s="353"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
@@ -30069,7 +30164,7 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="351"/>
+      <c r="Q9" s="353"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
@@ -30081,7 +30176,7 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="351"/>
+      <c r="Q10" s="353"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
@@ -30093,7 +30188,7 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="351"/>
+      <c r="Q11" s="353"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
@@ -30105,7 +30200,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="351"/>
+      <c r="Q12" s="353"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C54ED6-92D1-4E55-8F98-AF96D22A2137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295F4756-C7F0-4892-8428-1C09AC56C009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
@@ -3343,9 +3343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3355,89 +3353,44 @@
     <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3460,23 +3413,17 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="64" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="65" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3487,14 +3434,101 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3520,54 +3554,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3579,6 +3565,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3592,7 +3593,6 @@
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -4669,328 +4669,6 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="\$0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF003366"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -5383,6 +5061,328 @@
           <color rgb="FF000000"/>
         </vertical>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="185" formatCode="\$0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -16764,32 +16764,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1FB877EA-E9A3-4BD1-A492-C45A063DDEDE}" name="table1713" displayName="table1713" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="66" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{F62923DA-268D-4C05-A3FD-5B6724B9C52C}" name="Type" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{EB94C18A-53C7-49B4-9951-B0D45387F534}" name="Material" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{742DCF28-FF0E-4DEB-9692-48856C57FDDF}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="64">
+    <tableColumn id="4" xr3:uid="{BB064559-D4BA-4F16-8EC1-30E2B240321C}" name="Micron" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{304CED41-D1B2-4094-B75A-C9F02E2BBC34}" name="Density" dataDxfId="79">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="63">
+    <tableColumn id="6" xr3:uid="{3703A15F-9D1D-4E2C-ABDC-02144AEBEB95}" name="Total GSM" dataDxfId="78">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="62">
+    <tableColumn id="7" xr3:uid="{BC31FE8B-DCB1-4E2C-8E3E-C33A9BE69C66}" name="Cost Per Kg" dataDxfId="77">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="61" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="60">
+    <tableColumn id="8" xr3:uid="{F0C08983-AA5A-4AB5-9E4B-3B623409C8D0}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{7B582428-6E7D-4270-972B-EC6937A949FF}" name="Cost / M²" dataDxfId="75">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table1713[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="59">
+    <tableColumn id="10" xr3:uid="{5B1A4906-CAF6-4DBE-A9F3-96C66D941FC4}" name="Est._x000a_Required Kgs" dataDxfId="74">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="58">
+    <tableColumn id="11" xr3:uid="{278FA076-FBD1-45DE-85C5-F02299C9C71A}" name="Layer %" dataDxfId="73">
       <calculatedColumnFormula>table1713[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16876,47 +16876,47 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}" name="Table11" displayName="Table11" ref="A1:F46" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69" totalsRowBorderDxfId="68" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:F46" xr:uid="{D190CAB3-23AB-4480-A7AB-E53E1B4A3389}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="52" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="51" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="50" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="49" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="48" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="47" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{3B982C09-5FFF-4749-A77B-1A3F304690CC}" name="Substrate Family" dataDxfId="67" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{F17B36C7-B44A-44E3-87F2-2C18A83E9178}" name="Substrate Grade" dataDxfId="66" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{625C4FD8-DA79-4673-AA78-B61A17304DF3}" name="Density (g/cm3)" dataDxfId="65" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9EE73D4B-D438-4F05-8A77-7CA02A1A151B}" name="Hoover" dataDxfId="64" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{FB283264-0925-4473-A7EF-E54984885832}" name="User Price" dataDxfId="63" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{CB02BE89-6280-4DC3-B6D5-7502235403B8}" name="Market Price " dataDxfId="62" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD7FA48-1106-422A-B624-C4BF4F79E45E}" name="table17" displayName="table17" ref="A24:K30" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="81" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{96576271-5AB6-4D1F-A650-9AFB007DB6B2}" name="Type" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{D5E0E192-5AD5-4727-9F12-EAD3A3982878}" name="Material" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{0DB7A82F-E4FA-413B-A42B-A42EA7407217}" name="Solid_x000a_%" dataDxfId="55" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],3,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="80"/>
-    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="79">
+    <tableColumn id="4" xr3:uid="{229B6022-DBB2-4CCF-A1DD-CAC6A675883F}" name="Micron" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{ECD14A31-499F-4FEA-AB58-37B0A4874C9A}" name="Density" dataDxfId="53">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{DAE41353-B150-4A08-BB72-00C15FCE5305}" name="Total GSM" dataDxfId="52">
       <calculatedColumnFormula>IF(A25="Substrate",D25*E25,C25*D25)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{2D2E4074-B605-494F-B5C2-626AD0F02E8D}" name="Cost Per Kg" dataDxfId="51">
       <calculatedColumnFormula>VLOOKUP(B25,Material[],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="76" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="75">
+    <tableColumn id="8" xr3:uid="{BF124759-5704-403F-A548-F9852A5E0F80}" name="Waste_x000a_%" dataDxfId="50" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{DE2AE453-E261-446C-84FD-C8FABCC2AE41}" name="Cost / M²" dataDxfId="49">
       <calculatedColumnFormula>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table17[[#This Row],[Waste
 %]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="74">
+    <tableColumn id="10" xr3:uid="{22A61F1D-96F0-477F-984A-8988FEDF16FF}" name="Est._x000a_Required Kgs" dataDxfId="48">
       <calculatedColumnFormula>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="73">
+    <tableColumn id="11" xr3:uid="{7729127E-5092-4133-A3D4-F264CCBA79B7}" name="Layer %" dataDxfId="47">
       <calculatedColumnFormula>table17[[#This Row],[Total GSM]]/$B$37</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -17354,20 +17354,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="319" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17395,26 +17395,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="279" t="s">
+      <c r="A3" s="320" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="279"/>
-      <c r="C3" s="290" t="s">
+      <c r="B3" s="320"/>
+      <c r="C3" s="321" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="290"/>
-      <c r="E3" s="290"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="279" t="s">
+      <c r="G3" s="320" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="279"/>
-      <c r="I3" s="290" t="s">
+      <c r="H3" s="320"/>
+      <c r="I3" s="321" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17439,28 +17439,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="279" t="s">
+      <c r="A5" s="320" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="279"/>
-      <c r="C5" s="280" t="s">
+      <c r="B5" s="320"/>
+      <c r="C5" s="322" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="320" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="279"/>
-      <c r="I5" s="281">
+      <c r="H5" s="320"/>
+      <c r="I5" s="323">
         <v>10000</v>
       </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="280" t="s">
+      <c r="J5" s="323"/>
+      <c r="K5" s="322" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="280"/>
+      <c r="L5" s="322"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17491,132 +17491,132 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="282" t="s">
+      <c r="A9" s="313" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="282"/>
-      <c r="C9" s="282"/>
+      <c r="B9" s="313"/>
+      <c r="C9" s="313"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="282" t="s">
+      <c r="A10" s="313" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="282"/>
-      <c r="C10" s="282"/>
+      <c r="B10" s="313"/>
+      <c r="C10" s="313"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="288"/>
-      <c r="P10" s="288"/>
+      <c r="O10" s="314"/>
+      <c r="P10" s="314"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="291" t="s">
+      <c r="A12" s="315" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="292"/>
-      <c r="C12" s="293"/>
+      <c r="B12" s="316"/>
+      <c r="C12" s="317"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="294"/>
-      <c r="J12" s="294"/>
-      <c r="K12" s="294"/>
-      <c r="M12" s="294"/>
-      <c r="N12" s="294"/>
+      <c r="I12" s="318"/>
+      <c r="J12" s="318"/>
+      <c r="K12" s="318"/>
+      <c r="M12" s="318"/>
+      <c r="N12" s="318"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="286" t="s">
+      <c r="A13" s="311" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="287"/>
+      <c r="B13" s="312"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="283"/>
-      <c r="F13" s="283"/>
+      <c r="E13" s="306"/>
+      <c r="F13" s="306"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="283"/>
-      <c r="J13" s="283"/>
+      <c r="I13" s="306"/>
+      <c r="J13" s="306"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="295" t="s">
+      <c r="A14" s="309" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="296"/>
+      <c r="B14" s="310"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="283"/>
-      <c r="F14" s="283"/>
+      <c r="E14" s="306"/>
+      <c r="F14" s="306"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="283"/>
-      <c r="J14" s="283"/>
+      <c r="I14" s="306"/>
+      <c r="J14" s="306"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="283"/>
-      <c r="N14" s="283"/>
+      <c r="M14" s="306"/>
+      <c r="N14" s="306"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="295" t="s">
+      <c r="A15" s="309" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="296"/>
+      <c r="B15" s="310"/>
       <c r="C15" s="31">
-        <v>20</v>
-      </c>
-      <c r="E15" s="283"/>
-      <c r="F15" s="283"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="306"/>
+      <c r="F15" s="306"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="283"/>
-      <c r="N15" s="283"/>
+      <c r="M15" s="306"/>
+      <c r="N15" s="306"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="295" t="s">
+      <c r="A16" s="309" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="296"/>
+      <c r="B16" s="310"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="283"/>
-      <c r="J16" s="283"/>
+      <c r="I16" s="306"/>
+      <c r="J16" s="306"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="283"/>
-      <c r="N16" s="283"/>
+      <c r="M16" s="306"/>
+      <c r="N16" s="306"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="297" t="s">
+      <c r="A17" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="298"/>
+      <c r="B17" s="305"/>
       <c r="C17" s="32">
-        <v>4</v>
-      </c>
-      <c r="E17" s="283"/>
-      <c r="F17" s="283"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="306"/>
+      <c r="F17" s="306"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="283"/>
-      <c r="N17" s="283"/>
+      <c r="M17" s="306"/>
+      <c r="N17" s="306"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
         <v>10.656436487638533</v>
       </c>
-      <c r="M18" s="283"/>
-      <c r="N18" s="283"/>
+      <c r="M18" s="306"/>
+      <c r="N18" s="306"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L19">
@@ -17635,28 +17635,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="284"/>
+      <c r="C21" s="307"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="284"/>
-      <c r="G21" s="284"/>
-      <c r="H21" s="284"/>
+      <c r="E21" s="307"/>
+      <c r="F21" s="307"/>
+      <c r="G21" s="307"/>
+      <c r="H21" s="307"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="284"/>
+      <c r="C22" s="307"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
-      <c r="H22" s="284"/>
+      <c r="E22" s="307"/>
+      <c r="F22" s="307"/>
+      <c r="G22" s="307"/>
+      <c r="H22" s="307"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="285"/>
+      <c r="C23" s="308"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
+      <c r="E23" s="308"/>
+      <c r="F23" s="308"/>
+      <c r="G23" s="308"/>
+      <c r="H23" s="308"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -17832,12 +17832,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="299" t="s">
+      <c r="A31" s="297" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="300"/>
-      <c r="C31" s="300"/>
-      <c r="D31" s="300"/>
+      <c r="B31" s="298"/>
+      <c r="C31" s="298"/>
+      <c r="D31" s="298"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17894,52 +17894,52 @@
       <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="356" t="s">
+      <c r="A35" s="273" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="36">
         <f>B37/B36</f>
         <v>0.92257440116138401</v>
       </c>
-      <c r="C35" s="301" t="s">
+      <c r="C35" s="299" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="301"/>
+      <c r="D35" s="299"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>699.36183232800067</v>
       </c>
-      <c r="F35" s="301" t="s">
+      <c r="F35" s="299" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="301"/>
-      <c r="H35" s="301"/>
+      <c r="G35" s="299"/>
+      <c r="H35" s="299"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
-        <v>1020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="356" t="s">
+      <c r="A36" s="273" t="s">
         <v>82</v>
       </c>
       <c r="B36" s="37">
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
         <v>61.994999999999997</v>
       </c>
-      <c r="C36" s="301" t="s">
+      <c r="C36" s="299" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="301"/>
+      <c r="D36" s="299"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>1.429875</v>
       </c>
-      <c r="F36" s="301" t="s">
+      <c r="F36" s="299" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="301"/>
-      <c r="H36" s="301"/>
+      <c r="G36" s="299"/>
+      <c r="H36" s="299"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -17957,62 +17957,62 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="356" t="s">
+      <c r="A37" s="273" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="37">
         <f>SUM(F25:F30)</f>
         <v>57.195</v>
       </c>
-      <c r="C37" s="322" t="s">
+      <c r="C37" s="300" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="322"/>
+      <c r="D37" s="300"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>17.484045808200019</v>
       </c>
-      <c r="F37" s="301" t="s">
+      <c r="F37" s="299" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="301"/>
-      <c r="H37" s="301"/>
+      <c r="G37" s="299"/>
+      <c r="H37" s="299"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>6993.6183232800067</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="356" t="s">
+      <c r="A38" s="273" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
         <v>0.1230525</v>
       </c>
-      <c r="C38" s="301" t="s">
+      <c r="C38" s="299" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="301"/>
-      <c r="E38" s="15">
+      <c r="D38" s="299"/>
+      <c r="E38" s="15" t="e">
         <f>(E37/I35)*1000</f>
-        <v>17.141221380588252</v>
-      </c>
-      <c r="F38" s="301" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F38" s="299" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="301"/>
-      <c r="H38" s="301"/>
-      <c r="I38" s="38">
+      <c r="G38" s="299"/>
+      <c r="H38" s="299"/>
+      <c r="I38" s="38" t="e">
         <f>I36*E38</f>
-        <v>171412.21380588252</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="301" t="s">
+      <c r="C39" s="299" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="301"/>
+      <c r="D39" s="299"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>69.936183232800076</v>
@@ -18069,11 +18069,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="318" t="s">
+      <c r="A44" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="319"/>
-      <c r="C44" s="320"/>
+      <c r="B44" s="302"/>
+      <c r="C44" s="303"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -18103,11 +18103,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="321" t="s">
+      <c r="A46" s="286" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="321"/>
-      <c r="C46" s="321"/>
+      <c r="B46" s="286"/>
+      <c r="C46" s="286"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18122,11 +18122,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="321" t="s">
+      <c r="A47" s="286" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="321"/>
-      <c r="C47" s="321"/>
+      <c r="B47" s="286"/>
+      <c r="C47" s="286"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>59.60173029162047</v>
@@ -18142,11 +18142,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="321" t="s">
+      <c r="A48" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="321"/>
-      <c r="C48" s="321"/>
+      <c r="B48" s="286"/>
+      <c r="C48" s="286"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>4168.3175306666999</v>
@@ -18162,11 +18162,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="321" t="s">
+      <c r="A49" s="286" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="321"/>
-      <c r="C49" s="321"/>
+      <c r="B49" s="286"/>
+      <c r="C49" s="286"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18182,11 +18182,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="321" t="s">
+      <c r="A50" s="286" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="321"/>
-      <c r="C50" s="321"/>
+      <c r="B50" s="286"/>
+      <c r="C50" s="286"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>41683.175306666992</v>
@@ -18217,11 +18217,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="321" t="s">
+      <c r="A52" s="286" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="321"/>
-      <c r="C52" s="321"/>
+      <c r="B52" s="286"/>
+      <c r="C52" s="286"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18236,11 +18236,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="321" t="s">
+      <c r="A53" s="286" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="321"/>
-      <c r="C53" s="321"/>
+      <c r="B53" s="286"/>
+      <c r="C53" s="286"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>662.93579768320956</v>
@@ -18386,9 +18386,9 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4436.2256940541756</v>
       </c>
-      <c r="H60" s="315">
+      <c r="H60" s="287">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
-        <v>13971.149361338501</v>
+        <v>4436.2256940541756</v>
       </c>
       <c r="I60" s="82"/>
       <c r="J60" s="82"/>
@@ -18409,18 +18409,18 @@
       <c r="D61" s="112">
         <v>3</v>
       </c>
-      <c r="E61" s="106">
+      <c r="E61" s="106" t="e">
         <f t="shared" ref="E61:E66" si="0">IF(A61=TRUE, D61+(OQM/C61/60),"")</f>
-        <v>14.427480920392167</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F61" s="205">
         <v>300</v>
       </c>
-      <c r="G61" s="208">
+      <c r="G61" s="208" t="str">
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
-        <v>4328.2442761176499</v>
-      </c>
-      <c r="H61" s="316"/>
+        <v/>
+      </c>
+      <c r="H61" s="288"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18440,18 +18440,18 @@
       <c r="D62" s="112">
         <v>0.5</v>
       </c>
-      <c r="E62" s="106">
+      <c r="E62" s="106" t="e">
         <f t="shared" si="0"/>
-        <v>6.2137404601960835</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F62" s="205">
         <v>50</v>
       </c>
-      <c r="G62" s="208">
+      <c r="G62" s="208" t="str">
         <f t="shared" si="1"/>
-        <v>310.68702300980419</v>
-      </c>
-      <c r="H62" s="316"/>
+        <v/>
+      </c>
+      <c r="H62" s="288"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18471,18 +18471,18 @@
       <c r="D63" s="112">
         <v>1</v>
       </c>
-      <c r="E63" s="106">
+      <c r="E63" s="106" t="e">
         <f t="shared" si="0"/>
-        <v>15.28435115049021</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F63" s="205">
         <v>100</v>
       </c>
-      <c r="G63" s="208">
+      <c r="G63" s="208" t="str">
         <f t="shared" si="1"/>
-        <v>1528.4351150490211</v>
-      </c>
-      <c r="H63" s="316"/>
+        <v/>
+      </c>
+      <c r="H63" s="288"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18502,18 +18502,18 @@
       <c r="D64" s="112">
         <v>1</v>
       </c>
-      <c r="E64" s="106">
+      <c r="E64" s="106" t="e">
         <f t="shared" si="0"/>
-        <v>15.28435115049021</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F64" s="205">
         <v>100</v>
       </c>
-      <c r="G64" s="208">
+      <c r="G64" s="208" t="str">
         <f t="shared" si="1"/>
-        <v>1528.4351150490211</v>
-      </c>
-      <c r="H64" s="316"/>
+        <v/>
+      </c>
+      <c r="H64" s="288"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18533,18 +18533,18 @@
       <c r="D65" s="112">
         <v>1</v>
       </c>
-      <c r="E65" s="106">
+      <c r="E65" s="106" t="e">
         <f t="shared" si="0"/>
-        <v>15.28435115049021</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F65" s="205">
         <v>100</v>
       </c>
-      <c r="G65" s="208">
+      <c r="G65" s="208" t="str">
         <f t="shared" si="1"/>
-        <v>1528.4351150490211</v>
-      </c>
-      <c r="H65" s="316"/>
+        <v/>
+      </c>
+      <c r="H65" s="288"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18564,18 +18564,18 @@
       <c r="D66" s="112">
         <v>0.5</v>
       </c>
-      <c r="E66" s="106">
+      <c r="E66" s="106" t="e">
         <f t="shared" si="0"/>
-        <v>6.2137404601960835</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F66" s="205">
         <v>50</v>
       </c>
-      <c r="G66" s="208">
+      <c r="G66" s="208" t="str">
         <f t="shared" si="1"/>
-        <v>310.68702300980419</v>
-      </c>
-      <c r="H66" s="316"/>
+        <v/>
+      </c>
+      <c r="H66" s="288"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18605,7 +18605,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="316"/>
+      <c r="H67" s="288"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18635,7 +18635,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="316"/>
+      <c r="H68" s="288"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18665,7 +18665,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="317"/>
+      <c r="H69" s="289"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="H70" s="137">
         <f>H60/OQKG</f>
-        <v>1.3971149361338502</v>
+        <v>0.44362256940541756</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -18725,23 +18725,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="305"/>
-      <c r="C73" s="306" t="s">
+      <c r="B73" s="290"/>
+      <c r="C73" s="291" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="308" t="s">
+      <c r="E73" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="310" t="s">
+      <c r="F73" s="295" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="310" t="s">
+      <c r="G73" s="295" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="312" t="s">
+      <c r="H73" s="284" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18754,15 +18754,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="305"/>
-      <c r="C74" s="307"/>
+      <c r="B74" s="290"/>
+      <c r="C74" s="292"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="309"/>
-      <c r="F74" s="311"/>
-      <c r="G74" s="311"/>
-      <c r="H74" s="313"/>
+      <c r="E74" s="294"/>
+      <c r="F74" s="296"/>
+      <c r="G74" s="296"/>
+      <c r="H74" s="285"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -18792,11 +18792,11 @@
       </c>
       <c r="G75" s="185">
         <f>H70</f>
-        <v>1.3971149361338502</v>
+        <v>0.44362256940541756</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>4.4940071469914429</v>
+        <v>3.5405147802630101</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -18829,11 +18829,11 @@
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
-        <v>1.9976997193043891</v>
+        <v>0.63432482142857149</v>
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>6.4258684693043895</v>
+        <v>5.0624935714285719</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -18866,11 +18866,11 @@
       </c>
       <c r="G77" s="92">
         <f t="shared" si="2"/>
-        <v>7.9907988772175559E-2</v>
+        <v>2.5372992857142854E-2</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.25703473877217553</v>
+        <v>0.20249974285714284</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -18903,11 +18903,11 @@
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>1.997699719304389E-2</v>
+        <v>6.3432482142857134E-3</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>6.4258684693043883E-2</v>
+        <v>5.062493571428571E-2</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -18939,11 +18939,11 @@
       </c>
       <c r="G79" s="191">
         <f t="shared" si="3"/>
-        <v>9.9884985965219446</v>
+        <v>3.1716241071428568</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>32.129342346521945</v>
+        <v>25.312467857142856</v>
       </c>
       <c r="I79" s="220"/>
       <c r="J79" s="221"/>
@@ -18993,9 +18993,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="304"/>
-      <c r="I82" s="304"/>
-      <c r="J82" s="304"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -19003,19 +19003,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="303" t="s">
+      <c r="B83" s="279" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="303"/>
-      <c r="D83" s="303"/>
-      <c r="E83" s="303"/>
-      <c r="F83" s="303"/>
-      <c r="G83" s="303"/>
-      <c r="H83" s="303"/>
-      <c r="I83" s="303"/>
-      <c r="J83" s="303"/>
-      <c r="K83" s="303"/>
-      <c r="L83" s="303"/>
+      <c r="C83" s="279"/>
+      <c r="D83" s="279"/>
+      <c r="E83" s="279"/>
+      <c r="F83" s="279"/>
+      <c r="G83" s="279"/>
+      <c r="H83" s="279"/>
+      <c r="I83" s="279"/>
+      <c r="J83" s="279"/>
+      <c r="K83" s="279"/>
+      <c r="L83" s="279"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -19100,11 +19100,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="314"/>
-      <c r="I88" s="314"/>
+      <c r="H88" s="280"/>
+      <c r="I88" s="280"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="314"/>
-      <c r="L88" s="314"/>
+      <c r="K88" s="280"/>
+      <c r="L88" s="280"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19194,13 +19194,13 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="273" t="s">
+      <c r="Q92" s="281" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="273"/>
+      <c r="R92" s="281"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>4.4940071469914429</v>
+        <v>3.5405147802630101</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -19257,10 +19257,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="277" t="s">
+      <c r="T94" s="282" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="278"/>
+      <c r="U94" s="283"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19287,19 +19287,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>3.5485704829473828</v>
+        <v>2.59507811621895</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.7896227947307578</v>
+        <v>0.73296632757628888</v>
       </c>
       <c r="T95" s="274">
         <f>R96-R95</f>
-        <v>-2.0028561972330969</v>
+        <v>-1.0493638305046642</v>
       </c>
       <c r="U95" s="276">
         <f>(R96-R95)/R95</f>
-        <v>-0.56441212224973436</v>
+        <v>-0.40436695294305663</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>0.34395011738000447</v>
+        <v>0.43657896708440264</v>
       </c>
       <c r="T96" s="275"/>
       <c r="U96" s="276"/>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.21037720526924217</v>
+        <v>0.26703367242371112</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -19391,11 +19391,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>2.9482928612771571</v>
+        <v>1.9948004945487243</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>0.65604988261999553</v>
+        <v>0.56342103291559731</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -19787,51 +19787,67 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="302" t="s">
+      <c r="B122" s="277" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="302"/>
-      <c r="D122" s="302"/>
+      <c r="C122" s="277"/>
+      <c r="D122" s="277"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="302" t="s">
+      <c r="B123" s="277" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="302"/>
-      <c r="D123" s="302"/>
+      <c r="C123" s="277"/>
+      <c r="D123" s="277"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>-0.34218180961486055</v>
+        <v>1.071688147605764</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="C35:D35"/>
@@ -19845,44 +19861,28 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -19965,40 +19965,40 @@
       </c>
     </row>
     <row r="8" spans="7:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="354">
+      <c r="G8" s="355">
         <v>1</v>
       </c>
-      <c r="H8" s="355" t="s">
+      <c r="H8" s="356" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="355" t="s">
+      <c r="I8" s="356" t="s">
         <v>328</v>
       </c>
-      <c r="J8" s="355" t="s">
+      <c r="J8" s="356" t="s">
         <v>328</v>
       </c>
-      <c r="K8" s="355" t="s">
+      <c r="K8" s="356" t="s">
         <v>328</v>
       </c>
-      <c r="L8" s="355" t="s">
+      <c r="L8" s="356" t="s">
         <v>331</v>
       </c>
-      <c r="M8" s="355" t="s">
+      <c r="M8" s="356" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="355" t="s">
+      <c r="N8" s="356" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="7:14" x14ac:dyDescent="0.3">
-      <c r="G9" s="354"/>
-      <c r="H9" s="355"/>
-      <c r="I9" s="355"/>
-      <c r="J9" s="355"/>
-      <c r="K9" s="355"/>
-      <c r="L9" s="355"/>
-      <c r="M9" s="355"/>
-      <c r="N9" s="355"/>
+      <c r="G9" s="355"/>
+      <c r="H9" s="356"/>
+      <c r="I9" s="356"/>
+      <c r="J9" s="356"/>
+      <c r="K9" s="356"/>
+      <c r="L9" s="356"/>
+      <c r="M9" s="356"/>
+      <c r="N9" s="356"/>
     </row>
     <row r="17" spans="7:20" ht="55.2" x14ac:dyDescent="0.3">
       <c r="G17" s="268" t="s">
@@ -21055,20 +21055,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="319" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21096,26 +21096,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="279" t="s">
+      <c r="A3" s="320" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="279"/>
-      <c r="C3" s="290" t="s">
+      <c r="B3" s="320"/>
+      <c r="C3" s="321" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="290"/>
-      <c r="E3" s="290"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="279" t="s">
+      <c r="G3" s="320" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="279"/>
-      <c r="I3" s="290" t="s">
+      <c r="H3" s="320"/>
+      <c r="I3" s="321" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -21140,28 +21140,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="279" t="s">
+      <c r="A5" s="320" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="279"/>
-      <c r="C5" s="280" t="s">
+      <c r="B5" s="320"/>
+      <c r="C5" s="322" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="320" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="279"/>
-      <c r="I5" s="281">
+      <c r="H5" s="320"/>
+      <c r="I5" s="323">
         <v>10000</v>
       </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="280" t="s">
+      <c r="J5" s="323"/>
+      <c r="K5" s="322" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="280"/>
+      <c r="L5" s="322"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -21192,128 +21192,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="282" t="s">
+      <c r="A9" s="313" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="282"/>
-      <c r="C9" s="282"/>
+      <c r="B9" s="313"/>
+      <c r="C9" s="313"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="282" t="s">
+      <c r="A10" s="313" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="282"/>
-      <c r="C10" s="282"/>
+      <c r="B10" s="313"/>
+      <c r="C10" s="313"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="288"/>
-      <c r="P10" s="288"/>
+      <c r="O10" s="314"/>
+      <c r="P10" s="314"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="291" t="s">
+      <c r="A12" s="315" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="292"/>
-      <c r="C12" s="293"/>
+      <c r="B12" s="316"/>
+      <c r="C12" s="317"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="294"/>
-      <c r="J12" s="294"/>
-      <c r="K12" s="294"/>
-      <c r="M12" s="294"/>
-      <c r="N12" s="294"/>
+      <c r="I12" s="318"/>
+      <c r="J12" s="318"/>
+      <c r="K12" s="318"/>
+      <c r="M12" s="318"/>
+      <c r="N12" s="318"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="286" t="s">
+      <c r="A13" s="311" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="287"/>
+      <c r="B13" s="312"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="283"/>
-      <c r="F13" s="283"/>
+      <c r="E13" s="306"/>
+      <c r="F13" s="306"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="283"/>
-      <c r="J13" s="283"/>
+      <c r="I13" s="306"/>
+      <c r="J13" s="306"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="295" t="s">
+      <c r="A14" s="309" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="296"/>
+      <c r="B14" s="310"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="283"/>
-      <c r="F14" s="283"/>
+      <c r="E14" s="306"/>
+      <c r="F14" s="306"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="283"/>
-      <c r="J14" s="283"/>
+      <c r="I14" s="306"/>
+      <c r="J14" s="306"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="283"/>
-      <c r="N14" s="283"/>
+      <c r="M14" s="306"/>
+      <c r="N14" s="306"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="295" t="s">
+      <c r="A15" s="309" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="296"/>
+      <c r="B15" s="310"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="283"/>
-      <c r="F15" s="283"/>
+      <c r="E15" s="306"/>
+      <c r="F15" s="306"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="283"/>
-      <c r="N15" s="283"/>
+      <c r="M15" s="306"/>
+      <c r="N15" s="306"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="295" t="s">
+      <c r="A16" s="309" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="296"/>
+      <c r="B16" s="310"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="283"/>
-      <c r="J16" s="283"/>
+      <c r="I16" s="306"/>
+      <c r="J16" s="306"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="283"/>
-      <c r="N16" s="283"/>
+      <c r="M16" s="306"/>
+      <c r="N16" s="306"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="297" t="s">
+      <c r="A17" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="298"/>
+      <c r="B17" s="305"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="283"/>
-      <c r="F17" s="283"/>
+      <c r="E17" s="306"/>
+      <c r="F17" s="306"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="283"/>
-      <c r="N17" s="283"/>
+      <c r="M17" s="306"/>
+      <c r="N17" s="306"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="283"/>
-      <c r="N18" s="283"/>
+      <c r="M18" s="306"/>
+      <c r="N18" s="306"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21324,28 +21324,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="284"/>
+      <c r="C21" s="307"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="284"/>
-      <c r="G21" s="284"/>
-      <c r="H21" s="284"/>
+      <c r="E21" s="307"/>
+      <c r="F21" s="307"/>
+      <c r="G21" s="307"/>
+      <c r="H21" s="307"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="284"/>
+      <c r="C22" s="307"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
-      <c r="H22" s="284"/>
+      <c r="E22" s="307"/>
+      <c r="F22" s="307"/>
+      <c r="G22" s="307"/>
+      <c r="H22" s="307"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="285"/>
+      <c r="C23" s="308"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
+      <c r="E23" s="308"/>
+      <c r="F23" s="308"/>
+      <c r="G23" s="308"/>
+      <c r="H23" s="308"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21586,12 +21586,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="299" t="s">
+      <c r="A31" s="297" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="300"/>
-      <c r="C31" s="300"/>
-      <c r="D31" s="300"/>
+      <c r="B31" s="298"/>
+      <c r="C31" s="298"/>
+      <c r="D31" s="298"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21654,19 +21654,19 @@
         <f>B37/B36</f>
         <v>0.9813242784380305</v>
       </c>
-      <c r="C35" s="301" t="s">
+      <c r="C35" s="299" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="301"/>
+      <c r="D35" s="299"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>346.02076124567475</v>
       </c>
-      <c r="F35" s="301" t="s">
+      <c r="F35" s="299" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="301"/>
-      <c r="H35" s="301"/>
+      <c r="G35" s="299"/>
+      <c r="H35" s="299"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21680,19 +21680,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117.8</v>
       </c>
-      <c r="C36" s="301" t="s">
+      <c r="C36" s="299" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="301"/>
+      <c r="D36" s="299"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.89</v>
       </c>
-      <c r="F36" s="301" t="s">
+      <c r="F36" s="299" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="301"/>
-      <c r="H36" s="301"/>
+      <c r="G36" s="299"/>
+      <c r="H36" s="299"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21717,19 +21717,19 @@
         <f>SUM(F25:F30)</f>
         <v>115.6</v>
       </c>
-      <c r="C37" s="301" t="s">
+      <c r="C37" s="299" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="301"/>
+      <c r="D37" s="299"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.6505190311418687</v>
       </c>
-      <c r="F37" s="301" t="s">
+      <c r="F37" s="299" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="301"/>
-      <c r="H37" s="301"/>
+      <c r="G37" s="299"/>
+      <c r="H37" s="299"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3460.2076124567475</v>
@@ -21743,29 +21743,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22398500000000002</v>
       </c>
-      <c r="C38" s="301" t="s">
+      <c r="C38" s="299" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="301"/>
+      <c r="D38" s="299"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.4809010109234002</v>
       </c>
-      <c r="F38" s="301" t="s">
+      <c r="F38" s="299" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="301"/>
-      <c r="H38" s="301"/>
+      <c r="G38" s="299"/>
+      <c r="H38" s="299"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="301" t="s">
+      <c r="C39" s="299" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="301"/>
+      <c r="D39" s="299"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.602076124567475</v>
@@ -21822,11 +21822,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="318" t="s">
+      <c r="A44" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="319"/>
-      <c r="C44" s="320"/>
+      <c r="B44" s="302"/>
+      <c r="C44" s="303"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -21856,11 +21856,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="321" t="s">
+      <c r="A46" s="286" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="321"/>
-      <c r="C46" s="321"/>
+      <c r="B46" s="286"/>
+      <c r="C46" s="286"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -21875,11 +21875,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="321" t="s">
+      <c r="A47" s="286" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="321"/>
-      <c r="C47" s="321"/>
+      <c r="B47" s="286"/>
+      <c r="C47" s="286"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.397190403781075</v>
@@ -21895,11 +21895,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="321" t="s">
+      <c r="A48" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="321"/>
-      <c r="C48" s="321"/>
+      <c r="B48" s="286"/>
+      <c r="C48" s="286"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2193.6744084353313</v>
@@ -21915,11 +21915,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="321" t="s">
+      <c r="A49" s="286" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="321"/>
-      <c r="C49" s="321"/>
+      <c r="B49" s="286"/>
+      <c r="C49" s="286"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -21935,11 +21935,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="321" t="s">
+      <c r="A50" s="286" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="321"/>
-      <c r="C50" s="321"/>
+      <c r="B50" s="286"/>
+      <c r="C50" s="286"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>21936.744084353315</v>
@@ -21970,11 +21970,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="321" t="s">
+      <c r="A52" s="286" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="321"/>
-      <c r="C52" s="321"/>
+      <c r="B52" s="286"/>
+      <c r="C52" s="286"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -21989,11 +21989,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="321" t="s">
+      <c r="A53" s="286" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="321"/>
-      <c r="C53" s="321"/>
+      <c r="B53" s="286"/>
+      <c r="C53" s="286"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.22615683819515</v>
@@ -22139,7 +22139,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4092.6347009391993</v>
       </c>
-      <c r="H60" s="315">
+      <c r="H60" s="287">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9441.736856218844</v>
       </c>
@@ -22173,7 +22173,7 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2596.1802021846802</v>
       </c>
-      <c r="H61" s="316"/>
+      <c r="H61" s="288"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -22204,7 +22204,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H62" s="316"/>
+      <c r="H62" s="288"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22235,7 +22235,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H63" s="316"/>
+      <c r="H63" s="288"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22266,7 +22266,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H64" s="316"/>
+      <c r="H64" s="288"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22297,7 +22297,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H65" s="316"/>
+      <c r="H65" s="288"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22328,7 +22328,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H66" s="316"/>
+      <c r="H66" s="288"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22358,7 +22358,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="316"/>
+      <c r="H67" s="288"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22388,7 +22388,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="316"/>
+      <c r="H68" s="288"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22418,7 +22418,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="317"/>
+      <c r="H69" s="289"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22478,23 +22478,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="305"/>
-      <c r="C73" s="306" t="s">
+      <c r="B73" s="290"/>
+      <c r="C73" s="291" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="308" t="s">
+      <c r="E73" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="310" t="s">
+      <c r="F73" s="295" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="310" t="s">
+      <c r="G73" s="295" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="312" t="s">
+      <c r="H73" s="284" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22507,15 +22507,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="305"/>
-      <c r="C74" s="307"/>
+      <c r="B74" s="290"/>
+      <c r="C74" s="292"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="309"/>
-      <c r="F74" s="311"/>
-      <c r="G74" s="311"/>
-      <c r="H74" s="313"/>
+      <c r="E74" s="294"/>
+      <c r="F74" s="296"/>
+      <c r="G74" s="296"/>
+      <c r="H74" s="285"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22746,9 +22746,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="304"/>
-      <c r="I82" s="304"/>
-      <c r="J82" s="304"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22756,19 +22756,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="303" t="s">
+      <c r="B83" s="279" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="303"/>
-      <c r="D83" s="303"/>
-      <c r="E83" s="303"/>
-      <c r="F83" s="303"/>
-      <c r="G83" s="303"/>
-      <c r="H83" s="303"/>
-      <c r="I83" s="303"/>
-      <c r="J83" s="303"/>
-      <c r="K83" s="303"/>
-      <c r="L83" s="303"/>
+      <c r="C83" s="279"/>
+      <c r="D83" s="279"/>
+      <c r="E83" s="279"/>
+      <c r="F83" s="279"/>
+      <c r="G83" s="279"/>
+      <c r="H83" s="279"/>
+      <c r="I83" s="279"/>
+      <c r="J83" s="279"/>
+      <c r="K83" s="279"/>
+      <c r="L83" s="279"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -22853,11 +22853,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="314"/>
-      <c r="I88" s="314"/>
+      <c r="H88" s="280"/>
+      <c r="I88" s="280"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="314"/>
-      <c r="L88" s="314"/>
+      <c r="K88" s="280"/>
+      <c r="L88" s="280"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -22947,10 +22947,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="273" t="s">
+      <c r="Q92" s="281" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="273"/>
+      <c r="R92" s="281"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7630361423692897</v>
@@ -23010,10 +23010,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="277" t="s">
+      <c r="T94" s="282" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="278"/>
+      <c r="U94" s="283"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -23540,22 +23540,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="302" t="s">
+      <c r="B122" s="277" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="302"/>
-      <c r="D122" s="302"/>
+      <c r="C122" s="277"/>
+      <c r="D122" s="277"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="302" t="s">
+      <c r="B123" s="277" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="302"/>
-      <c r="D123" s="302"/>
+      <c r="C123" s="277"/>
+      <c r="D123" s="277"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-2.6611699687135438E-2</v>
@@ -23563,63 +23563,6 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23636,6 +23579,63 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -23742,16 +23742,16 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="323" t="s">
+      <c r="W1" s="324" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="323"/>
-      <c r="Y1" s="323"/>
-      <c r="Z1" s="323"/>
-      <c r="AA1" s="323"/>
-      <c r="AB1" s="323"/>
-      <c r="AC1" s="323"/>
-      <c r="AD1" s="323"/>
+      <c r="X1" s="324"/>
+      <c r="Y1" s="324"/>
+      <c r="Z1" s="324"/>
+      <c r="AA1" s="324"/>
+      <c r="AB1" s="324"/>
+      <c r="AC1" s="324"/>
+      <c r="AD1" s="324"/>
     </row>
     <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
@@ -24520,20 +24520,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="319" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24563,26 +24563,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="279" t="s">
+      <c r="A3" s="320" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="279"/>
-      <c r="C3" s="290" t="s">
+      <c r="B3" s="320"/>
+      <c r="C3" s="321" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="290"/>
-      <c r="E3" s="290"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="279" t="s">
+      <c r="G3" s="320" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="279"/>
-      <c r="I3" s="290" t="s">
+      <c r="H3" s="320"/>
+      <c r="I3" s="321" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24609,28 +24609,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="279" t="s">
+      <c r="A5" s="320" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="279"/>
-      <c r="C5" s="280" t="s">
+      <c r="B5" s="320"/>
+      <c r="C5" s="322" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="320" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="279"/>
-      <c r="I5" s="281">
+      <c r="H5" s="320"/>
+      <c r="I5" s="323">
         <v>20000</v>
       </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="280" t="s">
+      <c r="J5" s="323"/>
+      <c r="K5" s="322" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="280"/>
+      <c r="L5" s="322"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24663,105 +24663,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="282" t="s">
+      <c r="A9" s="313" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="282"/>
-      <c r="C9" s="282"/>
+      <c r="B9" s="313"/>
+      <c r="C9" s="313"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="282" t="s">
+      <c r="A10" s="313" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="282"/>
-      <c r="C10" s="282"/>
-      <c r="N10" s="288"/>
-      <c r="O10" s="288"/>
-      <c r="P10" s="288"/>
-      <c r="Q10" s="288"/>
+      <c r="B10" s="313"/>
+      <c r="C10" s="313"/>
+      <c r="N10" s="314"/>
+      <c r="O10" s="314"/>
+      <c r="P10" s="314"/>
+      <c r="Q10" s="314"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="294"/>
-      <c r="B12" s="294"/>
-      <c r="C12" s="294"/>
-      <c r="E12" s="337" t="s">
+      <c r="A12" s="318"/>
+      <c r="B12" s="318"/>
+      <c r="C12" s="318"/>
+      <c r="E12" s="328" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="338"/>
-      <c r="G12" s="339"/>
-      <c r="I12" s="294"/>
-      <c r="J12" s="294"/>
-      <c r="K12" s="294"/>
-      <c r="M12" s="294"/>
-      <c r="N12" s="294"/>
-      <c r="O12" s="294"/>
+      <c r="F12" s="329"/>
+      <c r="G12" s="330"/>
+      <c r="I12" s="318"/>
+      <c r="J12" s="318"/>
+      <c r="K12" s="318"/>
+      <c r="M12" s="318"/>
+      <c r="N12" s="318"/>
+      <c r="O12" s="318"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="283"/>
-      <c r="B13" s="283"/>
+      <c r="A13" s="306"/>
+      <c r="B13" s="306"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="340" t="s">
+      <c r="E13" s="331" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="341"/>
+      <c r="F13" s="332"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="283"/>
-      <c r="J13" s="283"/>
+      <c r="I13" s="306"/>
+      <c r="J13" s="306"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="283"/>
-      <c r="N13" s="283"/>
+      <c r="M13" s="306"/>
+      <c r="N13" s="306"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="283"/>
-      <c r="B14" s="283"/>
+      <c r="A14" s="306"/>
+      <c r="B14" s="306"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="295" t="s">
+      <c r="E14" s="309" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="296"/>
+      <c r="F14" s="310"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="283"/>
-      <c r="J14" s="283"/>
+      <c r="I14" s="306"/>
+      <c r="J14" s="306"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="283"/>
-      <c r="N14" s="283"/>
+      <c r="M14" s="306"/>
+      <c r="N14" s="306"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="283"/>
-      <c r="B15" s="283"/>
+      <c r="A15" s="306"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="335" t="s">
+      <c r="E15" s="326" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="336"/>
+      <c r="F15" s="327"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="283"/>
-      <c r="N15" s="283"/>
+      <c r="M15" s="306"/>
+      <c r="N15" s="306"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="283"/>
-      <c r="B16" s="283"/>
+      <c r="A16" s="306"/>
+      <c r="B16" s="306"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -24770,74 +24770,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="283"/>
-      <c r="J16" s="283"/>
+      <c r="I16" s="306"/>
+      <c r="J16" s="306"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="283"/>
-      <c r="N16" s="283"/>
+      <c r="M16" s="306"/>
+      <c r="N16" s="306"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="283"/>
-      <c r="B17" s="283"/>
+      <c r="A17" s="306"/>
+      <c r="B17" s="306"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="297" t="s">
+      <c r="E17" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="298"/>
+      <c r="F17" s="305"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="283"/>
-      <c r="N17" s="283"/>
+      <c r="M17" s="306"/>
+      <c r="N17" s="306"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="283"/>
-      <c r="N18" s="283"/>
+      <c r="M18" s="306"/>
+      <c r="N18" s="306"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="342"/>
-      <c r="N19" s="342"/>
+      <c r="M19" s="325"/>
+      <c r="N19" s="325"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="342"/>
-      <c r="N20" s="342"/>
+      <c r="M20" s="325"/>
+      <c r="N20" s="325"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="284" t="s">
+      <c r="C21" s="307" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="284" t="s">
+      <c r="E21" s="307" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="284"/>
-      <c r="G21" s="284" t="s">
+      <c r="F21" s="307"/>
+      <c r="G21" s="307" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="284" t="s">
+      <c r="H21" s="307" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="284"/>
+      <c r="C22" s="307"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
-      <c r="H22" s="284"/>
+      <c r="E22" s="307"/>
+      <c r="F22" s="307"/>
+      <c r="G22" s="307"/>
+      <c r="H22" s="307"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="285"/>
+      <c r="C23" s="308"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
+      <c r="E23" s="308"/>
+      <c r="F23" s="308"/>
+      <c r="G23" s="308"/>
+      <c r="H23" s="308"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -25014,12 +25014,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="299" t="s">
+      <c r="A31" s="297" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="300"/>
-      <c r="C31" s="300"/>
-      <c r="D31" s="300"/>
+      <c r="B31" s="298"/>
+      <c r="C31" s="298"/>
+      <c r="D31" s="298"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -25082,19 +25082,19 @@
         <f>B37/B36</f>
         <v>0.91666666666666674</v>
       </c>
-      <c r="C35" s="301" t="s">
+      <c r="C35" s="299" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="301"/>
+      <c r="D35" s="299"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5431.9647769676003</v>
       </c>
-      <c r="F35" s="301" t="s">
+      <c r="F35" s="299" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="301"/>
-      <c r="H35" s="301"/>
+      <c r="G35" s="299"/>
+      <c r="H35" s="299"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -25108,19 +25108,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37.799999999999997</v>
       </c>
-      <c r="C36" s="301" t="s">
+      <c r="C36" s="299" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="301"/>
+      <c r="D36" s="299"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.18409544999999999</v>
       </c>
-      <c r="F36" s="301" t="s">
+      <c r="F36" s="299" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="301"/>
-      <c r="H36" s="301"/>
+      <c r="G36" s="299"/>
+      <c r="H36" s="299"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -25139,19 +25139,19 @@
         <f>SUM(F25:F30)</f>
         <v>34.65</v>
       </c>
-      <c r="C37" s="301" t="s">
+      <c r="C37" s="299" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="301"/>
+      <c r="D37" s="299"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>28.860028860028862</v>
       </c>
-      <c r="F37" s="301" t="s">
+      <c r="F37" s="299" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="301"/>
-      <c r="H37" s="301"/>
+      <c r="G37" s="299"/>
+      <c r="H37" s="299"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>108639.29553935201</v>
@@ -25165,37 +25165,37 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10634300000000001</v>
       </c>
-      <c r="C38" s="301" t="s">
+      <c r="C38" s="299" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="301"/>
+      <c r="D38" s="299"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>28.574286000028575</v>
       </c>
-      <c r="F38" s="301" t="s">
+      <c r="F38" s="299" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="301"/>
-      <c r="H38" s="301"/>
+      <c r="G38" s="299"/>
+      <c r="H38" s="299"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="301" t="s">
+      <c r="C39" s="299" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="301"/>
+      <c r="D39" s="299"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="301"/>
-      <c r="D40" s="301"/>
+      <c r="C40" s="299"/>
+      <c r="D40" s="299"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25245,11 +25245,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="318" t="s">
+      <c r="A44" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="319"/>
-      <c r="C44" s="320"/>
+      <c r="B44" s="302"/>
+      <c r="C44" s="303"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25279,11 +25279,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="321" t="s">
+      <c r="A46" s="286" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="321"/>
-      <c r="C46" s="321"/>
+      <c r="B46" s="286"/>
+      <c r="C46" s="286"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25298,11 +25298,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="321" t="s">
+      <c r="A47" s="286" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="321"/>
-      <c r="C47" s="321"/>
+      <c r="B47" s="286"/>
+      <c r="C47" s="286"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.8170490707388822</v>
@@ -25318,11 +25318,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="321" t="s">
+      <c r="A48" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="321"/>
-      <c r="C48" s="321"/>
+      <c r="B48" s="286"/>
+      <c r="C48" s="286"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6836.3715691450298</v>
@@ -25338,11 +25338,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="321" t="s">
+      <c r="A49" s="286" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="321"/>
-      <c r="C49" s="321"/>
+      <c r="B49" s="286"/>
+      <c r="C49" s="286"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25358,11 +25358,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="321" t="s">
+      <c r="A50" s="286" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="321"/>
-      <c r="C50" s="321"/>
+      <c r="B50" s="286"/>
+      <c r="C50" s="286"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>42461.93521208092</v>
@@ -25393,11 +25393,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="321" t="s">
+      <c r="A52" s="286" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="321"/>
-      <c r="C52" s="321"/>
+      <c r="B52" s="286"/>
+      <c r="C52" s="286"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25412,11 +25412,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="321" t="s">
+      <c r="A53" s="286" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="321"/>
-      <c r="C53" s="321"/>
+      <c r="B53" s="286"/>
+      <c r="C53" s="286"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1737.6438086744588</v>
@@ -25559,7 +25559,7 @@
         <f>F60*E60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="332">
+      <c r="H60" s="333">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>141966.47760014096</v>
       </c>
@@ -25593,7 +25593,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>12329.714400011429</v>
       </c>
-      <c r="H61" s="333"/>
+      <c r="H61" s="334"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -25623,7 +25623,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H62" s="333"/>
+      <c r="H62" s="334"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -25653,7 +25653,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H63" s="333"/>
+      <c r="H63" s="334"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -25683,7 +25683,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H64" s="333"/>
+      <c r="H64" s="334"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -25713,7 +25713,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H65" s="333"/>
+      <c r="H65" s="334"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -25744,7 +25744,7 @@
         <f t="shared" si="3"/>
         <v>977.47620000095242</v>
       </c>
-      <c r="H66" s="333"/>
+      <c r="H66" s="334"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -25775,7 +25775,7 @@
         <f t="shared" si="3"/>
         <v>57198.572000057153</v>
       </c>
-      <c r="H67" s="333"/>
+      <c r="H67" s="334"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -25807,7 +25807,7 @@
         <f t="shared" si="3"/>
         <v>71460.715000071446</v>
       </c>
-      <c r="H68" s="333"/>
+      <c r="H68" s="334"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -25837,7 +25837,7 @@
         <f>F69*E69</f>
         <v>0</v>
       </c>
-      <c r="H69" s="334"/>
+      <c r="H69" s="335"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -25897,23 +25897,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="305"/>
-      <c r="C73" s="306" t="s">
+      <c r="B73" s="290"/>
+      <c r="C73" s="291" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="308" t="s">
+      <c r="E73" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="310" t="s">
+      <c r="F73" s="295" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="310" t="s">
+      <c r="G73" s="295" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="312" t="s">
+      <c r="H73" s="284" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -25927,15 +25927,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="305"/>
-      <c r="C74" s="307"/>
+      <c r="B74" s="290"/>
+      <c r="C74" s="292"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="309"/>
-      <c r="F74" s="311"/>
-      <c r="G74" s="311"/>
-      <c r="H74" s="313"/>
+      <c r="E74" s="294"/>
+      <c r="F74" s="296"/>
+      <c r="G74" s="296"/>
+      <c r="H74" s="285"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -26174,9 +26174,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="304"/>
-      <c r="I82" s="304"/>
-      <c r="J82" s="304"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -26184,19 +26184,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="303" t="s">
+      <c r="B83" s="279" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="303"/>
-      <c r="D83" s="303"/>
-      <c r="E83" s="303"/>
-      <c r="F83" s="303"/>
-      <c r="G83" s="303"/>
-      <c r="H83" s="303"/>
-      <c r="I83" s="303"/>
-      <c r="J83" s="303"/>
-      <c r="K83" s="303"/>
-      <c r="L83" s="303"/>
+      <c r="C83" s="279"/>
+      <c r="D83" s="279"/>
+      <c r="E83" s="279"/>
+      <c r="F83" s="279"/>
+      <c r="G83" s="279"/>
+      <c r="H83" s="279"/>
+      <c r="I83" s="279"/>
+      <c r="J83" s="279"/>
+      <c r="K83" s="279"/>
+      <c r="L83" s="279"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26262,17 +26262,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="324" t="s">
+      <c r="H87" s="336" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="325"/>
+      <c r="I87" s="337"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="326" t="s">
+      <c r="K87" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="327"/>
+      <c r="L87" s="339"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26284,20 +26284,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="328">
+      <c r="H88" s="340">
         <f>C75+H70</f>
         <v>10.167385929069098</v>
       </c>
-      <c r="I88" s="329"/>
+      <c r="I88" s="341"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.98761894452246557</v>
       </c>
-      <c r="K88" s="330">
+      <c r="K88" s="342">
         <f>E106+E122</f>
         <v>20.20888888888889</v>
       </c>
-      <c r="L88" s="331"/>
+      <c r="L88" s="343"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26369,10 +26369,10 @@
         <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="273" t="s">
+      <c r="Q92" s="281" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="273"/>
+      <c r="R92" s="281"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.388104543787712</v>
@@ -26426,10 +26426,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="277" t="s">
+      <c r="T94" s="282" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="278"/>
+      <c r="U94" s="283"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26965,11 +26965,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="302" t="s">
+      <c r="B122" s="277" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="302"/>
-      <c r="D122" s="302"/>
+      <c r="C122" s="277"/>
+      <c r="D122" s="277"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -26977,11 +26977,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="302" t="s">
+      <c r="B123" s="277" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="302"/>
-      <c r="D123" s="302"/>
+      <c r="C123" s="277"/>
+      <c r="D123" s="277"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.76989873089142391</v>
@@ -27011,29 +27011,47 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="A1:L1"/>
@@ -27050,47 +27068,29 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -27162,20 +27162,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="319" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
+      <c r="B1" s="319"/>
+      <c r="C1" s="319"/>
+      <c r="D1" s="319"/>
+      <c r="E1" s="319"/>
+      <c r="F1" s="319"/>
+      <c r="G1" s="319"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27205,26 +27205,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="279" t="s">
+      <c r="A3" s="320" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="279"/>
-      <c r="C3" s="290" t="s">
+      <c r="B3" s="320"/>
+      <c r="C3" s="321" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="290"/>
-      <c r="E3" s="290"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="279" t="s">
+      <c r="G3" s="320" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="279"/>
-      <c r="I3" s="290" t="s">
+      <c r="H3" s="320"/>
+      <c r="I3" s="321" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27251,28 +27251,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="279" t="s">
+      <c r="A5" s="320" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="279"/>
-      <c r="C5" s="280" t="s">
+      <c r="B5" s="320"/>
+      <c r="C5" s="322" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="322"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="320" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="279"/>
-      <c r="I5" s="281">
+      <c r="H5" s="320"/>
+      <c r="I5" s="323">
         <v>500</v>
       </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="280" t="s">
+      <c r="J5" s="323"/>
+      <c r="K5" s="322" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="280"/>
+      <c r="L5" s="322"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27305,86 +27305,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="282" t="s">
+      <c r="A9" s="313" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="282"/>
-      <c r="C9" s="282"/>
+      <c r="B9" s="313"/>
+      <c r="C9" s="313"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="282" t="s">
+      <c r="A10" s="313" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="282"/>
-      <c r="C10" s="282"/>
-      <c r="N10" s="288"/>
-      <c r="O10" s="288"/>
-      <c r="P10" s="288"/>
-      <c r="Q10" s="288"/>
+      <c r="B10" s="313"/>
+      <c r="C10" s="313"/>
+      <c r="N10" s="314"/>
+      <c r="O10" s="314"/>
+      <c r="P10" s="314"/>
+      <c r="Q10" s="314"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="294"/>
-      <c r="B12" s="294"/>
-      <c r="C12" s="294"/>
-      <c r="E12" s="294"/>
-      <c r="F12" s="294"/>
-      <c r="G12" s="294"/>
-      <c r="I12" s="343" t="s">
+      <c r="A12" s="318"/>
+      <c r="B12" s="318"/>
+      <c r="C12" s="318"/>
+      <c r="E12" s="318"/>
+      <c r="F12" s="318"/>
+      <c r="G12" s="318"/>
+      <c r="I12" s="350" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="344"/>
-      <c r="K12" s="345"/>
-      <c r="M12" s="343" t="s">
+      <c r="J12" s="351"/>
+      <c r="K12" s="352"/>
+      <c r="M12" s="350" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="344"/>
-      <c r="O12" s="345"/>
+      <c r="N12" s="351"/>
+      <c r="O12" s="352"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="283"/>
-      <c r="B13" s="283"/>
+      <c r="A13" s="306"/>
+      <c r="B13" s="306"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="283"/>
-      <c r="F13" s="283"/>
+      <c r="E13" s="306"/>
+      <c r="F13" s="306"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="340" t="s">
+      <c r="I13" s="331" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="341"/>
+      <c r="J13" s="332"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="340" t="s">
+      <c r="M13" s="331" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="341"/>
+      <c r="N13" s="332"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="283"/>
-      <c r="B14" s="283"/>
+      <c r="A14" s="306"/>
+      <c r="B14" s="306"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="283"/>
-      <c r="F14" s="283"/>
+      <c r="E14" s="306"/>
+      <c r="F14" s="306"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="295" t="s">
+      <c r="I14" s="309" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="296"/>
+      <c r="J14" s="310"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="295" t="s">
+      <c r="M14" s="309" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="296"/>
+      <c r="N14" s="310"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27392,11 +27392,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="283"/>
-      <c r="B15" s="283"/>
+      <c r="A15" s="306"/>
+      <c r="B15" s="306"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="283"/>
-      <c r="F15" s="283"/>
+      <c r="E15" s="306"/>
+      <c r="F15" s="306"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27405,10 +27405,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="295" t="s">
+      <c r="M15" s="309" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="296"/>
+      <c r="N15" s="310"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27417,103 +27417,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="283"/>
-      <c r="B16" s="283"/>
+      <c r="A16" s="306"/>
+      <c r="B16" s="306"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="297" t="s">
+      <c r="I16" s="304" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="298"/>
+      <c r="J16" s="305"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="295" t="s">
+      <c r="M16" s="309" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="296"/>
+      <c r="N16" s="310"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="283"/>
-      <c r="B17" s="283"/>
+      <c r="A17" s="306"/>
+      <c r="B17" s="306"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="283"/>
-      <c r="F17" s="283"/>
+      <c r="E17" s="306"/>
+      <c r="F17" s="306"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="295" t="s">
+      <c r="M17" s="309" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="296"/>
+      <c r="N17" s="310"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="295" t="s">
+      <c r="M18" s="309" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="296"/>
+      <c r="N18" s="310"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="348" t="s">
+      <c r="M19" s="344" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="349"/>
+      <c r="N19" s="345"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="350"/>
-      <c r="N20" s="351"/>
+      <c r="M20" s="346"/>
+      <c r="N20" s="347"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="284" t="s">
+      <c r="C21" s="307" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="284" t="s">
+      <c r="E21" s="307" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="284"/>
-      <c r="G21" s="284" t="s">
+      <c r="F21" s="307"/>
+      <c r="G21" s="307" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="284" t="s">
+      <c r="H21" s="307" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="284"/>
+      <c r="C22" s="307"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
-      <c r="H22" s="284"/>
+      <c r="E22" s="307"/>
+      <c r="F22" s="307"/>
+      <c r="G22" s="307"/>
+      <c r="H22" s="307"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="285"/>
+      <c r="C23" s="308"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
+      <c r="E23" s="308"/>
+      <c r="F23" s="308"/>
+      <c r="G23" s="308"/>
+      <c r="H23" s="308"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -27896,12 +27896,12 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="346" t="s">
+      <c r="A33" s="348" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="347"/>
-      <c r="C33" s="347"/>
-      <c r="D33" s="347"/>
+      <c r="B33" s="349"/>
+      <c r="C33" s="349"/>
+      <c r="D33" s="349"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -27947,19 +27947,19 @@
         <f>B37/B36</f>
         <v>1.0597680097680098</v>
       </c>
-      <c r="C35" s="301" t="s">
+      <c r="C35" s="299" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="301"/>
+      <c r="D35" s="299"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.809590059054404</v>
       </c>
-      <c r="F35" s="301" t="s">
+      <c r="F35" s="299" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="301"/>
-      <c r="H35" s="301"/>
+      <c r="G35" s="299"/>
+      <c r="H35" s="299"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -27973,19 +27973,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163.80000000000001</v>
       </c>
-      <c r="C36" s="301" t="s">
+      <c r="C36" s="299" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="301"/>
+      <c r="D36" s="299"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.745288000000002</v>
       </c>
-      <c r="F36" s="301" t="s">
+      <c r="F36" s="299" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="301"/>
-      <c r="H36" s="301"/>
+      <c r="G36" s="299"/>
+      <c r="H36" s="299"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -28004,19 +28004,19 @@
         <f>SUM(F25:F32)</f>
         <v>173.59</v>
       </c>
-      <c r="C37" s="301" t="s">
+      <c r="C37" s="299" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="301"/>
+      <c r="D37" s="299"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7607005011809438</v>
       </c>
-      <c r="F37" s="301" t="s">
+      <c r="F37" s="299" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="301"/>
-      <c r="H37" s="301"/>
+      <c r="G37" s="299"/>
+      <c r="H37" s="299"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>500</v>
@@ -28030,29 +28030,29 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.38158350000000002</v>
       </c>
-      <c r="C38" s="301" t="s">
+      <c r="C38" s="299" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="301"/>
+      <c r="D38" s="299"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.063895264400994</v>
       </c>
-      <c r="F38" s="301" t="s">
+      <c r="F38" s="299" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="301"/>
-      <c r="H38" s="301"/>
+      <c r="G38" s="299"/>
+      <c r="H38" s="299"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="301" t="s">
+      <c r="C39" s="299" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="301"/>
+      <c r="D39" s="299"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0009729183068661</v>
@@ -28106,11 +28106,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="318" t="s">
+      <c r="A44" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="319"/>
-      <c r="C44" s="320"/>
+      <c r="B44" s="302"/>
+      <c r="C44" s="303"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -28140,11 +28140,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="321" t="s">
+      <c r="A46" s="286" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="321"/>
-      <c r="C46" s="321"/>
+      <c r="B46" s="286"/>
+      <c r="C46" s="286"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -28159,11 +28159,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="321" t="s">
+      <c r="A47" s="286" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="321"/>
-      <c r="C47" s="321"/>
+      <c r="B47" s="286"/>
+      <c r="C47" s="286"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.372179596826548</v>
@@ -28179,11 +28179,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="321" t="s">
+      <c r="A48" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="321"/>
-      <c r="C48" s="321"/>
+      <c r="B48" s="286"/>
+      <c r="C48" s="286"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>283.01185101569587</v>
@@ -28199,11 +28199,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="321" t="s">
+      <c r="A49" s="286" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="321"/>
-      <c r="C49" s="321"/>
+      <c r="B49" s="286"/>
+      <c r="C49" s="286"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28219,11 +28219,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="321" t="s">
+      <c r="A50" s="286" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="321"/>
-      <c r="C50" s="321"/>
+      <c r="B50" s="286"/>
+      <c r="C50" s="286"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>912.94145488934146</v>
@@ -28254,11 +28254,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="321" t="s">
+      <c r="A52" s="286" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="321"/>
-      <c r="C52" s="321"/>
+      <c r="B52" s="286"/>
+      <c r="C52" s="286"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28273,11 +28273,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="321" t="s">
+      <c r="A53" s="286" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="321"/>
-      <c r="C53" s="321"/>
+      <c r="B53" s="286"/>
+      <c r="C53" s="286"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.25705038862782</v>
@@ -28423,7 +28423,7 @@
         <f>F60*E60</f>
         <v>6892.3268571428589</v>
       </c>
-      <c r="H60" s="332">
+      <c r="H60" s="333">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>17057.940892230581</v>
       </c>
@@ -28457,7 +28457,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>3249.4736842105267</v>
       </c>
-      <c r="H61" s="333"/>
+      <c r="H61" s="334"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -28488,7 +28488,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H62" s="333"/>
+      <c r="H62" s="334"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -28519,7 +28519,7 @@
         <f t="shared" si="3"/>
         <v>1078.9473684210527</v>
       </c>
-      <c r="H63" s="333"/>
+      <c r="H63" s="334"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -28550,7 +28550,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H64" s="333"/>
+      <c r="H64" s="334"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -28581,7 +28581,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H65" s="333"/>
+      <c r="H65" s="334"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -28612,7 +28612,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H66" s="333"/>
+      <c r="H66" s="334"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -28642,7 +28642,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H67" s="333"/>
+      <c r="H67" s="334"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -28673,7 +28673,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="333"/>
+      <c r="H68" s="334"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -28704,7 +28704,7 @@
         <f>F69*E69</f>
         <v>4216.6666666666661</v>
       </c>
-      <c r="H69" s="334"/>
+      <c r="H69" s="335"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -28764,23 +28764,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="305"/>
-      <c r="C73" s="306" t="s">
+      <c r="B73" s="290"/>
+      <c r="C73" s="291" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="308" t="s">
+      <c r="E73" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="310" t="s">
+      <c r="F73" s="295" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="310" t="s">
+      <c r="G73" s="295" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="312" t="s">
+      <c r="H73" s="284" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -28794,15 +28794,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="305"/>
-      <c r="C74" s="307"/>
+      <c r="B74" s="290"/>
+      <c r="C74" s="292"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="309"/>
-      <c r="F74" s="311"/>
-      <c r="G74" s="311"/>
-      <c r="H74" s="313"/>
+      <c r="E74" s="294"/>
+      <c r="F74" s="296"/>
+      <c r="G74" s="296"/>
+      <c r="H74" s="285"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -29041,9 +29041,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="304"/>
-      <c r="I82" s="304"/>
-      <c r="J82" s="304"/>
+      <c r="H82" s="278"/>
+      <c r="I82" s="278"/>
+      <c r="J82" s="278"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -29051,19 +29051,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="303" t="s">
+      <c r="B83" s="279" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="303"/>
-      <c r="D83" s="303"/>
-      <c r="E83" s="303"/>
-      <c r="F83" s="303"/>
-      <c r="G83" s="303"/>
-      <c r="H83" s="303"/>
-      <c r="I83" s="303"/>
-      <c r="J83" s="303"/>
-      <c r="K83" s="303"/>
-      <c r="L83" s="303"/>
+      <c r="C83" s="279"/>
+      <c r="D83" s="279"/>
+      <c r="E83" s="279"/>
+      <c r="F83" s="279"/>
+      <c r="G83" s="279"/>
+      <c r="H83" s="279"/>
+      <c r="I83" s="279"/>
+      <c r="J83" s="279"/>
+      <c r="K83" s="279"/>
+      <c r="L83" s="279"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -29129,17 +29129,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="324" t="s">
+      <c r="H87" s="336" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="325"/>
+      <c r="I87" s="337"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="326" t="s">
+      <c r="K87" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="327"/>
+      <c r="L87" s="339"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -29151,20 +29151,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="328">
+      <c r="H88" s="340">
         <f>C75+H70</f>
         <v>3.0787051830524823</v>
       </c>
-      <c r="I88" s="329"/>
+      <c r="I88" s="341"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>6.0858781331305026E-2</v>
       </c>
-      <c r="K88" s="330">
+      <c r="K88" s="342">
         <f>E106+E122</f>
         <v>3.2660714285714287</v>
       </c>
-      <c r="L88" s="331"/>
+      <c r="L88" s="343"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29235,10 +29235,10 @@
         <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="273" t="s">
+      <c r="Q92" s="281" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="273"/>
+      <c r="R92" s="281"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0381616609601965</v>
@@ -29296,10 +29296,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="277" t="s">
+      <c r="T94" s="282" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="278"/>
+      <c r="U94" s="283"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29851,11 +29851,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="302" t="s">
+      <c r="B122" s="277" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="302"/>
-      <c r="D122" s="302"/>
+      <c r="C122" s="277"/>
+      <c r="D122" s="277"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -29863,11 +29863,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="302" t="s">
+      <c r="B123" s="277" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="302"/>
-      <c r="D123" s="302"/>
+      <c r="C123" s="277"/>
+      <c r="D123" s="277"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>0.10324804175431759</v>
@@ -29897,6 +29897,72 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -29910,72 +29976,6 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -30026,17 +30026,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G1" s="352" t="s">
+      <c r="G1" s="353" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="352"/>
-      <c r="I1" s="352"/>
-      <c r="J1" s="352"/>
-      <c r="K1" s="352" t="s">
+      <c r="H1" s="353"/>
+      <c r="I1" s="353"/>
+      <c r="J1" s="353"/>
+      <c r="K1" s="353" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="352"/>
-      <c r="M1" s="352"/>
+      <c r="L1" s="353"/>
+      <c r="M1" s="353"/>
       <c r="N1" s="172"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
@@ -30138,7 +30138,7 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="353" t="s">
+      <c r="Q7" s="354" t="s">
         <v>218</v>
       </c>
     </row>
@@ -30152,7 +30152,7 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="353"/>
+      <c r="Q8" s="354"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
@@ -30164,7 +30164,7 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="353"/>
+      <c r="Q9" s="354"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
@@ -30176,7 +30176,7 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="353"/>
+      <c r="Q10" s="354"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
@@ -30188,7 +30188,7 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="353"/>
+      <c r="Q11" s="354"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
@@ -30200,7 +30200,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="353"/>
+      <c r="Q12" s="354"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295F4756-C7F0-4892-8428-1C09AC56C009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529A7954-5EC5-4FCA-94A2-2C36BB0BA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="PE Bag" sheetId="11" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Overall" sheetId="6" r:id="rId8"/>
     <sheet name="Sheet1" sheetId="7" r:id="rId9"/>
     <sheet name="Sheet2" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet4" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Substrate Costing Master'!$A$1:$F$46</definedName>
@@ -122,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="341">
   <si>
     <t>Roll</t>
   </si>
@@ -1149,12 +1150,24 @@
   <si>
     <t>Toluene</t>
   </si>
+  <si>
+    <t>Pieces/Kg</t>
+  </si>
+  <si>
+    <t>LM per Kg</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>∞</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="23">
+  <numFmts count="24">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.00\ &quot;mm&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -1178,8 +1191,9 @@
     <numFmt numFmtId="183" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
     <numFmt numFmtId="184" formatCode="0.0%"/>
     <numFmt numFmtId="185" formatCode="\$0.00"/>
+    <numFmt numFmtId="186" formatCode="#,##0\ &quot;Pcs&quot;"/>
   </numFmts>
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1529,6 +1543,19 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Trebuchet MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2706,7 +2733,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="357">
+  <cellXfs count="364">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3344,44 +3371,95 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3413,122 +3491,38 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3554,6 +3548,54 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3566,21 +3608,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3592,6 +3619,23 @@
     </xf>
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="186" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -17354,20 +17398,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="277" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="319"/>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
-      <c r="K1" s="319"/>
-      <c r="L1" s="319"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
+      <c r="K1" s="277"/>
+      <c r="L1" s="277"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17395,26 +17439,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="320" t="s">
+      <c r="A3" s="274" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="321" t="s">
+      <c r="B3" s="274"/>
+      <c r="C3" s="278" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="320" t="s">
+      <c r="G3" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="320"/>
-      <c r="I3" s="321" t="s">
+      <c r="H3" s="274"/>
+      <c r="I3" s="278" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="321"/>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="278"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17439,28 +17483,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="320" t="s">
+      <c r="A5" s="274" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="322" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="275" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
+      <c r="D5" s="275"/>
+      <c r="E5" s="275"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="274" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="320"/>
-      <c r="I5" s="323">
+      <c r="H5" s="274"/>
+      <c r="I5" s="276">
         <v>10000</v>
       </c>
-      <c r="J5" s="323"/>
-      <c r="K5" s="322" t="s">
+      <c r="J5" s="276"/>
+      <c r="K5" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="322"/>
+      <c r="L5" s="275"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17491,174 +17535,174 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="313" t="s">
+      <c r="A9" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="313"/>
-      <c r="C9" s="313"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="313" t="s">
+      <c r="A10" s="279" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="313"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="314"/>
-      <c r="P10" s="314"/>
+      <c r="O10" s="280"/>
+      <c r="P10" s="280"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="315" t="s">
+      <c r="A12" s="281" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="316"/>
-      <c r="C12" s="317"/>
+      <c r="B12" s="282"/>
+      <c r="C12" s="283"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="318"/>
-      <c r="J12" s="318"/>
-      <c r="K12" s="318"/>
-      <c r="M12" s="318"/>
-      <c r="N12" s="318"/>
+      <c r="I12" s="284"/>
+      <c r="J12" s="284"/>
+      <c r="K12" s="284"/>
+      <c r="M12" s="284"/>
+      <c r="N12" s="284"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="311" t="s">
+      <c r="A13" s="285" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="312"/>
+      <c r="B13" s="286"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="306"/>
-      <c r="F13" s="306"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="287"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="306"/>
-      <c r="J13" s="306"/>
+      <c r="I13" s="287"/>
+      <c r="J13" s="287"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="309" t="s">
+      <c r="A14" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="310"/>
+      <c r="B14" s="289"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="306"/>
-      <c r="F14" s="306"/>
+      <c r="E14" s="287"/>
+      <c r="F14" s="287"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="306"/>
-      <c r="J14" s="306"/>
+      <c r="I14" s="287"/>
+      <c r="J14" s="287"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="306"/>
-      <c r="N14" s="306"/>
+      <c r="M14" s="287"/>
+      <c r="N14" s="287"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="309" t="s">
+      <c r="A15" s="288" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="310"/>
+      <c r="B15" s="289"/>
       <c r="C15" s="31">
         <v>0</v>
       </c>
-      <c r="E15" s="306"/>
-      <c r="F15" s="306"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="306"/>
-      <c r="N15" s="306"/>
+      <c r="M15" s="287"/>
+      <c r="N15" s="287"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="309" t="s">
+      <c r="A16" s="288" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="310"/>
+      <c r="B16" s="289"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="306"/>
-      <c r="J16" s="306"/>
+      <c r="I16" s="287"/>
+      <c r="J16" s="287"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="306"/>
-      <c r="N16" s="306"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="304" t="s">
+      <c r="M16" s="287"/>
+      <c r="N16" s="287"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="305"/>
+      <c r="B17" s="291"/>
       <c r="C17" s="32">
         <v>0</v>
       </c>
-      <c r="E17" s="306"/>
-      <c r="F17" s="306"/>
+      <c r="E17" s="287"/>
+      <c r="F17" s="287"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="306"/>
-      <c r="N17" s="306"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M17" s="287"/>
+      <c r="N17" s="287"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
-        <v>10.656436487638533</v>
-      </c>
-      <c r="M18" s="306"/>
-      <c r="N18" s="306"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>12.787723785166239</v>
+      </c>
+      <c r="M18" s="287"/>
+      <c r="N18" s="287"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L19">
         <f>F25*G25</f>
-        <v>93.84</v>
+        <v>78.2</v>
       </c>
       <c r="M19" s="267"/>
       <c r="N19" s="267"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L20">
         <f>L19/1000</f>
-        <v>9.3840000000000007E-2</v>
+        <v>7.8200000000000006E-2</v>
       </c>
       <c r="M20" s="267"/>
       <c r="N20" s="267"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="307"/>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C21" s="292"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="307"/>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307"/>
-      <c r="H21" s="307"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="307"/>
+      <c r="E21" s="292"/>
+      <c r="F21" s="292"/>
+      <c r="G21" s="292"/>
+      <c r="H21" s="292"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C22" s="292"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="307"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="307"/>
-      <c r="H22" s="307"/>
-    </row>
-    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="308"/>
+      <c r="E22" s="292"/>
+      <c r="F22" s="292"/>
+      <c r="G22" s="292"/>
+      <c r="H22" s="292"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="293"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
-      <c r="G23" s="308"/>
-      <c r="H23" s="308"/>
-    </row>
-    <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="E23" s="293"/>
+      <c r="F23" s="293"/>
+      <c r="G23" s="293"/>
+      <c r="H23" s="293"/>
+    </row>
+    <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
         <v>11</v>
       </c>
@@ -17693,7 +17737,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="172" t="s">
         <v>34</v>
       </c>
@@ -17705,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="174">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E25" s="175">
         <f>VLOOKUP(B25,Material[],2,FALSE)</f>
@@ -17713,7 +17757,7 @@
       </c>
       <c r="F25" s="175">
         <f>IF(A25="Substrate",D25*E25,C25*D25)</f>
-        <v>55.2</v>
+        <v>46</v>
       </c>
       <c r="G25" s="176">
         <v>1.7</v>
@@ -17724,18 +17768,21 @@
       <c r="I25" s="178">
         <f>(IF(A25="Substrate",(F25*G25)/1000,(D25*G25)/1000))*(1+table1713[[#This Row],[Waste
 %]])</f>
-        <v>9.3840000000000007E-2</v>
+        <v>7.8200000000000006E-2</v>
       </c>
       <c r="J25" s="179">
         <f>IF(A25="Substrate",(($I$36*F25)/$B$37)*(1+H25),(($I$36*D25)/$B$37)*(1+H25))</f>
-        <v>9651.1932861264104</v>
+        <v>9584.3317012188782</v>
       </c>
       <c r="K25" s="180">
         <f>table1713[[#This Row],[Total GSM]]/$B$37</f>
-        <v>0.96511932861264105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0.95843317012188778</v>
+      </c>
+      <c r="O25" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="172" t="s">
         <v>27</v>
       </c>
@@ -17771,15 +17818,18 @@
       </c>
       <c r="J26" s="179">
         <f>IF(A26="Substrate",(($I$36*F26)/$B$37)*(1+H26),(($I$36*D26)/$B$37)*(1+H26))</f>
-        <v>996.59061106740103</v>
+        <v>1187.6237108032087</v>
       </c>
       <c r="K26" s="180">
         <f>table1713[[#This Row],[Total GSM]]/$B$37</f>
-        <v>3.4880671387359036E-2</v>
+        <v>4.1566829878112305E-2</v>
       </c>
       <c r="M26" s="101"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="172"/>
       <c r="B27" s="172"/>
       <c r="C27" s="173"/>
@@ -17791,8 +17841,11 @@
       <c r="I27" s="178"/>
       <c r="J27" s="179"/>
       <c r="K27" s="180"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="173"/>
@@ -17805,7 +17858,7 @@
       <c r="J28" s="179"/>
       <c r="K28" s="180"/>
     </row>
-    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="165"/>
       <c r="B29" s="172"/>
       <c r="C29" s="166"/>
@@ -17818,7 +17871,7 @@
       <c r="J29" s="52"/>
       <c r="K29" s="58"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="59"/>
       <c r="B30" s="46"/>
       <c r="C30" s="48"/>
@@ -17831,13 +17884,13 @@
       <c r="J30" s="52"/>
       <c r="K30" s="58"/>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="297" t="s">
+    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="295" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="298"/>
-      <c r="C31" s="298"/>
-      <c r="D31" s="298"/>
+      <c r="B31" s="296"/>
+      <c r="C31" s="296"/>
+      <c r="D31" s="296"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17857,11 +17910,11 @@
         <f>(SUMIFS(table1713[Est.
 Required Kgs],table1713[Type], "Ink") + SUMIFS(table1713[Est.
 Required Kgs],table1713[Material], "Solvent Base"))*$F$31</f>
-        <v>996.59061106740103</v>
+        <v>1187.6237108032087</v>
       </c>
       <c r="K31" s="64"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -17897,23 +17950,23 @@
       <c r="A35" s="273" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="358">
         <f>B37/B36</f>
-        <v>0.92257440116138401</v>
-      </c>
-      <c r="C35" s="299" t="s">
+        <v>0.92306952591595348</v>
+      </c>
+      <c r="C35" s="297" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="299"/>
+      <c r="D35" s="297"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
-        <v>699.36183232800067</v>
-      </c>
-      <c r="F35" s="299" t="s">
+        <v>833.42014793207625</v>
+      </c>
+      <c r="F35" s="297" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="299"/>
-      <c r="H35" s="299"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="297"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>0</v>
@@ -17923,23 +17976,23 @@
       <c r="A36" s="273" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="359">
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
-        <v>61.994999999999997</v>
-      </c>
-      <c r="C36" s="299" t="s">
+        <v>51.994999999999997</v>
+      </c>
+      <c r="C36" s="297" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="299"/>
+      <c r="D36" s="297"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
-        <v>1.429875</v>
-      </c>
-      <c r="F36" s="299" t="s">
+        <v>1.199875</v>
+      </c>
+      <c r="F36" s="297" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="299"/>
-      <c r="H36" s="299"/>
+      <c r="G36" s="297"/>
+      <c r="H36" s="297"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -17960,26 +18013,26 @@
       <c r="A37" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="359">
         <f>SUM(F25:F30)</f>
-        <v>57.195</v>
-      </c>
-      <c r="C37" s="300" t="s">
+        <v>47.994999999999997</v>
+      </c>
+      <c r="C37" s="298" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="300"/>
-      <c r="E37" s="15">
+      <c r="D37" s="298"/>
+      <c r="E37" s="357">
         <f>1000/B37</f>
-        <v>17.484045808200019</v>
-      </c>
-      <c r="F37" s="299" t="s">
+        <v>20.835503698301906</v>
+      </c>
+      <c r="F37" s="297" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="299"/>
-      <c r="H37" s="299"/>
+      <c r="G37" s="297"/>
+      <c r="H37" s="297"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
-        <v>6993.6183232800067</v>
+        <v>8334.2014793207618</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -17988,34 +18041,34 @@
       </c>
       <c r="B38" s="16">
         <f>SUM(I25:I30)+I31</f>
-        <v>0.1230525</v>
-      </c>
-      <c r="C38" s="299" t="s">
+        <v>0.10741250000000001</v>
+      </c>
+      <c r="C38" s="297" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="299"/>
+      <c r="D38" s="297"/>
       <c r="E38" s="15" t="e">
         <f>(E37/I35)*1000</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="299" t="s">
+      <c r="F38" s="297" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="299"/>
-      <c r="H38" s="299"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="297"/>
       <c r="I38" s="38" t="e">
         <f>I36*E38</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="299" t="s">
+      <c r="C39" s="297" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="299"/>
+      <c r="D39" s="297"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
-        <v>69.936183232800076</v>
+        <v>83.342014793207625</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -18069,11 +18122,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="301" t="s">
+      <c r="A44" s="299" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="302"/>
-      <c r="C44" s="303"/>
+      <c r="B44" s="300"/>
+      <c r="C44" s="301"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -18103,11 +18156,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="286" t="s">
+      <c r="A46" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="286"/>
-      <c r="C46" s="286"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18122,14 +18175,14 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="286" t="s">
+      <c r="A47" s="294" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="286"/>
-      <c r="C47" s="286"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
-        <v>59.60173029162047</v>
+        <v>59.633717188336227</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -18142,14 +18195,14 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="286" t="s">
+      <c r="A48" s="294" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="286"/>
-      <c r="C48" s="286"/>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
-        <v>4168.3175306666999</v>
+        <v>4969.9941400842772</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -18162,11 +18215,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="286" t="s">
+      <c r="A49" s="294" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="286"/>
-      <c r="C49" s="286"/>
+      <c r="B49" s="294"/>
+      <c r="C49" s="294"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18182,14 +18235,14 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="286" t="s">
+      <c r="A50" s="294" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="286"/>
-      <c r="C50" s="286"/>
+      <c r="B50" s="294"/>
+      <c r="C50" s="294"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
-        <v>41683.175306666992</v>
+        <v>49699.941400842778</v>
       </c>
       <c r="E50" s="82"/>
       <c r="F50" s="82"/>
@@ -18217,11 +18270,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="286" t="s">
+      <c r="A52" s="294" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="286"/>
-      <c r="C52" s="286"/>
+      <c r="B52" s="294"/>
+      <c r="C52" s="294"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18236,14 +18289,14 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="286" t="s">
+      <c r="A53" s="294" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="286"/>
-      <c r="C53" s="286"/>
+      <c r="B53" s="294"/>
+      <c r="C53" s="294"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
-        <v>662.93579768320956</v>
+        <v>662.77051272480605</v>
       </c>
       <c r="E53" s="82"/>
       <c r="F53" s="82"/>
@@ -18377,18 +18430,18 @@
         <f>IF(A60=TRUE, (D60+(SUMIFS(table1713[Est.
 Required Kgs], table1713[Material], "LDPE Transparent") + SUMIFS(table1713[Est.
 Required Kgs], table1713[Material], "LDPE White"))/C60), "")</f>
-        <v>14.787418980180586</v>
+        <v>14.691902430312684</v>
       </c>
       <c r="F60" s="204">
         <v>300</v>
       </c>
       <c r="G60" s="207">
         <f>IFERROR(F60*E60,"")</f>
-        <v>4436.2256940541756</v>
-      </c>
-      <c r="H60" s="287">
+        <v>4407.5707290938053</v>
+      </c>
+      <c r="H60" s="304">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
-        <v>4436.2256940541756</v>
+        <v>4407.5707290938053</v>
       </c>
       <c r="I60" s="82"/>
       <c r="J60" s="82"/>
@@ -18420,7 +18473,7 @@
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="288"/>
+      <c r="H61" s="305"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18451,7 +18504,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="288"/>
+      <c r="H62" s="305"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18482,7 +18535,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="288"/>
+      <c r="H63" s="305"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18513,7 +18566,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H64" s="288"/>
+      <c r="H64" s="305"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18544,7 +18597,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H65" s="288"/>
+      <c r="H65" s="305"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18575,7 +18628,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="288"/>
+      <c r="H66" s="305"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18605,7 +18658,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="288"/>
+      <c r="H67" s="305"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18635,7 +18688,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="288"/>
+      <c r="H68" s="305"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18665,7 +18718,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="289"/>
+      <c r="H69" s="306"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18684,7 +18737,7 @@
       </c>
       <c r="H70" s="137">
         <f>H60/OQKG</f>
-        <v>0.44362256940541756</v>
+        <v>0.44075707290938054</v>
       </c>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
@@ -18725,23 +18778,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="290"/>
-      <c r="C73" s="291" t="s">
+      <c r="B73" s="307"/>
+      <c r="C73" s="308" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="293" t="s">
+      <c r="E73" s="310" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="295" t="s">
+      <c r="F73" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="295" t="s">
+      <c r="G73" s="312" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="284" t="s">
+      <c r="H73" s="302" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18754,15 +18807,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="290"/>
-      <c r="C74" s="292"/>
+      <c r="B74" s="307"/>
+      <c r="C74" s="309"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="294"/>
-      <c r="F74" s="296"/>
-      <c r="G74" s="296"/>
-      <c r="H74" s="285"/>
+      <c r="E74" s="311"/>
+      <c r="F74" s="313"/>
+      <c r="G74" s="313"/>
+      <c r="H74" s="303"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -18778,11 +18831,11 @@
       </c>
       <c r="C75" s="183">
         <f>(B38/B37*1000)</f>
-        <v>2.1514555468135326</v>
+        <v>2.2379935409938536</v>
       </c>
       <c r="D75" s="183">
         <f>C75*D74</f>
-        <v>0.64543666404405975</v>
+        <v>0.67139806229815602</v>
       </c>
       <c r="E75" s="184">
         <v>0.1</v>
@@ -18792,11 +18845,11 @@
       </c>
       <c r="G75" s="185">
         <f>H70</f>
-        <v>0.44362256940541756</v>
+        <v>0.44075707290938054</v>
       </c>
       <c r="H75" s="186">
         <f>SUM(C75:G75)</f>
-        <v>3.5405147802630101</v>
+        <v>3.6501486762013902</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="88"/>
@@ -18813,27 +18866,27 @@
       </c>
       <c r="C76" s="91">
         <f>(C75/$E$35)*1000</f>
-        <v>3.0763125000000002</v>
+        <v>2.6853125000000002</v>
       </c>
       <c r="D76" s="91">
         <f>(D75/$E$35)*1000</f>
-        <v>0.92289374999999996</v>
+        <v>0.80559375</v>
       </c>
       <c r="E76" s="91">
         <f>(E75/$E$35)*1000</f>
-        <v>0.14298750000000002</v>
+        <v>0.11998750000000001</v>
       </c>
       <c r="F76" s="91">
         <f>(F75/$E$35)*1000</f>
-        <v>0.28597500000000003</v>
+        <v>0.23997500000000002</v>
       </c>
       <c r="G76" s="91">
         <f>(G75/$E$35)*1000</f>
-        <v>0.63432482142857149</v>
+        <v>0.52885339285714306</v>
       </c>
       <c r="H76" s="188">
         <f>SUM(C76:G76)</f>
-        <v>5.0624935714285719</v>
+        <v>4.3797221428571431</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="88"/>
@@ -18850,27 +18903,27 @@
       </c>
       <c r="C77" s="92">
         <f>(C75/$E$37)</f>
-        <v>0.12305249999999998</v>
+        <v>0.10741250000000001</v>
       </c>
       <c r="D77" s="92">
         <f t="shared" ref="D77:G77" si="2">(D75/$E$37)</f>
-        <v>3.6915749999999997E-2</v>
+        <v>3.2223749999999995E-2</v>
       </c>
       <c r="E77" s="92">
         <f t="shared" si="2"/>
-        <v>5.7194999999999998E-3</v>
+        <v>4.7994999999999999E-3</v>
       </c>
       <c r="F77" s="92">
         <f t="shared" si="2"/>
-        <v>1.1439E-2</v>
+        <v>9.5989999999999999E-3</v>
       </c>
       <c r="G77" s="92">
         <f t="shared" si="2"/>
-        <v>2.5372992857142854E-2</v>
+        <v>2.1154135714285718E-2</v>
       </c>
       <c r="H77" s="189">
         <f>SUM(C77:G77)</f>
-        <v>0.20249974285714284</v>
+        <v>0.17518888571428576</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="93"/>
@@ -18887,27 +18940,27 @@
       </c>
       <c r="C78" s="92">
         <f>(C75/$E$39)</f>
-        <v>3.0763124999999995E-2</v>
+        <v>2.6853125000000002E-2</v>
       </c>
       <c r="D78" s="92">
         <f>(D75/$E$39)</f>
-        <v>9.2289374999999993E-3</v>
+        <v>8.0559374999999989E-3</v>
       </c>
       <c r="E78" s="92">
         <f>(E75/$E$39)</f>
-        <v>1.4298749999999999E-3</v>
+        <v>1.199875E-3</v>
       </c>
       <c r="F78" s="92">
         <f>(F75/$E$39)</f>
-        <v>2.8597499999999999E-3</v>
+        <v>2.39975E-3</v>
       </c>
       <c r="G78" s="92">
         <f>(G75/$E$39)</f>
-        <v>6.3432482142857134E-3</v>
+        <v>5.2885339285714296E-3</v>
       </c>
       <c r="H78" s="189">
         <f>SUM(C78:G78)</f>
-        <v>5.062493571428571E-2</v>
+        <v>4.379722142857144E-2</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="93"/>
@@ -18923,27 +18976,27 @@
       </c>
       <c r="C79" s="191">
         <f>C78*500</f>
-        <v>15.381562499999998</v>
+        <v>13.426562500000001</v>
       </c>
       <c r="D79" s="191">
         <f>D78*500</f>
-        <v>4.6144687499999995</v>
+        <v>4.0279687499999994</v>
       </c>
       <c r="E79" s="191">
         <f t="shared" ref="E79:G79" si="3">E78*500</f>
-        <v>0.7149375</v>
+        <v>0.59993750000000001</v>
       </c>
       <c r="F79" s="191">
         <f t="shared" si="3"/>
-        <v>1.429875</v>
+        <v>1.199875</v>
       </c>
       <c r="G79" s="191">
         <f t="shared" si="3"/>
-        <v>3.1716241071428568</v>
+        <v>2.6442669642857148</v>
       </c>
       <c r="H79" s="192">
         <f>SUM(C79:G79)</f>
-        <v>25.312467857142856</v>
+        <v>21.898610714285716</v>
       </c>
       <c r="I79" s="220"/>
       <c r="J79" s="221"/>
@@ -18993,9 +19046,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="278"/>
-      <c r="I82" s="278"/>
-      <c r="J82" s="278"/>
+      <c r="H82" s="318"/>
+      <c r="I82" s="318"/>
+      <c r="J82" s="318"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -19003,19 +19056,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="279" t="s">
+      <c r="B83" s="319" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="279"/>
-      <c r="D83" s="279"/>
-      <c r="E83" s="279"/>
-      <c r="F83" s="279"/>
-      <c r="G83" s="279"/>
-      <c r="H83" s="279"/>
-      <c r="I83" s="279"/>
-      <c r="J83" s="279"/>
-      <c r="K83" s="279"/>
-      <c r="L83" s="279"/>
+      <c r="C83" s="319"/>
+      <c r="D83" s="319"/>
+      <c r="E83" s="319"/>
+      <c r="F83" s="319"/>
+      <c r="G83" s="319"/>
+      <c r="H83" s="319"/>
+      <c r="I83" s="319"/>
+      <c r="J83" s="319"/>
+      <c r="K83" s="319"/>
+      <c r="L83" s="319"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -19100,11 +19153,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="280"/>
-      <c r="I88" s="280"/>
+      <c r="H88" s="320"/>
+      <c r="I88" s="320"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="280"/>
-      <c r="L88" s="280"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="320"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19194,13 +19247,13 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="281" t="s">
+      <c r="Q92" s="321" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="281"/>
+      <c r="R92" s="321"/>
       <c r="S92" s="112">
         <f>H75</f>
-        <v>3.5405147802630101</v>
+        <v>3.6501486762013902</v>
       </c>
       <c r="T92" s="210" t="s">
         <v>162</v>
@@ -19257,10 +19310,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="282" t="s">
+      <c r="T94" s="322" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="283"/>
+      <c r="U94" s="323"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19287,19 +19340,19 @@
       </c>
       <c r="R95" s="175">
         <f>C75+H70</f>
-        <v>2.59507811621895</v>
+        <v>2.678750613903234</v>
       </c>
       <c r="S95" s="211">
         <f>R95/S92</f>
-        <v>0.73296632757628888</v>
-      </c>
-      <c r="T95" s="274">
+        <v>0.7338743847253193</v>
+      </c>
+      <c r="T95" s="314">
         <f>R96-R95</f>
-        <v>-1.0493638305046642</v>
-      </c>
-      <c r="U95" s="276">
+        <v>-1.1330363281889482</v>
+      </c>
+      <c r="U95" s="316">
         <f>(R96-R95)/R95</f>
-        <v>-0.40436695294305663</v>
+        <v>-0.42297193412043299</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
@@ -19331,10 +19384,10 @@
       </c>
       <c r="S96" s="211">
         <f>R96/S92</f>
-        <v>0.43657896708440264</v>
-      </c>
-      <c r="T96" s="275"/>
-      <c r="U96" s="276"/>
+        <v>0.42346611681660823</v>
+      </c>
+      <c r="T96" s="315"/>
+      <c r="U96" s="316"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -19360,11 +19413,11 @@
       </c>
       <c r="R97" s="217">
         <f>S92-R95</f>
-        <v>0.94543666404406013</v>
+        <v>0.97139806229815617</v>
       </c>
       <c r="S97" s="218">
         <f>R97/S92</f>
-        <v>0.26703367242371112</v>
+        <v>0.2661256152746807</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
@@ -19391,11 +19444,11 @@
       </c>
       <c r="R98" s="175">
         <f>S92-R96</f>
-        <v>1.9948004945487243</v>
+        <v>2.1044343904871043</v>
       </c>
       <c r="S98" s="211">
         <f>R98/S92</f>
-        <v>0.56342103291559731</v>
+        <v>0.57653388318339172</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
@@ -19542,7 +19595,7 @@
       </c>
       <c r="E107" s="159">
         <f>(E106-C75)/C75</f>
-        <v>-0.70872432498323878</v>
+        <v>-0.71998727646534</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
@@ -19787,67 +19840,51 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="277" t="s">
+      <c r="B122" s="317" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="277"/>
-      <c r="D122" s="277"/>
+      <c r="C122" s="317"/>
+      <c r="D122" s="317"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="277" t="s">
+      <c r="B123" s="317" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="277"/>
-      <c r="D123" s="277"/>
+      <c r="C123" s="317"/>
+      <c r="D123" s="317"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
-        <v>1.071688147605764</v>
+        <v>1.0851568256888184</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="C35:D35"/>
@@ -19861,28 +19898,44 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -20126,6 +20179,101 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC5812A-307F-453C-92CE-92FF0734E5BC}">
+  <dimension ref="B2:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="360">
+        <v>0</v>
+      </c>
+      <c r="C2" s="360">
+        <f>B4+1</f>
+        <v>81</v>
+      </c>
+      <c r="D2" s="360">
+        <f>C4+1</f>
+        <v>151</v>
+      </c>
+      <c r="E2" s="360">
+        <f t="shared" ref="E2:I2" si="0">D4+1</f>
+        <v>301</v>
+      </c>
+      <c r="F2" s="360">
+        <f t="shared" si="0"/>
+        <v>601</v>
+      </c>
+      <c r="G2" s="360">
+        <f t="shared" si="0"/>
+        <v>1501</v>
+      </c>
+      <c r="H2" s="360">
+        <f t="shared" si="0"/>
+        <v>3001</v>
+      </c>
+      <c r="I2" s="360">
+        <f t="shared" si="0"/>
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="E3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="G3" s="361" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="362"/>
+      <c r="I3" s="362"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="360">
+        <v>80</v>
+      </c>
+      <c r="C4" s="360">
+        <v>150</v>
+      </c>
+      <c r="D4" s="360">
+        <v>300</v>
+      </c>
+      <c r="E4" s="360">
+        <v>600</v>
+      </c>
+      <c r="F4" s="360">
+        <v>1500</v>
+      </c>
+      <c r="G4" s="360">
+        <v>3000</v>
+      </c>
+      <c r="H4" s="360">
+        <v>5000</v>
+      </c>
+      <c r="I4" s="363" t="s">
+        <v>340</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20A07BB-02D0-4AF9-8BEB-9FE7CE591B3C}">
   <dimension ref="A1:F46"/>
@@ -21055,20 +21203,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="277" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="319"/>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
-      <c r="K1" s="319"/>
-      <c r="L1" s="319"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
+      <c r="K1" s="277"/>
+      <c r="L1" s="277"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21096,26 +21244,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="320" t="s">
+      <c r="A3" s="274" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="321" t="s">
+      <c r="B3" s="274"/>
+      <c r="C3" s="278" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="320" t="s">
+      <c r="G3" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="320"/>
-      <c r="I3" s="321" t="s">
+      <c r="H3" s="274"/>
+      <c r="I3" s="278" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="321"/>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="278"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -21140,28 +21288,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="320" t="s">
+      <c r="A5" s="274" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="322" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="275" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
+      <c r="D5" s="275"/>
+      <c r="E5" s="275"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="274" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="320"/>
-      <c r="I5" s="323">
+      <c r="H5" s="274"/>
+      <c r="I5" s="276">
         <v>10000</v>
       </c>
-      <c r="J5" s="323"/>
-      <c r="K5" s="322" t="s">
+      <c r="J5" s="276"/>
+      <c r="K5" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="322"/>
+      <c r="L5" s="275"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -21192,128 +21340,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="313" t="s">
+      <c r="A9" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="313"/>
-      <c r="C9" s="313"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="313" t="s">
+      <c r="A10" s="279" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="313"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="314"/>
-      <c r="P10" s="314"/>
+      <c r="O10" s="280"/>
+      <c r="P10" s="280"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="315" t="s">
+      <c r="A12" s="281" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="316"/>
-      <c r="C12" s="317"/>
+      <c r="B12" s="282"/>
+      <c r="C12" s="283"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="318"/>
-      <c r="J12" s="318"/>
-      <c r="K12" s="318"/>
-      <c r="M12" s="318"/>
-      <c r="N12" s="318"/>
+      <c r="I12" s="284"/>
+      <c r="J12" s="284"/>
+      <c r="K12" s="284"/>
+      <c r="M12" s="284"/>
+      <c r="N12" s="284"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="311" t="s">
+      <c r="A13" s="285" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="312"/>
+      <c r="B13" s="286"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="306"/>
-      <c r="F13" s="306"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="287"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="306"/>
-      <c r="J13" s="306"/>
+      <c r="I13" s="287"/>
+      <c r="J13" s="287"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="309" t="s">
+      <c r="A14" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="310"/>
+      <c r="B14" s="289"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="306"/>
-      <c r="F14" s="306"/>
+      <c r="E14" s="287"/>
+      <c r="F14" s="287"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="306"/>
-      <c r="J14" s="306"/>
+      <c r="I14" s="287"/>
+      <c r="J14" s="287"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="306"/>
-      <c r="N14" s="306"/>
+      <c r="M14" s="287"/>
+      <c r="N14" s="287"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="309" t="s">
+      <c r="A15" s="288" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="310"/>
+      <c r="B15" s="289"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="306"/>
-      <c r="F15" s="306"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="306"/>
-      <c r="N15" s="306"/>
+      <c r="M15" s="287"/>
+      <c r="N15" s="287"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="309" t="s">
+      <c r="A16" s="288" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="310"/>
+      <c r="B16" s="289"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="306"/>
-      <c r="J16" s="306"/>
+      <c r="I16" s="287"/>
+      <c r="J16" s="287"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="306"/>
-      <c r="N16" s="306"/>
+      <c r="M16" s="287"/>
+      <c r="N16" s="287"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="304" t="s">
+      <c r="A17" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="305"/>
+      <c r="B17" s="291"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="306"/>
-      <c r="F17" s="306"/>
+      <c r="E17" s="287"/>
+      <c r="F17" s="287"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="306"/>
-      <c r="N17" s="306"/>
+      <c r="M17" s="287"/>
+      <c r="N17" s="287"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="306"/>
-      <c r="N18" s="306"/>
+      <c r="M18" s="287"/>
+      <c r="N18" s="287"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21324,28 +21472,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="307"/>
+      <c r="C21" s="292"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="307"/>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307"/>
-      <c r="H21" s="307"/>
+      <c r="E21" s="292"/>
+      <c r="F21" s="292"/>
+      <c r="G21" s="292"/>
+      <c r="H21" s="292"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="307"/>
+      <c r="C22" s="292"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="307"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="307"/>
-      <c r="H22" s="307"/>
+      <c r="E22" s="292"/>
+      <c r="F22" s="292"/>
+      <c r="G22" s="292"/>
+      <c r="H22" s="292"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="308"/>
+      <c r="C23" s="293"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
-      <c r="G23" s="308"/>
-      <c r="H23" s="308"/>
+      <c r="E23" s="293"/>
+      <c r="F23" s="293"/>
+      <c r="G23" s="293"/>
+      <c r="H23" s="293"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21586,12 +21734,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="297" t="s">
+      <c r="A31" s="295" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="298"/>
-      <c r="C31" s="298"/>
-      <c r="D31" s="298"/>
+      <c r="B31" s="296"/>
+      <c r="C31" s="296"/>
+      <c r="D31" s="296"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21654,19 +21802,19 @@
         <f>B37/B36</f>
         <v>0.9813242784380305</v>
       </c>
-      <c r="C35" s="299" t="s">
+      <c r="C35" s="297" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="299"/>
+      <c r="D35" s="297"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>346.02076124567475</v>
       </c>
-      <c r="F35" s="299" t="s">
+      <c r="F35" s="297" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="299"/>
-      <c r="H35" s="299"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="297"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21680,19 +21828,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117.8</v>
       </c>
-      <c r="C36" s="299" t="s">
+      <c r="C36" s="297" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="299"/>
+      <c r="D36" s="297"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.89</v>
       </c>
-      <c r="F36" s="299" t="s">
+      <c r="F36" s="297" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="299"/>
-      <c r="H36" s="299"/>
+      <c r="G36" s="297"/>
+      <c r="H36" s="297"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21717,19 +21865,19 @@
         <f>SUM(F25:F30)</f>
         <v>115.6</v>
       </c>
-      <c r="C37" s="299" t="s">
+      <c r="C37" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="299"/>
+      <c r="D37" s="297"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.6505190311418687</v>
       </c>
-      <c r="F37" s="299" t="s">
+      <c r="F37" s="297" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="299"/>
-      <c r="H37" s="299"/>
+      <c r="G37" s="297"/>
+      <c r="H37" s="297"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3460.2076124567475</v>
@@ -21743,29 +21891,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22398500000000002</v>
       </c>
-      <c r="C38" s="299" t="s">
+      <c r="C38" s="297" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="299"/>
+      <c r="D38" s="297"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.4809010109234002</v>
       </c>
-      <c r="F38" s="299" t="s">
+      <c r="F38" s="297" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="299"/>
-      <c r="H38" s="299"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="297"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="299" t="s">
+      <c r="C39" s="297" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="299"/>
+      <c r="D39" s="297"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.602076124567475</v>
@@ -21822,11 +21970,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="301" t="s">
+      <c r="A44" s="299" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="302"/>
-      <c r="C44" s="303"/>
+      <c r="B44" s="300"/>
+      <c r="C44" s="301"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -21856,11 +22004,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="286" t="s">
+      <c r="A46" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="286"/>
-      <c r="C46" s="286"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -21875,11 +22023,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="286" t="s">
+      <c r="A47" s="294" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="286"/>
-      <c r="C47" s="286"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.397190403781075</v>
@@ -21895,11 +22043,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="286" t="s">
+      <c r="A48" s="294" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="286"/>
-      <c r="C48" s="286"/>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2193.6744084353313</v>
@@ -21915,11 +22063,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="286" t="s">
+      <c r="A49" s="294" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="286"/>
-      <c r="C49" s="286"/>
+      <c r="B49" s="294"/>
+      <c r="C49" s="294"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -21935,11 +22083,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="286" t="s">
+      <c r="A50" s="294" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="286"/>
-      <c r="C50" s="286"/>
+      <c r="B50" s="294"/>
+      <c r="C50" s="294"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>21936.744084353315</v>
@@ -21970,11 +22118,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="286" t="s">
+      <c r="A52" s="294" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="286"/>
-      <c r="C52" s="286"/>
+      <c r="B52" s="294"/>
+      <c r="C52" s="294"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -21989,11 +22137,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="286" t="s">
+      <c r="A53" s="294" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="286"/>
-      <c r="C53" s="286"/>
+      <c r="B53" s="294"/>
+      <c r="C53" s="294"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.22615683819515</v>
@@ -22139,7 +22287,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4092.6347009391993</v>
       </c>
-      <c r="H60" s="287">
+      <c r="H60" s="304">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9441.736856218844</v>
       </c>
@@ -22173,7 +22321,7 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2596.1802021846802</v>
       </c>
-      <c r="H61" s="288"/>
+      <c r="H61" s="305"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -22204,7 +22352,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H62" s="288"/>
+      <c r="H62" s="305"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22235,7 +22383,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H63" s="288"/>
+      <c r="H63" s="305"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22266,7 +22414,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H64" s="288"/>
+      <c r="H64" s="305"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22297,7 +22445,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H65" s="288"/>
+      <c r="H65" s="305"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22328,7 +22476,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H66" s="288"/>
+      <c r="H66" s="305"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22358,7 +22506,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="288"/>
+      <c r="H67" s="305"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22388,7 +22536,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="288"/>
+      <c r="H68" s="305"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22418,7 +22566,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="289"/>
+      <c r="H69" s="306"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22478,23 +22626,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="290"/>
-      <c r="C73" s="291" t="s">
+      <c r="B73" s="307"/>
+      <c r="C73" s="308" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="293" t="s">
+      <c r="E73" s="310" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="295" t="s">
+      <c r="F73" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="295" t="s">
+      <c r="G73" s="312" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="284" t="s">
+      <c r="H73" s="302" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22507,15 +22655,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="290"/>
-      <c r="C74" s="292"/>
+      <c r="B74" s="307"/>
+      <c r="C74" s="309"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="294"/>
-      <c r="F74" s="296"/>
-      <c r="G74" s="296"/>
-      <c r="H74" s="285"/>
+      <c r="E74" s="311"/>
+      <c r="F74" s="313"/>
+      <c r="G74" s="313"/>
+      <c r="H74" s="303"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22746,9 +22894,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="278"/>
-      <c r="I82" s="278"/>
-      <c r="J82" s="278"/>
+      <c r="H82" s="318"/>
+      <c r="I82" s="318"/>
+      <c r="J82" s="318"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22756,19 +22904,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="279" t="s">
+      <c r="B83" s="319" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="279"/>
-      <c r="D83" s="279"/>
-      <c r="E83" s="279"/>
-      <c r="F83" s="279"/>
-      <c r="G83" s="279"/>
-      <c r="H83" s="279"/>
-      <c r="I83" s="279"/>
-      <c r="J83" s="279"/>
-      <c r="K83" s="279"/>
-      <c r="L83" s="279"/>
+      <c r="C83" s="319"/>
+      <c r="D83" s="319"/>
+      <c r="E83" s="319"/>
+      <c r="F83" s="319"/>
+      <c r="G83" s="319"/>
+      <c r="H83" s="319"/>
+      <c r="I83" s="319"/>
+      <c r="J83" s="319"/>
+      <c r="K83" s="319"/>
+      <c r="L83" s="319"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -22853,11 +23001,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="280"/>
-      <c r="I88" s="280"/>
+      <c r="H88" s="320"/>
+      <c r="I88" s="320"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="280"/>
-      <c r="L88" s="280"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="320"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -22947,10 +23095,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="281" t="s">
+      <c r="Q92" s="321" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="281"/>
+      <c r="R92" s="321"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7630361423692897</v>
@@ -23010,10 +23158,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="282" t="s">
+      <c r="T94" s="322" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="283"/>
+      <c r="U94" s="323"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -23046,11 +23194,11 @@
         <f>R95/S92</f>
         <v>0.76580720508248346</v>
       </c>
-      <c r="T95" s="274">
+      <c r="T95" s="314">
         <f>R96-R95</f>
         <v>-6.8260190812196253E-2</v>
       </c>
-      <c r="U95" s="276">
+      <c r="U95" s="316">
         <f>(R96-R95)/R95</f>
         <v>-2.368697819819552E-2</v>
       </c>
@@ -23086,8 +23234,8 @@
         <f>R96/S92</f>
         <v>0.74766754651167366</v>
       </c>
-      <c r="T96" s="275"/>
-      <c r="U96" s="276"/>
+      <c r="T96" s="315"/>
+      <c r="U96" s="316"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -23540,22 +23688,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="277" t="s">
+      <c r="B122" s="317" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="277"/>
-      <c r="D122" s="277"/>
+      <c r="C122" s="317"/>
+      <c r="D122" s="317"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="277" t="s">
+      <c r="B123" s="317" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="277"/>
-      <c r="D123" s="277"/>
+      <c r="C123" s="317"/>
+      <c r="D123" s="317"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-2.6611699687135438E-2</v>
@@ -23563,6 +23711,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23579,63 +23784,6 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -24520,20 +24668,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="277" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="319"/>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
-      <c r="K1" s="319"/>
-      <c r="L1" s="319"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
+      <c r="K1" s="277"/>
+      <c r="L1" s="277"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24563,26 +24711,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="320" t="s">
+      <c r="A3" s="274" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="321" t="s">
+      <c r="B3" s="274"/>
+      <c r="C3" s="278" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="320" t="s">
+      <c r="G3" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="320"/>
-      <c r="I3" s="321" t="s">
+      <c r="H3" s="274"/>
+      <c r="I3" s="278" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="321"/>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="278"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24609,28 +24757,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="320" t="s">
+      <c r="A5" s="274" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="322" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="275" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
+      <c r="D5" s="275"/>
+      <c r="E5" s="275"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="274" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="320"/>
-      <c r="I5" s="323">
+      <c r="H5" s="274"/>
+      <c r="I5" s="276">
         <v>20000</v>
       </c>
-      <c r="J5" s="323"/>
-      <c r="K5" s="322" t="s">
+      <c r="J5" s="276"/>
+      <c r="K5" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="322"/>
+      <c r="L5" s="275"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24663,105 +24811,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="313" t="s">
+      <c r="A9" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="313"/>
-      <c r="C9" s="313"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="313" t="s">
+      <c r="A10" s="279" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="313"/>
-      <c r="N10" s="314"/>
-      <c r="O10" s="314"/>
-      <c r="P10" s="314"/>
-      <c r="Q10" s="314"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
+      <c r="N10" s="280"/>
+      <c r="O10" s="280"/>
+      <c r="P10" s="280"/>
+      <c r="Q10" s="280"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="318"/>
-      <c r="B12" s="318"/>
-      <c r="C12" s="318"/>
-      <c r="E12" s="328" t="s">
+      <c r="A12" s="284"/>
+      <c r="B12" s="284"/>
+      <c r="C12" s="284"/>
+      <c r="E12" s="338" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="329"/>
-      <c r="G12" s="330"/>
-      <c r="I12" s="318"/>
-      <c r="J12" s="318"/>
-      <c r="K12" s="318"/>
-      <c r="M12" s="318"/>
-      <c r="N12" s="318"/>
-      <c r="O12" s="318"/>
+      <c r="F12" s="339"/>
+      <c r="G12" s="340"/>
+      <c r="I12" s="284"/>
+      <c r="J12" s="284"/>
+      <c r="K12" s="284"/>
+      <c r="M12" s="284"/>
+      <c r="N12" s="284"/>
+      <c r="O12" s="284"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="306"/>
-      <c r="B13" s="306"/>
+      <c r="A13" s="287"/>
+      <c r="B13" s="287"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="331" t="s">
+      <c r="E13" s="341" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="332"/>
+      <c r="F13" s="342"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="306"/>
-      <c r="J13" s="306"/>
+      <c r="I13" s="287"/>
+      <c r="J13" s="287"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="306"/>
-      <c r="N13" s="306"/>
+      <c r="M13" s="287"/>
+      <c r="N13" s="287"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="306"/>
-      <c r="B14" s="306"/>
+      <c r="A14" s="287"/>
+      <c r="B14" s="287"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="309" t="s">
+      <c r="E14" s="288" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="310"/>
+      <c r="F14" s="289"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="306"/>
-      <c r="J14" s="306"/>
+      <c r="I14" s="287"/>
+      <c r="J14" s="287"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="306"/>
-      <c r="N14" s="306"/>
+      <c r="M14" s="287"/>
+      <c r="N14" s="287"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="306"/>
-      <c r="B15" s="306"/>
+      <c r="A15" s="287"/>
+      <c r="B15" s="287"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="326" t="s">
+      <c r="E15" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="327"/>
+      <c r="F15" s="337"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="306"/>
-      <c r="N15" s="306"/>
+      <c r="M15" s="287"/>
+      <c r="N15" s="287"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="306"/>
-      <c r="B16" s="306"/>
+      <c r="A16" s="287"/>
+      <c r="B16" s="287"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -24770,74 +24918,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="306"/>
-      <c r="J16" s="306"/>
+      <c r="I16" s="287"/>
+      <c r="J16" s="287"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="306"/>
-      <c r="N16" s="306"/>
+      <c r="M16" s="287"/>
+      <c r="N16" s="287"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="306"/>
-      <c r="B17" s="306"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="304" t="s">
+      <c r="E17" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="305"/>
+      <c r="F17" s="291"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="306"/>
-      <c r="N17" s="306"/>
+      <c r="M17" s="287"/>
+      <c r="N17" s="287"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="306"/>
-      <c r="N18" s="306"/>
+      <c r="M18" s="287"/>
+      <c r="N18" s="287"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="325"/>
-      <c r="N19" s="325"/>
+      <c r="M19" s="343"/>
+      <c r="N19" s="343"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="325"/>
-      <c r="N20" s="325"/>
+      <c r="M20" s="343"/>
+      <c r="N20" s="343"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="307" t="s">
+      <c r="C21" s="292" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="307" t="s">
+      <c r="E21" s="292" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307" t="s">
+      <c r="F21" s="292"/>
+      <c r="G21" s="292" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="307" t="s">
+      <c r="H21" s="292" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="307"/>
+      <c r="C22" s="292"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="307"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="307"/>
-      <c r="H22" s="307"/>
+      <c r="E22" s="292"/>
+      <c r="F22" s="292"/>
+      <c r="G22" s="292"/>
+      <c r="H22" s="292"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="308"/>
+      <c r="C23" s="293"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
-      <c r="G23" s="308"/>
-      <c r="H23" s="308"/>
+      <c r="E23" s="293"/>
+      <c r="F23" s="293"/>
+      <c r="G23" s="293"/>
+      <c r="H23" s="293"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -25014,12 +25162,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="297" t="s">
+      <c r="A31" s="295" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="298"/>
-      <c r="C31" s="298"/>
-      <c r="D31" s="298"/>
+      <c r="B31" s="296"/>
+      <c r="C31" s="296"/>
+      <c r="D31" s="296"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -25082,19 +25230,19 @@
         <f>B37/B36</f>
         <v>0.91666666666666674</v>
       </c>
-      <c r="C35" s="299" t="s">
+      <c r="C35" s="297" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="299"/>
+      <c r="D35" s="297"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5431.9647769676003</v>
       </c>
-      <c r="F35" s="299" t="s">
+      <c r="F35" s="297" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="299"/>
-      <c r="H35" s="299"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="297"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -25108,19 +25256,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37.799999999999997</v>
       </c>
-      <c r="C36" s="299" t="s">
+      <c r="C36" s="297" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="299"/>
+      <c r="D36" s="297"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.18409544999999999</v>
       </c>
-      <c r="F36" s="299" t="s">
+      <c r="F36" s="297" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="299"/>
-      <c r="H36" s="299"/>
+      <c r="G36" s="297"/>
+      <c r="H36" s="297"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -25139,19 +25287,19 @@
         <f>SUM(F25:F30)</f>
         <v>34.65</v>
       </c>
-      <c r="C37" s="299" t="s">
+      <c r="C37" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="299"/>
+      <c r="D37" s="297"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>28.860028860028862</v>
       </c>
-      <c r="F37" s="299" t="s">
+      <c r="F37" s="297" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="299"/>
-      <c r="H37" s="299"/>
+      <c r="G37" s="297"/>
+      <c r="H37" s="297"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>108639.29553935201</v>
@@ -25165,37 +25313,37 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10634300000000001</v>
       </c>
-      <c r="C38" s="299" t="s">
+      <c r="C38" s="297" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="299"/>
+      <c r="D38" s="297"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>28.574286000028575</v>
       </c>
-      <c r="F38" s="299" t="s">
+      <c r="F38" s="297" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="299"/>
-      <c r="H38" s="299"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="297"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="299" t="s">
+      <c r="C39" s="297" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="299"/>
+      <c r="D39" s="297"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="299"/>
-      <c r="D40" s="299"/>
+      <c r="C40" s="297"/>
+      <c r="D40" s="297"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25245,11 +25393,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="301" t="s">
+      <c r="A44" s="299" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="302"/>
-      <c r="C44" s="303"/>
+      <c r="B44" s="300"/>
+      <c r="C44" s="301"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25279,11 +25427,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="286" t="s">
+      <c r="A46" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="286"/>
-      <c r="C46" s="286"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25298,11 +25446,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="286" t="s">
+      <c r="A47" s="294" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="286"/>
-      <c r="C47" s="286"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.8170490707388822</v>
@@ -25318,11 +25466,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="286" t="s">
+      <c r="A48" s="294" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="286"/>
-      <c r="C48" s="286"/>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6836.3715691450298</v>
@@ -25338,11 +25486,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="286" t="s">
+      <c r="A49" s="294" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="286"/>
-      <c r="C49" s="286"/>
+      <c r="B49" s="294"/>
+      <c r="C49" s="294"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25358,11 +25506,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="286" t="s">
+      <c r="A50" s="294" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="286"/>
-      <c r="C50" s="286"/>
+      <c r="B50" s="294"/>
+      <c r="C50" s="294"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>42461.93521208092</v>
@@ -25393,11 +25541,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="286" t="s">
+      <c r="A52" s="294" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="286"/>
-      <c r="C52" s="286"/>
+      <c r="B52" s="294"/>
+      <c r="C52" s="294"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25412,11 +25560,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="286" t="s">
+      <c r="A53" s="294" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="286"/>
-      <c r="C53" s="286"/>
+      <c r="B53" s="294"/>
+      <c r="C53" s="294"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1737.6438086744588</v>
@@ -25897,23 +26045,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="290"/>
-      <c r="C73" s="291" t="s">
+      <c r="B73" s="307"/>
+      <c r="C73" s="308" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="293" t="s">
+      <c r="E73" s="310" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="295" t="s">
+      <c r="F73" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="295" t="s">
+      <c r="G73" s="312" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="284" t="s">
+      <c r="H73" s="302" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -25927,15 +26075,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="290"/>
-      <c r="C74" s="292"/>
+      <c r="B74" s="307"/>
+      <c r="C74" s="309"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="294"/>
-      <c r="F74" s="296"/>
-      <c r="G74" s="296"/>
-      <c r="H74" s="285"/>
+      <c r="E74" s="311"/>
+      <c r="F74" s="313"/>
+      <c r="G74" s="313"/>
+      <c r="H74" s="303"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -26174,9 +26322,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="278"/>
-      <c r="I82" s="278"/>
-      <c r="J82" s="278"/>
+      <c r="H82" s="318"/>
+      <c r="I82" s="318"/>
+      <c r="J82" s="318"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -26184,19 +26332,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="279" t="s">
+      <c r="B83" s="319" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="279"/>
-      <c r="D83" s="279"/>
-      <c r="E83" s="279"/>
-      <c r="F83" s="279"/>
-      <c r="G83" s="279"/>
-      <c r="H83" s="279"/>
-      <c r="I83" s="279"/>
-      <c r="J83" s="279"/>
-      <c r="K83" s="279"/>
-      <c r="L83" s="279"/>
+      <c r="C83" s="319"/>
+      <c r="D83" s="319"/>
+      <c r="E83" s="319"/>
+      <c r="F83" s="319"/>
+      <c r="G83" s="319"/>
+      <c r="H83" s="319"/>
+      <c r="I83" s="319"/>
+      <c r="J83" s="319"/>
+      <c r="K83" s="319"/>
+      <c r="L83" s="319"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26262,17 +26410,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="336" t="s">
+      <c r="H87" s="325" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="337"/>
+      <c r="I87" s="326"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="338" t="s">
+      <c r="K87" s="327" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="339"/>
+      <c r="L87" s="328"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26284,20 +26432,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="340">
+      <c r="H88" s="329">
         <f>C75+H70</f>
         <v>10.167385929069098</v>
       </c>
-      <c r="I88" s="341"/>
+      <c r="I88" s="330"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.98761894452246557</v>
       </c>
-      <c r="K88" s="342">
+      <c r="K88" s="331">
         <f>E106+E122</f>
         <v>20.20888888888889</v>
       </c>
-      <c r="L88" s="343"/>
+      <c r="L88" s="332"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26369,10 +26517,10 @@
         <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="281" t="s">
+      <c r="Q92" s="321" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="281"/>
+      <c r="R92" s="321"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.388104543787712</v>
@@ -26426,10 +26574,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="282" t="s">
+      <c r="T94" s="322" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="283"/>
+      <c r="U94" s="323"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26461,11 +26609,11 @@
         <f>R95/S92</f>
         <v>0.89280756863225985</v>
       </c>
-      <c r="T95" s="274">
+      <c r="T95" s="314">
         <f>R96-R95</f>
         <v>10.041502959819791</v>
       </c>
-      <c r="U95" s="276">
+      <c r="U95" s="316">
         <f>(R96-R95)/R95</f>
         <v>0.98761894452246557</v>
       </c>
@@ -26502,8 +26650,8 @@
         <f>R96/S92</f>
         <v>1.7745612372265211</v>
       </c>
-      <c r="T96" s="275"/>
-      <c r="U96" s="276"/>
+      <c r="T96" s="315"/>
+      <c r="U96" s="316"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -26965,11 +27113,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="277" t="s">
+      <c r="B122" s="317" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="277"/>
-      <c r="D122" s="277"/>
+      <c r="C122" s="317"/>
+      <c r="D122" s="317"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -26977,11 +27125,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="277" t="s">
+      <c r="B123" s="317" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="277"/>
-      <c r="D123" s="277"/>
+      <c r="C123" s="317"/>
+      <c r="D123" s="317"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.76989873089142391</v>
@@ -27011,31 +27159,45 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="A47:C47"/>
@@ -27052,45 +27214,31 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -27162,20 +27310,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="277" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="319"/>
-      <c r="C1" s="319"/>
-      <c r="D1" s="319"/>
-      <c r="E1" s="319"/>
-      <c r="F1" s="319"/>
-      <c r="G1" s="319"/>
-      <c r="H1" s="319"/>
-      <c r="I1" s="319"/>
-      <c r="J1" s="319"/>
-      <c r="K1" s="319"/>
-      <c r="L1" s="319"/>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
+      <c r="K1" s="277"/>
+      <c r="L1" s="277"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27205,26 +27353,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="320" t="s">
+      <c r="A3" s="274" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="320"/>
-      <c r="C3" s="321" t="s">
+      <c r="B3" s="274"/>
+      <c r="C3" s="278" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="320" t="s">
+      <c r="G3" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="320"/>
-      <c r="I3" s="321" t="s">
+      <c r="H3" s="274"/>
+      <c r="I3" s="278" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="321"/>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="278"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27251,28 +27399,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="320" t="s">
+      <c r="A5" s="274" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="320"/>
-      <c r="C5" s="322" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="275" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="322"/>
-      <c r="E5" s="322"/>
+      <c r="D5" s="275"/>
+      <c r="E5" s="275"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="274" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="320"/>
-      <c r="I5" s="323">
+      <c r="H5" s="274"/>
+      <c r="I5" s="276">
         <v>500</v>
       </c>
-      <c r="J5" s="323"/>
-      <c r="K5" s="322" t="s">
+      <c r="J5" s="276"/>
+      <c r="K5" s="275" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="322"/>
+      <c r="L5" s="275"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27305,86 +27453,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="313" t="s">
+      <c r="A9" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="313"/>
-      <c r="C9" s="313"/>
+      <c r="B9" s="279"/>
+      <c r="C9" s="279"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="313" t="s">
+      <c r="A10" s="279" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="313"/>
-      <c r="N10" s="314"/>
-      <c r="O10" s="314"/>
-      <c r="P10" s="314"/>
-      <c r="Q10" s="314"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
+      <c r="N10" s="280"/>
+      <c r="O10" s="280"/>
+      <c r="P10" s="280"/>
+      <c r="Q10" s="280"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="318"/>
-      <c r="B12" s="318"/>
-      <c r="C12" s="318"/>
-      <c r="E12" s="318"/>
-      <c r="F12" s="318"/>
-      <c r="G12" s="318"/>
-      <c r="I12" s="350" t="s">
+      <c r="A12" s="284"/>
+      <c r="B12" s="284"/>
+      <c r="C12" s="284"/>
+      <c r="E12" s="284"/>
+      <c r="F12" s="284"/>
+      <c r="G12" s="284"/>
+      <c r="I12" s="344" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="351"/>
-      <c r="K12" s="352"/>
-      <c r="M12" s="350" t="s">
+      <c r="J12" s="345"/>
+      <c r="K12" s="346"/>
+      <c r="M12" s="344" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="351"/>
-      <c r="O12" s="352"/>
+      <c r="N12" s="345"/>
+      <c r="O12" s="346"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="306"/>
-      <c r="B13" s="306"/>
+      <c r="A13" s="287"/>
+      <c r="B13" s="287"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="306"/>
-      <c r="F13" s="306"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="287"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="331" t="s">
+      <c r="I13" s="341" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="332"/>
+      <c r="J13" s="342"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="331" t="s">
+      <c r="M13" s="341" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="332"/>
+      <c r="N13" s="342"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="306"/>
-      <c r="B14" s="306"/>
+      <c r="A14" s="287"/>
+      <c r="B14" s="287"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="306"/>
-      <c r="F14" s="306"/>
+      <c r="E14" s="287"/>
+      <c r="F14" s="287"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="309" t="s">
+      <c r="I14" s="288" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="310"/>
+      <c r="J14" s="289"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="309" t="s">
+      <c r="M14" s="288" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="310"/>
+      <c r="N14" s="289"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27392,11 +27540,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="306"/>
-      <c r="B15" s="306"/>
+      <c r="A15" s="287"/>
+      <c r="B15" s="287"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="306"/>
-      <c r="F15" s="306"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27405,10 +27553,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="309" t="s">
+      <c r="M15" s="288" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="310"/>
+      <c r="N15" s="289"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27417,103 +27565,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="306"/>
-      <c r="B16" s="306"/>
+      <c r="A16" s="287"/>
+      <c r="B16" s="287"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="304" t="s">
+      <c r="I16" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="305"/>
+      <c r="J16" s="291"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="309" t="s">
+      <c r="M16" s="288" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="310"/>
+      <c r="N16" s="289"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="306"/>
-      <c r="B17" s="306"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="306"/>
-      <c r="F17" s="306"/>
+      <c r="E17" s="287"/>
+      <c r="F17" s="287"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="309" t="s">
+      <c r="M17" s="288" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="310"/>
+      <c r="N17" s="289"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="309" t="s">
+      <c r="M18" s="288" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="310"/>
+      <c r="N18" s="289"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="344" t="s">
+      <c r="M19" s="349" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="345"/>
+      <c r="N19" s="350"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="346"/>
-      <c r="N20" s="347"/>
+      <c r="M20" s="351"/>
+      <c r="N20" s="352"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="307" t="s">
+      <c r="C21" s="292" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="307" t="s">
+      <c r="E21" s="292" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307" t="s">
+      <c r="F21" s="292"/>
+      <c r="G21" s="292" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="307" t="s">
+      <c r="H21" s="292" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="307"/>
+      <c r="C22" s="292"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="307"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="307"/>
-      <c r="H22" s="307"/>
+      <c r="E22" s="292"/>
+      <c r="F22" s="292"/>
+      <c r="G22" s="292"/>
+      <c r="H22" s="292"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="308"/>
+      <c r="C23" s="293"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
-      <c r="G23" s="308"/>
-      <c r="H23" s="308"/>
+      <c r="E23" s="293"/>
+      <c r="F23" s="293"/>
+      <c r="G23" s="293"/>
+      <c r="H23" s="293"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -27896,12 +28044,12 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="348" t="s">
+      <c r="A33" s="347" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="349"/>
-      <c r="C33" s="349"/>
-      <c r="D33" s="349"/>
+      <c r="B33" s="348"/>
+      <c r="C33" s="348"/>
+      <c r="D33" s="348"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -27947,19 +28095,19 @@
         <f>B37/B36</f>
         <v>1.0597680097680098</v>
       </c>
-      <c r="C35" s="299" t="s">
+      <c r="C35" s="297" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="299"/>
+      <c r="D35" s="297"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.809590059054404</v>
       </c>
-      <c r="F35" s="299" t="s">
+      <c r="F35" s="297" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="299"/>
-      <c r="H35" s="299"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="297"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -27973,19 +28121,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163.80000000000001</v>
       </c>
-      <c r="C36" s="299" t="s">
+      <c r="C36" s="297" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="299"/>
+      <c r="D36" s="297"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.745288000000002</v>
       </c>
-      <c r="F36" s="299" t="s">
+      <c r="F36" s="297" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="299"/>
-      <c r="H36" s="299"/>
+      <c r="G36" s="297"/>
+      <c r="H36" s="297"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -28004,19 +28152,19 @@
         <f>SUM(F25:F32)</f>
         <v>173.59</v>
       </c>
-      <c r="C37" s="299" t="s">
+      <c r="C37" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="299"/>
+      <c r="D37" s="297"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7607005011809438</v>
       </c>
-      <c r="F37" s="299" t="s">
+      <c r="F37" s="297" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="299"/>
-      <c r="H37" s="299"/>
+      <c r="G37" s="297"/>
+      <c r="H37" s="297"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>500</v>
@@ -28030,29 +28178,29 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.38158350000000002</v>
       </c>
-      <c r="C38" s="299" t="s">
+      <c r="C38" s="297" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="299"/>
+      <c r="D38" s="297"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.063895264400994</v>
       </c>
-      <c r="F38" s="299" t="s">
+      <c r="F38" s="297" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="299"/>
-      <c r="H38" s="299"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="297"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="299" t="s">
+      <c r="C39" s="297" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="299"/>
+      <c r="D39" s="297"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0009729183068661</v>
@@ -28106,11 +28254,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="301" t="s">
+      <c r="A44" s="299" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="302"/>
-      <c r="C44" s="303"/>
+      <c r="B44" s="300"/>
+      <c r="C44" s="301"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -28140,11 +28288,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="286" t="s">
+      <c r="A46" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="286"/>
-      <c r="C46" s="286"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -28159,11 +28307,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="286" t="s">
+      <c r="A47" s="294" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="286"/>
-      <c r="C47" s="286"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.372179596826548</v>
@@ -28179,11 +28327,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="286" t="s">
+      <c r="A48" s="294" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="286"/>
-      <c r="C48" s="286"/>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>283.01185101569587</v>
@@ -28199,11 +28347,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="286" t="s">
+      <c r="A49" s="294" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="286"/>
-      <c r="C49" s="286"/>
+      <c r="B49" s="294"/>
+      <c r="C49" s="294"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28219,11 +28367,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="286" t="s">
+      <c r="A50" s="294" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="286"/>
-      <c r="C50" s="286"/>
+      <c r="B50" s="294"/>
+      <c r="C50" s="294"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>912.94145488934146</v>
@@ -28254,11 +28402,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="286" t="s">
+      <c r="A52" s="294" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="286"/>
-      <c r="C52" s="286"/>
+      <c r="B52" s="294"/>
+      <c r="C52" s="294"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28273,11 +28421,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="286" t="s">
+      <c r="A53" s="294" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="286"/>
-      <c r="C53" s="286"/>
+      <c r="B53" s="294"/>
+      <c r="C53" s="294"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.25705038862782</v>
@@ -28764,23 +28912,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="290"/>
-      <c r="C73" s="291" t="s">
+      <c r="B73" s="307"/>
+      <c r="C73" s="308" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="293" t="s">
+      <c r="E73" s="310" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="295" t="s">
+      <c r="F73" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="295" t="s">
+      <c r="G73" s="312" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="284" t="s">
+      <c r="H73" s="302" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -28794,15 +28942,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="290"/>
-      <c r="C74" s="292"/>
+      <c r="B74" s="307"/>
+      <c r="C74" s="309"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="294"/>
-      <c r="F74" s="296"/>
-      <c r="G74" s="296"/>
-      <c r="H74" s="285"/>
+      <c r="E74" s="311"/>
+      <c r="F74" s="313"/>
+      <c r="G74" s="313"/>
+      <c r="H74" s="303"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -29041,9 +29189,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="278"/>
-      <c r="I82" s="278"/>
-      <c r="J82" s="278"/>
+      <c r="H82" s="318"/>
+      <c r="I82" s="318"/>
+      <c r="J82" s="318"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -29051,19 +29199,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="279" t="s">
+      <c r="B83" s="319" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="279"/>
-      <c r="D83" s="279"/>
-      <c r="E83" s="279"/>
-      <c r="F83" s="279"/>
-      <c r="G83" s="279"/>
-      <c r="H83" s="279"/>
-      <c r="I83" s="279"/>
-      <c r="J83" s="279"/>
-      <c r="K83" s="279"/>
-      <c r="L83" s="279"/>
+      <c r="C83" s="319"/>
+      <c r="D83" s="319"/>
+      <c r="E83" s="319"/>
+      <c r="F83" s="319"/>
+      <c r="G83" s="319"/>
+      <c r="H83" s="319"/>
+      <c r="I83" s="319"/>
+      <c r="J83" s="319"/>
+      <c r="K83" s="319"/>
+      <c r="L83" s="319"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -29129,17 +29277,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="336" t="s">
+      <c r="H87" s="325" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="337"/>
+      <c r="I87" s="326"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="338" t="s">
+      <c r="K87" s="327" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="339"/>
+      <c r="L87" s="328"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -29151,20 +29299,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="340">
+      <c r="H88" s="329">
         <f>C75+H70</f>
         <v>3.0787051830524823</v>
       </c>
-      <c r="I88" s="341"/>
+      <c r="I88" s="330"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>6.0858781331305026E-2</v>
       </c>
-      <c r="K88" s="342">
+      <c r="K88" s="331">
         <f>E106+E122</f>
         <v>3.2660714285714287</v>
       </c>
-      <c r="L88" s="343"/>
+      <c r="L88" s="332"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29235,10 +29383,10 @@
         <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="281" t="s">
+      <c r="Q92" s="321" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="281"/>
+      <c r="R92" s="321"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0381616609601965</v>
@@ -29296,10 +29444,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="282" t="s">
+      <c r="T94" s="322" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="283"/>
+      <c r="U94" s="323"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29333,11 +29481,11 @@
         <f>R95/S92</f>
         <v>0.76240265782733074</v>
       </c>
-      <c r="T95" s="274">
+      <c r="T95" s="314">
         <f>R96-R95</f>
         <v>0.18736624551894643</v>
       </c>
-      <c r="U95" s="276">
+      <c r="U95" s="316">
         <f>(R96-R95)/R95</f>
         <v>6.0858781331305026E-2</v>
       </c>
@@ -29376,8 +29524,8 @@
         <f>R96/S92</f>
         <v>0.80880155446645008</v>
       </c>
-      <c r="T96" s="275"/>
-      <c r="U96" s="276"/>
+      <c r="T96" s="315"/>
+      <c r="U96" s="316"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -29851,11 +29999,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="277" t="s">
+      <c r="B122" s="317" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="277"/>
-      <c r="D122" s="277"/>
+      <c r="C122" s="317"/>
+      <c r="D122" s="317"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -29863,11 +30011,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="277" t="s">
+      <c r="B123" s="317" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="277"/>
-      <c r="D123" s="277"/>
+      <c r="C123" s="317"/>
+      <c r="D123" s="317"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>0.10324804175431759</v>
@@ -29897,72 +30045,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -29976,6 +30058,72 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529A7954-5EC5-4FCA-94A2-2C36BB0BA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895582E6-7D68-4AB7-AC12-A112B6DBD80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4291752228" uniqueCount="353">
   <si>
     <t>Roll</t>
   </si>
@@ -1161,6 +1161,42 @@
   </si>
   <si>
     <t>∞</t>
+  </si>
+  <si>
+    <t>Cost breakdown</t>
+  </si>
+  <si>
+    <t>Substrates</t>
+  </si>
+  <si>
+    <t>sum of all substrates cost per Kg and per M2</t>
+  </si>
+  <si>
+    <t>Ink, Solvent, Ahdesive &amp; Coating</t>
+  </si>
+  <si>
+    <t>Waste</t>
+  </si>
+  <si>
+    <t>based on the band calclaution</t>
+  </si>
+  <si>
+    <t>coast of the falies packaging in the structure er kg and per m2</t>
+  </si>
+  <si>
+    <t>PrePress</t>
+  </si>
+  <si>
+    <t>Cost of Prepress as capture under Tooling / development charge, per kg and per m2</t>
+  </si>
+  <si>
+    <t>Total RM</t>
+  </si>
+  <si>
+    <t>sum of all above in kg and in m2</t>
+  </si>
+  <si>
+    <t>sum of cost of the families Ink &amp; Coating, Adhesive,Solvent per kg and per m2</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1229,7 @@
     <numFmt numFmtId="185" formatCode="\$0.00"/>
     <numFmt numFmtId="186" formatCode="#,##0\ &quot;Pcs&quot;"/>
   </numFmts>
-  <fonts count="53" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1558,6 +1594,30 @@
       <name val="Trebuchet MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF78716C"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1639,7 +1699,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="84">
+  <borders count="86">
     <border>
       <left/>
       <right/>
@@ -2724,6 +2784,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE7E5E4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE7E5E4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2733,7 +2811,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3371,95 +3449,61 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="186" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3491,38 +3535,122 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3548,54 +3676,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3607,6 +3687,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3620,22 +3715,23 @@
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -16697,99 +16793,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>440871</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>45719</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>594918</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>42609</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D6A5981-F640-E0D0-A92C-F71EB9A51CA4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3488871" y="971005"/>
-          <a:ext cx="7926447" cy="5058747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>58264</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>72665</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13C73FAC-99C2-B66B-F79F-D83BD0C8A207}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11430000" y="1589315"/>
-          <a:ext cx="7983064" cy="3915321"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
 <FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
   <bag type="Checkbox"/>
@@ -17398,20 +17401,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="326" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="277"/>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
+      <c r="K1" s="326"/>
+      <c r="L1" s="326"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17439,26 +17442,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="327" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="278" t="s">
+      <c r="B3" s="327"/>
+      <c r="C3" s="328" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="327" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="278" t="s">
+      <c r="H3" s="327"/>
+      <c r="I3" s="328" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="278"/>
-      <c r="K3" s="278"/>
-      <c r="L3" s="278"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17483,28 +17486,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="327"/>
+      <c r="C5" s="329" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="329"/>
+      <c r="E5" s="329"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="327" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="327"/>
+      <c r="I5" s="330">
         <v>10000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="330"/>
+      <c r="K5" s="329" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="329"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17535,132 +17538,132 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="279" t="s">
+      <c r="A9" s="320" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="279"/>
-      <c r="C9" s="279"/>
+      <c r="B9" s="320"/>
+      <c r="C9" s="320"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="320" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
+      <c r="B10" s="320"/>
+      <c r="C10" s="320"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="280"/>
-      <c r="P10" s="280"/>
+      <c r="O10" s="321"/>
+      <c r="P10" s="321"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="281" t="s">
+      <c r="A12" s="322" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="282"/>
-      <c r="C12" s="283"/>
+      <c r="B12" s="323"/>
+      <c r="C12" s="324"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="284"/>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
+      <c r="I12" s="325"/>
+      <c r="J12" s="325"/>
+      <c r="K12" s="325"/>
+      <c r="M12" s="325"/>
+      <c r="N12" s="325"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="285" t="s">
+      <c r="A13" s="318" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="286"/>
+      <c r="B13" s="319"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="287"/>
-      <c r="F13" s="287"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="313"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="287"/>
-      <c r="J13" s="287"/>
+      <c r="I13" s="313"/>
+      <c r="J13" s="313"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="288" t="s">
+      <c r="A14" s="316" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="289"/>
+      <c r="B14" s="317"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="287"/>
-      <c r="F14" s="287"/>
+      <c r="E14" s="313"/>
+      <c r="F14" s="313"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="287"/>
-      <c r="J14" s="287"/>
+      <c r="I14" s="313"/>
+      <c r="J14" s="313"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="287"/>
-      <c r="N14" s="287"/>
+      <c r="M14" s="313"/>
+      <c r="N14" s="313"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="288" t="s">
+      <c r="A15" s="316" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="289"/>
+      <c r="B15" s="317"/>
       <c r="C15" s="31">
         <v>0</v>
       </c>
-      <c r="E15" s="287"/>
-      <c r="F15" s="287"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="313"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="287"/>
-      <c r="N15" s="287"/>
+      <c r="M15" s="313"/>
+      <c r="N15" s="313"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="316" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="289"/>
+      <c r="B16" s="317"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="287"/>
-      <c r="J16" s="287"/>
+      <c r="I16" s="313"/>
+      <c r="J16" s="313"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="287"/>
-      <c r="N16" s="287"/>
+      <c r="M16" s="313"/>
+      <c r="N16" s="313"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="290" t="s">
+      <c r="A17" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="291"/>
+      <c r="B17" s="312"/>
       <c r="C17" s="32">
         <v>0</v>
       </c>
-      <c r="E17" s="287"/>
-      <c r="F17" s="287"/>
+      <c r="E17" s="313"/>
+      <c r="F17" s="313"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="287"/>
-      <c r="N17" s="287"/>
+      <c r="M17" s="313"/>
+      <c r="N17" s="313"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
         <v>12.787723785166239</v>
       </c>
-      <c r="M18" s="287"/>
-      <c r="N18" s="287"/>
+      <c r="M18" s="313"/>
+      <c r="N18" s="313"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L19">
@@ -17679,28 +17682,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="292"/>
+      <c r="C21" s="314"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="292"/>
-      <c r="F21" s="292"/>
-      <c r="G21" s="292"/>
-      <c r="H21" s="292"/>
+      <c r="E21" s="314"/>
+      <c r="F21" s="314"/>
+      <c r="G21" s="314"/>
+      <c r="H21" s="314"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="292"/>
+      <c r="C22" s="314"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="292"/>
-      <c r="G22" s="292"/>
-      <c r="H22" s="292"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="314"/>
+      <c r="H22" s="314"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="293"/>
+      <c r="C23" s="315"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="293"/>
-      <c r="F23" s="293"/>
-      <c r="G23" s="293"/>
-      <c r="H23" s="293"/>
+      <c r="E23" s="315"/>
+      <c r="F23" s="315"/>
+      <c r="G23" s="315"/>
+      <c r="H23" s="315"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -17885,12 +17888,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="295" t="s">
+      <c r="A31" s="304" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="296"/>
-      <c r="C31" s="296"/>
-      <c r="D31" s="296"/>
+      <c r="B31" s="305"/>
+      <c r="C31" s="305"/>
+      <c r="D31" s="305"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17950,23 +17953,23 @@
       <c r="A35" s="273" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="358">
+      <c r="B35" s="275">
         <f>B37/B36</f>
         <v>0.92306952591595348</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="306" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="306"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>833.42014793207625</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="306" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="306"/>
+      <c r="H35" s="306"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>0</v>
@@ -17976,23 +17979,23 @@
       <c r="A36" s="273" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="359">
+      <c r="B36" s="276">
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
         <v>51.994999999999997</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="306" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="306"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>1.199875</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="306" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="306"/>
+      <c r="H36" s="306"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -18013,23 +18016,23 @@
       <c r="A37" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="359">
+      <c r="B37" s="276">
         <f>SUM(F25:F30)</f>
         <v>47.994999999999997</v>
       </c>
-      <c r="C37" s="298" t="s">
+      <c r="C37" s="307" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="298"/>
-      <c r="E37" s="357">
+      <c r="D37" s="307"/>
+      <c r="E37" s="274">
         <f>1000/B37</f>
         <v>20.835503698301906</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="306" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="306"/>
+      <c r="H37" s="306"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>8334.2014793207618</v>
@@ -18043,29 +18046,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10741250000000001</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="306"/>
       <c r="E38" s="15" t="e">
         <f>(E37/I35)*1000</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="306" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="306"/>
+      <c r="H38" s="306"/>
       <c r="I38" s="38" t="e">
         <f>I36*E38</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="297" t="s">
+      <c r="C39" s="306" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="306"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>83.342014793207625</v>
@@ -18122,11 +18125,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="299" t="s">
+      <c r="A44" s="308" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="300"/>
-      <c r="C44" s="301"/>
+      <c r="B44" s="309"/>
+      <c r="C44" s="310"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -18156,11 +18159,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="294" t="s">
+      <c r="A46" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
+      <c r="B46" s="293"/>
+      <c r="C46" s="293"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18175,11 +18178,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="294" t="s">
+      <c r="A47" s="293" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
+      <c r="B47" s="293"/>
+      <c r="C47" s="293"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>59.633717188336227</v>
@@ -18195,11 +18198,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="294" t="s">
+      <c r="A48" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
+      <c r="B48" s="293"/>
+      <c r="C48" s="293"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>4969.9941400842772</v>
@@ -18215,11 +18218,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="293" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
+      <c r="B49" s="293"/>
+      <c r="C49" s="293"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18235,11 +18238,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="294" t="s">
+      <c r="A50" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="294"/>
-      <c r="C50" s="294"/>
+      <c r="B50" s="293"/>
+      <c r="C50" s="293"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>49699.941400842778</v>
@@ -18270,11 +18273,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="294" t="s">
+      <c r="A52" s="293" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="294"/>
-      <c r="C52" s="294"/>
+      <c r="B52" s="293"/>
+      <c r="C52" s="293"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18289,11 +18292,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="294" t="s">
+      <c r="A53" s="293" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="294"/>
-      <c r="C53" s="294"/>
+      <c r="B53" s="293"/>
+      <c r="C53" s="293"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>662.77051272480605</v>
@@ -18439,7 +18442,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4407.5707290938053</v>
       </c>
-      <c r="H60" s="304">
+      <c r="H60" s="294">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>4407.5707290938053</v>
       </c>
@@ -18473,7 +18476,7 @@
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="305"/>
+      <c r="H61" s="295"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18504,7 +18507,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="305"/>
+      <c r="H62" s="295"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18535,7 +18538,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="305"/>
+      <c r="H63" s="295"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18566,7 +18569,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H64" s="305"/>
+      <c r="H64" s="295"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18597,7 +18600,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H65" s="305"/>
+      <c r="H65" s="295"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18628,7 +18631,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="305"/>
+      <c r="H66" s="295"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18658,7 +18661,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="305"/>
+      <c r="H67" s="295"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18688,7 +18691,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="305"/>
+      <c r="H68" s="295"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18718,7 +18721,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="306"/>
+      <c r="H69" s="296"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18778,23 +18781,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="307"/>
-      <c r="C73" s="308" t="s">
+      <c r="B73" s="297"/>
+      <c r="C73" s="298" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="310" t="s">
+      <c r="E73" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="312" t="s">
+      <c r="F73" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="312" t="s">
+      <c r="G73" s="302" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="302" t="s">
+      <c r="H73" s="291" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18807,15 +18810,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="307"/>
-      <c r="C74" s="309"/>
+      <c r="B74" s="297"/>
+      <c r="C74" s="299"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="311"/>
-      <c r="F74" s="313"/>
-      <c r="G74" s="313"/>
-      <c r="H74" s="303"/>
+      <c r="E74" s="301"/>
+      <c r="F74" s="303"/>
+      <c r="G74" s="303"/>
+      <c r="H74" s="292"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -19046,9 +19049,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="318"/>
-      <c r="I82" s="318"/>
-      <c r="J82" s="318"/>
+      <c r="H82" s="285"/>
+      <c r="I82" s="285"/>
+      <c r="J82" s="285"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -19056,19 +19059,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="319" t="s">
+      <c r="B83" s="286" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="319"/>
-      <c r="D83" s="319"/>
-      <c r="E83" s="319"/>
-      <c r="F83" s="319"/>
-      <c r="G83" s="319"/>
-      <c r="H83" s="319"/>
-      <c r="I83" s="319"/>
-      <c r="J83" s="319"/>
-      <c r="K83" s="319"/>
-      <c r="L83" s="319"/>
+      <c r="C83" s="286"/>
+      <c r="D83" s="286"/>
+      <c r="E83" s="286"/>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="286"/>
+      <c r="I83" s="286"/>
+      <c r="J83" s="286"/>
+      <c r="K83" s="286"/>
+      <c r="L83" s="286"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -19153,11 +19156,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="320"/>
-      <c r="I88" s="320"/>
+      <c r="H88" s="287"/>
+      <c r="I88" s="287"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="320"/>
-      <c r="L88" s="320"/>
+      <c r="K88" s="287"/>
+      <c r="L88" s="287"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19247,10 +19250,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="321" t="s">
+      <c r="Q92" s="288" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="321"/>
+      <c r="R92" s="288"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.6501486762013902</v>
@@ -19310,10 +19313,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="322" t="s">
+      <c r="T94" s="289" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="323"/>
+      <c r="U94" s="290"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19346,11 +19349,11 @@
         <f>R95/S92</f>
         <v>0.7338743847253193</v>
       </c>
-      <c r="T95" s="314">
+      <c r="T95" s="281">
         <f>R96-R95</f>
         <v>-1.1330363281889482</v>
       </c>
-      <c r="U95" s="316">
+      <c r="U95" s="283">
         <f>(R96-R95)/R95</f>
         <v>-0.42297193412043299</v>
       </c>
@@ -19386,8 +19389,8 @@
         <f>R96/S92</f>
         <v>0.42346611681660823</v>
       </c>
-      <c r="T96" s="315"/>
-      <c r="U96" s="316"/>
+      <c r="T96" s="282"/>
+      <c r="U96" s="283"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -19840,22 +19843,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="317" t="s">
+      <c r="B122" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="317"/>
-      <c r="D122" s="317"/>
+      <c r="C122" s="284"/>
+      <c r="D122" s="284"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="317" t="s">
+      <c r="B123" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="317"/>
-      <c r="D123" s="317"/>
+      <c r="C123" s="284"/>
+      <c r="D123" s="284"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>1.0851568256888184</v>
@@ -19863,28 +19866,44 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="C35:D35"/>
@@ -19898,44 +19917,28 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -20018,40 +20021,40 @@
       </c>
     </row>
     <row r="8" spans="7:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="355">
+      <c r="G8" s="362">
         <v>1</v>
       </c>
-      <c r="H8" s="356" t="s">
+      <c r="H8" s="363" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="356" t="s">
+      <c r="I8" s="363" t="s">
         <v>328</v>
       </c>
-      <c r="J8" s="356" t="s">
+      <c r="J8" s="363" t="s">
         <v>328</v>
       </c>
-      <c r="K8" s="356" t="s">
+      <c r="K8" s="363" t="s">
         <v>328</v>
       </c>
-      <c r="L8" s="356" t="s">
+      <c r="L8" s="363" t="s">
         <v>331</v>
       </c>
-      <c r="M8" s="356" t="s">
+      <c r="M8" s="363" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="356" t="s">
+      <c r="N8" s="363" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="7:14" x14ac:dyDescent="0.3">
-      <c r="G9" s="355"/>
-      <c r="H9" s="356"/>
-      <c r="I9" s="356"/>
-      <c r="J9" s="356"/>
-      <c r="K9" s="356"/>
-      <c r="L9" s="356"/>
-      <c r="M9" s="356"/>
-      <c r="N9" s="356"/>
+      <c r="G9" s="362"/>
+      <c r="H9" s="363"/>
+      <c r="I9" s="363"/>
+      <c r="J9" s="363"/>
+      <c r="K9" s="363"/>
+      <c r="L9" s="363"/>
+      <c r="M9" s="363"/>
+      <c r="N9" s="363"/>
     </row>
     <row r="17" spans="7:20" ht="55.2" x14ac:dyDescent="0.3">
       <c r="G17" s="268" t="s">
@@ -20175,102 +20178,185 @@
     <mergeCell ref="L8:L9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC5812A-307F-453C-92CE-92FF0734E5BC}">
-  <dimension ref="B2:I4"/>
+  <dimension ref="B2:L23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="360">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="277">
         <v>0</v>
       </c>
-      <c r="C2" s="360">
+      <c r="C2" s="277">
         <f>B4+1</f>
         <v>81</v>
       </c>
-      <c r="D2" s="360">
+      <c r="D2" s="277">
         <f>C4+1</f>
         <v>151</v>
       </c>
-      <c r="E2" s="360">
+      <c r="E2" s="277">
         <f t="shared" ref="E2:I2" si="0">D4+1</f>
         <v>301</v>
       </c>
-      <c r="F2" s="360">
+      <c r="F2" s="277">
         <f t="shared" si="0"/>
         <v>601</v>
       </c>
-      <c r="G2" s="360">
+      <c r="G2" s="277">
         <f t="shared" si="0"/>
         <v>1501</v>
       </c>
-      <c r="H2" s="360">
+      <c r="H2" s="277">
         <f t="shared" si="0"/>
         <v>3001</v>
       </c>
-      <c r="I2" s="360">
+      <c r="I2" s="277">
         <f t="shared" si="0"/>
         <v>5001</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="361" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="C3" s="361" t="s">
+      <c r="C3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="D3" s="361" t="s">
+      <c r="D3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="E3" s="361" t="s">
+      <c r="E3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="F3" s="361" t="s">
+      <c r="F3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="G3" s="361" t="s">
+      <c r="G3" s="278" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="362"/>
-      <c r="I3" s="362"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="360">
+      <c r="H3" s="279"/>
+      <c r="I3" s="279"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="277">
         <v>80</v>
       </c>
-      <c r="C4" s="360">
+      <c r="C4" s="277">
         <v>150</v>
       </c>
-      <c r="D4" s="360">
+      <c r="D4" s="277">
         <v>300</v>
       </c>
-      <c r="E4" s="360">
+      <c r="E4" s="277">
         <v>600</v>
       </c>
-      <c r="F4" s="360">
+      <c r="F4" s="277">
         <v>1500</v>
       </c>
-      <c r="G4" s="360">
+      <c r="G4" s="277">
         <v>3000</v>
       </c>
-      <c r="H4" s="360">
+      <c r="H4" s="277">
         <v>5000</v>
       </c>
-      <c r="I4" s="363" t="s">
+      <c r="I4" s="280" t="s">
         <v>340</v>
       </c>
     </row>
+    <row r="9" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K9" s="368" t="s">
+        <v>341</v>
+      </c>
+      <c r="L9" s="368"/>
+    </row>
+    <row r="10" spans="2:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="K10" s="364"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K12" t="s">
+        <v>344</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K13" t="s">
+        <v>345</v>
+      </c>
+      <c r="L13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K14" t="s">
+        <v>188</v>
+      </c>
+      <c r="L14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>348</v>
+      </c>
+      <c r="L15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K16" s="369" t="s">
+        <v>350</v>
+      </c>
+      <c r="L16" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K17" s="365"/>
+    </row>
+    <row r="18" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K18" s="365"/>
+    </row>
+    <row r="19" spans="11:11" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K19" s="365"/>
+    </row>
+    <row r="20" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K20" s="366"/>
+    </row>
+    <row r="21" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K21" s="367"/>
+    </row>
+    <row r="22" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K22" s="367"/>
+    </row>
+    <row r="23" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K23" s="367"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="K9:L9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21203,20 +21289,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="326" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="277"/>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
+      <c r="K1" s="326"/>
+      <c r="L1" s="326"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21244,26 +21330,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="327" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="278" t="s">
+      <c r="B3" s="327"/>
+      <c r="C3" s="328" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="327" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="278" t="s">
+      <c r="H3" s="327"/>
+      <c r="I3" s="328" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="278"/>
-      <c r="K3" s="278"/>
-      <c r="L3" s="278"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -21288,28 +21374,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="327"/>
+      <c r="C5" s="329" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="329"/>
+      <c r="E5" s="329"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="327" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="327"/>
+      <c r="I5" s="330">
         <v>10000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="330"/>
+      <c r="K5" s="329" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="329"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -21340,128 +21426,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="279" t="s">
+      <c r="A9" s="320" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="279"/>
-      <c r="C9" s="279"/>
+      <c r="B9" s="320"/>
+      <c r="C9" s="320"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="320" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
+      <c r="B10" s="320"/>
+      <c r="C10" s="320"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="280"/>
-      <c r="P10" s="280"/>
+      <c r="O10" s="321"/>
+      <c r="P10" s="321"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="281" t="s">
+      <c r="A12" s="322" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="282"/>
-      <c r="C12" s="283"/>
+      <c r="B12" s="323"/>
+      <c r="C12" s="324"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="284"/>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
+      <c r="I12" s="325"/>
+      <c r="J12" s="325"/>
+      <c r="K12" s="325"/>
+      <c r="M12" s="325"/>
+      <c r="N12" s="325"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="285" t="s">
+      <c r="A13" s="318" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="286"/>
+      <c r="B13" s="319"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="287"/>
-      <c r="F13" s="287"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="313"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="287"/>
-      <c r="J13" s="287"/>
+      <c r="I13" s="313"/>
+      <c r="J13" s="313"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="288" t="s">
+      <c r="A14" s="316" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="289"/>
+      <c r="B14" s="317"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="287"/>
-      <c r="F14" s="287"/>
+      <c r="E14" s="313"/>
+      <c r="F14" s="313"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="287"/>
-      <c r="J14" s="287"/>
+      <c r="I14" s="313"/>
+      <c r="J14" s="313"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="287"/>
-      <c r="N14" s="287"/>
+      <c r="M14" s="313"/>
+      <c r="N14" s="313"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="288" t="s">
+      <c r="A15" s="316" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="289"/>
+      <c r="B15" s="317"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="287"/>
-      <c r="F15" s="287"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="313"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="287"/>
-      <c r="N15" s="287"/>
+      <c r="M15" s="313"/>
+      <c r="N15" s="313"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="316" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="289"/>
+      <c r="B16" s="317"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="287"/>
-      <c r="J16" s="287"/>
+      <c r="I16" s="313"/>
+      <c r="J16" s="313"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="287"/>
-      <c r="N16" s="287"/>
+      <c r="M16" s="313"/>
+      <c r="N16" s="313"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="290" t="s">
+      <c r="A17" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="291"/>
+      <c r="B17" s="312"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="287"/>
-      <c r="F17" s="287"/>
+      <c r="E17" s="313"/>
+      <c r="F17" s="313"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="287"/>
-      <c r="N17" s="287"/>
+      <c r="M17" s="313"/>
+      <c r="N17" s="313"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="287"/>
-      <c r="N18" s="287"/>
+      <c r="M18" s="313"/>
+      <c r="N18" s="313"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21472,28 +21558,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="292"/>
+      <c r="C21" s="314"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="292"/>
-      <c r="F21" s="292"/>
-      <c r="G21" s="292"/>
-      <c r="H21" s="292"/>
+      <c r="E21" s="314"/>
+      <c r="F21" s="314"/>
+      <c r="G21" s="314"/>
+      <c r="H21" s="314"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="292"/>
+      <c r="C22" s="314"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="292"/>
-      <c r="G22" s="292"/>
-      <c r="H22" s="292"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="314"/>
+      <c r="H22" s="314"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="293"/>
+      <c r="C23" s="315"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="293"/>
-      <c r="F23" s="293"/>
-      <c r="G23" s="293"/>
-      <c r="H23" s="293"/>
+      <c r="E23" s="315"/>
+      <c r="F23" s="315"/>
+      <c r="G23" s="315"/>
+      <c r="H23" s="315"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21734,12 +21820,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="295" t="s">
+      <c r="A31" s="304" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="296"/>
-      <c r="C31" s="296"/>
-      <c r="D31" s="296"/>
+      <c r="B31" s="305"/>
+      <c r="C31" s="305"/>
+      <c r="D31" s="305"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21802,19 +21888,19 @@
         <f>B37/B36</f>
         <v>0.9813242784380305</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="306" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="306"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>346.02076124567475</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="306" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="306"/>
+      <c r="H35" s="306"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21828,19 +21914,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117.8</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="306" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="306"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.89</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="306" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="306"/>
+      <c r="H36" s="306"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21865,19 +21951,19 @@
         <f>SUM(F25:F30)</f>
         <v>115.6</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="306" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="306"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.6505190311418687</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="306" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="306"/>
+      <c r="H37" s="306"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3460.2076124567475</v>
@@ -21891,29 +21977,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22398500000000002</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="306"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.4809010109234002</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="306" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="306"/>
+      <c r="H38" s="306"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="297" t="s">
+      <c r="C39" s="306" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="306"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.602076124567475</v>
@@ -21970,11 +22056,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="299" t="s">
+      <c r="A44" s="308" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="300"/>
-      <c r="C44" s="301"/>
+      <c r="B44" s="309"/>
+      <c r="C44" s="310"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -22004,11 +22090,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="294" t="s">
+      <c r="A46" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
+      <c r="B46" s="293"/>
+      <c r="C46" s="293"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -22023,11 +22109,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="294" t="s">
+      <c r="A47" s="293" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
+      <c r="B47" s="293"/>
+      <c r="C47" s="293"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.397190403781075</v>
@@ -22043,11 +22129,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="294" t="s">
+      <c r="A48" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
+      <c r="B48" s="293"/>
+      <c r="C48" s="293"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2193.6744084353313</v>
@@ -22063,11 +22149,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="293" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
+      <c r="B49" s="293"/>
+      <c r="C49" s="293"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -22083,11 +22169,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="294" t="s">
+      <c r="A50" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="294"/>
-      <c r="C50" s="294"/>
+      <c r="B50" s="293"/>
+      <c r="C50" s="293"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>21936.744084353315</v>
@@ -22118,11 +22204,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="294" t="s">
+      <c r="A52" s="293" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="294"/>
-      <c r="C52" s="294"/>
+      <c r="B52" s="293"/>
+      <c r="C52" s="293"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -22137,11 +22223,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="294" t="s">
+      <c r="A53" s="293" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="294"/>
-      <c r="C53" s="294"/>
+      <c r="B53" s="293"/>
+      <c r="C53" s="293"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.22615683819515</v>
@@ -22287,7 +22373,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4092.6347009391993</v>
       </c>
-      <c r="H60" s="304">
+      <c r="H60" s="294">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9441.736856218844</v>
       </c>
@@ -22321,7 +22407,7 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2596.1802021846802</v>
       </c>
-      <c r="H61" s="305"/>
+      <c r="H61" s="295"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -22352,7 +22438,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H62" s="305"/>
+      <c r="H62" s="295"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22383,7 +22469,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H63" s="305"/>
+      <c r="H63" s="295"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22414,7 +22500,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H64" s="305"/>
+      <c r="H64" s="295"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22445,7 +22531,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H65" s="305"/>
+      <c r="H65" s="295"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22476,7 +22562,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H66" s="305"/>
+      <c r="H66" s="295"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22506,7 +22592,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="305"/>
+      <c r="H67" s="295"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22536,7 +22622,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="305"/>
+      <c r="H68" s="295"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22566,7 +22652,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="306"/>
+      <c r="H69" s="296"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22626,23 +22712,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="307"/>
-      <c r="C73" s="308" t="s">
+      <c r="B73" s="297"/>
+      <c r="C73" s="298" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="310" t="s">
+      <c r="E73" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="312" t="s">
+      <c r="F73" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="312" t="s">
+      <c r="G73" s="302" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="302" t="s">
+      <c r="H73" s="291" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22655,15 +22741,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="307"/>
-      <c r="C74" s="309"/>
+      <c r="B74" s="297"/>
+      <c r="C74" s="299"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="311"/>
-      <c r="F74" s="313"/>
-      <c r="G74" s="313"/>
-      <c r="H74" s="303"/>
+      <c r="E74" s="301"/>
+      <c r="F74" s="303"/>
+      <c r="G74" s="303"/>
+      <c r="H74" s="292"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22894,9 +22980,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="318"/>
-      <c r="I82" s="318"/>
-      <c r="J82" s="318"/>
+      <c r="H82" s="285"/>
+      <c r="I82" s="285"/>
+      <c r="J82" s="285"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22904,19 +22990,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="319" t="s">
+      <c r="B83" s="286" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="319"/>
-      <c r="D83" s="319"/>
-      <c r="E83" s="319"/>
-      <c r="F83" s="319"/>
-      <c r="G83" s="319"/>
-      <c r="H83" s="319"/>
-      <c r="I83" s="319"/>
-      <c r="J83" s="319"/>
-      <c r="K83" s="319"/>
-      <c r="L83" s="319"/>
+      <c r="C83" s="286"/>
+      <c r="D83" s="286"/>
+      <c r="E83" s="286"/>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="286"/>
+      <c r="I83" s="286"/>
+      <c r="J83" s="286"/>
+      <c r="K83" s="286"/>
+      <c r="L83" s="286"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -23001,11 +23087,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="320"/>
-      <c r="I88" s="320"/>
+      <c r="H88" s="287"/>
+      <c r="I88" s="287"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="320"/>
-      <c r="L88" s="320"/>
+      <c r="K88" s="287"/>
+      <c r="L88" s="287"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -23095,10 +23181,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="321" t="s">
+      <c r="Q92" s="288" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="321"/>
+      <c r="R92" s="288"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7630361423692897</v>
@@ -23158,10 +23244,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="322" t="s">
+      <c r="T94" s="289" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="323"/>
+      <c r="U94" s="290"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -23194,11 +23280,11 @@
         <f>R95/S92</f>
         <v>0.76580720508248346</v>
       </c>
-      <c r="T95" s="314">
+      <c r="T95" s="281">
         <f>R96-R95</f>
         <v>-6.8260190812196253E-2</v>
       </c>
-      <c r="U95" s="316">
+      <c r="U95" s="283">
         <f>(R96-R95)/R95</f>
         <v>-2.368697819819552E-2</v>
       </c>
@@ -23234,8 +23320,8 @@
         <f>R96/S92</f>
         <v>0.74766754651167366</v>
       </c>
-      <c r="T96" s="315"/>
-      <c r="U96" s="316"/>
+      <c r="T96" s="282"/>
+      <c r="U96" s="283"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -23688,22 +23774,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="317" t="s">
+      <c r="B122" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="317"/>
-      <c r="D122" s="317"/>
+      <c r="C122" s="284"/>
+      <c r="D122" s="284"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="317" t="s">
+      <c r="B123" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="317"/>
-      <c r="D123" s="317"/>
+      <c r="C123" s="284"/>
+      <c r="D123" s="284"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-2.6611699687135438E-2</v>
@@ -23711,63 +23797,6 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23784,6 +23813,63 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -23890,16 +23976,16 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="324" t="s">
+      <c r="W1" s="331" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
+      <c r="X1" s="331"/>
+      <c r="Y1" s="331"/>
+      <c r="Z1" s="331"/>
+      <c r="AA1" s="331"/>
+      <c r="AB1" s="331"/>
+      <c r="AC1" s="331"/>
+      <c r="AD1" s="331"/>
     </row>
     <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
@@ -24668,20 +24754,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="326" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="277"/>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
+      <c r="K1" s="326"/>
+      <c r="L1" s="326"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24711,26 +24797,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="327" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="278" t="s">
+      <c r="B3" s="327"/>
+      <c r="C3" s="328" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="327" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="278" t="s">
+      <c r="H3" s="327"/>
+      <c r="I3" s="328" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="278"/>
-      <c r="K3" s="278"/>
-      <c r="L3" s="278"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24757,28 +24843,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="327"/>
+      <c r="C5" s="329" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="329"/>
+      <c r="E5" s="329"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="327" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="327"/>
+      <c r="I5" s="330">
         <v>20000</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="330"/>
+      <c r="K5" s="329" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="329"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24811,105 +24897,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="279" t="s">
+      <c r="A9" s="320" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="279"/>
-      <c r="C9" s="279"/>
+      <c r="B9" s="320"/>
+      <c r="C9" s="320"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="320" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
-      <c r="N10" s="280"/>
-      <c r="O10" s="280"/>
-      <c r="P10" s="280"/>
-      <c r="Q10" s="280"/>
+      <c r="B10" s="320"/>
+      <c r="C10" s="320"/>
+      <c r="N10" s="321"/>
+      <c r="O10" s="321"/>
+      <c r="P10" s="321"/>
+      <c r="Q10" s="321"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="284"/>
-      <c r="B12" s="284"/>
-      <c r="C12" s="284"/>
-      <c r="E12" s="338" t="s">
+      <c r="A12" s="325"/>
+      <c r="B12" s="325"/>
+      <c r="C12" s="325"/>
+      <c r="E12" s="335" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="339"/>
-      <c r="G12" s="340"/>
-      <c r="I12" s="284"/>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
-      <c r="O12" s="284"/>
+      <c r="F12" s="336"/>
+      <c r="G12" s="337"/>
+      <c r="I12" s="325"/>
+      <c r="J12" s="325"/>
+      <c r="K12" s="325"/>
+      <c r="M12" s="325"/>
+      <c r="N12" s="325"/>
+      <c r="O12" s="325"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="287"/>
-      <c r="B13" s="287"/>
+      <c r="A13" s="313"/>
+      <c r="B13" s="313"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="341" t="s">
+      <c r="E13" s="338" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="342"/>
+      <c r="F13" s="339"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="287"/>
-      <c r="J13" s="287"/>
+      <c r="I13" s="313"/>
+      <c r="J13" s="313"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="287"/>
-      <c r="N13" s="287"/>
+      <c r="M13" s="313"/>
+      <c r="N13" s="313"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="287"/>
-      <c r="B14" s="287"/>
+      <c r="A14" s="313"/>
+      <c r="B14" s="313"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="288" t="s">
+      <c r="E14" s="316" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="289"/>
+      <c r="F14" s="317"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="287"/>
-      <c r="J14" s="287"/>
+      <c r="I14" s="313"/>
+      <c r="J14" s="313"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="287"/>
-      <c r="N14" s="287"/>
+      <c r="M14" s="313"/>
+      <c r="N14" s="313"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="287"/>
-      <c r="B15" s="287"/>
+      <c r="A15" s="313"/>
+      <c r="B15" s="313"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="336" t="s">
+      <c r="E15" s="333" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="337"/>
+      <c r="F15" s="334"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="287"/>
-      <c r="N15" s="287"/>
+      <c r="M15" s="313"/>
+      <c r="N15" s="313"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="287"/>
-      <c r="B16" s="287"/>
+      <c r="A16" s="313"/>
+      <c r="B16" s="313"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -24918,74 +25004,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="287"/>
-      <c r="J16" s="287"/>
+      <c r="I16" s="313"/>
+      <c r="J16" s="313"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="287"/>
-      <c r="N16" s="287"/>
+      <c r="M16" s="313"/>
+      <c r="N16" s="313"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
+      <c r="A17" s="313"/>
+      <c r="B17" s="313"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="290" t="s">
+      <c r="E17" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="291"/>
+      <c r="F17" s="312"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="287"/>
-      <c r="N17" s="287"/>
+      <c r="M17" s="313"/>
+      <c r="N17" s="313"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="287"/>
-      <c r="N18" s="287"/>
+      <c r="M18" s="313"/>
+      <c r="N18" s="313"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="343"/>
-      <c r="N19" s="343"/>
+      <c r="M19" s="332"/>
+      <c r="N19" s="332"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="343"/>
-      <c r="N20" s="343"/>
+      <c r="M20" s="332"/>
+      <c r="N20" s="332"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="292" t="s">
+      <c r="C21" s="314" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="292" t="s">
+      <c r="E21" s="314" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="292"/>
-      <c r="G21" s="292" t="s">
+      <c r="F21" s="314"/>
+      <c r="G21" s="314" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="292" t="s">
+      <c r="H21" s="314" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="292"/>
+      <c r="C22" s="314"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="292"/>
-      <c r="G22" s="292"/>
-      <c r="H22" s="292"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="314"/>
+      <c r="H22" s="314"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="293"/>
+      <c r="C23" s="315"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="293"/>
-      <c r="F23" s="293"/>
-      <c r="G23" s="293"/>
-      <c r="H23" s="293"/>
+      <c r="E23" s="315"/>
+      <c r="F23" s="315"/>
+      <c r="G23" s="315"/>
+      <c r="H23" s="315"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -25162,12 +25248,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="295" t="s">
+      <c r="A31" s="304" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="296"/>
-      <c r="C31" s="296"/>
-      <c r="D31" s="296"/>
+      <c r="B31" s="305"/>
+      <c r="C31" s="305"/>
+      <c r="D31" s="305"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -25230,19 +25316,19 @@
         <f>B37/B36</f>
         <v>0.91666666666666674</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="306" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="306"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5431.9647769676003</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="306" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="306"/>
+      <c r="H35" s="306"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -25256,19 +25342,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37.799999999999997</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="306" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="306"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.18409544999999999</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="306" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="306"/>
+      <c r="H36" s="306"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -25287,19 +25373,19 @@
         <f>SUM(F25:F30)</f>
         <v>34.65</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="306" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="306"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>28.860028860028862</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="306" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="306"/>
+      <c r="H37" s="306"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>108639.29553935201</v>
@@ -25313,37 +25399,37 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10634300000000001</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="306"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>28.574286000028575</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="306" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="306"/>
+      <c r="H38" s="306"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="297" t="s">
+      <c r="C39" s="306" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="306"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="297"/>
-      <c r="D40" s="297"/>
+      <c r="C40" s="306"/>
+      <c r="D40" s="306"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25393,11 +25479,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="299" t="s">
+      <c r="A44" s="308" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="300"/>
-      <c r="C44" s="301"/>
+      <c r="B44" s="309"/>
+      <c r="C44" s="310"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25427,11 +25513,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="294" t="s">
+      <c r="A46" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
+      <c r="B46" s="293"/>
+      <c r="C46" s="293"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25446,11 +25532,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="294" t="s">
+      <c r="A47" s="293" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
+      <c r="B47" s="293"/>
+      <c r="C47" s="293"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.8170490707388822</v>
@@ -25466,11 +25552,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="294" t="s">
+      <c r="A48" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
+      <c r="B48" s="293"/>
+      <c r="C48" s="293"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6836.3715691450298</v>
@@ -25486,11 +25572,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="293" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
+      <c r="B49" s="293"/>
+      <c r="C49" s="293"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25506,11 +25592,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="294" t="s">
+      <c r="A50" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="294"/>
-      <c r="C50" s="294"/>
+      <c r="B50" s="293"/>
+      <c r="C50" s="293"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>42461.93521208092</v>
@@ -25541,11 +25627,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="294" t="s">
+      <c r="A52" s="293" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="294"/>
-      <c r="C52" s="294"/>
+      <c r="B52" s="293"/>
+      <c r="C52" s="293"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25560,11 +25646,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="294" t="s">
+      <c r="A53" s="293" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="294"/>
-      <c r="C53" s="294"/>
+      <c r="B53" s="293"/>
+      <c r="C53" s="293"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1737.6438086744588</v>
@@ -25707,7 +25793,7 @@
         <f>F60*E60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="333">
+      <c r="H60" s="340">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>141966.47760014096</v>
       </c>
@@ -25741,7 +25827,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>12329.714400011429</v>
       </c>
-      <c r="H61" s="334"/>
+      <c r="H61" s="341"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -25771,7 +25857,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H62" s="334"/>
+      <c r="H62" s="341"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -25801,7 +25887,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H63" s="334"/>
+      <c r="H63" s="341"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -25831,7 +25917,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H64" s="334"/>
+      <c r="H64" s="341"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -25861,7 +25947,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H65" s="334"/>
+      <c r="H65" s="341"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -25892,7 +25978,7 @@
         <f t="shared" si="3"/>
         <v>977.47620000095242</v>
       </c>
-      <c r="H66" s="334"/>
+      <c r="H66" s="341"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -25923,7 +26009,7 @@
         <f t="shared" si="3"/>
         <v>57198.572000057153</v>
       </c>
-      <c r="H67" s="334"/>
+      <c r="H67" s="341"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -25955,7 +26041,7 @@
         <f t="shared" si="3"/>
         <v>71460.715000071446</v>
       </c>
-      <c r="H68" s="334"/>
+      <c r="H68" s="341"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -25985,7 +26071,7 @@
         <f>F69*E69</f>
         <v>0</v>
       </c>
-      <c r="H69" s="335"/>
+      <c r="H69" s="342"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -26045,23 +26131,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="307"/>
-      <c r="C73" s="308" t="s">
+      <c r="B73" s="297"/>
+      <c r="C73" s="298" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="310" t="s">
+      <c r="E73" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="312" t="s">
+      <c r="F73" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="312" t="s">
+      <c r="G73" s="302" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="302" t="s">
+      <c r="H73" s="291" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -26075,15 +26161,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="307"/>
-      <c r="C74" s="309"/>
+      <c r="B74" s="297"/>
+      <c r="C74" s="299"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="311"/>
-      <c r="F74" s="313"/>
-      <c r="G74" s="313"/>
-      <c r="H74" s="303"/>
+      <c r="E74" s="301"/>
+      <c r="F74" s="303"/>
+      <c r="G74" s="303"/>
+      <c r="H74" s="292"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -26322,9 +26408,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="318"/>
-      <c r="I82" s="318"/>
-      <c r="J82" s="318"/>
+      <c r="H82" s="285"/>
+      <c r="I82" s="285"/>
+      <c r="J82" s="285"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -26332,19 +26418,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="319" t="s">
+      <c r="B83" s="286" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="319"/>
-      <c r="D83" s="319"/>
-      <c r="E83" s="319"/>
-      <c r="F83" s="319"/>
-      <c r="G83" s="319"/>
-      <c r="H83" s="319"/>
-      <c r="I83" s="319"/>
-      <c r="J83" s="319"/>
-      <c r="K83" s="319"/>
-      <c r="L83" s="319"/>
+      <c r="C83" s="286"/>
+      <c r="D83" s="286"/>
+      <c r="E83" s="286"/>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="286"/>
+      <c r="I83" s="286"/>
+      <c r="J83" s="286"/>
+      <c r="K83" s="286"/>
+      <c r="L83" s="286"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26410,17 +26496,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="325" t="s">
+      <c r="H87" s="343" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="326"/>
+      <c r="I87" s="344"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="327" t="s">
+      <c r="K87" s="345" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="328"/>
+      <c r="L87" s="346"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26432,20 +26518,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="329">
+      <c r="H88" s="347">
         <f>C75+H70</f>
         <v>10.167385929069098</v>
       </c>
-      <c r="I88" s="330"/>
+      <c r="I88" s="348"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.98761894452246557</v>
       </c>
-      <c r="K88" s="331">
+      <c r="K88" s="349">
         <f>E106+E122</f>
         <v>20.20888888888889</v>
       </c>
-      <c r="L88" s="332"/>
+      <c r="L88" s="350"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26517,10 +26603,10 @@
         <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="321" t="s">
+      <c r="Q92" s="288" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="321"/>
+      <c r="R92" s="288"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.388104543787712</v>
@@ -26574,10 +26660,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="322" t="s">
+      <c r="T94" s="289" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="323"/>
+      <c r="U94" s="290"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26609,11 +26695,11 @@
         <f>R95/S92</f>
         <v>0.89280756863225985</v>
       </c>
-      <c r="T95" s="314">
+      <c r="T95" s="281">
         <f>R96-R95</f>
         <v>10.041502959819791</v>
       </c>
-      <c r="U95" s="316">
+      <c r="U95" s="283">
         <f>(R96-R95)/R95</f>
         <v>0.98761894452246557</v>
       </c>
@@ -26650,8 +26736,8 @@
         <f>R96/S92</f>
         <v>1.7745612372265211</v>
       </c>
-      <c r="T96" s="315"/>
-      <c r="U96" s="316"/>
+      <c r="T96" s="282"/>
+      <c r="U96" s="283"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -27113,11 +27199,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="317" t="s">
+      <c r="B122" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="317"/>
-      <c r="D122" s="317"/>
+      <c r="C122" s="284"/>
+      <c r="D122" s="284"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -27125,11 +27211,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="317" t="s">
+      <c r="B123" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="317"/>
-      <c r="D123" s="317"/>
+      <c r="C123" s="284"/>
+      <c r="D123" s="284"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.76989873089142391</v>
@@ -27159,29 +27245,47 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="A1:L1"/>
@@ -27198,47 +27302,29 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F37:H37"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -27310,20 +27396,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="277" t="s">
+      <c r="A1" s="326" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="277"/>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
+      <c r="K1" s="326"/>
+      <c r="L1" s="326"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27353,26 +27439,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274" t="s">
+      <c r="A3" s="327" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="274"/>
-      <c r="C3" s="278" t="s">
+      <c r="B3" s="327"/>
+      <c r="C3" s="328" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="274" t="s">
+      <c r="G3" s="327" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="274"/>
-      <c r="I3" s="278" t="s">
+      <c r="H3" s="327"/>
+      <c r="I3" s="328" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="278"/>
-      <c r="K3" s="278"/>
-      <c r="L3" s="278"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27399,28 +27485,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274" t="s">
+      <c r="A5" s="327" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="274"/>
-      <c r="C5" s="275" t="s">
+      <c r="B5" s="327"/>
+      <c r="C5" s="329" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
+      <c r="D5" s="329"/>
+      <c r="E5" s="329"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="274" t="s">
+      <c r="G5" s="327" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="274"/>
-      <c r="I5" s="276">
+      <c r="H5" s="327"/>
+      <c r="I5" s="330">
         <v>500</v>
       </c>
-      <c r="J5" s="276"/>
-      <c r="K5" s="275" t="s">
+      <c r="J5" s="330"/>
+      <c r="K5" s="329" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="275"/>
+      <c r="L5" s="329"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27453,86 +27539,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="279" t="s">
+      <c r="A9" s="320" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="279"/>
-      <c r="C9" s="279"/>
+      <c r="B9" s="320"/>
+      <c r="C9" s="320"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="320" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
-      <c r="N10" s="280"/>
-      <c r="O10" s="280"/>
-      <c r="P10" s="280"/>
-      <c r="Q10" s="280"/>
+      <c r="B10" s="320"/>
+      <c r="C10" s="320"/>
+      <c r="N10" s="321"/>
+      <c r="O10" s="321"/>
+      <c r="P10" s="321"/>
+      <c r="Q10" s="321"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="284"/>
-      <c r="B12" s="284"/>
-      <c r="C12" s="284"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="284"/>
-      <c r="G12" s="284"/>
-      <c r="I12" s="344" t="s">
+      <c r="A12" s="325"/>
+      <c r="B12" s="325"/>
+      <c r="C12" s="325"/>
+      <c r="E12" s="325"/>
+      <c r="F12" s="325"/>
+      <c r="G12" s="325"/>
+      <c r="I12" s="357" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="345"/>
-      <c r="K12" s="346"/>
-      <c r="M12" s="344" t="s">
+      <c r="J12" s="358"/>
+      <c r="K12" s="359"/>
+      <c r="M12" s="357" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="345"/>
-      <c r="O12" s="346"/>
+      <c r="N12" s="358"/>
+      <c r="O12" s="359"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="287"/>
-      <c r="B13" s="287"/>
+      <c r="A13" s="313"/>
+      <c r="B13" s="313"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="287"/>
-      <c r="F13" s="287"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="313"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="341" t="s">
+      <c r="I13" s="338" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="342"/>
+      <c r="J13" s="339"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="341" t="s">
+      <c r="M13" s="338" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="342"/>
+      <c r="N13" s="339"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="287"/>
-      <c r="B14" s="287"/>
+      <c r="A14" s="313"/>
+      <c r="B14" s="313"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="287"/>
-      <c r="F14" s="287"/>
+      <c r="E14" s="313"/>
+      <c r="F14" s="313"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="288" t="s">
+      <c r="I14" s="316" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="289"/>
+      <c r="J14" s="317"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="288" t="s">
+      <c r="M14" s="316" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="289"/>
+      <c r="N14" s="317"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27540,11 +27626,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="287"/>
-      <c r="B15" s="287"/>
+      <c r="A15" s="313"/>
+      <c r="B15" s="313"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="287"/>
-      <c r="F15" s="287"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="313"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27553,10 +27639,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="288" t="s">
+      <c r="M15" s="316" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="289"/>
+      <c r="N15" s="317"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27565,103 +27651,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287"/>
-      <c r="B16" s="287"/>
+      <c r="A16" s="313"/>
+      <c r="B16" s="313"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="290" t="s">
+      <c r="I16" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="291"/>
+      <c r="J16" s="312"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="288" t="s">
+      <c r="M16" s="316" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="289"/>
+      <c r="N16" s="317"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
+      <c r="A17" s="313"/>
+      <c r="B17" s="313"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="287"/>
-      <c r="F17" s="287"/>
+      <c r="E17" s="313"/>
+      <c r="F17" s="313"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="288" t="s">
+      <c r="M17" s="316" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="289"/>
+      <c r="N17" s="317"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="288" t="s">
+      <c r="M18" s="316" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="289"/>
+      <c r="N18" s="317"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="349" t="s">
+      <c r="M19" s="351" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="350"/>
+      <c r="N19" s="352"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="351"/>
-      <c r="N20" s="352"/>
+      <c r="M20" s="353"/>
+      <c r="N20" s="354"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="292" t="s">
+      <c r="C21" s="314" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="292" t="s">
+      <c r="E21" s="314" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="292"/>
-      <c r="G21" s="292" t="s">
+      <c r="F21" s="314"/>
+      <c r="G21" s="314" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="292" t="s">
+      <c r="H21" s="314" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="292"/>
+      <c r="C22" s="314"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="292"/>
-      <c r="G22" s="292"/>
-      <c r="H22" s="292"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="314"/>
+      <c r="H22" s="314"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="293"/>
+      <c r="C23" s="315"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="293"/>
-      <c r="F23" s="293"/>
-      <c r="G23" s="293"/>
-      <c r="H23" s="293"/>
+      <c r="E23" s="315"/>
+      <c r="F23" s="315"/>
+      <c r="G23" s="315"/>
+      <c r="H23" s="315"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -28044,12 +28130,12 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="347" t="s">
+      <c r="A33" s="355" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="348"/>
-      <c r="C33" s="348"/>
-      <c r="D33" s="348"/>
+      <c r="B33" s="356"/>
+      <c r="C33" s="356"/>
+      <c r="D33" s="356"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -28095,19 +28181,19 @@
         <f>B37/B36</f>
         <v>1.0597680097680098</v>
       </c>
-      <c r="C35" s="297" t="s">
+      <c r="C35" s="306" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="297"/>
+      <c r="D35" s="306"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.809590059054404</v>
       </c>
-      <c r="F35" s="297" t="s">
+      <c r="F35" s="306" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="297"/>
-      <c r="H35" s="297"/>
+      <c r="G35" s="306"/>
+      <c r="H35" s="306"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -28121,19 +28207,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163.80000000000001</v>
       </c>
-      <c r="C36" s="297" t="s">
+      <c r="C36" s="306" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="297"/>
+      <c r="D36" s="306"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.745288000000002</v>
       </c>
-      <c r="F36" s="297" t="s">
+      <c r="F36" s="306" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="297"/>
-      <c r="H36" s="297"/>
+      <c r="G36" s="306"/>
+      <c r="H36" s="306"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -28152,19 +28238,19 @@
         <f>SUM(F25:F32)</f>
         <v>173.59</v>
       </c>
-      <c r="C37" s="297" t="s">
+      <c r="C37" s="306" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="297"/>
+      <c r="D37" s="306"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7607005011809438</v>
       </c>
-      <c r="F37" s="297" t="s">
+      <c r="F37" s="306" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="297"/>
-      <c r="H37" s="297"/>
+      <c r="G37" s="306"/>
+      <c r="H37" s="306"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>500</v>
@@ -28178,29 +28264,29 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.38158350000000002</v>
       </c>
-      <c r="C38" s="297" t="s">
+      <c r="C38" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="297"/>
+      <c r="D38" s="306"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.063895264400994</v>
       </c>
-      <c r="F38" s="297" t="s">
+      <c r="F38" s="306" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="297"/>
-      <c r="H38" s="297"/>
+      <c r="G38" s="306"/>
+      <c r="H38" s="306"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="297" t="s">
+      <c r="C39" s="306" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="297"/>
+      <c r="D39" s="306"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0009729183068661</v>
@@ -28254,11 +28340,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="299" t="s">
+      <c r="A44" s="308" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="300"/>
-      <c r="C44" s="301"/>
+      <c r="B44" s="309"/>
+      <c r="C44" s="310"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -28288,11 +28374,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="294" t="s">
+      <c r="A46" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
+      <c r="B46" s="293"/>
+      <c r="C46" s="293"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -28307,11 +28393,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="294" t="s">
+      <c r="A47" s="293" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
+      <c r="B47" s="293"/>
+      <c r="C47" s="293"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.372179596826548</v>
@@ -28327,11 +28413,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="294" t="s">
+      <c r="A48" s="293" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
+      <c r="B48" s="293"/>
+      <c r="C48" s="293"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>283.01185101569587</v>
@@ -28347,11 +28433,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="293" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
+      <c r="B49" s="293"/>
+      <c r="C49" s="293"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28367,11 +28453,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="294" t="s">
+      <c r="A50" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="294"/>
-      <c r="C50" s="294"/>
+      <c r="B50" s="293"/>
+      <c r="C50" s="293"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>912.94145488934146</v>
@@ -28402,11 +28488,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="294" t="s">
+      <c r="A52" s="293" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="294"/>
-      <c r="C52" s="294"/>
+      <c r="B52" s="293"/>
+      <c r="C52" s="293"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28421,11 +28507,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="294" t="s">
+      <c r="A53" s="293" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="294"/>
-      <c r="C53" s="294"/>
+      <c r="B53" s="293"/>
+      <c r="C53" s="293"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.25705038862782</v>
@@ -28571,7 +28657,7 @@
         <f>F60*E60</f>
         <v>6892.3268571428589</v>
       </c>
-      <c r="H60" s="333">
+      <c r="H60" s="340">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>17057.940892230581</v>
       </c>
@@ -28605,7 +28691,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>3249.4736842105267</v>
       </c>
-      <c r="H61" s="334"/>
+      <c r="H61" s="341"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -28636,7 +28722,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H62" s="334"/>
+      <c r="H62" s="341"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -28667,7 +28753,7 @@
         <f t="shared" si="3"/>
         <v>1078.9473684210527</v>
       </c>
-      <c r="H63" s="334"/>
+      <c r="H63" s="341"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -28698,7 +28784,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H64" s="334"/>
+      <c r="H64" s="341"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -28729,7 +28815,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H65" s="334"/>
+      <c r="H65" s="341"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -28760,7 +28846,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H66" s="334"/>
+      <c r="H66" s="341"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -28790,7 +28876,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H67" s="334"/>
+      <c r="H67" s="341"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -28821,7 +28907,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="334"/>
+      <c r="H68" s="341"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -28852,7 +28938,7 @@
         <f>F69*E69</f>
         <v>4216.6666666666661</v>
       </c>
-      <c r="H69" s="335"/>
+      <c r="H69" s="342"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -28912,23 +28998,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="307"/>
-      <c r="C73" s="308" t="s">
+      <c r="B73" s="297"/>
+      <c r="C73" s="298" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="310" t="s">
+      <c r="E73" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="312" t="s">
+      <c r="F73" s="302" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="312" t="s">
+      <c r="G73" s="302" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="302" t="s">
+      <c r="H73" s="291" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -28942,15 +29028,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="307"/>
-      <c r="C74" s="309"/>
+      <c r="B74" s="297"/>
+      <c r="C74" s="299"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="311"/>
-      <c r="F74" s="313"/>
-      <c r="G74" s="313"/>
-      <c r="H74" s="303"/>
+      <c r="E74" s="301"/>
+      <c r="F74" s="303"/>
+      <c r="G74" s="303"/>
+      <c r="H74" s="292"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -29189,9 +29275,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="318"/>
-      <c r="I82" s="318"/>
-      <c r="J82" s="318"/>
+      <c r="H82" s="285"/>
+      <c r="I82" s="285"/>
+      <c r="J82" s="285"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -29199,19 +29285,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="319" t="s">
+      <c r="B83" s="286" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="319"/>
-      <c r="D83" s="319"/>
-      <c r="E83" s="319"/>
-      <c r="F83" s="319"/>
-      <c r="G83" s="319"/>
-      <c r="H83" s="319"/>
-      <c r="I83" s="319"/>
-      <c r="J83" s="319"/>
-      <c r="K83" s="319"/>
-      <c r="L83" s="319"/>
+      <c r="C83" s="286"/>
+      <c r="D83" s="286"/>
+      <c r="E83" s="286"/>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="286"/>
+      <c r="I83" s="286"/>
+      <c r="J83" s="286"/>
+      <c r="K83" s="286"/>
+      <c r="L83" s="286"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -29277,17 +29363,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="325" t="s">
+      <c r="H87" s="343" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="326"/>
+      <c r="I87" s="344"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="327" t="s">
+      <c r="K87" s="345" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="328"/>
+      <c r="L87" s="346"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -29299,20 +29385,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="329">
+      <c r="H88" s="347">
         <f>C75+H70</f>
         <v>3.0787051830524823</v>
       </c>
-      <c r="I88" s="330"/>
+      <c r="I88" s="348"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>6.0858781331305026E-2</v>
       </c>
-      <c r="K88" s="331">
+      <c r="K88" s="349">
         <f>E106+E122</f>
         <v>3.2660714285714287</v>
       </c>
-      <c r="L88" s="332"/>
+      <c r="L88" s="350"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29383,10 +29469,10 @@
         <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="321" t="s">
+      <c r="Q92" s="288" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="321"/>
+      <c r="R92" s="288"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0381616609601965</v>
@@ -29444,10 +29530,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="322" t="s">
+      <c r="T94" s="289" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="323"/>
+      <c r="U94" s="290"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29481,11 +29567,11 @@
         <f>R95/S92</f>
         <v>0.76240265782733074</v>
       </c>
-      <c r="T95" s="314">
+      <c r="T95" s="281">
         <f>R96-R95</f>
         <v>0.18736624551894643</v>
       </c>
-      <c r="U95" s="316">
+      <c r="U95" s="283">
         <f>(R96-R95)/R95</f>
         <v>6.0858781331305026E-2</v>
       </c>
@@ -29524,8 +29610,8 @@
         <f>R96/S92</f>
         <v>0.80880155446645008</v>
       </c>
-      <c r="T96" s="315"/>
-      <c r="U96" s="316"/>
+      <c r="T96" s="282"/>
+      <c r="U96" s="283"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -29999,11 +30085,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="317" t="s">
+      <c r="B122" s="284" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="317"/>
-      <c r="D122" s="317"/>
+      <c r="C122" s="284"/>
+      <c r="D122" s="284"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -30011,11 +30097,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="317" t="s">
+      <c r="B123" s="284" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="317"/>
-      <c r="D123" s="317"/>
+      <c r="C123" s="284"/>
+      <c r="D123" s="284"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>0.10324804175431759</v>
@@ -30045,6 +30131,72 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -30058,72 +30210,6 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -30174,17 +30260,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G1" s="353" t="s">
+      <c r="G1" s="360" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="353"/>
-      <c r="I1" s="353"/>
-      <c r="J1" s="353"/>
-      <c r="K1" s="353" t="s">
+      <c r="H1" s="360"/>
+      <c r="I1" s="360"/>
+      <c r="J1" s="360"/>
+      <c r="K1" s="360" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="353"/>
-      <c r="M1" s="353"/>
+      <c r="L1" s="360"/>
+      <c r="M1" s="360"/>
       <c r="N1" s="172"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
@@ -30286,7 +30372,7 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="354" t="s">
+      <c r="Q7" s="361" t="s">
         <v>218</v>
       </c>
     </row>
@@ -30300,7 +30386,7 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="354"/>
+      <c r="Q8" s="361"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
@@ -30312,7 +30398,7 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="354"/>
+      <c r="Q9" s="361"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
@@ -30324,7 +30410,7 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="354"/>
+      <c r="Q10" s="361"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
@@ -30336,7 +30422,7 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="354"/>
+      <c r="Q11" s="361"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
@@ -30348,7 +30434,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="354"/>
+      <c r="Q12" s="361"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895582E6-7D68-4AB7-AC12-A112B6DBD80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B648D80-0CA4-4A2B-AE36-331E727C597F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="21870" windowHeight="13050" tabRatio="685" firstSheet="1" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="PE Bag" sheetId="11" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4291752228" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="353">
   <si>
     <t>Roll</t>
   </si>

--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,97 +8,99 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B648D80-0CA4-4A2B-AE36-331E727C597F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53D7500-E22D-45EC-8D67-A71876518AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="21870" windowHeight="13050" tabRatio="685" firstSheet="1" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="685" firstSheet="1" activeTab="10" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
   <sheets>
     <sheet name="PE Bag" sheetId="11" r:id="rId1"/>
     <sheet name="Substrate Costing Master" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId3"/>
     <sheet name="Roll" sheetId="4" r:id="rId4"/>
-    <sheet name="Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Sleeve" sheetId="3" r:id="rId6"/>
-    <sheet name="Pouch" sheetId="5" r:id="rId7"/>
-    <sheet name="Overall" sheetId="6" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId9"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet4" sheetId="12" r:id="rId11"/>
+    <sheet name="Sheet5" sheetId="13" r:id="rId5"/>
+    <sheet name="Data" sheetId="2" r:id="rId6"/>
+    <sheet name="Sleeve" sheetId="3" r:id="rId7"/>
+    <sheet name="Pouch" sheetId="5" r:id="rId8"/>
+    <sheet name="Overall" sheetId="6" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="14" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId12"/>
+    <sheet name="Sheet4" sheetId="12" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Substrate Costing Master'!$A$1:$F$46</definedName>
     <definedName name="Adhesive" localSheetId="0">A[Adhesive]</definedName>
+    <definedName name="Adhesive" localSheetId="7">A[Adhesive]</definedName>
+    <definedName name="Adhesive" localSheetId="3">A[Adhesive]</definedName>
     <definedName name="Adhesive" localSheetId="6">A[Adhesive]</definedName>
-    <definedName name="Adhesive" localSheetId="3">A[Adhesive]</definedName>
-    <definedName name="Adhesive" localSheetId="5">A[Adhesive]</definedName>
     <definedName name="Adhesive">A[Adhesive]</definedName>
     <definedName name="CO_Pouch" localSheetId="0">'PE Bag'!$K$14</definedName>
-    <definedName name="CO_Pouch" localSheetId="6">Pouch!$K$14</definedName>
+    <definedName name="CO_Pouch" localSheetId="7">Pouch!$K$14</definedName>
     <definedName name="CO_Pouch" localSheetId="3">Roll!$K$14</definedName>
     <definedName name="CO_Pouch">Sleeve!$K$14</definedName>
     <definedName name="CO_Roll" localSheetId="0">'PE Bag'!$C$14</definedName>
-    <definedName name="CO_Roll" localSheetId="6">Pouch!$C$14</definedName>
+    <definedName name="CO_Roll" localSheetId="7">Pouch!$C$14</definedName>
     <definedName name="CO_Roll" localSheetId="3">Roll!$C$14</definedName>
     <definedName name="CO_Roll">Sleeve!$C$14</definedName>
     <definedName name="CO_Sleeve" localSheetId="0">'PE Bag'!$G$15</definedName>
-    <definedName name="CO_Sleeve" localSheetId="6">Pouch!$G$15</definedName>
+    <definedName name="CO_Sleeve" localSheetId="7">Pouch!$G$15</definedName>
     <definedName name="CO_Sleeve" localSheetId="3">Roll!$G$15</definedName>
     <definedName name="CO_Sleeve">Sleeve!$G$15</definedName>
     <definedName name="FLW" localSheetId="0">'PE Bag'!$I$35</definedName>
-    <definedName name="FLW" localSheetId="6">Pouch!$I$35</definedName>
+    <definedName name="FLW" localSheetId="7">Pouch!$I$35</definedName>
     <definedName name="FLW" localSheetId="3">Roll!$I$35</definedName>
     <definedName name="FLW">Sleeve!$I$35</definedName>
     <definedName name="Forms">Overall!$G$2:$M$2</definedName>
     <definedName name="Ink" localSheetId="0">Table4[Ink]</definedName>
+    <definedName name="Ink" localSheetId="7">Table4[Ink]</definedName>
+    <definedName name="Ink" localSheetId="3">Table4[Ink]</definedName>
     <definedName name="Ink" localSheetId="6">Table4[Ink]</definedName>
-    <definedName name="Ink" localSheetId="3">Table4[Ink]</definedName>
-    <definedName name="Ink" localSheetId="5">Table4[Ink]</definedName>
     <definedName name="Ink">Table4[Ink]</definedName>
     <definedName name="Nb_Ups_Sleeve" localSheetId="0">'PE Bag'!$G$17</definedName>
-    <definedName name="Nb_Ups_Sleeve" localSheetId="6">Pouch!$G$17</definedName>
+    <definedName name="Nb_Ups_Sleeve" localSheetId="7">Pouch!$G$17</definedName>
     <definedName name="Nb_Ups_Sleeve" localSheetId="3">Roll!$G$17</definedName>
     <definedName name="Nb_Ups_Sleeve">Sleeve!$G$17</definedName>
     <definedName name="OQKG" localSheetId="0">'PE Bag'!$I$36</definedName>
-    <definedName name="OQKG" localSheetId="6">Pouch!$I$36</definedName>
+    <definedName name="OQKG" localSheetId="7">Pouch!$I$36</definedName>
     <definedName name="OQKG" localSheetId="3">Roll!$I$36</definedName>
     <definedName name="OQKG">Sleeve!$I$36</definedName>
     <definedName name="OQM" localSheetId="0">'PE Bag'!$I$38</definedName>
-    <definedName name="OQM" localSheetId="6">Pouch!$I$38</definedName>
+    <definedName name="OQM" localSheetId="7">Pouch!$I$38</definedName>
     <definedName name="OQM" localSheetId="3">Roll!$I$38</definedName>
     <definedName name="OQM">Sleeve!$I$38</definedName>
     <definedName name="Packaging" localSheetId="0">A[Packaging]</definedName>
     <definedName name="Packaging">A[Packaging]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PE Bag'!$A$1:$L$79</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Pouch!$A$1:$O$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Pouch!$A$1:$O$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Roll!$A$1:$L$79</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">Sleeve!$A$1:$L$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Sleeve!$A$1:$L$78</definedName>
     <definedName name="Ptypes" localSheetId="0">PTypeT[Product Type]</definedName>
+    <definedName name="Ptypes" localSheetId="7">PTypeT[Product Type]</definedName>
+    <definedName name="Ptypes" localSheetId="3">PTypeT[Product Type]</definedName>
     <definedName name="Ptypes" localSheetId="6">PTypeT[Product Type]</definedName>
-    <definedName name="Ptypes" localSheetId="3">PTypeT[Product Type]</definedName>
-    <definedName name="Ptypes" localSheetId="5">PTypeT[Product Type]</definedName>
     <definedName name="Ptypes">PTypeT[Product Type]</definedName>
     <definedName name="Substrate" localSheetId="0">Table3[Substrate]</definedName>
+    <definedName name="Substrate" localSheetId="7">Table3[Substrate]</definedName>
+    <definedName name="Substrate" localSheetId="3">Table3[Substrate]</definedName>
     <definedName name="Substrate" localSheetId="6">Table3[Substrate]</definedName>
-    <definedName name="Substrate" localSheetId="3">Table3[Substrate]</definedName>
-    <definedName name="Substrate" localSheetId="5">Table3[Substrate]</definedName>
     <definedName name="Substrate">Table3[Substrate]</definedName>
     <definedName name="Substrates" localSheetId="0">Table3[Substrate]</definedName>
+    <definedName name="Substrates" localSheetId="7">Table3[Substrate]</definedName>
+    <definedName name="Substrates" localSheetId="3">Table3[Substrate]</definedName>
     <definedName name="Substrates" localSheetId="6">Table3[Substrate]</definedName>
-    <definedName name="Substrates" localSheetId="3">Table3[Substrate]</definedName>
-    <definedName name="Substrates" localSheetId="5">Table3[Substrate]</definedName>
     <definedName name="Substrates">Table3[Substrate]</definedName>
     <definedName name="Type" localSheetId="0">T[Material Type]</definedName>
+    <definedName name="Type" localSheetId="7">T[Material Type]</definedName>
+    <definedName name="Type" localSheetId="3">T[Material Type]</definedName>
     <definedName name="Type" localSheetId="6">T[Material Type]</definedName>
-    <definedName name="Type" localSheetId="3">T[Material Type]</definedName>
-    <definedName name="Type" localSheetId="5">T[Material Type]</definedName>
     <definedName name="Type">T[Material Type]</definedName>
     <definedName name="Unit" localSheetId="0">UT[Units]</definedName>
+    <definedName name="Unit" localSheetId="7">UT[Units]</definedName>
+    <definedName name="Unit" localSheetId="3">UT[Units]</definedName>
     <definedName name="Unit" localSheetId="6">UT[Units]</definedName>
-    <definedName name="Unit" localSheetId="3">UT[Units]</definedName>
-    <definedName name="Unit" localSheetId="5">UT[Units]</definedName>
     <definedName name="Unit">UT[Units]</definedName>
     <definedName name="UnitsDD" localSheetId="0">'PE Bag'!$K$5</definedName>
-    <definedName name="UnitsDD" localSheetId="6">Pouch!$K$5</definedName>
+    <definedName name="UnitsDD" localSheetId="7">Pouch!$K$5</definedName>
     <definedName name="UnitsDD" localSheetId="3">Roll!$K$5</definedName>
     <definedName name="UnitsDD">Sleeve!$K$5</definedName>
   </definedNames>
@@ -123,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="368">
   <si>
     <t>Roll</t>
   </si>
@@ -1197,6 +1199,193 @@
   </si>
   <si>
     <t>sum of cost of the families Ink &amp; Coating, Adhesive,Solvent per kg and per m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactering &amp; Operating </t>
+  </si>
+  <si>
+    <t>Markup over RM or per kg cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation </t>
+  </si>
+  <si>
+    <t>As already defined</t>
+  </si>
+  <si>
+    <r>
+      <t>Substrates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 1.69/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.1143/m²</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ink, Solvent, Adhesive &amp; Coating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.73/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.0497/m²</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Waste</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.27/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.0180/m²</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total RM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 2.68/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.1820/m²</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Manufacturing &amp; Operating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 1.20/kg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PrePress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.30/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.0203/m²</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Transportation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.50/kg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Selling price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0C0A09"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 4.68/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF78716C"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>USD 0.3176/m²</t>
+    </r>
+  </si>
+  <si>
+    <t>Currency / kg</t>
+  </si>
+  <si>
+    <t>Currency / m²</t>
+  </si>
+  <si>
+    <t>Currency / LM</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1418,7 @@
     <numFmt numFmtId="185" formatCode="\$0.00"/>
     <numFmt numFmtId="186" formatCode="#,##0\ &quot;Pcs&quot;"/>
   </numFmts>
-  <fonts count="57" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1602,12 +1791,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FF78716C"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color rgb="FF0C0A09"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -1617,6 +1800,42 @@
       <color rgb="FF0C0A09"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF78716C"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF78716C"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0C0A09"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2811,7 +3030,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3466,44 +3685,107 @@
     <xf numFmtId="186" fontId="51" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="63" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3535,122 +3817,38 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3676,6 +3874,54 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3687,21 +3933,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3715,24 +3946,24 @@
     <xf numFmtId="0" fontId="49" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -16793,6 +17024,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1958340</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>250288</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>164598</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F387C65-B803-B29C-F82F-4C251C953A71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5006340" y="3078480"/>
+          <a:ext cx="5249008" cy="5506218"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
 <FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
   <bag type="Checkbox"/>
@@ -17401,20 +17681,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
-      <c r="K1" s="326"/>
-      <c r="L1" s="326"/>
+      <c r="B1" s="288"/>
+      <c r="C1" s="288"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -17442,26 +17722,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="327" t="s">
+      <c r="A3" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="327"/>
-      <c r="C3" s="328" t="s">
+      <c r="B3" s="285"/>
+      <c r="C3" s="289" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="328"/>
-      <c r="E3" s="328"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="327" t="s">
+      <c r="G3" s="285" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="327"/>
-      <c r="I3" s="328" t="s">
+      <c r="H3" s="285"/>
+      <c r="I3" s="289" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="328"/>
-      <c r="K3" s="328"/>
-      <c r="L3" s="328"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -17486,28 +17766,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="327" t="s">
+      <c r="A5" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="327"/>
-      <c r="C5" s="329" t="s">
+      <c r="B5" s="285"/>
+      <c r="C5" s="286" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="329"/>
-      <c r="E5" s="329"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="327" t="s">
+      <c r="G5" s="285" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="327"/>
-      <c r="I5" s="330">
+      <c r="H5" s="285"/>
+      <c r="I5" s="287">
         <v>10000</v>
       </c>
-      <c r="J5" s="330"/>
-      <c r="K5" s="329" t="s">
+      <c r="J5" s="287"/>
+      <c r="K5" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="329"/>
+      <c r="L5" s="286"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -17538,132 +17818,132 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="320" t="s">
+      <c r="A9" s="290" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="320"/>
-      <c r="C9" s="320"/>
+      <c r="B9" s="290"/>
+      <c r="C9" s="290"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="320" t="s">
+      <c r="A10" s="290" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="320"/>
-      <c r="C10" s="320"/>
+      <c r="B10" s="290"/>
+      <c r="C10" s="290"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="321"/>
-      <c r="P10" s="321"/>
+      <c r="O10" s="291"/>
+      <c r="P10" s="291"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="322" t="s">
+      <c r="A12" s="292" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="323"/>
-      <c r="C12" s="324"/>
+      <c r="B12" s="293"/>
+      <c r="C12" s="294"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="325"/>
-      <c r="J12" s="325"/>
-      <c r="K12" s="325"/>
-      <c r="M12" s="325"/>
-      <c r="N12" s="325"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="295"/>
+      <c r="K12" s="295"/>
+      <c r="M12" s="295"/>
+      <c r="N12" s="295"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="318" t="s">
+      <c r="A13" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="319"/>
+      <c r="B13" s="297"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="313"/>
-      <c r="F13" s="313"/>
+      <c r="E13" s="298"/>
+      <c r="F13" s="298"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="313"/>
-      <c r="J13" s="313"/>
+      <c r="I13" s="298"/>
+      <c r="J13" s="298"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="316" t="s">
+      <c r="A14" s="299" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="317"/>
+      <c r="B14" s="300"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="313"/>
-      <c r="F14" s="313"/>
+      <c r="E14" s="298"/>
+      <c r="F14" s="298"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="313"/>
-      <c r="J14" s="313"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="298"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="313"/>
-      <c r="N14" s="313"/>
+      <c r="M14" s="298"/>
+      <c r="N14" s="298"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="316" t="s">
+      <c r="A15" s="299" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="317"/>
+      <c r="B15" s="300"/>
       <c r="C15" s="31">
         <v>0</v>
       </c>
-      <c r="E15" s="313"/>
-      <c r="F15" s="313"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="298"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="313"/>
-      <c r="N15" s="313"/>
+      <c r="M15" s="298"/>
+      <c r="N15" s="298"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="316" t="s">
+      <c r="A16" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="317"/>
+      <c r="B16" s="300"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="313"/>
-      <c r="J16" s="313"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="298"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="313"/>
-      <c r="N16" s="313"/>
+      <c r="M16" s="298"/>
+      <c r="N16" s="298"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="311" t="s">
+      <c r="A17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="312"/>
+      <c r="B17" s="302"/>
       <c r="C17" s="32">
         <v>0</v>
       </c>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
+      <c r="E17" s="298"/>
+      <c r="F17" s="298"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="313"/>
-      <c r="N17" s="313"/>
+      <c r="M17" s="298"/>
+      <c r="N17" s="298"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L18">
         <f>1000/L19</f>
         <v>12.787723785166239</v>
       </c>
-      <c r="M18" s="313"/>
-      <c r="N18" s="313"/>
+      <c r="M18" s="298"/>
+      <c r="N18" s="298"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L19">
@@ -17682,28 +17962,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="314"/>
+      <c r="C21" s="303"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="314"/>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314"/>
-      <c r="H21" s="314"/>
+      <c r="E21" s="303"/>
+      <c r="F21" s="303"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="303"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="314"/>
+      <c r="C22" s="303"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="314"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="303"/>
+      <c r="G22" s="303"/>
+      <c r="H22" s="303"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="315"/>
+      <c r="C23" s="304"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="315"/>
-      <c r="F23" s="315"/>
-      <c r="G23" s="315"/>
-      <c r="H23" s="315"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="304"/>
+      <c r="H23" s="304"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -17888,12 +18168,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="304" t="s">
+      <c r="A31" s="306" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="305"/>
-      <c r="C31" s="305"/>
-      <c r="D31" s="305"/>
+      <c r="B31" s="307"/>
+      <c r="C31" s="307"/>
+      <c r="D31" s="307"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -17957,19 +18237,19 @@
         <f>B37/B36</f>
         <v>0.92306952591595348</v>
       </c>
-      <c r="C35" s="306" t="s">
+      <c r="C35" s="308" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="306"/>
+      <c r="D35" s="308"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>833.42014793207625</v>
       </c>
-      <c r="F35" s="306" t="s">
+      <c r="F35" s="308" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="306"/>
-      <c r="H35" s="306"/>
+      <c r="G35" s="308"/>
+      <c r="H35" s="308"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>0</v>
@@ -17983,19 +18263,19 @@
         <f>SUMIFS(table1713[Micron],table1713[Type],"substrate")+SUMIFS(table1713[Total GSM],table1713[Type],"Ink")+SUMIFS(table1713[Total GSM],table1713[Type],"Adhesive")</f>
         <v>51.994999999999997</v>
       </c>
-      <c r="C36" s="306" t="s">
+      <c r="C36" s="308" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="306"/>
+      <c r="D36" s="308"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>1.199875</v>
       </c>
-      <c r="F36" s="306" t="s">
+      <c r="F36" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="306"/>
-      <c r="H36" s="306"/>
+      <c r="G36" s="308"/>
+      <c r="H36" s="308"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -18020,19 +18300,19 @@
         <f>SUM(F25:F30)</f>
         <v>47.994999999999997</v>
       </c>
-      <c r="C37" s="307" t="s">
+      <c r="C37" s="309" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="307"/>
+      <c r="D37" s="309"/>
       <c r="E37" s="274">
         <f>1000/B37</f>
         <v>20.835503698301906</v>
       </c>
-      <c r="F37" s="306" t="s">
+      <c r="F37" s="308" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="306"/>
-      <c r="H37" s="306"/>
+      <c r="G37" s="308"/>
+      <c r="H37" s="308"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>8334.2014793207618</v>
@@ -18046,29 +18326,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10741250000000001</v>
       </c>
-      <c r="C38" s="306" t="s">
+      <c r="C38" s="308" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="306"/>
+      <c r="D38" s="308"/>
       <c r="E38" s="15" t="e">
         <f>(E37/I35)*1000</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="306" t="s">
+      <c r="F38" s="308" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="306"/>
-      <c r="H38" s="306"/>
+      <c r="G38" s="308"/>
+      <c r="H38" s="308"/>
       <c r="I38" s="38" t="e">
         <f>I36*E38</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="306" t="s">
+      <c r="C39" s="308" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="306"/>
+      <c r="D39" s="308"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>83.342014793207625</v>
@@ -18125,11 +18405,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="308" t="s">
+      <c r="A44" s="310" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="309"/>
-      <c r="C44" s="310"/>
+      <c r="B44" s="311"/>
+      <c r="C44" s="312"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -18159,11 +18439,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="293" t="s">
+      <c r="A46" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="293"/>
-      <c r="C46" s="293"/>
+      <c r="B46" s="305"/>
+      <c r="C46" s="305"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -18178,11 +18458,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="293" t="s">
+      <c r="A47" s="305" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="293"/>
-      <c r="C47" s="293"/>
+      <c r="B47" s="305"/>
+      <c r="C47" s="305"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>59.633717188336227</v>
@@ -18198,11 +18478,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="293" t="s">
+      <c r="A48" s="305" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="293"/>
-      <c r="C48" s="293"/>
+      <c r="B48" s="305"/>
+      <c r="C48" s="305"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>4969.9941400842772</v>
@@ -18218,11 +18498,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="293" t="s">
+      <c r="A49" s="305" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="293"/>
-      <c r="C49" s="293"/>
+      <c r="B49" s="305"/>
+      <c r="C49" s="305"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -18238,11 +18518,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="293" t="s">
+      <c r="A50" s="305" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="293"/>
-      <c r="C50" s="293"/>
+      <c r="B50" s="305"/>
+      <c r="C50" s="305"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>49699.941400842778</v>
@@ -18273,11 +18553,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="293" t="s">
+      <c r="A52" s="305" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="293"/>
-      <c r="C52" s="293"/>
+      <c r="B52" s="305"/>
+      <c r="C52" s="305"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -18292,11 +18572,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="293" t="s">
+      <c r="A53" s="305" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="293"/>
-      <c r="C53" s="293"/>
+      <c r="B53" s="305"/>
+      <c r="C53" s="305"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>662.77051272480605</v>
@@ -18442,7 +18722,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4407.5707290938053</v>
       </c>
-      <c r="H60" s="294">
+      <c r="H60" s="315">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>4407.5707290938053</v>
       </c>
@@ -18476,7 +18756,7 @@
         <f t="shared" ref="G61:G69" si="1">IFERROR(F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="295"/>
+      <c r="H61" s="316"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -18507,7 +18787,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H62" s="295"/>
+      <c r="H62" s="316"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -18538,7 +18818,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H63" s="295"/>
+      <c r="H63" s="316"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -18569,7 +18849,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H64" s="295"/>
+      <c r="H64" s="316"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -18600,7 +18880,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H65" s="295"/>
+      <c r="H65" s="316"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -18631,7 +18911,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H66" s="295"/>
+      <c r="H66" s="316"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -18661,7 +18941,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H67" s="295"/>
+      <c r="H67" s="316"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -18691,7 +18971,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H68" s="295"/>
+      <c r="H68" s="316"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -18721,7 +19001,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H69" s="296"/>
+      <c r="H69" s="317"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -18781,23 +19061,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="297"/>
-      <c r="C73" s="298" t="s">
+      <c r="B73" s="318"/>
+      <c r="C73" s="319" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="300" t="s">
+      <c r="E73" s="321" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="302" t="s">
+      <c r="F73" s="323" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="302" t="s">
+      <c r="G73" s="323" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="291" t="s">
+      <c r="H73" s="313" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -18810,15 +19090,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="297"/>
-      <c r="C74" s="299"/>
+      <c r="B74" s="318"/>
+      <c r="C74" s="320"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="301"/>
-      <c r="F74" s="303"/>
-      <c r="G74" s="303"/>
-      <c r="H74" s="292"/>
+      <c r="E74" s="322"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="324"/>
+      <c r="H74" s="314"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -19049,9 +19329,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="285"/>
-      <c r="I82" s="285"/>
-      <c r="J82" s="285"/>
+      <c r="H82" s="329"/>
+      <c r="I82" s="329"/>
+      <c r="J82" s="329"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -19059,19 +19339,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="286" t="s">
+      <c r="B83" s="330" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="286"/>
-      <c r="D83" s="286"/>
-      <c r="E83" s="286"/>
-      <c r="F83" s="286"/>
-      <c r="G83" s="286"/>
-      <c r="H83" s="286"/>
-      <c r="I83" s="286"/>
-      <c r="J83" s="286"/>
-      <c r="K83" s="286"/>
-      <c r="L83" s="286"/>
+      <c r="C83" s="330"/>
+      <c r="D83" s="330"/>
+      <c r="E83" s="330"/>
+      <c r="F83" s="330"/>
+      <c r="G83" s="330"/>
+      <c r="H83" s="330"/>
+      <c r="I83" s="330"/>
+      <c r="J83" s="330"/>
+      <c r="K83" s="330"/>
+      <c r="L83" s="330"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -19156,11 +19436,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="287"/>
-      <c r="I88" s="287"/>
+      <c r="H88" s="331"/>
+      <c r="I88" s="331"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="287"/>
-      <c r="L88" s="287"/>
+      <c r="K88" s="331"/>
+      <c r="L88" s="331"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -19250,10 +19530,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="288" t="s">
+      <c r="Q92" s="332" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="288"/>
+      <c r="R92" s="332"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.6501486762013902</v>
@@ -19313,10 +19593,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="289" t="s">
+      <c r="T94" s="333" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="290"/>
+      <c r="U94" s="334"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -19349,11 +19629,11 @@
         <f>R95/S92</f>
         <v>0.7338743847253193</v>
       </c>
-      <c r="T95" s="281">
+      <c r="T95" s="325">
         <f>R96-R95</f>
         <v>-1.1330363281889482</v>
       </c>
-      <c r="U95" s="283">
+      <c r="U95" s="327">
         <f>(R96-R95)/R95</f>
         <v>-0.42297193412043299</v>
       </c>
@@ -19389,8 +19669,8 @@
         <f>R96/S92</f>
         <v>0.42346611681660823</v>
       </c>
-      <c r="T96" s="282"/>
-      <c r="U96" s="283"/>
+      <c r="T96" s="326"/>
+      <c r="U96" s="327"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -19843,22 +20123,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="284" t="s">
+      <c r="B122" s="328" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="284"/>
-      <c r="D122" s="284"/>
+      <c r="C122" s="328"/>
+      <c r="D122" s="328"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="284" t="s">
+      <c r="B123" s="328" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="284"/>
-      <c r="D123" s="284"/>
+      <c r="C123" s="328"/>
+      <c r="D123" s="328"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>1.0851568256888184</v>
@@ -19866,44 +20146,28 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="C35:D35"/>
@@ -19917,28 +20181,44 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5" xr:uid="{5C2F12C3-696A-4D06-9C34-8B4F07F5489F}">
@@ -19979,6 +20259,571 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941D5018-3274-429A-BC96-6832248D126F}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I1" s="233" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="233" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="233" t="s">
+        <v>220</v>
+      </c>
+      <c r="L1" s="233" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="233" t="s">
+        <v>221</v>
+      </c>
+      <c r="N1" s="233" t="s">
+        <v>222</v>
+      </c>
+      <c r="O1" s="233" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I2" s="234" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="236">
+        <v>100</v>
+      </c>
+      <c r="L2" s="236">
+        <v>2.7</v>
+      </c>
+      <c r="M2" s="236">
+        <v>5</v>
+      </c>
+      <c r="N2" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O2" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I3" s="234" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K3" s="236">
+        <v>100</v>
+      </c>
+      <c r="L3" s="236">
+        <v>0.91</v>
+      </c>
+      <c r="M3" s="236">
+        <v>5</v>
+      </c>
+      <c r="N3" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O3" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I4" s="234" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K4" s="236">
+        <v>100</v>
+      </c>
+      <c r="L4" s="236">
+        <v>0.91</v>
+      </c>
+      <c r="M4" s="236">
+        <v>5</v>
+      </c>
+      <c r="N4" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O4" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="239">
+        <v>0.91</v>
+      </c>
+      <c r="I5" s="234" t="s">
+        <v>227</v>
+      </c>
+      <c r="J5" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K5" s="236">
+        <v>100</v>
+      </c>
+      <c r="L5" s="236">
+        <v>0.95</v>
+      </c>
+      <c r="M5" s="236">
+        <v>5</v>
+      </c>
+      <c r="N5" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O5" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="240">
+        <v>1.4</v>
+      </c>
+      <c r="G6" s="231" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="234" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="235"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="237"/>
+      <c r="O6" s="238"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="239">
+        <v>0.91</v>
+      </c>
+      <c r="G7" s="231" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="234" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" s="236">
+        <v>100</v>
+      </c>
+      <c r="L7" s="236">
+        <v>0.92</v>
+      </c>
+      <c r="M7" s="236">
+        <v>5</v>
+      </c>
+      <c r="N7" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O7" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="240">
+        <v>2.7</v>
+      </c>
+      <c r="G8" s="231" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="234" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K8" s="236">
+        <v>100</v>
+      </c>
+      <c r="L8" s="236">
+        <v>0.92</v>
+      </c>
+      <c r="M8" s="236">
+        <v>5</v>
+      </c>
+      <c r="N8" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="239">
+        <v>0.92</v>
+      </c>
+      <c r="G9" s="231" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="234" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K9" s="236">
+        <v>100</v>
+      </c>
+      <c r="L9" s="236">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M9" s="236">
+        <v>5</v>
+      </c>
+      <c r="N9" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O9" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="240">
+        <v>0.93</v>
+      </c>
+      <c r="G10" s="231" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="234" t="s">
+        <v>241</v>
+      </c>
+      <c r="J10" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K10" s="236">
+        <v>100</v>
+      </c>
+      <c r="L10" s="236">
+        <v>1</v>
+      </c>
+      <c r="M10" s="236">
+        <v>8</v>
+      </c>
+      <c r="N10" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="239">
+        <v>1.24</v>
+      </c>
+      <c r="G11" s="231" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" s="234" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" s="236">
+        <v>100</v>
+      </c>
+      <c r="L11" s="236">
+        <v>1.38</v>
+      </c>
+      <c r="M11" s="236">
+        <v>5</v>
+      </c>
+      <c r="N11" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O11" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" s="240">
+        <v>0.92</v>
+      </c>
+      <c r="G12" s="231" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="234" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="235" t="s">
+        <v>224</v>
+      </c>
+      <c r="K12" s="236">
+        <v>100</v>
+      </c>
+      <c r="L12" s="236">
+        <v>1.38</v>
+      </c>
+      <c r="M12" s="236">
+        <v>5</v>
+      </c>
+      <c r="N12" s="237" t="s">
+        <v>225</v>
+      </c>
+      <c r="O12" s="238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="239">
+        <v>1</v>
+      </c>
+      <c r="G13" s="229" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="234" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="240">
+        <v>1</v>
+      </c>
+      <c r="G14" s="231" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="234" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="239">
+        <v>1</v>
+      </c>
+      <c r="G15" s="231" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="231" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="241" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="242">
+        <v>1</v>
+      </c>
+      <c r="G16" s="230" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="231" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="231" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="234" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="231" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="234" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="229" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="229" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="230" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="231" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="232" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>249</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I2:O12">
+    <sortCondition ref="I2:I12"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B26283A-876D-4B37-98A9-075713B589D3}">
+  <dimension ref="F3:I11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="33.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F3" s="374"/>
+      <c r="G3" s="374" t="s">
+        <v>365</v>
+      </c>
+      <c r="H3" s="374" t="s">
+        <v>366</v>
+      </c>
+      <c r="I3" s="374" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F4" s="375" t="s">
+        <v>342</v>
+      </c>
+      <c r="G4" s="375"/>
+      <c r="H4" s="375"/>
+      <c r="I4" s="375"/>
+    </row>
+    <row r="5" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F5" s="372" t="s">
+        <v>344</v>
+      </c>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+    </row>
+    <row r="6" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F6" s="371" t="s">
+        <v>345</v>
+      </c>
+      <c r="G6" s="371"/>
+      <c r="H6" s="371"/>
+      <c r="I6" s="371"/>
+    </row>
+    <row r="7" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F7" s="372" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="372"/>
+      <c r="H7" s="372"/>
+      <c r="I7" s="372"/>
+    </row>
+    <row r="8" spans="6:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="376" t="s">
+        <v>350</v>
+      </c>
+      <c r="G8" s="371"/>
+      <c r="H8" s="371"/>
+      <c r="I8" s="371"/>
+    </row>
+    <row r="9" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F9" s="377" t="s">
+        <v>353</v>
+      </c>
+      <c r="G9" s="372"/>
+      <c r="H9" s="372"/>
+      <c r="I9" s="372"/>
+    </row>
+    <row r="10" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F10" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="G10" s="371"/>
+      <c r="H10" s="371"/>
+      <c r="I10" s="371"/>
+    </row>
+    <row r="11" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="373" t="s">
+        <v>355</v>
+      </c>
+      <c r="G11" s="373"/>
+      <c r="H11" s="373"/>
+      <c r="I11" s="373"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="23" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64514EA5-211E-42DB-B908-1C8FEC7CF710}">
   <dimension ref="G7:T25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -20021,40 +20866,40 @@
       </c>
     </row>
     <row r="8" spans="7:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="362">
+      <c r="G8" s="366">
         <v>1</v>
       </c>
-      <c r="H8" s="363" t="s">
+      <c r="H8" s="367" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="363" t="s">
+      <c r="I8" s="367" t="s">
         <v>328</v>
       </c>
-      <c r="J8" s="363" t="s">
+      <c r="J8" s="367" t="s">
         <v>328</v>
       </c>
-      <c r="K8" s="363" t="s">
+      <c r="K8" s="367" t="s">
         <v>328</v>
       </c>
-      <c r="L8" s="363" t="s">
+      <c r="L8" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="M8" s="363" t="s">
+      <c r="M8" s="367" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="363" t="s">
+      <c r="N8" s="367" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" spans="7:14" x14ac:dyDescent="0.3">
-      <c r="G9" s="362"/>
-      <c r="H9" s="363"/>
-      <c r="I9" s="363"/>
-      <c r="J9" s="363"/>
-      <c r="K9" s="363"/>
-      <c r="L9" s="363"/>
-      <c r="M9" s="363"/>
-      <c r="N9" s="363"/>
+      <c r="G9" s="366"/>
+      <c r="H9" s="367"/>
+      <c r="I9" s="367"/>
+      <c r="J9" s="367"/>
+      <c r="K9" s="367"/>
+      <c r="L9" s="367"/>
+      <c r="M9" s="367"/>
+      <c r="N9" s="367"/>
     </row>
     <row r="17" spans="7:20" ht="55.2" x14ac:dyDescent="0.3">
       <c r="G17" s="268" t="s">
@@ -20181,9 +21026,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC5812A-307F-453C-92CE-92FF0734E5BC}">
-  <dimension ref="B2:L23"/>
+  <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -20273,45 +21118,61 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K9" s="368" t="s">
+    <row r="5" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K5" s="284" t="s">
         <v>341</v>
       </c>
-      <c r="L9" s="368"/>
-    </row>
-    <row r="10" spans="2:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="K10" s="364"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K11" t="s">
+      <c r="L5" s="284"/>
+    </row>
+    <row r="6" spans="2:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="K6" s="281"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K7" t="s">
         <v>342</v>
       </c>
+      <c r="L7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K9" t="s">
+        <v>345</v>
+      </c>
+      <c r="L9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>188</v>
+      </c>
+      <c r="L10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="283" t="s">
+        <v>350</v>
+      </c>
       <c r="L11" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K12" t="s">
-        <v>344</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K13" t="s">
-        <v>345</v>
-      </c>
-      <c r="L13" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K14" t="s">
-        <v>188</v>
+        <v>353</v>
       </c>
       <c r="L14" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -20322,38 +21183,26 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K16" s="369" t="s">
-        <v>350</v>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>355</v>
       </c>
       <c r="L16" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K17" s="365"/>
+      <c r="K17" s="282"/>
     </row>
     <row r="18" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K18" s="365"/>
-    </row>
-    <row r="19" spans="11:11" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K19" s="365"/>
-    </row>
-    <row r="20" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K20" s="366"/>
-    </row>
-    <row r="21" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K21" s="367"/>
-    </row>
-    <row r="22" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K22" s="367"/>
-    </row>
-    <row r="23" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="K23" s="367"/>
+      <c r="K18" s="282"/>
+    </row>
+    <row r="19" spans="11:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K19" s="282"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -21289,20 +22138,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
-      <c r="K1" s="326"/>
-      <c r="L1" s="326"/>
+      <c r="B1" s="288"/>
+      <c r="C1" s="288"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -21330,26 +22179,26 @@
       <c r="R2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="327" t="s">
+      <c r="A3" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="327"/>
-      <c r="C3" s="328" t="s">
+      <c r="B3" s="285"/>
+      <c r="C3" s="289" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="328"/>
-      <c r="E3" s="328"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="327" t="s">
+      <c r="G3" s="285" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="327"/>
-      <c r="I3" s="328" t="s">
+      <c r="H3" s="285"/>
+      <c r="I3" s="289" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="328"/>
-      <c r="K3" s="328"/>
-      <c r="L3" s="328"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -21374,28 +22223,28 @@
       <c r="Q4" s="9"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="327" t="s">
+      <c r="A5" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="327"/>
-      <c r="C5" s="329" t="s">
+      <c r="B5" s="285"/>
+      <c r="C5" s="286" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="329"/>
-      <c r="E5" s="329"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="327" t="s">
+      <c r="G5" s="285" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="327"/>
-      <c r="I5" s="330">
+      <c r="H5" s="285"/>
+      <c r="I5" s="287">
         <v>10000</v>
       </c>
-      <c r="J5" s="330"/>
-      <c r="K5" s="329" t="s">
+      <c r="J5" s="287"/>
+      <c r="K5" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="329"/>
+      <c r="L5" s="286"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
@@ -21426,128 +22275,128 @@
       <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="320" t="s">
+      <c r="A9" s="290" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="320"/>
-      <c r="C9" s="320"/>
+      <c r="B9" s="290"/>
+      <c r="C9" s="290"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="320" t="s">
+      <c r="A10" s="290" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="320"/>
-      <c r="C10" s="320"/>
+      <c r="B10" s="290"/>
+      <c r="C10" s="290"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="321"/>
-      <c r="P10" s="321"/>
+      <c r="O10" s="291"/>
+      <c r="P10" s="291"/>
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="322" t="s">
+      <c r="A12" s="292" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="323"/>
-      <c r="C12" s="324"/>
+      <c r="B12" s="293"/>
+      <c r="C12" s="294"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="I12" s="325"/>
-      <c r="J12" s="325"/>
-      <c r="K12" s="325"/>
-      <c r="M12" s="325"/>
-      <c r="N12" s="325"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="295"/>
+      <c r="K12" s="295"/>
+      <c r="M12" s="295"/>
+      <c r="N12" s="295"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="318" t="s">
+      <c r="A13" s="296" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="319"/>
+      <c r="B13" s="297"/>
       <c r="C13" s="135">
         <v>250</v>
       </c>
-      <c r="E13" s="313"/>
-      <c r="F13" s="313"/>
+      <c r="E13" s="298"/>
+      <c r="F13" s="298"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="313"/>
-      <c r="J13" s="313"/>
+      <c r="I13" s="298"/>
+      <c r="J13" s="298"/>
       <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="316" t="s">
+      <c r="A14" s="299" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="317"/>
+      <c r="B14" s="300"/>
       <c r="C14" s="30">
         <v>100</v>
       </c>
-      <c r="E14" s="313"/>
-      <c r="F14" s="313"/>
+      <c r="E14" s="298"/>
+      <c r="F14" s="298"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="313"/>
-      <c r="J14" s="313"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="298"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="313"/>
-      <c r="N14" s="313"/>
+      <c r="M14" s="298"/>
+      <c r="N14" s="298"/>
       <c r="O14" s="21"/>
       <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="316" t="s">
+      <c r="A15" s="299" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="317"/>
+      <c r="B15" s="300"/>
       <c r="C15" s="31">
         <v>20</v>
       </c>
-      <c r="E15" s="313"/>
-      <c r="F15" s="313"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="298"/>
       <c r="G15" s="21"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="313"/>
-      <c r="N15" s="313"/>
+      <c r="M15" s="298"/>
+      <c r="N15" s="298"/>
       <c r="O15" s="21"/>
       <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="316" t="s">
+      <c r="A16" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="317"/>
+      <c r="B16" s="300"/>
       <c r="C16" s="136">
         <v>1</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="313"/>
-      <c r="J16" s="313"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="298"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="313"/>
-      <c r="N16" s="313"/>
+      <c r="M16" s="298"/>
+      <c r="N16" s="298"/>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="311" t="s">
+      <c r="A17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="312"/>
+      <c r="B17" s="302"/>
       <c r="C17" s="32">
         <v>4</v>
       </c>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
+      <c r="E17" s="298"/>
+      <c r="F17" s="298"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="313"/>
-      <c r="N17" s="313"/>
+      <c r="M17" s="298"/>
+      <c r="N17" s="298"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="313"/>
-      <c r="N18" s="313"/>
+      <c r="M18" s="298"/>
+      <c r="N18" s="298"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M19" s="267"/>
@@ -21558,28 +22407,28 @@
       <c r="N20" s="267"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="314"/>
+      <c r="C21" s="303"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="314"/>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314"/>
-      <c r="H21" s="314"/>
+      <c r="E21" s="303"/>
+      <c r="F21" s="303"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="303"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C22" s="314"/>
+      <c r="C22" s="303"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="314"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="303"/>
+      <c r="G22" s="303"/>
+      <c r="H22" s="303"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="315"/>
+      <c r="C23" s="304"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="315"/>
-      <c r="F23" s="315"/>
-      <c r="G23" s="315"/>
-      <c r="H23" s="315"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="304"/>
+      <c r="H23" s="304"/>
     </row>
     <row r="24" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -21820,12 +22669,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="304" t="s">
+      <c r="A31" s="306" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="305"/>
-      <c r="C31" s="305"/>
-      <c r="D31" s="305"/>
+      <c r="B31" s="307"/>
+      <c r="C31" s="307"/>
+      <c r="D31" s="307"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -21888,19 +22737,19 @@
         <f>B37/B36</f>
         <v>0.9813242784380305</v>
       </c>
-      <c r="C35" s="306" t="s">
+      <c r="C35" s="308" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="306"/>
+      <c r="D35" s="308"/>
       <c r="E35" s="134">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>346.02076124567475</v>
       </c>
-      <c r="F35" s="306" t="s">
+      <c r="F35" s="308" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="306"/>
-      <c r="H35" s="306"/>
+      <c r="G35" s="308"/>
+      <c r="H35" s="308"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1020</v>
@@ -21914,19 +22763,19 @@
         <f>SUMIFS(table17[Micron],table17[Type],"substrate")+SUMIFS(table17[Total GSM],table17[Type],"Ink")+SUMIFS(table17[Total GSM],table17[Type],"Adhesive")</f>
         <v>117.8</v>
       </c>
-      <c r="C36" s="306" t="s">
+      <c r="C36" s="308" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="306"/>
+      <c r="D36" s="308"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>2.89</v>
       </c>
-      <c r="F36" s="306" t="s">
+      <c r="F36" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="306"/>
-      <c r="H36" s="306"/>
+      <c r="G36" s="308"/>
+      <c r="H36" s="308"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -21951,19 +22800,19 @@
         <f>SUM(F25:F30)</f>
         <v>115.6</v>
       </c>
-      <c r="C37" s="306" t="s">
+      <c r="C37" s="308" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="306"/>
+      <c r="D37" s="308"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>8.6505190311418687</v>
       </c>
-      <c r="F37" s="306" t="s">
+      <c r="F37" s="308" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="306"/>
-      <c r="H37" s="306"/>
+      <c r="G37" s="308"/>
+      <c r="H37" s="308"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>3460.2076124567475</v>
@@ -21977,29 +22826,29 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.22398500000000002</v>
       </c>
-      <c r="C38" s="306" t="s">
+      <c r="C38" s="308" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="306"/>
+      <c r="D38" s="308"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>8.4809010109234002</v>
       </c>
-      <c r="F38" s="306" t="s">
+      <c r="F38" s="308" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="306"/>
-      <c r="H38" s="306"/>
+      <c r="G38" s="308"/>
+      <c r="H38" s="308"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>84809.010109234005</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="306" t="s">
+      <c r="C39" s="308" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="306"/>
+      <c r="D39" s="308"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>34.602076124567475</v>
@@ -22056,11 +22905,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="308" t="s">
+      <c r="A44" s="310" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="309"/>
-      <c r="C44" s="310"/>
+      <c r="B44" s="311"/>
+      <c r="C44" s="312"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -22090,11 +22939,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="293" t="s">
+      <c r="A46" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="293"/>
-      <c r="C46" s="293"/>
+      <c r="B46" s="305"/>
+      <c r="C46" s="305"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -22109,11 +22958,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="293" t="s">
+      <c r="A47" s="305" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="293"/>
-      <c r="C47" s="293"/>
+      <c r="B47" s="305"/>
+      <c r="C47" s="305"/>
       <c r="D47" s="127">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>63.397190403781075</v>
@@ -22129,11 +22978,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="293" t="s">
+      <c r="A48" s="305" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="293"/>
-      <c r="C48" s="293"/>
+      <c r="B48" s="305"/>
+      <c r="C48" s="305"/>
       <c r="D48" s="128">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>2193.6744084353313</v>
@@ -22149,11 +22998,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="293" t="s">
+      <c r="A49" s="305" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="293"/>
-      <c r="C49" s="293"/>
+      <c r="B49" s="305"/>
+      <c r="C49" s="305"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>250</v>
@@ -22169,11 +23018,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="293" t="s">
+      <c r="A50" s="305" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="293"/>
-      <c r="C50" s="293"/>
+      <c r="B50" s="305"/>
+      <c r="C50" s="305"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>21936.744084353315</v>
@@ -22204,11 +23053,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="293" t="s">
+      <c r="A52" s="305" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="293"/>
-      <c r="C52" s="293"/>
+      <c r="B52" s="305"/>
+      <c r="C52" s="305"/>
       <c r="D52" s="78">
         <v>74</v>
       </c>
@@ -22223,11 +23072,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="293" t="s">
+      <c r="A53" s="305" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="293"/>
-      <c r="C53" s="293"/>
+      <c r="B53" s="305"/>
+      <c r="C53" s="305"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>644.22615683819515</v>
@@ -22373,7 +23222,7 @@
         <f>IFERROR(F60*E60,"")</f>
         <v>4092.6347009391993</v>
       </c>
-      <c r="H60" s="294">
+      <c r="H60" s="315">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>9441.736856218844</v>
       </c>
@@ -22407,7 +23256,7 @@
         <f t="shared" ref="G61:G69" si="2">IFERROR(F61*E61,"")</f>
         <v>2596.1802021846802</v>
       </c>
-      <c r="H61" s="295"/>
+      <c r="H61" s="316"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -22438,7 +23287,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H62" s="295"/>
+      <c r="H62" s="316"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -22469,7 +23318,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H63" s="295"/>
+      <c r="H63" s="316"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -22500,7 +23349,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H64" s="295"/>
+      <c r="H64" s="316"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -22531,7 +23380,7 @@
         <f t="shared" si="2"/>
         <v>806.74175091028349</v>
       </c>
-      <c r="H65" s="295"/>
+      <c r="H65" s="316"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -22562,7 +23411,7 @@
         <f t="shared" si="2"/>
         <v>166.34835018205669</v>
       </c>
-      <c r="H66" s="295"/>
+      <c r="H66" s="316"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -22592,7 +23441,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H67" s="295"/>
+      <c r="H67" s="316"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -22622,7 +23471,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H68" s="295"/>
+      <c r="H68" s="316"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -22652,7 +23501,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H69" s="296"/>
+      <c r="H69" s="317"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -22712,23 +23561,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="297"/>
-      <c r="C73" s="298" t="s">
+      <c r="B73" s="318"/>
+      <c r="C73" s="319" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="300" t="s">
+      <c r="E73" s="321" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="302" t="s">
+      <c r="F73" s="323" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="302" t="s">
+      <c r="G73" s="323" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="291" t="s">
+      <c r="H73" s="313" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -22741,15 +23590,15 @@
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="297"/>
-      <c r="C74" s="299"/>
+      <c r="B74" s="318"/>
+      <c r="C74" s="320"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="301"/>
-      <c r="F74" s="303"/>
-      <c r="G74" s="303"/>
-      <c r="H74" s="292"/>
+      <c r="E74" s="322"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="324"/>
+      <c r="H74" s="314"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -22980,9 +23829,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="285"/>
-      <c r="I82" s="285"/>
-      <c r="J82" s="285"/>
+      <c r="H82" s="329"/>
+      <c r="I82" s="329"/>
+      <c r="J82" s="329"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -22990,19 +23839,19 @@
     </row>
     <row r="83" spans="1:25" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="286" t="s">
+      <c r="B83" s="330" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="286"/>
-      <c r="D83" s="286"/>
-      <c r="E83" s="286"/>
-      <c r="F83" s="286"/>
-      <c r="G83" s="286"/>
-      <c r="H83" s="286"/>
-      <c r="I83" s="286"/>
-      <c r="J83" s="286"/>
-      <c r="K83" s="286"/>
-      <c r="L83" s="286"/>
+      <c r="C83" s="330"/>
+      <c r="D83" s="330"/>
+      <c r="E83" s="330"/>
+      <c r="F83" s="330"/>
+      <c r="G83" s="330"/>
+      <c r="H83" s="330"/>
+      <c r="I83" s="330"/>
+      <c r="J83" s="330"/>
+      <c r="K83" s="330"/>
+      <c r="L83" s="330"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -23087,11 +23936,11 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="287"/>
-      <c r="I88" s="287"/>
+      <c r="H88" s="331"/>
+      <c r="I88" s="331"/>
       <c r="J88" s="213"/>
-      <c r="K88" s="287"/>
-      <c r="L88" s="287"/>
+      <c r="K88" s="331"/>
+      <c r="L88" s="331"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
       <c r="S88" s="130"/>
@@ -23181,10 +24030,10 @@
       <c r="M92" s="41"/>
       <c r="N92" s="41"/>
       <c r="O92" s="41"/>
-      <c r="Q92" s="288" t="s">
+      <c r="Q92" s="332" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="288"/>
+      <c r="R92" s="332"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>3.7630361423692897</v>
@@ -23244,10 +24093,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="289" t="s">
+      <c r="T94" s="333" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="290"/>
+      <c r="U94" s="334"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
@@ -23280,11 +24129,11 @@
         <f>R95/S92</f>
         <v>0.76580720508248346</v>
       </c>
-      <c r="T95" s="281">
+      <c r="T95" s="325">
         <f>R96-R95</f>
         <v>-6.8260190812196253E-2</v>
       </c>
-      <c r="U95" s="283">
+      <c r="U95" s="327">
         <f>(R96-R95)/R95</f>
         <v>-2.368697819819552E-2</v>
       </c>
@@ -23320,8 +24169,8 @@
         <f>R96/S92</f>
         <v>0.74766754651167366</v>
       </c>
-      <c r="T96" s="282"/>
-      <c r="U96" s="283"/>
+      <c r="T96" s="326"/>
+      <c r="U96" s="327"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="53"/>
@@ -23774,22 +24623,22 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="284" t="s">
+      <c r="B122" s="328" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="284"/>
-      <c r="D122" s="284"/>
+      <c r="C122" s="328"/>
+      <c r="D122" s="328"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.919047619047619</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="284" t="s">
+      <c r="B123" s="328" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="284"/>
-      <c r="D123" s="284"/>
+      <c r="C123" s="328"/>
+      <c r="D123" s="328"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-2.6611699687135438E-2</v>
@@ -23797,6 +24646,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T95:T96"/>
     <mergeCell ref="U95:U96"/>
@@ -23813,63 +24719,6 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="O10:P10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B30" xr:uid="{258B5AFF-B470-4ED5-B7DC-EBBE2B8E0F2B}">
@@ -23910,6 +24759,68 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3E513-15A0-4FE8-A31E-37EBAF26C5B4}">
+  <dimension ref="C5:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C5" s="368" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="272"/>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C7" s="369" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="C8" s="369" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="369" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" ht="21" x14ac:dyDescent="0.3">
+      <c r="C10" s="370" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="C11" s="369" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C12" s="369" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="369" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" ht="21" x14ac:dyDescent="0.3">
+      <c r="C14" s="370" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E99D9E2-9AEA-4645-813E-C86DFAF6C53F}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
@@ -23976,16 +24887,16 @@
       <c r="T1" t="s">
         <v>188</v>
       </c>
-      <c r="W1" s="331" t="s">
+      <c r="W1" s="335" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="331"/>
-      <c r="Y1" s="331"/>
-      <c r="Z1" s="331"/>
-      <c r="AA1" s="331"/>
-      <c r="AB1" s="331"/>
-      <c r="AC1" s="331"/>
-      <c r="AD1" s="331"/>
+      <c r="X1" s="335"/>
+      <c r="Y1" s="335"/>
+      <c r="Z1" s="335"/>
+      <c r="AA1" s="335"/>
+      <c r="AB1" s="335"/>
+      <c r="AC1" s="335"/>
+      <c r="AD1" s="335"/>
     </row>
     <row r="2" spans="4:30" x14ac:dyDescent="0.3">
       <c r="D2" s="102" t="s">
@@ -24724,7 +25635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D83BBB9-D6D7-4548-8051-07540CE54455}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -24754,20 +25665,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
-      <c r="K1" s="326"/>
-      <c r="L1" s="326"/>
+      <c r="B1" s="288"/>
+      <c r="C1" s="288"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -24797,26 +25708,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="327" t="s">
+      <c r="A3" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="327"/>
-      <c r="C3" s="328" t="s">
+      <c r="B3" s="285"/>
+      <c r="C3" s="289" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="328"/>
-      <c r="E3" s="328"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="327" t="s">
+      <c r="G3" s="285" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="327"/>
-      <c r="I3" s="328" t="s">
+      <c r="H3" s="285"/>
+      <c r="I3" s="289" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="328"/>
-      <c r="K3" s="328"/>
-      <c r="L3" s="328"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -24843,28 +25754,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="327" t="s">
+      <c r="A5" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="327"/>
-      <c r="C5" s="329" t="s">
+      <c r="B5" s="285"/>
+      <c r="C5" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="329"/>
-      <c r="E5" s="329"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="327" t="s">
+      <c r="G5" s="285" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="327"/>
-      <c r="I5" s="330">
+      <c r="H5" s="285"/>
+      <c r="I5" s="287">
         <v>20000</v>
       </c>
-      <c r="J5" s="330"/>
-      <c r="K5" s="329" t="s">
+      <c r="J5" s="287"/>
+      <c r="K5" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="329"/>
+      <c r="L5" s="286"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -24897,105 +25808,105 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="320" t="s">
+      <c r="A9" s="290" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="320"/>
-      <c r="C9" s="320"/>
+      <c r="B9" s="290"/>
+      <c r="C9" s="290"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="320" t="s">
+      <c r="A10" s="290" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="320"/>
-      <c r="C10" s="320"/>
-      <c r="N10" s="321"/>
-      <c r="O10" s="321"/>
-      <c r="P10" s="321"/>
-      <c r="Q10" s="321"/>
+      <c r="B10" s="290"/>
+      <c r="C10" s="290"/>
+      <c r="N10" s="291"/>
+      <c r="O10" s="291"/>
+      <c r="P10" s="291"/>
+      <c r="Q10" s="291"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="325"/>
-      <c r="B12" s="325"/>
-      <c r="C12" s="325"/>
-      <c r="E12" s="335" t="s">
+      <c r="A12" s="295"/>
+      <c r="B12" s="295"/>
+      <c r="C12" s="295"/>
+      <c r="E12" s="349" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="336"/>
-      <c r="G12" s="337"/>
-      <c r="I12" s="325"/>
-      <c r="J12" s="325"/>
-      <c r="K12" s="325"/>
-      <c r="M12" s="325"/>
-      <c r="N12" s="325"/>
-      <c r="O12" s="325"/>
+      <c r="F12" s="350"/>
+      <c r="G12" s="351"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="295"/>
+      <c r="K12" s="295"/>
+      <c r="M12" s="295"/>
+      <c r="N12" s="295"/>
+      <c r="O12" s="295"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="313"/>
-      <c r="B13" s="313"/>
+      <c r="A13" s="298"/>
+      <c r="B13" s="298"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="338" t="s">
+      <c r="E13" s="352" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="339"/>
+      <c r="F13" s="353"/>
       <c r="G13" s="29">
         <v>102</v>
       </c>
-      <c r="I13" s="313"/>
-      <c r="J13" s="313"/>
+      <c r="I13" s="298"/>
+      <c r="J13" s="298"/>
       <c r="K13" s="21"/>
-      <c r="M13" s="313"/>
-      <c r="N13" s="313"/>
+      <c r="M13" s="298"/>
+      <c r="N13" s="298"/>
       <c r="O13" s="129"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="313"/>
-      <c r="B14" s="313"/>
+      <c r="A14" s="298"/>
+      <c r="B14" s="298"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="316" t="s">
+      <c r="E14" s="299" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="317"/>
+      <c r="F14" s="300"/>
       <c r="G14" s="30">
         <v>33</v>
       </c>
-      <c r="I14" s="313"/>
-      <c r="J14" s="313"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="298"/>
       <c r="K14" s="21"/>
-      <c r="M14" s="313"/>
-      <c r="N14" s="313"/>
+      <c r="M14" s="298"/>
+      <c r="N14" s="298"/>
       <c r="O14" s="130"/>
       <c r="P14" s="21"/>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="313"/>
-      <c r="B15" s="313"/>
+      <c r="A15" s="298"/>
+      <c r="B15" s="298"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="333" t="s">
+      <c r="E15" s="347" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="334"/>
+      <c r="F15" s="348"/>
       <c r="G15" s="30">
         <v>161</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="131"/>
-      <c r="M15" s="313"/>
-      <c r="N15" s="313"/>
+      <c r="M15" s="298"/>
+      <c r="N15" s="298"/>
       <c r="O15" s="130"/>
       <c r="P15" s="21"/>
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="313"/>
-      <c r="B16" s="313"/>
+      <c r="A16" s="298"/>
+      <c r="B16" s="298"/>
       <c r="C16" s="6"/>
       <c r="E16" s="23" t="s">
         <v>6</v>
@@ -25004,74 +25915,74 @@
       <c r="G16" s="31">
         <v>20</v>
       </c>
-      <c r="I16" s="313"/>
-      <c r="J16" s="313"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="298"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="313"/>
-      <c r="N16" s="313"/>
+      <c r="M16" s="298"/>
+      <c r="N16" s="298"/>
       <c r="O16" s="129"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="313"/>
-      <c r="B17" s="313"/>
+      <c r="A17" s="298"/>
+      <c r="B17" s="298"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="311" t="s">
+      <c r="E17" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="312"/>
+      <c r="F17" s="302"/>
       <c r="G17" s="32">
         <v>30</v>
       </c>
-      <c r="M17" s="313"/>
-      <c r="N17" s="313"/>
+      <c r="M17" s="298"/>
+      <c r="N17" s="298"/>
       <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="313"/>
-      <c r="N18" s="313"/>
+      <c r="M18" s="298"/>
+      <c r="N18" s="298"/>
       <c r="O18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="332"/>
-      <c r="N19" s="332"/>
+      <c r="M19" s="354"/>
+      <c r="N19" s="354"/>
       <c r="O19" s="132"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M20" s="332"/>
-      <c r="N20" s="332"/>
+      <c r="M20" s="354"/>
+      <c r="N20" s="354"/>
       <c r="O20" s="133"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="314" t="s">
+      <c r="C21" s="303" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="314" t="s">
+      <c r="E21" s="303" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314" t="s">
+      <c r="F21" s="303"/>
+      <c r="G21" s="303" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="314" t="s">
+      <c r="H21" s="303" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="314"/>
+      <c r="C22" s="303"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="314"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="303"/>
+      <c r="G22" s="303"/>
+      <c r="H22" s="303"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="315"/>
+      <c r="C23" s="304"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="315"/>
-      <c r="F23" s="315"/>
-      <c r="G23" s="315"/>
-      <c r="H23" s="315"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="304"/>
+      <c r="H23" s="304"/>
     </row>
     <row r="24" spans="1:15" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
@@ -25248,12 +26159,12 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="304" t="s">
+      <c r="A31" s="306" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="305"/>
-      <c r="C31" s="305"/>
-      <c r="D31" s="305"/>
+      <c r="B31" s="307"/>
+      <c r="C31" s="307"/>
+      <c r="D31" s="307"/>
       <c r="E31" s="60">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -25316,19 +26227,19 @@
         <f>B37/B36</f>
         <v>0.91666666666666674</v>
       </c>
-      <c r="C35" s="306" t="s">
+      <c r="C35" s="308" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="306"/>
+      <c r="D35" s="308"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>5431.9647769676003</v>
       </c>
-      <c r="F35" s="306" t="s">
+      <c r="F35" s="308" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="306"/>
-      <c r="H35" s="306"/>
+      <c r="G35" s="308"/>
+      <c r="H35" s="308"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>1010</v>
@@ -25342,19 +26253,19 @@
         <f>SUMIFS(table1[Micron],table1[Type],"substrate")+SUMIFS(table1[Total GSM],table1[Type],"Ink")+SUMIFS(table1[Total GSM],table1[Type],"Adhesive")</f>
         <v>37.799999999999997</v>
       </c>
-      <c r="C36" s="306" t="s">
+      <c r="C36" s="308" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="306"/>
+      <c r="D36" s="308"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>0.18409544999999999</v>
       </c>
-      <c r="F36" s="306" t="s">
+      <c r="F36" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="306"/>
-      <c r="H36" s="306"/>
+      <c r="G36" s="308"/>
+      <c r="H36" s="308"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -25373,19 +26284,19 @@
         <f>SUM(F25:F30)</f>
         <v>34.65</v>
       </c>
-      <c r="C37" s="306" t="s">
+      <c r="C37" s="308" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="306"/>
+      <c r="D37" s="308"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>28.860028860028862</v>
       </c>
-      <c r="F37" s="306" t="s">
+      <c r="F37" s="308" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="306"/>
-      <c r="H37" s="306"/>
+      <c r="G37" s="308"/>
+      <c r="H37" s="308"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>108639.29553935201</v>
@@ -25399,37 +26310,37 @@
         <f>SUM(I25:I30)+I31</f>
         <v>0.10634300000000001</v>
       </c>
-      <c r="C38" s="306" t="s">
+      <c r="C38" s="308" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="306"/>
+      <c r="D38" s="308"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>28.574286000028575</v>
       </c>
-      <c r="F38" s="306" t="s">
+      <c r="F38" s="308" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="306"/>
-      <c r="H38" s="306"/>
+      <c r="G38" s="308"/>
+      <c r="H38" s="308"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>571485.72000057145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="306" t="s">
+      <c r="C39" s="308" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="306"/>
+      <c r="D39" s="308"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>874.5463290917836</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="306"/>
-      <c r="D40" s="306"/>
+      <c r="C40" s="308"/>
+      <c r="D40" s="308"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="82"/>
@@ -25479,11 +26390,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="308" t="s">
+      <c r="A44" s="310" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="309"/>
-      <c r="C44" s="310"/>
+      <c r="B44" s="311"/>
+      <c r="C44" s="312"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -25513,11 +26424,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="293" t="s">
+      <c r="A46" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="293"/>
-      <c r="C46" s="293"/>
+      <c r="B46" s="305"/>
+      <c r="C46" s="305"/>
       <c r="D46" s="77">
         <v>600</v>
       </c>
@@ -25532,11 +26443,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="293" t="s">
+      <c r="A47" s="305" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="293"/>
-      <c r="C47" s="293"/>
+      <c r="B47" s="305"/>
+      <c r="C47" s="305"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>7.8170490707388822</v>
@@ -25552,11 +26463,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="293" t="s">
+      <c r="A48" s="305" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="293"/>
-      <c r="C48" s="293"/>
+      <c r="B48" s="305"/>
+      <c r="C48" s="305"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>6836.3715691450298</v>
@@ -25572,11 +26483,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="293" t="s">
+      <c r="A49" s="305" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="293"/>
-      <c r="C49" s="293"/>
+      <c r="B49" s="305"/>
+      <c r="C49" s="305"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>33</v>
@@ -25592,11 +26503,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="293" t="s">
+      <c r="A50" s="305" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="293"/>
-      <c r="C50" s="293"/>
+      <c r="B50" s="305"/>
+      <c r="C50" s="305"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>42461.93521208092</v>
@@ -25627,11 +26538,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="293" t="s">
+      <c r="A52" s="305" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="293"/>
-      <c r="C52" s="293"/>
+      <c r="B52" s="305"/>
+      <c r="C52" s="305"/>
       <c r="D52" s="78">
         <v>71</v>
       </c>
@@ -25646,11 +26557,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="293" t="s">
+      <c r="A53" s="305" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="293"/>
-      <c r="C53" s="293"/>
+      <c r="B53" s="305"/>
+      <c r="C53" s="305"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>1737.6438086744588</v>
@@ -25793,7 +26704,7 @@
         <f>F60*E60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="340">
+      <c r="H60" s="344">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>141966.47760014096</v>
       </c>
@@ -25827,7 +26738,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>12329.714400011429</v>
       </c>
-      <c r="H61" s="341"/>
+      <c r="H61" s="345"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -25857,7 +26768,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H62" s="341"/>
+      <c r="H62" s="345"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -25887,7 +26798,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H63" s="341"/>
+      <c r="H63" s="345"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -25917,7 +26828,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H64" s="341"/>
+      <c r="H64" s="345"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -25947,7 +26858,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H65" s="341"/>
+      <c r="H65" s="345"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -25978,7 +26889,7 @@
         <f t="shared" si="3"/>
         <v>977.47620000095242</v>
       </c>
-      <c r="H66" s="341"/>
+      <c r="H66" s="345"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -26009,7 +26920,7 @@
         <f t="shared" si="3"/>
         <v>57198.572000057153</v>
       </c>
-      <c r="H67" s="341"/>
+      <c r="H67" s="345"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -26041,7 +26952,7 @@
         <f t="shared" si="3"/>
         <v>71460.715000071446</v>
       </c>
-      <c r="H68" s="341"/>
+      <c r="H68" s="345"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -26071,7 +26982,7 @@
         <f>F69*E69</f>
         <v>0</v>
       </c>
-      <c r="H69" s="342"/>
+      <c r="H69" s="346"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -26131,23 +27042,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="297"/>
-      <c r="C73" s="298" t="s">
+      <c r="B73" s="318"/>
+      <c r="C73" s="319" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="300" t="s">
+      <c r="E73" s="321" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="302" t="s">
+      <c r="F73" s="323" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="302" t="s">
+      <c r="G73" s="323" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="291" t="s">
+      <c r="H73" s="313" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -26161,15 +27072,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="297"/>
-      <c r="C74" s="299"/>
+      <c r="B74" s="318"/>
+      <c r="C74" s="320"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="301"/>
-      <c r="F74" s="303"/>
-      <c r="G74" s="303"/>
-      <c r="H74" s="292"/>
+      <c r="E74" s="322"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="324"/>
+      <c r="H74" s="314"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -26408,9 +27319,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="285"/>
-      <c r="I82" s="285"/>
-      <c r="J82" s="285"/>
+      <c r="H82" s="329"/>
+      <c r="I82" s="329"/>
+      <c r="J82" s="329"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -26418,19 +27329,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="286" t="s">
+      <c r="B83" s="330" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="286"/>
-      <c r="D83" s="286"/>
-      <c r="E83" s="286"/>
-      <c r="F83" s="286"/>
-      <c r="G83" s="286"/>
-      <c r="H83" s="286"/>
-      <c r="I83" s="286"/>
-      <c r="J83" s="286"/>
-      <c r="K83" s="286"/>
-      <c r="L83" s="286"/>
+      <c r="C83" s="330"/>
+      <c r="D83" s="330"/>
+      <c r="E83" s="330"/>
+      <c r="F83" s="330"/>
+      <c r="G83" s="330"/>
+      <c r="H83" s="330"/>
+      <c r="I83" s="330"/>
+      <c r="J83" s="330"/>
+      <c r="K83" s="330"/>
+      <c r="L83" s="330"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -26496,17 +27407,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="343" t="s">
+      <c r="H87" s="336" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="344"/>
+      <c r="I87" s="337"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="345" t="s">
+      <c r="K87" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="346"/>
+      <c r="L87" s="339"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -26518,20 +27429,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="347">
+      <c r="H88" s="340">
         <f>C75+H70</f>
         <v>10.167385929069098</v>
       </c>
-      <c r="I88" s="348"/>
+      <c r="I88" s="341"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>0.98761894452246557</v>
       </c>
-      <c r="K88" s="349">
+      <c r="K88" s="342">
         <f>E106+E122</f>
         <v>20.20888888888889</v>
       </c>
-      <c r="L88" s="350"/>
+      <c r="L88" s="343"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -26603,10 +27514,10 @@
         <v>0.88048809666228023</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="288" t="s">
+      <c r="Q92" s="332" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="288"/>
+      <c r="R92" s="332"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>11.388104543787712</v>
@@ -26660,10 +27571,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="289" t="s">
+      <c r="T94" s="333" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="290"/>
+      <c r="U94" s="334"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -26695,11 +27606,11 @@
         <f>R95/S92</f>
         <v>0.89280756863225985</v>
       </c>
-      <c r="T95" s="281">
+      <c r="T95" s="325">
         <f>R96-R95</f>
         <v>10.041502959819791</v>
       </c>
-      <c r="U95" s="283">
+      <c r="U95" s="327">
         <f>(R96-R95)/R95</f>
         <v>0.98761894452246557</v>
       </c>
@@ -26736,8 +27647,8 @@
         <f>R96/S92</f>
         <v>1.7745612372265211</v>
       </c>
-      <c r="T96" s="282"/>
-      <c r="U96" s="283"/>
+      <c r="T96" s="326"/>
+      <c r="U96" s="327"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -27199,11 +28110,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="284" t="s">
+      <c r="B122" s="328" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="284"/>
-      <c r="D122" s="284"/>
+      <c r="C122" s="328"/>
+      <c r="D122" s="328"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>1.6333333333333333</v>
@@ -27211,11 +28122,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="284" t="s">
+      <c r="B123" s="328" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="284"/>
-      <c r="D123" s="284"/>
+      <c r="C123" s="328"/>
+      <c r="D123" s="328"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>-0.76989873089142391</v>
@@ -27245,31 +28156,45 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H60:H69"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:T96"/>
+    <mergeCell ref="U95:U96"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F36:H36"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="A47:C47"/>
@@ -27286,45 +28211,31 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="Q92:R92"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:T96"/>
-    <mergeCell ref="U95:U96"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H60:H69"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -27365,7 +28276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42444A01-6BD4-415F-ACC7-DA57DCC971A9}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
@@ -27396,20 +28307,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326"/>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
-      <c r="K1" s="326"/>
-      <c r="L1" s="326"/>
+      <c r="B1" s="288"/>
+      <c r="C1" s="288"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
@@ -27439,26 +28350,26 @@
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="327" t="s">
+      <c r="A3" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="327"/>
-      <c r="C3" s="328" t="s">
+      <c r="B3" s="285"/>
+      <c r="C3" s="289" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="328"/>
-      <c r="E3" s="328"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="327" t="s">
+      <c r="G3" s="285" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="327"/>
-      <c r="I3" s="328" t="s">
+      <c r="H3" s="285"/>
+      <c r="I3" s="289" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="328"/>
-      <c r="K3" s="328"/>
-      <c r="L3" s="328"/>
+      <c r="J3" s="289"/>
+      <c r="K3" s="289"/>
+      <c r="L3" s="289"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -27485,28 +28396,28 @@
       <c r="R4" s="9"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="327" t="s">
+      <c r="A5" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="327"/>
-      <c r="C5" s="329" t="s">
+      <c r="B5" s="285"/>
+      <c r="C5" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="329"/>
-      <c r="E5" s="329"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="286"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="327" t="s">
+      <c r="G5" s="285" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="327"/>
-      <c r="I5" s="330">
+      <c r="H5" s="285"/>
+      <c r="I5" s="287">
         <v>500</v>
       </c>
-      <c r="J5" s="330"/>
-      <c r="K5" s="329" t="s">
+      <c r="J5" s="287"/>
+      <c r="K5" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="329"/>
+      <c r="L5" s="286"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
@@ -27539,86 +28450,86 @@
       <c r="P8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="320" t="s">
+      <c r="A9" s="290" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="320"/>
-      <c r="C9" s="320"/>
+      <c r="B9" s="290"/>
+      <c r="C9" s="290"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="320" t="s">
+      <c r="A10" s="290" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="320"/>
-      <c r="C10" s="320"/>
-      <c r="N10" s="321"/>
-      <c r="O10" s="321"/>
-      <c r="P10" s="321"/>
-      <c r="Q10" s="321"/>
+      <c r="B10" s="290"/>
+      <c r="C10" s="290"/>
+      <c r="N10" s="291"/>
+      <c r="O10" s="291"/>
+      <c r="P10" s="291"/>
+      <c r="Q10" s="291"/>
       <c r="R10" s="44"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="325"/>
-      <c r="B12" s="325"/>
-      <c r="C12" s="325"/>
-      <c r="E12" s="325"/>
-      <c r="F12" s="325"/>
-      <c r="G12" s="325"/>
-      <c r="I12" s="357" t="s">
+      <c r="A12" s="295"/>
+      <c r="B12" s="295"/>
+      <c r="C12" s="295"/>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="I12" s="355" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="358"/>
-      <c r="K12" s="359"/>
-      <c r="M12" s="357" t="s">
+      <c r="J12" s="356"/>
+      <c r="K12" s="357"/>
+      <c r="M12" s="355" t="s">
         <v>73</v>
       </c>
-      <c r="N12" s="358"/>
-      <c r="O12" s="359"/>
+      <c r="N12" s="356"/>
+      <c r="O12" s="357"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="313"/>
-      <c r="B13" s="313"/>
+      <c r="A13" s="298"/>
+      <c r="B13" s="298"/>
       <c r="C13" s="21"/>
-      <c r="E13" s="313"/>
-      <c r="F13" s="313"/>
+      <c r="E13" s="298"/>
+      <c r="F13" s="298"/>
       <c r="G13" s="21"/>
-      <c r="I13" s="338" t="s">
+      <c r="I13" s="352" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="339"/>
+      <c r="J13" s="353"/>
       <c r="K13" s="29">
         <v>720</v>
       </c>
-      <c r="M13" s="338" t="s">
+      <c r="M13" s="352" t="s">
         <v>75</v>
       </c>
-      <c r="N13" s="339"/>
+      <c r="N13" s="353"/>
       <c r="O13" s="33">
         <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="313"/>
-      <c r="B14" s="313"/>
+      <c r="A14" s="298"/>
+      <c r="B14" s="298"/>
       <c r="C14" s="21"/>
-      <c r="E14" s="313"/>
-      <c r="F14" s="313"/>
+      <c r="E14" s="298"/>
+      <c r="F14" s="298"/>
       <c r="G14" s="21"/>
-      <c r="I14" s="316" t="s">
+      <c r="I14" s="299" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="317"/>
+      <c r="J14" s="300"/>
       <c r="K14" s="30">
         <v>310</v>
       </c>
-      <c r="M14" s="316" t="s">
+      <c r="M14" s="299" t="s">
         <v>76</v>
       </c>
-      <c r="N14" s="317"/>
+      <c r="N14" s="300"/>
       <c r="O14" s="34">
         <v>0.25</v>
       </c>
@@ -27626,11 +28537,11 @@
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="313"/>
-      <c r="B15" s="313"/>
+      <c r="A15" s="298"/>
+      <c r="B15" s="298"/>
       <c r="C15" s="131"/>
-      <c r="E15" s="313"/>
-      <c r="F15" s="313"/>
+      <c r="E15" s="298"/>
+      <c r="F15" s="298"/>
       <c r="G15" s="21"/>
       <c r="I15" s="23" t="s">
         <v>6</v>
@@ -27639,10 +28550,10 @@
       <c r="K15" s="31">
         <v>20</v>
       </c>
-      <c r="M15" s="316" t="s">
+      <c r="M15" s="299" t="s">
         <v>74</v>
       </c>
-      <c r="N15" s="317"/>
+      <c r="N15" s="300"/>
       <c r="O15" s="24">
         <f>O14/O13</f>
         <v>3.6023054755043228E-2</v>
@@ -27651,103 +28562,103 @@
       <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="313"/>
-      <c r="B16" s="313"/>
+      <c r="A16" s="298"/>
+      <c r="B16" s="298"/>
       <c r="C16" s="6"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="131"/>
-      <c r="I16" s="311" t="s">
+      <c r="I16" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="312"/>
+      <c r="J16" s="302"/>
       <c r="K16" s="32">
         <v>3</v>
       </c>
-      <c r="M16" s="316" t="s">
+      <c r="M16" s="299" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="317"/>
+      <c r="N16" s="300"/>
       <c r="O16" s="25">
         <f>K14*O13*0.001</f>
         <v>2.1514000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="313"/>
-      <c r="B17" s="313"/>
+      <c r="A17" s="298"/>
+      <c r="B17" s="298"/>
       <c r="C17" s="6"/>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
+      <c r="E17" s="298"/>
+      <c r="F17" s="298"/>
       <c r="G17" s="6"/>
-      <c r="M17" s="316" t="s">
+      <c r="M17" s="299" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="317"/>
+      <c r="N17" s="300"/>
       <c r="O17" s="24">
         <f>O16*O15</f>
         <v>7.7500000000000013E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M18" s="316" t="s">
+      <c r="M18" s="299" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="317"/>
+      <c r="N18" s="300"/>
       <c r="O18" s="26">
         <f>O17*E35</f>
         <v>2.0002432295767165</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="M19" s="351" t="s">
+      <c r="M19" s="360" t="s">
         <v>80</v>
       </c>
-      <c r="N19" s="352"/>
+      <c r="N19" s="361"/>
       <c r="O19" s="27">
         <f>(O16*I37*1000)/O13</f>
         <v>155000</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M20" s="353"/>
-      <c r="N20" s="354"/>
+      <c r="M20" s="362"/>
+      <c r="N20" s="363"/>
       <c r="O20" s="28">
         <f>O16*I37</f>
         <v>1075.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="314" t="s">
+      <c r="C21" s="303" t="s">
         <v>81</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="314" t="s">
+      <c r="E21" s="303" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314" t="s">
+      <c r="F21" s="303"/>
+      <c r="G21" s="303" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="314" t="s">
+      <c r="H21" s="303" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="314"/>
+      <c r="C22" s="303"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="314"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="303"/>
+      <c r="G22" s="303"/>
+      <c r="H22" s="303"/>
     </row>
     <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="315"/>
+      <c r="C23" s="304"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="315"/>
-      <c r="F23" s="315"/>
-      <c r="G23" s="315"/>
-      <c r="H23" s="315"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="304"/>
+      <c r="H23" s="304"/>
     </row>
     <row r="24" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
@@ -28130,12 +29041,12 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="355" t="s">
+      <c r="A33" s="358" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="356"/>
-      <c r="C33" s="356"/>
-      <c r="D33" s="356"/>
+      <c r="B33" s="359"/>
+      <c r="C33" s="359"/>
+      <c r="D33" s="359"/>
       <c r="E33" s="194">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -28181,19 +29092,19 @@
         <f>B37/B36</f>
         <v>1.0597680097680098</v>
       </c>
-      <c r="C35" s="306" t="s">
+      <c r="C35" s="308" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="306"/>
+      <c r="D35" s="308"/>
       <c r="E35" s="35">
         <f>IF(C5="Roll", (1000/(C13*C14*B37*0.001*0.001))*C16, IF(C5="Sleeve", (1000/(G14*G15*B37*0.001*0.001))*1, IF(C5="Bag or Pouch", (1000/(K14*K13*B37*0.001*0.001))*1, "")))</f>
         <v>25.809590059054404</v>
       </c>
-      <c r="F35" s="306" t="s">
+      <c r="F35" s="308" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="306"/>
-      <c r="H35" s="306"/>
+      <c r="G35" s="308"/>
+      <c r="H35" s="308"/>
       <c r="I35">
         <f>IF(C5="Roll", ((C13*C17)+C15), IF(C5="Sleeve", ((G14*G17)+G16), IF(C5="Bag or Pouch", ((K14*K16)+K15), "")))</f>
         <v>950</v>
@@ -28207,19 +29118,19 @@
         <f>SUMIFS(table111[Micron],table111[Type],"substrate")+SUMIFS(table111[Total GSM],table111[Type],"Ink")+SUMIFS(table111[Total GSM],table111[Type],"Adhesive")</f>
         <v>163.80000000000001</v>
       </c>
-      <c r="C36" s="306" t="s">
+      <c r="C36" s="308" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="306"/>
+      <c r="D36" s="308"/>
       <c r="E36" s="15">
         <f>1000/E35</f>
         <v>38.745288000000002</v>
       </c>
-      <c r="F36" s="306" t="s">
+      <c r="F36" s="308" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="306"/>
-      <c r="H36" s="306"/>
+      <c r="G36" s="308"/>
+      <c r="H36" s="308"/>
       <c r="I36" s="38">
         <f>IF(UnitsDD="Kgs", I5,
  IF(UnitsDD="Kpcs", I5*E36,
@@ -28238,19 +29149,19 @@
         <f>SUM(F25:F32)</f>
         <v>173.59</v>
       </c>
-      <c r="C37" s="306" t="s">
+      <c r="C37" s="308" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="306"/>
+      <c r="D37" s="308"/>
       <c r="E37" s="15">
         <f>1000/B37</f>
         <v>5.7607005011809438</v>
       </c>
-      <c r="F37" s="306" t="s">
+      <c r="F37" s="308" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="306"/>
-      <c r="H37" s="306"/>
+      <c r="G37" s="308"/>
+      <c r="H37" s="308"/>
       <c r="I37" s="38">
         <f>(I36*1000)/E36/1000</f>
         <v>500</v>
@@ -28264,29 +29175,29 @@
         <f>SUM(I25:I32)+I33</f>
         <v>0.38158350000000002</v>
       </c>
-      <c r="C38" s="306" t="s">
+      <c r="C38" s="308" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="306"/>
+      <c r="D38" s="308"/>
       <c r="E38" s="15">
         <f>(E37/I35)*1000</f>
         <v>6.063895264400994</v>
       </c>
-      <c r="F38" s="306" t="s">
+      <c r="F38" s="308" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="306"/>
-      <c r="H38" s="306"/>
+      <c r="G38" s="308"/>
+      <c r="H38" s="308"/>
       <c r="I38" s="38">
         <f>I36*E38</f>
         <v>117473.68421052633</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C39" s="306" t="s">
+      <c r="C39" s="308" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="306"/>
+      <c r="D39" s="308"/>
       <c r="E39" s="15">
         <f>IF(C5="Roll", ((E37/C13)*1000), IF(C5="Sleeve", ((E37/G14)*1000), IF(C5="Bag or Pouch", ((E37/K13)*1000), "")))</f>
         <v>8.0009729183068661</v>
@@ -28340,11 +29251,11 @@
       <c r="M43" s="82"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="308" t="s">
+      <c r="A44" s="310" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="309"/>
-      <c r="C44" s="310"/>
+      <c r="B44" s="311"/>
+      <c r="C44" s="312"/>
       <c r="D44" s="79">
         <v>176</v>
       </c>
@@ -28374,11 +29285,11 @@
       <c r="M45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="293" t="s">
+      <c r="A46" s="305" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="293"/>
-      <c r="C46" s="293"/>
+      <c r="B46" s="305"/>
+      <c r="C46" s="305"/>
       <c r="D46" s="77">
         <v>300</v>
       </c>
@@ -28393,11 +29304,11 @@
       <c r="M46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="293" t="s">
+      <c r="A47" s="305" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="293"/>
-      <c r="C47" s="293"/>
+      <c r="B47" s="305"/>
+      <c r="C47" s="305"/>
       <c r="D47" s="95">
         <f>IF(C5="Roll",(((D46/2)^2-(D44/2)^2)*PI()*C13*B35/1000000),IF(C5="Sleeve",(((D46/2)^2-(D44/2)^2)*PI()*G14*B35/1000000),IF(C5="Bag or Pouch",(((D46/2)^2-(D44/2)^2)*PI()*K13*B35/1000000))))</f>
         <v>35.372179596826548</v>
@@ -28413,11 +29324,11 @@
       <c r="M47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="293" t="s">
+      <c r="A48" s="305" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="293"/>
-      <c r="C48" s="293"/>
+      <c r="B48" s="305"/>
+      <c r="C48" s="305"/>
       <c r="D48" s="96">
         <f>IF(C5="Roll",((D47*1000/B35)/((B36/10000)*(C13/10))/100),IF(C5="Sleeve",((D47*1000/B35)/((B36/10000)*(G14/10))/100),IF(C5="Bag or Pouch",((D47*1000/B35)/((B36/10000)*(K13/10))/100))))</f>
         <v>283.01185101569587</v>
@@ -28433,11 +29344,11 @@
       <c r="M48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="293" t="s">
+      <c r="A49" s="305" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="293"/>
-      <c r="C49" s="293"/>
+      <c r="B49" s="305"/>
+      <c r="C49" s="305"/>
       <c r="D49" s="97">
         <f>IF(C5="Roll",C13,IF(C5="Sleeve", G14,IF(C5="Bag or Pouch", K13)))</f>
         <v>720</v>
@@ -28453,11 +29364,11 @@
       <c r="M49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="293" t="s">
+      <c r="A50" s="305" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="293"/>
-      <c r="C50" s="293"/>
+      <c r="B50" s="305"/>
+      <c r="C50" s="305"/>
       <c r="D50" s="98">
         <f>(D47*E35)</f>
         <v>912.94145488934146</v>
@@ -28488,11 +29399,11 @@
       <c r="M51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="293" t="s">
+      <c r="A52" s="305" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="293"/>
-      <c r="C52" s="293"/>
+      <c r="B52" s="305"/>
+      <c r="C52" s="305"/>
       <c r="D52" s="78">
         <v>221</v>
       </c>
@@ -28507,11 +29418,11 @@
       <c r="M52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="293" t="s">
+      <c r="A53" s="305" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="293"/>
-      <c r="C53" s="293"/>
+      <c r="B53" s="305"/>
+      <c r="C53" s="305"/>
       <c r="D53" s="100">
         <f>IF(C5="Roll",(2*SQRT((((D52*1000)/B35)/(C13/10)/PI())+((D44/2/10)^2))*10),IF(C5="Sleeve",(2*SQRT((((D52*1000)/B35)/(G14/10)/PI())+((D44/2/10)^2))*10),IF(C5="Bag or Pouch",(2*SQRT((((D52*1000)/B35)/(K13/10)/PI())+((D44/2/10)^2))*10))))</f>
         <v>632.25705038862782</v>
@@ -28657,7 +29568,7 @@
         <f>F60*E60</f>
         <v>6892.3268571428589</v>
       </c>
-      <c r="H60" s="340">
+      <c r="H60" s="344">
         <f>SUMIF($A$60:$A$69,"true",$G$60:$G$69)</f>
         <v>17057.940892230581</v>
       </c>
@@ -28691,7 +29602,7 @@
         <f t="shared" ref="G61:G68" si="3">F61*E61</f>
         <v>3249.4736842105267</v>
       </c>
-      <c r="H61" s="341"/>
+      <c r="H61" s="345"/>
       <c r="I61" s="82"/>
       <c r="J61" s="85"/>
       <c r="K61" s="82"/>
@@ -28722,7 +29633,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H62" s="341"/>
+      <c r="H62" s="345"/>
       <c r="I62" s="82"/>
       <c r="J62" s="86"/>
       <c r="K62" s="82"/>
@@ -28753,7 +29664,7 @@
         <f t="shared" si="3"/>
         <v>1078.9473684210527</v>
       </c>
-      <c r="H63" s="341"/>
+      <c r="H63" s="345"/>
       <c r="I63" s="82"/>
       <c r="J63" s="86"/>
       <c r="K63" s="82"/>
@@ -28784,7 +29695,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H64" s="341"/>
+      <c r="H64" s="345"/>
       <c r="I64" s="82"/>
       <c r="J64" s="86"/>
       <c r="K64" s="82"/>
@@ -28815,7 +29726,7 @@
         <f t="shared" si="3"/>
         <v>589.47368421052636</v>
       </c>
-      <c r="H65" s="341"/>
+      <c r="H65" s="345"/>
       <c r="I65" s="82"/>
       <c r="J65" s="86"/>
       <c r="K65" s="82"/>
@@ -28846,7 +29757,7 @@
         <f t="shared" si="3"/>
         <v>220.78947368421055</v>
       </c>
-      <c r="H66" s="341"/>
+      <c r="H66" s="345"/>
       <c r="I66" s="82"/>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
@@ -28876,7 +29787,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H67" s="341"/>
+      <c r="H67" s="345"/>
       <c r="I67" s="82"/>
       <c r="J67" s="82"/>
       <c r="K67" s="82"/>
@@ -28907,7 +29818,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="341"/>
+      <c r="H68" s="345"/>
       <c r="I68" s="82"/>
       <c r="J68" s="82"/>
       <c r="K68" s="82"/>
@@ -28938,7 +29849,7 @@
         <f>F69*E69</f>
         <v>4216.6666666666661</v>
       </c>
-      <c r="H69" s="342"/>
+      <c r="H69" s="346"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
       <c r="K69" s="82"/>
@@ -28998,23 +29909,23 @@
       <c r="M72" s="82"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B73" s="297"/>
-      <c r="C73" s="298" t="s">
+      <c r="B73" s="318"/>
+      <c r="C73" s="319" t="s">
         <v>41</v>
       </c>
       <c r="D73" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="300" t="s">
+      <c r="E73" s="321" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="302" t="s">
+      <c r="F73" s="323" t="s">
         <v>43</v>
       </c>
-      <c r="G73" s="302" t="s">
+      <c r="G73" s="323" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="291" t="s">
+      <c r="H73" s="313" t="s">
         <v>44</v>
       </c>
       <c r="I73" s="83"/>
@@ -29028,15 +29939,15 @@
     </row>
     <row r="74" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="82"/>
-      <c r="B74" s="297"/>
-      <c r="C74" s="299"/>
+      <c r="B74" s="318"/>
+      <c r="C74" s="320"/>
       <c r="D74" s="181">
         <v>0.3</v>
       </c>
-      <c r="E74" s="301"/>
-      <c r="F74" s="303"/>
-      <c r="G74" s="303"/>
-      <c r="H74" s="292"/>
+      <c r="E74" s="322"/>
+      <c r="F74" s="324"/>
+      <c r="G74" s="324"/>
+      <c r="H74" s="314"/>
       <c r="I74" s="83"/>
       <c r="J74" s="90"/>
       <c r="K74" s="90"/>
@@ -29275,9 +30186,9 @@
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="285"/>
-      <c r="I82" s="285"/>
-      <c r="J82" s="285"/>
+      <c r="H82" s="329"/>
+      <c r="I82" s="329"/>
+      <c r="J82" s="329"/>
       <c r="K82" s="41"/>
       <c r="L82" s="41"/>
       <c r="M82" s="41"/>
@@ -29285,19 +30196,19 @@
     </row>
     <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="54"/>
-      <c r="B83" s="286" t="s">
+      <c r="B83" s="330" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="286"/>
-      <c r="D83" s="286"/>
-      <c r="E83" s="286"/>
-      <c r="F83" s="286"/>
-      <c r="G83" s="286"/>
-      <c r="H83" s="286"/>
-      <c r="I83" s="286"/>
-      <c r="J83" s="286"/>
-      <c r="K83" s="286"/>
-      <c r="L83" s="286"/>
+      <c r="C83" s="330"/>
+      <c r="D83" s="330"/>
+      <c r="E83" s="330"/>
+      <c r="F83" s="330"/>
+      <c r="G83" s="330"/>
+      <c r="H83" s="330"/>
+      <c r="I83" s="330"/>
+      <c r="J83" s="330"/>
+      <c r="K83" s="330"/>
+      <c r="L83" s="330"/>
       <c r="M83" s="41"/>
       <c r="N83" s="41"/>
     </row>
@@ -29363,17 +30274,17 @@
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="343" t="s">
+      <c r="H87" s="336" t="s">
         <v>146</v>
       </c>
-      <c r="I87" s="344"/>
+      <c r="I87" s="337"/>
       <c r="J87" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K87" s="345" t="s">
+      <c r="K87" s="338" t="s">
         <v>147</v>
       </c>
-      <c r="L87" s="346"/>
+      <c r="L87" s="339"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
     </row>
@@ -29385,20 +30296,20 @@
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="347">
+      <c r="H88" s="340">
         <f>C75+H70</f>
         <v>3.0787051830524823</v>
       </c>
-      <c r="I88" s="348"/>
+      <c r="I88" s="341"/>
       <c r="J88" s="162">
         <f>(K88-H88)/H88</f>
         <v>6.0858781331305026E-2</v>
       </c>
-      <c r="K88" s="349">
+      <c r="K88" s="342">
         <f>E106+E122</f>
         <v>3.2660714285714287</v>
       </c>
-      <c r="L88" s="350"/>
+      <c r="L88" s="343"/>
       <c r="M88" s="41"/>
       <c r="N88" s="41"/>
     </row>
@@ -29469,10 +30380,10 @@
         <v>0.10023346303501944</v>
       </c>
       <c r="P92" s="222"/>
-      <c r="Q92" s="288" t="s">
+      <c r="Q92" s="332" t="s">
         <v>159</v>
       </c>
-      <c r="R92" s="288"/>
+      <c r="R92" s="332"/>
       <c r="S92" s="112">
         <f>H75</f>
         <v>4.0381616609601965</v>
@@ -29530,10 +30441,10 @@
       <c r="S94" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="T94" s="289" t="s">
+      <c r="T94" s="333" t="s">
         <v>148</v>
       </c>
-      <c r="U94" s="290"/>
+      <c r="U94" s="334"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B95" s="146" t="str">
@@ -29567,11 +30478,11 @@
         <f>R95/S92</f>
         <v>0.76240265782733074</v>
       </c>
-      <c r="T95" s="281">
+      <c r="T95" s="325">
         <f>R96-R95</f>
         <v>0.18736624551894643</v>
       </c>
-      <c r="U95" s="283">
+      <c r="U95" s="327">
         <f>(R96-R95)/R95</f>
         <v>6.0858781331305026E-2</v>
       </c>
@@ -29610,8 +30521,8 @@
         <f>R96/S92</f>
         <v>0.80880155446645008</v>
       </c>
-      <c r="T96" s="282"/>
-      <c r="U96" s="283"/>
+      <c r="T96" s="326"/>
+      <c r="U96" s="327"/>
     </row>
     <row r="97" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B97" s="146" t="str">
@@ -30085,11 +30996,11 @@
       <c r="P121" s="222"/>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B122" s="284" t="s">
+      <c r="B122" s="328" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="284"/>
-      <c r="D122" s="284"/>
+      <c r="C122" s="328"/>
+      <c r="D122" s="328"/>
       <c r="E122" s="140">
         <f>E121/C85</f>
         <v>0.97142857142857142</v>
@@ -30097,11 +31008,11 @@
       <c r="P122" s="222"/>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B123" s="284" t="s">
+      <c r="B123" s="328" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="284"/>
-      <c r="D123" s="284"/>
+      <c r="C123" s="328"/>
+      <c r="D123" s="328"/>
       <c r="E123" s="159">
         <f>(E122-H70)/H70</f>
         <v>0.10324804175431759</v>
@@ -30131,72 +31042,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N20"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
     <mergeCell ref="Q92:R92"/>
     <mergeCell ref="T94:U94"/>
     <mergeCell ref="T95:T96"/>
@@ -30210,6 +31055,72 @@
     <mergeCell ref="F73:F74"/>
     <mergeCell ref="G73:G74"/>
     <mergeCell ref="H73:H74"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N20"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="K88:L88"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B32" xr:uid="{2AFEC1F7-42E6-4A1F-B5F3-709469322160}">
@@ -30246,7 +31157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56876A7-A503-4EE5-BF05-536BED17384A}">
   <dimension ref="B1:Q12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -30260,17 +31171,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G1" s="360" t="s">
+      <c r="G1" s="364" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="360"/>
-      <c r="I1" s="360"/>
-      <c r="J1" s="360"/>
-      <c r="K1" s="360" t="s">
+      <c r="H1" s="364"/>
+      <c r="I1" s="364"/>
+      <c r="J1" s="364"/>
+      <c r="K1" s="364" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="360"/>
-      <c r="M1" s="360"/>
+      <c r="L1" s="364"/>
+      <c r="M1" s="364"/>
       <c r="N1" s="172"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
@@ -30372,7 +31283,7 @@
       <c r="P7" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="361" t="s">
+      <c r="Q7" s="365" t="s">
         <v>218</v>
       </c>
     </row>
@@ -30386,7 +31297,7 @@
       <c r="P8" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="Q8" s="361"/>
+      <c r="Q8" s="365"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
@@ -30398,7 +31309,7 @@
       <c r="P9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q9" s="361"/>
+      <c r="Q9" s="365"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N10" t="s">
@@ -30410,7 +31321,7 @@
       <c r="P10" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="Q10" s="361"/>
+      <c r="Q10" s="365"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N11" t="s">
@@ -30422,7 +31333,7 @@
       <c r="P11" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="Q11" s="361"/>
+      <c r="Q11" s="365"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="N12" t="s">
@@ -30434,7 +31345,7 @@
       <c r="P12" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Q12" s="361"/>
+      <c r="Q12" s="365"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O8:O11">
@@ -30452,475 +31363,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941D5018-3274-429A-BC96-6832248D126F}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="I1" s="233" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="233" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="233" t="s">
-        <v>220</v>
-      </c>
-      <c r="L1" s="233" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="233" t="s">
-        <v>221</v>
-      </c>
-      <c r="N1" s="233" t="s">
-        <v>222</v>
-      </c>
-      <c r="O1" s="233" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I2" s="234" t="s">
-        <v>124</v>
-      </c>
-      <c r="J2" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="236">
-        <v>100</v>
-      </c>
-      <c r="L2" s="236">
-        <v>2.7</v>
-      </c>
-      <c r="M2" s="236">
-        <v>5</v>
-      </c>
-      <c r="N2" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O2" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I3" s="234" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K3" s="236">
-        <v>100</v>
-      </c>
-      <c r="L3" s="236">
-        <v>0.91</v>
-      </c>
-      <c r="M3" s="236">
-        <v>5</v>
-      </c>
-      <c r="N3" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O3" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I4" s="234" t="s">
-        <v>115</v>
-      </c>
-      <c r="J4" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K4" s="236">
-        <v>100</v>
-      </c>
-      <c r="L4" s="236">
-        <v>0.91</v>
-      </c>
-      <c r="M4" s="236">
-        <v>5</v>
-      </c>
-      <c r="N4" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O4" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="239">
-        <v>0.91</v>
-      </c>
-      <c r="I5" s="234" t="s">
-        <v>227</v>
-      </c>
-      <c r="J5" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K5" s="236">
-        <v>100</v>
-      </c>
-      <c r="L5" s="236">
-        <v>0.95</v>
-      </c>
-      <c r="M5" s="236">
-        <v>5</v>
-      </c>
-      <c r="N5" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="240">
-        <v>1.4</v>
-      </c>
-      <c r="G6" s="231" t="s">
-        <v>124</v>
-      </c>
-      <c r="I6" s="234" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="235"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="237"/>
-      <c r="O6" s="238"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="239">
-        <v>0.91</v>
-      </c>
-      <c r="G7" s="231" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="234" t="s">
-        <v>228</v>
-      </c>
-      <c r="J7" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K7" s="236">
-        <v>100</v>
-      </c>
-      <c r="L7" s="236">
-        <v>0.92</v>
-      </c>
-      <c r="M7" s="236">
-        <v>5</v>
-      </c>
-      <c r="N7" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="240">
-        <v>2.7</v>
-      </c>
-      <c r="G8" s="231" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="236">
-        <v>100</v>
-      </c>
-      <c r="L8" s="236">
-        <v>0.92</v>
-      </c>
-      <c r="M8" s="236">
-        <v>5</v>
-      </c>
-      <c r="N8" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="239">
-        <v>0.92</v>
-      </c>
-      <c r="G9" s="231" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="234" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K9" s="236">
-        <v>100</v>
-      </c>
-      <c r="L9" s="236">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="M9" s="236">
-        <v>5</v>
-      </c>
-      <c r="N9" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="240">
-        <v>0.93</v>
-      </c>
-      <c r="G10" s="231" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="234" t="s">
-        <v>241</v>
-      </c>
-      <c r="J10" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K10" s="236">
-        <v>100</v>
-      </c>
-      <c r="L10" s="236">
-        <v>1</v>
-      </c>
-      <c r="M10" s="236">
-        <v>8</v>
-      </c>
-      <c r="N10" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="239">
-        <v>1.24</v>
-      </c>
-      <c r="G11" s="231" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="234" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K11" s="236">
-        <v>100</v>
-      </c>
-      <c r="L11" s="236">
-        <v>1.38</v>
-      </c>
-      <c r="M11" s="236">
-        <v>5</v>
-      </c>
-      <c r="N11" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O11" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="240">
-        <v>0.92</v>
-      </c>
-      <c r="G12" s="231" t="s">
-        <v>123</v>
-      </c>
-      <c r="I12" s="234" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="235" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="236">
-        <v>100</v>
-      </c>
-      <c r="L12" s="236">
-        <v>1.38</v>
-      </c>
-      <c r="M12" s="236">
-        <v>5</v>
-      </c>
-      <c r="N12" s="237" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="238" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B13" s="239">
-        <v>1</v>
-      </c>
-      <c r="G13" s="229" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="234" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="240">
-        <v>1</v>
-      </c>
-      <c r="G14" s="231" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="234" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" s="239">
-        <v>1</v>
-      </c>
-      <c r="G15" s="231" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" s="231" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="241" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="242">
-        <v>1</v>
-      </c>
-      <c r="G16" s="230" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="231" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G17" s="231" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="234" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G18" s="231" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="234" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="19" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G19" s="229" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="229" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G20" s="230" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="230" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G21" s="231" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G22" s="232" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="I23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="I24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I2:O12">
-    <sortCondition ref="I2:I12"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Costing_form ES.xlsx
+++ b/Costing_form ES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49B8309-2BAF-41FD-B10F-4C158A2E3085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4681C70B-271A-469B-BD45-2C085138D707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="685" firstSheet="1" activeTab="11" xr2:uid="{8B4D55F6-3FB6-4E47-8881-ACB8C7217C59}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="388">
   <si>
     <t>Roll</t>
   </si>
@@ -1430,6 +1430,24 @@
   </si>
   <si>
     <t>WIDE FILM</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>AED/kg</t>
+  </si>
+  <si>
+    <t>AED/m²</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>µ</t>
+  </si>
+  <si>
+    <t>Cost Contribution</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1480,7 @@
     <numFmt numFmtId="185" formatCode="\$0.00"/>
     <numFmt numFmtId="186" formatCode="#,##0\ &quot;Pcs&quot;"/>
   </numFmts>
-  <fonts count="61" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1875,8 +1893,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1955,8 +1980,20 @@
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="87">
+  <borders count="90">
     <border>
       <left/>
       <right/>
@@ -3068,6 +3105,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3077,7 +3155,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="375">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4006,6 +4084,24 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="15" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -22118,13 +22214,24 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95296C8-8124-492C-9697-6CF01E844FAD}">
-  <dimension ref="I9:M17"/>
+  <dimension ref="C9:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
     <col min="9" max="9" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C9" s="375" t="s">
+        <v>385</v>
+      </c>
+      <c r="D9" s="375"/>
+      <c r="E9" s="377" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" s="378"/>
       <c r="I9" s="371" t="s">
         <v>365</v>
       </c>
@@ -22135,7 +22242,19 @@
         <v>5.0027744175807163</v>
       </c>
     </row>
-    <row r="10" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C10" s="376" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="376" t="s">
+        <v>382</v>
+      </c>
+      <c r="E10" s="379" t="s">
+        <v>383</v>
+      </c>
+      <c r="F10" s="380" t="s">
+        <v>384</v>
+      </c>
       <c r="I10" s="371" t="s">
         <v>373</v>
       </c>
@@ -22146,7 +22265,11 @@
         <v>5.6340752840663653</v>
       </c>
     </row>
-    <row r="11" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C11" s="376"/>
+      <c r="D11" s="376"/>
+      <c r="E11" s="379"/>
+      <c r="F11" s="380"/>
       <c r="I11" s="371" t="s">
         <v>374</v>
       </c>
@@ -22157,7 +22280,11 @@
         <v>6.4243902109353286</v>
       </c>
     </row>
-    <row r="12" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C12" s="376"/>
+      <c r="D12" s="376"/>
+      <c r="E12" s="379"/>
+      <c r="F12" s="380"/>
       <c r="I12" s="371" t="s">
         <v>375</v>
       </c>
@@ -22168,7 +22295,11 @@
         <v>5.0285713564027636</v>
       </c>
     </row>
-    <row r="13" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C13" s="376"/>
+      <c r="D13" s="376"/>
+      <c r="E13" s="379"/>
+      <c r="F13" s="380"/>
       <c r="I13" s="371" t="s">
         <v>377</v>
       </c>
@@ -22179,7 +22310,11 @@
         <v>3.8592165558162406</v>
       </c>
     </row>
-    <row r="14" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C14" s="376"/>
+      <c r="D14" s="376"/>
+      <c r="E14" s="379"/>
+      <c r="F14" s="380"/>
       <c r="I14" s="371" t="s">
         <v>378</v>
       </c>
@@ -22190,7 +22325,11 @@
         <v>1.857303462541994</v>
       </c>
     </row>
-    <row r="15" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C15" s="376"/>
+      <c r="D15" s="376"/>
+      <c r="E15" s="379"/>
+      <c r="F15" s="380"/>
       <c r="I15" s="371" t="s">
         <v>379</v>
       </c>
@@ -22201,7 +22340,11 @@
         <v>4.0823118593359249</v>
       </c>
     </row>
-    <row r="16" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C16" s="376"/>
+      <c r="D16" s="376"/>
+      <c r="E16" s="379"/>
+      <c r="F16" s="380"/>
       <c r="I16" s="371" t="s">
         <v>380</v>
       </c>
@@ -22212,7 +22355,11 @@
         <v>11.164240115322043</v>
       </c>
     </row>
-    <row r="17" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C17" s="376"/>
+      <c r="D17" s="376"/>
+      <c r="E17" s="379"/>
+      <c r="F17" s="380"/>
       <c r="I17" s="371" t="s">
         <v>381</v>
       </c>
@@ -22223,7 +22370,18 @@
         <v>3.2822710067490681</v>
       </c>
     </row>
+    <row r="18" spans="3:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="C18" s="376"/>
+      <c r="D18" s="376"/>
+      <c r="E18" s="379"/>
+      <c r="F18" s="380"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+  </mergeCells>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
